--- a/eval-suite/out/platform_dataset_intranet.xlsx
+++ b/eval-suite/out/platform_dataset_intranet.xlsx
@@ -484,7 +484,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -501,9 +502,50 @@
 |---|------|--------|------|
 | 1 | ods.ods_trade_order_di | 订单明细接入表 | a |
 ---
-产物清单：
-- ddl/create_table_dwb_trade_order_d.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_trade_order_d.sql——
+/* =====================================================
+   表名: dws.dwb_trade_order_d
+   规则: R0001 - 订单汇总主加工
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-06
+   说明: 单源表 ods_trade_order_di 按 订单ID(order_id)+客户ID(cust_id) 分组聚合， 对金额求和(SUM)，收敛到"一行=一个订单+客户组合"的目标粒度，直产目标 F 表。 单表无 JOIN、仅 1 个聚合字段，复杂度低，无需分段建中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_order_d (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    total_amount        DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_order_d IS '订单汇总表';
+COMMENT ON COLUMN dws.dwb_trade_order_d.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.total_amount IS '订单总额';
+COMMENT ON COLUMN dws.dwb_trade_order_d.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_order_d.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_order_d.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_order_d.dw_last_update_date IS '更新时间';
+——select/R0001_select.sql——
+/* R0001: 订单汇总主加工（单源表 ods_trade_order_di 按 订单ID(order_id)+客户ID(cust_id) 分组聚合，对金额求和(SUM)，收敛到"一行=一个订单+客户组合"的目标粒度，直产目标 F 表。单表无 JOIN、仅 1 个聚合字段，复杂度低，无需分段建中间表。） */
+SELECT
+    a."订单ID" AS order_id,
+    a."客户ID" AS cust_id,
+    COALESCE(SUM(a."金额"), 0) AS total_amount,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di a
+GROUP BY a."订单ID", a."客户ID"
 档案来源：../10_project_deliver/002_dwb_trade_order_d</t>
         </is>
       </c>
@@ -545,7 +587,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -566,9 +609,124 @@
 | 4 | ods.ods_payment_di | 支付明细 | pay |
 | 5 | ods.ods_logistics_di | 物流明细 | log |
 ---
-产物清单：
-- ddl/create_table_dwb_trade_wide_f.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_trade_wide_f.sql——
+/* =====================================================
+   表名: dws.dwb_trade_wide_f
+   规则: R0001 - 交易宽表全量装配
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 5表JOIN宽表，复杂度未达分段阈值，pay/log收敛用CTE内联处理，商品维取最新有效行，单条INSERT直产目标F表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_wide_f (
+    order_id            VARCHAR(64),  /* 订单ID */
+    cust_id             VARCHAR(64),  /* 客户ID */
+    product_id          VARCHAR(64),  /* 商品ID */
+    order_amt           DECIMAL(18,2),  /* 订单金额 */
+    order_qty           DECIMAL(18,4),  /* 订单数量 */
+    cust_name           VARCHAR(200),  /* 客户名称 */
+    cust_level          VARCHAR(10),  /* 客户等级 */
+    product_name        VARCHAR(200),  /* 商品名称 */
+    category_code       VARCHAR(50),  /* 商品分类 */
+    total_pay_amt       DECIMAL(18,2),  /* 支付总额 */
+    total_ship_fee      DECIMAL(18,2),  /* 运费总额 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次 */
+    last_upd_cycle_id   BIGINT,  /* 更新批次 */
+    dw_last_update_date TIMESTAMP(0)  /* 更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_wide_f IS '交易宽表';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_id IS '商品ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_amt IS '订单金额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_qty IS '订单数量';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_name IS '客户名称';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_level IS '客户等级';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_name IS '商品名称';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.category_code IS '商品分类';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.total_pay_amt IS '支付总额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.total_ship_fee IS '运费总额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.dw_last_update_date IS '更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 交易宽表全量装配
+   设计意图: 5表JOIN宽表，复杂度未达分段阈值，
+             pay/log 收敛用 CTE 内联处理，
+             商品维取最新有效行，单条 SELECT 直产目标 F 表
+   粒度: 一行=一个订单（输入输出无变化）
+   目标表: dws.dwb_trade_wide_f
+   ===================================================== */
+WITH
+/* CTE 1: pay_agg - 支付明细按 order_id 收敛（一个订单可有多笔支付，GROUP BY 收敛到每订单一行） */
+pay_agg AS (
+    SELECT
+        "订单ID" AS order_id,
+        COALESCE(SUM("支付金额"), 0) AS total_pay_amt
+    FROM ods.ods_payment_di
+    WHERE COALESCE(del_flag, 'N') = 'N'
+    GROUP BY "订单ID"
+),
+/* CTE 2: log_agg - 物流明细按 order_id 收敛（一个订单可有多条物流，GROUP BY 收敛到每订单一行） */
+log_agg AS (
+    SELECT
+        "订单ID" AS order_id,
+        COALESCE(SUM("运费"), 0) AS total_ship_fee
+    FROM ods.ods_logistics_di
+    WHERE COALESCE(del_flag, 'N') = 'N'
+    GROUP BY "订单ID"
+),
+/* CTE 3: prod_latest - 商品维取最新有效行（消除多版本历史行，ROW_NUMBER 按 product_id 取最新） */
+prod_latest AS (
+    SELECT
+        "商品ID" AS product_id,
+        "商品名称" AS product_name,
+        "商品分类" AS category_code,
+        ROW_NUMBER() OVER (
+            PARTITION BY "商品ID"
+            ORDER BY dw_last_update_date DESC NULLS LAST
+        ) AS _rn
+    FROM dwrdim.dim_product_d
+    WHERE COALESCE(del_flag, 'N') = 'N'
+)
+/* 主查询: 5 表 JOIN 组装宽表（粒度=订单，无变化；LEFT JOIN 右侧字段 COALESCE 兜底） */
+SELECT
+    o."订单ID" AS order_id,
+    o."客户ID" AS cust_id,
+    o."商品ID" AS product_id,
+    o."订单金额" AS order_amt,
+    o."订单数量" AS order_qty,
+    COALESCE(c."客户名称", '') AS cust_name,
+    COALESCE(c."客户等级", '') AS cust_level,
+    COALESCE(pl.product_name, '') AS product_name,
+    COALESCE(pl.category_code, '') AS category_code,
+    COALESCE(pay.total_pay_amt, 0) AS total_pay_amt,
+    COALESCE(log.total_ship_fee, 0) AS total_ship_fee,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di o
+LEFT JOIN dwrdim.dim_cust_d c
+    ON o."客户ID" = c."客户ID"
+    AND COALESCE(c.del_flag, 'N') = 'N'
+LEFT JOIN prod_latest pl
+    ON o."商品ID" = pl.product_id
+    AND pl._rn = 1
+LEFT JOIN pay_agg pay
+    ON o."订单ID" = pay.order_id
+LEFT JOIN log_agg log
+    ON o."订单ID" = log.order_id
+WHERE COALESCE(o.del_flag, 'N') = 'N';
 档案来源：../10_project_deliver/003_dwb_trade_wide_f</t>
         </is>
       </c>
@@ -618,7 +776,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -638,9 +797,136 @@
 | 3 | sdord.dwd_order_f | 订单明细事实表 | dof |
 | 4 | sdrev.dwd_review_f | 评价事实表 | drf5 |
 ---
-产物清单：
-- ddl/create_table_dwb_shop_center_f.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_shop_center_f.sql——
+/* =====================================================
+   表名: slshp.dwb_shop_center_f
+   规则: R0001 - 店铺中心宽表装配
+   分布键: shop_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 dim_shop_f 为主表，LEFT JOIN 地区维度取省份名，并通过两个 CTE 把订单/评价事实表预聚合到店铺粒度后关联，一次产出店铺中心宽表全量字段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slshp.dwb_shop_center_f (
+    shop_id             bigint,  /* 店铺ID */
+    shop_name           varchar(200),  /* 店铺名称 */
+    company_name        varchar(200),  /* 公司名称 */
+    open_time           datetime,  /* 开店时间 */
+    province_code       varchar(20),  /* 省份编码 */
+    shop_score          decimal(3,2),  /* 店铺评分 */
+    service_score       decimal(3,2),  /* 服务评分 */
+    logistics_score     decimal(3,2),  /* 物流评分 */
+    shop_type_name      varchar(50),  /* 店铺类型 */
+    shop_status_name    varchar(50),  /* 店铺状态 */
+    open_days           int,  /* 营业天数 */
+    province_name       varchar(50),  /* 省份名称 */
+    total_order_cnt     int,  /* 累计订单数 */
+    total_sales_amount  decimal(18,2),  /* 累计销售额 */
+    total_buyer_cnt     int,  /* 累计购买人数 */
+    review_cnt          int,  /* 评价数 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(shop_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slshp.dwb_shop_center_f IS '店铺中心宽表';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.company_name IS '公司名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_time IS '开店时间';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_score IS '店铺评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.service_score IS '服务评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.logistics_score IS '物流评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_status_name IS '店铺状态';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_days IS '营业天数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_order_cnt IS '累计订单数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_buyer_cnt IS '累计购买人数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.review_cnt IS '评价数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* R0001: 店铺中心宽表装配
+   以 dim_shop_f 为主表，LEFT JOIN 地区维度取省份名，并通过两个 CTE 把订单/评价事实表
+   预聚合到店铺粒度后关联，一次产出店铺中心宽表全量字段。
+   字段命名假设（dwd_order_f 的实付金额/购买用户字段名 ts 切片未给出，按常见命名推断）：
+     - 实付金额列假设为 pay_amount（最符合"实付金额"语义）
+     - 购买用户列假设为 user_id
+   若源表 DDL 字段名不同，需同步调整 order_agg CTE 内引用。 */
+WITH
+/* CTE 1: order_agg — 按 shop_id 预聚合订单（累计订单数、累计销售额、累计去重购买人数） */
+order_agg AS (
+    SELECT
+        dof.shop_id AS shop_id,
+        COUNT(1) AS total_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0) AS total_sales_amount,
+        COUNT(DISTINCT dof.user_id) AS total_buyer_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE dof.del_flag = 'N'
+    GROUP BY dof.shop_id
+),
+/* CTE 2: review_agg — 按 shop_id 预聚合评价（评价数） */
+review_agg AS (
+    SELECT
+        drf5.shop_id AS shop_id,
+        COUNT(1) AS review_cnt
+    FROM sdrev.dwd_review_f drf5
+    WHERE drf5.del_flag = 'N'
+    GROUP BY drf5.shop_id
+)
+/* 主查询：dim_shop_f 主表
+   → LEFT JOIN dim_region_f 取省份名（region_code 唯一，不膨胀）
+   → LEFT JOIN order_agg / review_agg（CTE 已按 shop_id 收敛，不膨胀）取店铺度量 */
+SELECT
+    dsf.shop_id AS shop_id,
+    dsf.shop_name AS shop_name,
+    dsf.company_name AS company_name,
+    dsf.open_time AS open_time,
+    dsf.province_code AS province_code,
+    COALESCE(dsf.shop_score, 0) AS shop_score,
+    COALESCE(dsf.service_score, 0) AS service_score,
+    COALESCE(dsf.logistics_score, 0) AS logistics_score,
+    CASE dsf.shop_type
+        WHEN 'FLAGSHIP' THEN '旗舰店'
+        WHEN 'SPECIALTY' THEN '专卖店'
+        WHEN 'FRANCHISE' THEN '专营店'
+        ELSE '其他'
+    END AS shop_type_name,
+    CASE dsf.shop_status
+        WHEN 'OPEN' THEN '营业中'
+        WHEN 'CLOSED' THEN '已关闭'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS shop_status_name,
+    COALESCE(CURRENT_DATE - dsf.open_time::date, 0)::int AS open_days,
+    COALESCE(drf.region_name, '') AS province_name,
+    COALESCE(order_agg.total_order_cnt, 0) AS total_order_cnt,
+    COALESCE(order_agg.total_sales_amount, 0) AS total_sales_amount,
+    COALESCE(order_agg.total_buyer_cnt, 0) AS total_buyer_cnt,
+    COALESCE(review_agg.review_cnt, 0) AS review_cnt,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_shop_f dsf
+LEFT JOIN dim.dim_region_f drf
+    ON dsf.province_code = drf.region_code
+    AND drf.del_flag = 'N'
+LEFT JOIN order_agg
+    ON dsf.shop_id = order_agg.shop_id
+LEFT JOIN review_agg
+    ON dsf.shop_id = review_agg.shop_id
+WHERE dsf.del_flag = 'N';
 档案来源：../10_project_deliver/004_dwb_shop_center_f</t>
         </is>
       </c>
@@ -695,7 +981,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -720,11 +1007,186 @@
 | 8 | sdref.dwd_refund_f | 退款事实表 | drf9 |
 | 9 | sdlog.dwd_cart_f | 购物车事实表 | dcf |
 ---
-产物清单：
-- ddl/create_table_dwb_user_center_f.sql
-- ddl/create_table_dwb_user_center_f_tmp1.sql
-- ddl/create_table_dwb_user_center_f_tmp2.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_user_center_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f
+   规则: R0003 - 用户中心宽表装配
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 dim_user_f 为主表左联维度表与中间表，CTE 聚合行为/优惠/退款/购物车事实，计算派生转化率与标签，产出最终宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f (
+    user_id             bigint,  /* 用户ID */
+    user_name           varchar(100),  /* 用户姓名 */
+    user_phone_masked   varchar(20),  /* 手机号(脱敏) */
+    gender_name         varchar(10),  /* 性别 */
+    birthday            date,  /* 出生日期 */
+    age                 int,  /* 年龄 */
+    register_time       datetime,  /* 注册时间 */
+    register_days       int,  /* 注册天数 */
+    last_login_time     datetime,  /* 最近登录时间 */
+    level_id            int,  /* 等级ID */
+    level_name          varchar(50),  /* 等级名称 */
+    level_min_points    int,  /* 等级所需积分 */
+    province_code       varchar(20),  /* 省份编码 */
+    province_name       varchar(50),  /* 省份名称 */
+    city_code           varchar(20),  /* 城市编码 */
+    city_name           varchar(50),  /* 城市名称 */
+    source_name         varchar(50),  /* 注册来源 */
+    member_points       int,  /* 会员积分 */
+    member_balance      decimal(18,2),  /* 会员余额 */
+    user_status_name    varchar(20),  /* 用户状态 */
+    total_pv_cnt        int,  /* 浏览次数 */
+    total_collect_cnt   int,  /* 收藏次数 */
+    total_cart_cnt      int,  /* 加购次数 */
+    pv_to_order_rate    decimal(5,2),  /* 浏览-下单转化率(%) */
+    pv_to_cart_rate     decimal(5,2),  /* 浏览-加购转化率(%) */
+    coupon_used_cnt     int,  /* 优惠券使用次数 */
+    coupon_total_amount decimal(18,2),  /* 优惠券使用金额 */
+    refund_cnt          int,  /* 退款次数 */
+    refund_rate         decimal(5,2),  /* 退款率(%) */
+    cart_product_cnt    int,  /* 购物车商品数 */
+    cart_total_amount   decimal(18,2),  /* 购物车金额 */
+    order_freq_label    varchar(20),  /* 下单频率标签 */
+    consume_level_label varchar(20),  /* 消费能力标签 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.gender_name IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_center_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_center_f.age IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_days IS '注册天数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_login_time IS '最近登录时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_min_points IS '等级所需积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_code IS '城市编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.source_name IS '注册来源';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_balance IS '会员余额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_status_name IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_pv_cnt IS '浏览次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_collect_cnt IS '收藏次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_cart_cnt IS '加购次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_order_rate IS '浏览-下单转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_cart_rate IS '浏览-加购转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_used_cnt IS '优惠券使用次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_total_amount IS '优惠券使用金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_cnt IS '退款次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_rate IS '退款率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_product_cnt IS '购物车商品数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_total_amount IS '购物车金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.order_freq_label IS '下单频率标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.consume_level_label IS '消费能力标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slusr.dwb_user_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_user_center_f_tmp1.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp1
+   规则: R0001 - 订单聚合中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp1 (
+    total_order_cnt  int,  /* 历史订单数 */
+    total_pay_amount decimal(18,2),  /* 历史消费金额 */
+    avg_order_amount decimal(18,2),  /* 平均客单价 */
+    last_order_time  datetime,  /* 最近下单时间 */
+    first_order_time datetime,  /* 首次下单时间 */
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp1 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_user_center_f_tmp2.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp2
+   规则: R0002 - RFM 评分中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 基于订单聚合指标用 NTILE(5) 窗口函数跨全量用户打分，产出 RFM 三维分数与价值分层
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp2 (
+    rfm_r_score int,  /* RFM-R值 */
+    rfm_f_score int,  /* RFM-F值 */
+    rfm_m_score int,  /* RFM-M值 */
+    rfm_segment varchar(20),  /* 用户价值分层 */
+    /* 审计字段 */
+    del_flag    NVARCHAR(1),
+    crt_cycle_id BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp2 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_r_score IS 'RFM-R值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_f_score IS 'RFM-F值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_m_score IS 'RFM-M值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_segment IS '用户价值分层';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* R0001: 订单聚合中间表（将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用） */
+SELECT
+    dof.user_id AS user_id,
+    COUNT(1) AS total_order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS total_pay_amount,
+    SUM(dof.pay_amount) / NULLIF(COUNT(1), 0) AS avg_order_amount,
+    MAX(dof.create_time) AS last_order_time,
+    MIN(dof.create_time) AS first_order_time,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.user_id;
 档案来源：../10_project_deliver/005_dwb_user_center_f</t>
         </is>
       </c>
@@ -778,7 +1240,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -803,10 +1266,245 @@
 | 8 | dim.dim_user_profile_d | 用户画像维度表 | dup |
 | 9 | dim.dim_user_base_d | 用户基础维度表 | dub10 |
 ---
-产物清单：
-- ddl/create_table_dwb_user_behavior_f.sql
-- select/R0001_select.sql
-档案来源：../10_project_deliver/006_dwb_user_behavior_f</t>
+——ddl/create_table_dwb_user_behavior_f.sql——
+/* =====================================================
+   表名: slord.dwb_user_behavior_f
+   规则: R0001 - 用户行为宽表三场景 UNION ALL 加工
+   分布键: behavior_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将三类互斥的用户行为事件流（电商交易、内容互动、社交关系）按统一的 用户+行为+领域扩展 字段模型 UNION ALL 合并到一张行为宽表。 因 user_* 与通用行为字段在三场景物理上同属每一行，无法分配到多条场景规则， 故用单条 INSERT 承载全部 184 个目标字段，三场景作为并联 JOIN 子图 在同一规则的 SQL 内并行产出，最终 UNION ALL。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_user_behavior_f (
+    user_user_id                   bigint,  /* 用户ID */
+    user_user_name                 varchar(100),  /* 用户姓名 */
+    user_user_phone                varchar(20),  /* 手机号 */
+    user_gender                    varchar(10),  /* 性别 */
+    user_age                       int,  /* 年龄 */
+    user_birthday                  date,  /* 出生日期 */
+    user_province_name             varchar(50),  /* 省份 */
+    user_city_name                 varchar(50),  /* 城市 */
+    user_user_level                int,  /* 用户等级 */
+    user_user_level_name           varchar(50),  /* 用户等级名称 */
+    user_vip_status                int,  /* VIP状态 */
+    user_register_time             timestamp,  /* 注册时间 */
+    user_register_date             date,  /* 注册日期 */
+    user_user_status               varchar(20),  /* 用户状态 */
+    user_user_status_name          varchar(50),  /* 用户状态名称 */
+    user_source_channel            varchar(50),  /* 来源渠道 */
+    user_source_type               varchar(50),  /* 来源类型 */
+    user_first_active_time         timestamp,  /* 首次活跃时间 */
+    user_last_active_time          timestamp,  /* 最后活跃时间 */
+    user_active_days               int,  /* 活跃天数 */
+    user_total_score               int,  /* 总积分 */
+    user_credit_score              int,  /* 信用分 */
+    user_risk_level                varchar(20),  /* 风险等级 */
+    user_device_type               varchar(50),  /* 设备类型 */
+    user_os_type                   varchar(50),  /* 操作系统 */
+    user_app_version               varchar(20),  /* APP版本 */
+    user_ip_address                varchar(50),  /* IP地址 */
+    user_network_type              varchar(20),  /* 网络类型 */
+    user_is_real_name              int,  /* 是否实名 */
+    user_verify_status             varchar(20),  /* 认证状态 */
+    behavior_id                    bigint,  /* 行为ID */
+    behavior_time                  timestamp,  /* 行为时间 */
+    behavior_date                  date,  /* 行为日期 */
+    behavior_hour                  int,  /* 行为小时 */
+    behavior_weekday               int,  /* 行为星期 */
+    behavior_month                 int,  /* 行为月份 */
+    behavior_quarter               int,  /* 行为季度 */
+    behavior_year                  int,  /* 行为年份 */
+    is_weekend                     int,  /* 是否周末 */
+    time_period                    varchar(20),  /* 时间段 */
+    order_order_id                 bigint,  /* 订单ID */
+    order_order_no                 varchar(50),  /* 订单编号 */
+    order_order_status             varchar(20),  /* 订单状态 */
+    order_order_status_name        varchar(50),  /* 订单状态名称 */
+    order_order_amount             decimal(18,2),  /* 订单金额 */
+    order_discount_amount          decimal(18,2),  /* 优惠金额 */
+    order_actual_amount            decimal(18,2),  /* 实付金额 */
+    order_payment_method           varchar(50),  /* 支付方式 */
+    order_payment_time             timestamp,  /* 支付时间 */
+    order_shipping_fee             decimal(18,2),  /* 运费 */
+    order_product_count            int,  /* 商品数量 */
+    order_sku_count                int,  /* SKU数量 */
+    order_is_first_order           int,  /* 是否首单 */
+    order_coupon_id                int,  /* 优惠券ID */
+    order_coupon_name              varchar(100),  /* 优惠券名称 */
+    order_points_used              int,  /* 使用积分 */
+    order_points_earned            int,  /* 获得积分 */
+    order_complete_time            timestamp,  /* 完成时间 */
+    order_cancel_time              timestamp,  /* 取消时间 */
+    order_cancel_reason            varchar(200),  /* 取消原因 */
+    order_merchant_id              int,  /* 商家ID */
+    order_merchant_name            varchar(200),  /* 商家名称 */
+    order_delivery_type            varchar(50),  /* 配送方式 */
+    order_delivery_time            timestamp,  /* 配送时间 */
+    order_receive_time             timestamp,  /* 收货时间 */
+    order_receive_status           varchar(20),  /* 收货状态 */
+    order_order_source             varchar(50),  /* 订单来源 */
+    order_remark                   varchar(500),  /* 订单备注 */
+    order_invoice_type             varchar(20),  /* 发票类型 */
+    order_invoice_title            varchar(200),  /* 发票抬头 */
+    prod_product_id                bigint,  /* 商品ID */
+    prod_product_name              varchar(200),  /* 商品名称 */
+    prod_product_code              varchar(50),  /* 商品编码 */
+    prod_sku_id                    bigint,  /* SKU_ID */
+    prod_sku_name                  varchar(200),  /* SKU名称 */
+    prod_brand_id                  int,  /* 品牌ID */
+    prod_brand_name                varchar(100),  /* 品牌名称 */
+    prod_category_id               int,  /* 类目ID */
+    prod_category_name             varchar(100),  /* 类目名称 */
+    prod_category_level1           varchar(100),  /* 一级类目 */
+    prod_category_level2           varchar(100),  /* 二级类目 */
+    prod_category_level3           varchar(100),  /* 三级类目 */
+    prod_price                     decimal(18,2),  /* 商品价格 */
+    prod_cost_price                decimal(18,2),  /* 成本价 */
+    prod_profit_rate               decimal(5,2),  /* 利润率 */
+    prod_stock_status              varchar(20),  /* 库存状态 */
+    prod_sale_status               varchar(20),  /* 销售状态 */
+    prod_product_type              varchar(50),  /* 商品类型 */
+    prod_is_virtual                int,  /* 是否虚拟商品 */
+    prod_supplier_id               int,  /* 供应商ID */
+    content_interaction_id         bigint,  /* 互动ID */
+    content_content_id             bigint,  /* 内容ID */
+    content_interaction_type       varchar(50),  /* 互动类型 */
+    content_interaction_type_name  varchar(50),  /* 互动类型名称 */
+    content_duration_seconds       int,  /* 浏览时长(秒) */
+    content_duration_minutes       decimal(5,2),  /* 浏览时长(分) */
+    content_comment_content        varchar(1000),  /* 评论内容 */
+    content_comment_word_count     int,  /* 评论字数 */
+    content_share_platform         varchar(50),  /* 分享平台 */
+    content_share_count            int,  /* 分享次数 */
+    content_like_count             int,  /* 点赞数 */
+    content_comment_count          int,  /* 评论数 */
+    content_collect_count          int,  /* 收藏数 */
+    content_forward_count          int,  /* 转发数 */
+    content_is_original            int,  /* 是否原创 */
+    content_source_type            varchar(50),  /* 来源类型 */
+    content_browse_depth           int,  /* 浏览深度 */
+    content_scroll_percentage      decimal(5,2),  /* 滚动百分比 */
+    content_click_count            int,  /* 点击次数 */
+    content_stay_time              int,  /* 停留时长 */
+    content_bounce_flag            int,  /* 是否跳出 */
+    content_exit_page              varchar(200),  /* 退出页面 */
+    content_session_id             varchar(100),  /* 会话ID */
+    content_page_view_count        int,  /* 页面浏览数 */
+    content_unique_visitor         int,  /* 独立访客标识 */
+    content_referer_url            varchar(500),  /* 来源URL */
+    content_utm_source             varchar(100),  /* UTM来源 */
+    content_utm_medium             varchar(100),  /* UTM媒介 */
+    content_utm_campaign           varchar(100),  /* UTM活动 */
+    content_interaction_device     varchar(50),  /* 互动设备 */
+    content_content_title          varchar(200),  /* 内容标题 */
+    content_content_type           varchar(50),  /* 内容类型 */
+    content_content_category       varchar(50),  /* 内容分类 */
+    content_author_id              bigint,  /* 作者ID */
+    content_author_name            varchar(100),  /* 作者名称 */
+    content_publish_time           timestamp,  /* 发布时间 */
+    content_publish_date           date,  /* 发布日期 */
+    content_content_length         int,  /* 内容长度 */
+    content_word_count             int,  /* 字数 */
+    content_read_count             int,  /* 阅读数 */
+    content_content_like_count     int,  /* 内容点赞数 */
+    content_cont…（截断）
+——select/R0001_select.sql——
+/* =========================================================================
+ * 规则编号: R0001
+ * 规则名称: 用户行为宽表三场景 UNION ALL 加工
+ * 目标表:   dwb_user_behavior_f
+ * 设计意图:
+ *   将三类互斥的用户行为事件流（电商交易 / 内容互动 / 社交关系）按统一的
+ *   用户 + 行为 + 领域扩展 字段模型 UNION ALL 合并到一张行为宽表。
+ *   因 user_* 与通用行为字段在三场景物理上同属每一行，无法分配到多条场景规则，
+ *   故用单条 SELECT 承载全部 184 个目标字段（含 4 审计字段），三场景作为
+ *   并联 JOIN 子图在同一 SQL 内并行产出，最终 UNION ALL。
+ * 三场景说明:
+ *   场景1 电商交易: 主表 ods.ods_order_main_f(oom)
+ *                   + dim.dim_product_d(dpd, oom.product_id=dpd.product_id)
+ *                   + dim.dim_user_base_d(dub, oom.user_id=dub.user_id)
+ *                   → order_*/prod_* 取真值, 其余领域字段 NULL
+ *   场景2 内容互动: 主表 ods.ods_content_interaction_f(oci)
+ *                   + dim.dim_content_d(dcd, oci.content_id=dcd.content_id)
+ *                   + dim.dim_user_base_d(dub7, oci.user_id=dub7.user_id)
+ *                   → content_* 取真值, 其余领域字段 NULL
+ *   场景3 社交关系: 主表 ods.ods_social_relation_f(osr)
+ *                   + dim.dim_user_profile_d(dup, osr.user_id=dup.user_id)
+ *                   + dim.dim_user_base_d(dub10, osr.user_id=dub10.user_id)
+ *                   → social_*/profile_* 取真值, 其余领域字段 NULL
+ * 通用字段:
+ *   user_* (30个) — 三场景分别取各自 JOIN 的 dub/dub7/dub10
+ *   behavior_time/日期/时间派生 — S1/S3 用 create_time, S2 用 interaction_time
+ * 粒度: 无变化（行级追加，无聚合无展开）
+ * ========================================================================= */
+-- =======================================================
+-- 场景1: 电商交易 (oom + dpd + dub)
+-- =======================================================
+SELECT
+  -- ========== user_* (30) ==========
+  dub.user_id                                                            AS user_user_id,
+  COALESCE(dub.user_name, '')                                            AS user_user_name,
+  CONCAT(LEFT(COALESCE(dub.user_phone, ''), 3), '****',
+         RIGHT(COALESCE(dub.user_phone, ''), 4))                         AS user_user_phone,
+  CASE dub.gender WHEN 'M' THEN '男' WHEN 'F' THEN '女'
+       ELSE '未知' END                                                   AS user_gender,
+  CAST(EXTRACT(YEAR FROM CURRENT_DATE) AS INTEGER)
+    - CAST(EXTRACT(YEAR FROM dub.birthday) AS INTEGER)                   AS user_age,
+  dub.birthday                                                           AS user_birthday,
+  COALESCE(dub.province_name, '')                                        AS user_province_name,
+  COALESCE(dub.city_name, '')                                            AS user_city_name,
+  COALESCE(dub.user_level, 0)                                            AS user_user_level,
+  COALESCE(dub.user_level_name, '')                                      AS user_user_level_name,
+  COALESCE(dub.vip_status, 0)                                            AS user_vip_status,
+  dub.register_time                                                      AS user_register_time,
+  CAST(dub.register_time AS DATE)                                        AS user_register_date,
+  COALESCE(dub.user_status, '')                                          AS user_user_status,
+  CASE dub.user_status WHEN 'ACTIVE' THEN '正常' WHEN 'INACTIVE' THEN '未激活'
+       WHEN 'BANNED' THEN '封禁' ELSE '未知' END                         AS user_user_status_name,
+  COALESCE(dub.source_channel, '')                                       AS user_source_channel,
+  COALESCE(dub.source_type, '')                                          AS user_source_type,
+  dub.first_active_time                                                  AS user_first_active_time,
+  dub.last_active_time                                                   AS user_last_active_time,
+  COALESCE(dub.active_days, 0)                                           AS user_active_days,
+  COALESCE(dub.total_score, 0)                                           AS user_total_score,
+  COALESCE(dub.credit_score, 0)                                          AS user_credit_score,
+  COALESCE(dub.risk_level, '')                                           AS user_risk_level,
+  COALESCE(dub.device_type, '')                                          AS user_device_type,
+  COALESCE(dub.os_type, '')                                              AS user_os_type,
+  COALESCE(dub.app_version, '')                                          AS user_app_version,
+  COALESCE(dub.ip_address, '')                                           AS user_ip_address,
+  COALESCE(dub.network_type, '')                                         AS user_network_type,
+  COALESCE(dub.is_real_name, 0)                                          AS user_is_real_name,
+  COALESCE(dub.verify_status, '')                                        AS user_verify_status,
+  -- ========== behavior_* (10) ==========
+  CAST(NULL AS BIGINT)                                                   AS behavior_id,
+  oom.create_time                                                        AS behavior_time,
+  CAST(oom.create_time AS DATE)                                          AS behavior_date,
+  CAST(EXTRACT(HOUR FROM oom.create_time) AS INTEGER)                    AS behavior_hour,
+  CAST(EXTRACT(DOW FROM oom.create_time) + 1 AS INTEGER)                 AS behavior_weekday,
+  CAST(EXTRACT(MONTH FROM oom.create_time) AS INTEGER)                   AS behavior_month,
+  CAST(EXTRACT(QUARTER FROM oom.create_time) AS INTEGER)                 AS behavior_quarter,
+  CAST(EXTRACT(YEAR FROM oom.create_time) AS INTEGER)                    AS behavior_year,
+  CASE WHEN EXTRACT(DOW FROM oom.create_time) IN (0, 6) THEN 1 ELSE 0 END AS is_weekend,
+  CASE WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 0 AND 5 THEN '凌晨'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 6 AND 11 THEN '上午'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 12 AND 13 THEN '中午'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 14 AND 17 THEN '下午'
+       ELSE '晚上' END                                                   AS time_period,
+  -- ========== order_* (30) ==========
+  oom.order_id                                                           AS order_order_id,
+  oom.order_no                                                           AS order_order_no,
+  oom.order_status                                                       AS order_order_status,
+  CASE oom.order_status WHEN 'PENDING' THEN '待支付' WHEN 'PAID' THEN '已支付'
+       WHEN 'SHIPPED' THEN '已发货' WHEN 'COMPLETED' THEN '已完成'
+       WHEN 'CANCELLED' THEN '已取消' ELSE '未知' END                    AS order_order_status_name,
+  oom.order_amount                                                       AS order_order_amount,
+  oom.discount_amount                                                    AS order_discount_amount,
+  oom.actual_amount                                                      AS order_actual_amount,
+  oom.payment_method                                                     AS order_payment_method,
+  oom.payment_time                                                       AS order_payment_time,
+  oom.shipping_fee                                                       AS order_shipping_fee,
+  oom.product_count                                                      AS order_p…（截断）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -858,7 +1556,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -879,9 +1578,162 @@
 | 4 | dim.dim_warehouse_f | 仓库维度表 | dwf |
 | 5 | sdinv.dwd_inventory_f | 库存事实表 | dif |
 ---
-产物清单：
-- ddl/create_table_dwb_supply_chain_center_f.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_supply_chain_center_f.sql——
+/* =====================================================
+   表名: slscc.dwb_supply_chain_center_f
+   规则: R0001 - 供应链中心宽表主加工
+   分布键: purchase_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以采购事实表为主表，左关联供应商/商品/仓库维度及库存事实表，加工状态/等级/类型映射与金额/周转天数，产出供应链中心宽表 F 表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slscc.dwb_supply_chain_center_f (
+    purchase_id          bigint,  /* 采购单ID */
+    purchase_no          varchar(64),  /* 采购单号 */
+    purchase_status_name varchar(50),  /* 采购状态 */
+    create_time          datetime,  /* 创建时间 */
+    supplier_id          bigint,  /* 供应商ID */
+    supplier_name        varchar(200),  /* 供应商名称 */
+    supplier_level_name  varchar(50),  /* 供应商等级 */
+    cooperation_years    int,  /* 合作年限 */
+    product_id           bigint,  /* 商品ID */
+    product_name         varchar(200),  /* 商品名称 */
+    purchase_qty         int,  /* 采购数量 */
+    purchase_price       decimal(18,2),  /* 采购单价 */
+    purchase_amount      decimal(18,2),  /* 采购金额 */
+    warehouse_id         bigint,  /* 仓库ID */
+    warehouse_name       varchar(100),  /* 仓库名称 */
+    warehouse_type_name  varchar(50),  /* 仓库类型 */
+    current_stock_qty    int,  /* 当前库存 */
+    locked_qty           int,  /* 锁定库存 */
+    stock_days           int,  /* 库存周转天数 */
+    del_flag             NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id         BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id    BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(purchase_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slscc.dwb_supply_chain_center_f IS '供应链中心宽表';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_id IS '采购单ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_no IS '采购单号';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_status_name IS '采购状态';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_id IS '供应商ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_name IS '供应商名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_level_name IS '供应商等级';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.cooperation_years IS '合作年限';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_qty IS '采购数量';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_price IS '采购单价';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_amount IS '采购金额';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_id IS '仓库ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_name IS '仓库名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_type_name IS '仓库类型';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.current_stock_qty IS '当前库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.locked_qty IS '锁定库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.stock_days IS '库存周转天数';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 供应链中心宽表主加工
+   目标表: slscc.dwb_supply_chain_center_f
+   设计意图: 以采购事实表为主表，左关联供应商/商品/仓库维度及库存事实表，
+             加工状态/等级/类型映射与金额/周转天数，产出供应链中心宽表 F 表
+   粒度: 一行 = 一条供应链中心记录 (按 purchase_id)
+   加载策略: 全量调度
+   来源表:
+     - sdinv.dwd_purchase_f (dpf, 主表)
+     - dim.dim_supplier_f (dsf)
+     - dim.dim_product_f (dpf4)
+     - dim.dim_warehouse_f (dwf)
+     - sdinv.dwd_inventory_f (dif, 需收敛)
+   ===================================================== */
+SELECT
+    dpf.purchase_id AS purchase_id,
+    dpf.purchase_no AS purchase_no,
+    /* 采购状态码转中文 (源字段 dpf.purchase_status) */
+    CASE dpf.purchase_status
+        WHEN 'DRAFT'     THEN '草稿'
+        WHEN 'SUBMITTED' THEN '已提交'
+        WHEN 'APPROVED'  THEN '已审批'
+        WHEN 'RECEIVED'  THEN '已入库'
+        WHEN 'CLOSED'    THEN '已关闭'
+        ELSE '其他'
+    END AS purchase_status_name,
+    dpf.create_time AS create_time,
+    dpf.supplier_id AS supplier_id,
+    COALESCE(dsf.supplier_name, '') AS supplier_name,
+    /* 供应商等级码转中文 (源字段 dsf.supplier_level) */
+    CASE dsf.supplier_level
+        WHEN 'A' THEN 'A级供应商'
+        WHEN 'B' THEN 'B级供应商'
+        WHEN 'C' THEN 'C级供应商'
+        ELSE '其他'
+    END AS supplier_level_name,
+    COALESCE(dsf.cooperation_years, 0) AS cooperation_years,
+    dpf.product_id AS product_id,
+    COALESCE(dpf4.product_name, '') AS product_name,
+    COALESCE(dpf.purchase_qty, 0) AS purchase_qty,
+    COALESCE(dpf.purchase_price, 0) AS purchase_price,
+    /* 采购金额 = 采购数量 × 采购单价 */
+    COALESCE(dpf.purchase_qty, 0) * COALESCE(dpf.purchase_price, 0) AS purchase_amount,
+    dpf.warehouse_id AS warehouse_id,
+    COALESCE(dwf.warehouse_name, '') AS warehouse_name,
+    /* 仓库类型码转中文 (源字段 dwf.warehouse_type) */
+    CASE dwf.warehouse_type
+        WHEN 'SELF'         THEN '自营仓'
+        WHEN 'THIRD_PARTY'  THEN '第三方仓'
+        ELSE '其他'
+    END AS warehouse_type_name,
+    COALESCE(inv.stock_qty, 0) AS current_stock_qty,
+    COALESCE(inv.locked_qty, 0) AS locked_qty,
+    /* ⚠️ 上游缺口: 库存周转天数依赖销量源表 (近30天销量),
+       该源表不在 source_tables 中 (见 ts.json design_logic 待补源说明),
+       暂输出 NULL, 待销量事实表接入后补全计算逻辑 */
+    NULL::int AS stock_days,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdinv.dwd_purchase_f dpf
+LEFT JOIN dim.dim_supplier_f dsf
+    ON dpf.supplier_id = dsf.supplier_id
+    AND dsf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf4
+    ON dpf.product_id = dpf4.product_id
+    AND dpf4.del_flag = 'N'
+LEFT JOIN dim.dim_warehouse_f dwf
+    ON dpf.warehouse_id = dwf.warehouse_id
+    AND dwf.del_flag = 'N'
+/* 库存收敛 (关联安全策略): dwd_inventory_f 按 (product_id, warehouse_id) 可能有多行,
+   取每个组合的最新有效库存行 (_rn=1), 避免 LEFT JOIN 导致主表放大.
+   实现 join_safety strategy: GROUP BY (product_id, warehouse_id) 收敛 + 取当前有效库存行 */
+LEFT JOIN (
+    SELECT
+        product_id,
+        warehouse_id,
+        stock_qty,
+        locked_qty,
+        ROW_NUMBER() OVER (
+            PARTITION BY product_id, warehouse_id
+            ORDER BY update_time DESC NULLS LAST
+        ) AS _rn
+    FROM sdinv.dwd_inventory_f
+    WHERE del_flag = 'N'
+) inv
+    ON dpf.product_id = inv.product_id
+    AND dpf.warehouse_id = inv.warehouse_id
+    AND inv._rn = 1
+WHERE dpf.del_flag = 'N';
 档案来源：../10_project_deliver/007_dwb_supply_chain_f</t>
         </is>
       </c>
@@ -932,7 +1784,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -953,9 +1806,165 @@
 | 4 | dim.dim_product_f | 商品维度表 | dpf |
 | 5 | sdcs.dwd_service_ticket_f | 工单事实表 | dst |
 ---
-产物清单：
-- ddl/create_table_dwb_after_sale_center_f.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_after_sale_center_f.sql——
+/* =====================================================
+   表名: slas.dwb_after_sale_center_f
+   规则: R0001 - 售后服务中心宽表组装
+   分布键: refund_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以退款事实表 dwd_refund_f 为主表，左关联订单、用户、商品、工单四表拼装售后中心宽表， 保持输出粒度=一个售后服务记录；对所有加工类字段做枚举值中文化与派生指标计算， 直取字段透传，审计字段按标准赋值，单条 INSERT 完成，无需物理中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slas.dwb_after_sale_center_f (
+    refund_id           bigint,  /* 退款ID */
+    refund_no           varchar(64),  /* 退款单号 */
+    refund_type_name    varchar(50),  /* 退款类型 */
+    refund_status_name  varchar(50),  /* 退款状态 */
+    apply_time          datetime,  /* 申请时间 */
+    complete_time       datetime,  /* 完成时间 */
+    process_days        int,  /* 处理天数 */
+    refund_amount       decimal(18,2),  /* 退款金额 */
+    refund_reason       varchar(200),  /* 退款原因 */
+    order_id            bigint,  /* 订单ID */
+    user_id             bigint,  /* 用户ID */
+    product_id          bigint,  /* 商品ID */
+    order_no            varchar(64),  /* 订单号 */
+    order_pay_amount    decimal(18,2),  /* 订单实付金额 */
+    refund_rate         decimal(5,2),  /* 退款比例(%) */
+    user_name           varchar(100),  /* 用户姓名 */
+    product_name        varchar(200),  /* 商品名称 */
+    ticket_id           bigint,  /* 工单ID */
+    ticket_status_name  varchar(50),  /* 工单状态 */
+    handler_name        varchar(50),  /* 处理人 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(refund_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slas.dwb_after_sale_center_f IS '售后服务中心宽表';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_id IS '退款ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_no IS '退款单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_type_name IS '退款类型';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_status_name IS '退款状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.apply_time IS '申请时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.complete_time IS '完成时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.process_days IS '处理天数';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_amount IS '退款金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_reason IS '退款原因';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_pay_amount IS '订单实付金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_rate IS '退款比例(%)';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_id IS '工单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_status_name IS '工单状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.handler_name IS '处理人';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 售后服务中心宽表组装
+   目标表: slas.dwb_after_sale_center_f
+   粒度:   一行 = 一个售后服务记录（业务键/distribution_key = refund_id）
+   设计意图: 以退款事实表 dwd_refund_f 为主表，左关联订单/用户/商品/工单四表
+             拼装售后中心宽表。关联安全：dof(订单事实表)、dst(工单事实表)
+             关联前需收敛至 order_id / refund_id 唯一粒度，防止 fan-out；
+             duf(用户维表)、dpf(商品维表) join_key 唯一，直接关联。
+   ===================================================== */
+SELECT
+    drf.refund_id                                                  AS refund_id,
+    COALESCE(drf.refund_no, '')                                    AS refund_no,
+    CASE drf.refund_type
+        WHEN 'ONLY_REFUND'   THEN '仅退款'
+        WHEN 'RETURN_REFUND' THEN '退货退款'
+        WHEN 'EXCHANGE'      THEN '换货'
+        ELSE '其他'
+    END                                                            AS refund_type_name,
+    CASE drf.refund_status
+        WHEN 'APPLYING' THEN '申请中'
+        WHEN 'APPROVED' THEN '已同意'
+        WHEN 'SUCCESS'  THEN '退款成功'
+        WHEN 'REJECTED' THEN '已拒绝'
+        ELSE '其他'
+    END                                                            AS refund_status_name,
+    drf.apply_time                                                 AS apply_time,
+    drf.complete_time                                              AS complete_time,
+    /* 处理天数 = 完成日期 - 申请日期；完成时间为空时用当前日期替代，申请时间为空记为 0 */
+    COALESCE(
+        (COALESCE(drf.complete_time, CURRENT_TIMESTAMP)::date - drf.apply_time::date),
+        0
+    )                                                              AS process_days,
+    COALESCE(drf.refund_amount, 0)                                 AS refund_amount,
+    COALESCE(drf.refund_reason, '')                                AS refund_reason,
+    drf.order_id                                                   AS order_id,
+    drf.user_id                                                    AS user_id,
+    drf.product_id                                                 AS product_id,
+    COALESCE(dof.order_no, '')                                     AS order_no,
+    COALESCE(dof._pay_amount, 0)                                   AS order_pay_amount,
+    /* 退款比例(%) = 退款金额 / 订单实付金额 * 100，保留两位小数；实付金额为零或空记为 0 */
+    CASE
+        WHEN COALESCE(dof._pay_amount, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(drf.refund_amount, 0) / dof._pay_amount * 100, 2)
+    END                                                            AS refund_rate,
+    COALESCE(duf.user_name, '')                                    AS user_name,
+    COALESCE(dpf.product_name, '')                                 AS product_name,
+    dst.ticket_id                                                  AS ticket_id,
+    CASE dst.ticket_status
+        WHEN 'PENDING'    THEN '待处理'
+        WHEN 'PROCESSING' THEN '处理中'
+        WHEN 'RESOLVED'   THEN '已解决'
+        WHEN 'CLOSED'     THEN '已关闭'
+        ELSE '其他'
+    END                                                            AS ticket_status_name,
+    COALESCE(dst.handler_name, '')                                 AS handler_name,
+    'N'                                                            AS del_flag,
+    '${P_CYCLE_ID}'                                                AS crt_cycle_id,
+    '${P_CYCLE_ID}'                                                AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP                                              AS dw_last_update_date
+FROM sdref.dwd_refund_f drf
+/* dof(订单事实表)按 order_id 收敛至订单粒度：order_no 取唯一值、pay_amount 取订单实付金额，
+   保证每个 order_id 只出一行，避免订单明细一对多造成退款记录 fan-out */
+LEFT JOIN (
+    SELECT
+        order_id,
+        MAX(order_no)   AS order_no,
+        MAX(pay_amount) AS _pay_amount
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY order_id
+) dof ON drf.order_id = dof.order_id
+/* duf(用户维表) user_id 唯一，直接关联 */
+LEFT JOIN dim.dim_user_f duf
+    ON drf.user_id = duf.user_id
+    AND duf.del_flag = 'N'
+/* dpf(商品维表) product_id 唯一，直接关联 */
+LEFT JOIN dim.dim_product_f dpf
+    ON drf.product_id = dpf.product_id
+    AND dpf.del_flag = 'N'
+/* dst(工单事实表)按 refund_id 收敛：一个退款对应多张工单时取最新一条工单
+   (ORDER BY ticket_id DESC 取 rn=1)，保证每个 refund_id 只出一行 */
+LEFT JOIN (
+    SELECT
+        refund_id,
+        ticket_id,
+        ticket_status,
+        handler_name,
+        ROW_NUMBER() OVER (PARTITION BY refund_id ORDER BY ticket_id DESC) AS _rn
+    FROM sdcs.dwd_service_ticket_f
+    WHERE del_flag = 'N'
+) dst ON drf.refund_id = dst.refund_id AND dst._rn = 1
+WHERE drf.del_flag = 'N';
 档案来源：../10_project_deliver/008_dwb_after_sale_center_f</t>
         </is>
       </c>
@@ -1009,7 +2018,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -1032,11 +2042,197 @@
 | 6 | sdord.dwd_order_detail_f | 订单商品明细事实表 | dod |
 | 7 | sdrev.dwd_review_f | 评价事实表 | drf |
 ---
-产物清单：
-- ddl/create_table_dwb_product_center_f.sql
-- ddl/create_table_dwb_product_review_tmp1.sql
-- ddl/create_table_dwb_product_sales_tmp1.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_product_center_f.sql——
+/* =====================================================
+   表名: slprd.dwb_product_center_f
+   规则: R0003 - 商品中心宽表装配
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 dim_product_f 为主表，LEFT JOIN 分类/品牌/店铺维度、库存快照及销售/评价汇总中间表，装配出每行一个商品的宽表(含价格折扣、库存状态等加工字段)
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_center_f (
+    product_id          bigint,  /* 商品ID */
+    product_name        varchar(200),  /* 商品名称 */
+    product_code        varchar(50),  /* 商品编码 */
+    create_time         datetime,  /* 创建时间 */
+    on_shelf_time       datetime,  /* 上架时间 */
+    cost_price          decimal(18,2),  /* 成本价 */
+    sale_price          decimal(18,2),  /* 销售价 */
+    market_price        decimal(18,2),  /* 市场价 */
+    weight              decimal(10,2),  /* 重量(kg) */
+    volume              decimal(10,4),  /* 体积(m³) */
+    product_tag         varchar(200),  /* 商品标签 */
+    category_id         bigint,  /* 分类ID */
+    category_name       varchar(100),  /* 分类名称 */
+    category_path       varchar(200),  /* 分类路径 */
+    brand_id            bigint,  /* 品牌ID */
+    brand_name          varchar(100),  /* 品牌名称 */
+    brand_origin        varchar(50),  /* 品牌产地 */
+    shop_id             bigint,  /* 店铺ID */
+    shop_name           varchar(200),  /* 店铺名称 */
+    stock_qty           int,  /* 库存数量 */
+    locked_qty          int,  /* 锁定数量 */
+    warning_qty         int,  /* 库存预警值 */
+    product_status_name varchar(20),  /* 商品状态 */
+    discount_rate       decimal(5,2),  /* 折扣率(%) */
+    gross_profit        decimal(18,2),  /* 单品毛利 */
+    gross_profit_rate   decimal(5,2),  /* 毛利率(%) */
+    available_qty       int,  /* 可售数量 */
+    stock_status        varchar(20),  /* 库存状态 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_center_f IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_code IS '商品编码';
+COMMENT ON COLUMN slprd.dwb_product_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slprd.dwb_product_center_f.on_shelf_time IS '上架时间';
+COMMENT ON COLUMN slprd.dwb_product_center_f.cost_price IS '成本价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.sale_price IS '销售价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.market_price IS '市场价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.weight IS '重量(kg)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.volume IS '体积(m³)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_tag IS '商品标签';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_id IS '分类ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_name IS '分类名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_path IS '分类路径';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_id IS '品牌ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_name IS '品牌名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slprd.dwb_product_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.stock_qty IS '库存数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.locked_qty IS '锁定数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.warning_qty IS '库存预警值';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_status_name IS '商品状态';
+COMMENT ON COLUMN slprd.dwb_product_center_f.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.gross_profit IS '单品毛利';
+COMMENT ON COLUMN slprd.dwb_product_center_f.gross_profit_rate IS '毛利率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.available_qty IS '可售数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.stock_status IS '库存状态';
+COMMENT ON COLUMN slprd.dwb_product_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slprd.dwb_product_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_product_review_tmp1.sql——
+/* =====================================================
+   表名: slprd.dwb_product_review_tmp1
+   规则: R0002 - 商品评价汇总中间表
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 把评价表(多行/商品)按 product_id 聚合到商品粒度，产出评价数/平均评分/好评率，供 R0003 关联，避免主表行数发散
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_review_tmp1 (
+    review_cnt       int,  /* 评价数 */
+    avg_rating       decimal(2,1),  /* 平均评分 */
+    good_review_rate decimal(5,2),  /* 好评率(%) */
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_review_tmp1 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.review_cnt IS '评价数';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.avg_rating IS '平均评分';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.good_review_rate IS '好评率(%)';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_review_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_product_sales_tmp1.sql——
+/* =====================================================
+   表名: slprd.dwb_product_sales_tmp1
+   规则: R0001 - 商品销售汇总中间表
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 把订单明细(多行/商品)按 product_id 聚合到商品粒度，产出销量/销售额/买家数/近30天销量，供 R0003 关联，避免主表行数发散
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_sales_tmp1 (
+    total_sales_qty    int,  /* 累计销量 */
+    total_sales_amount decimal(18,2),  /* 累计销售额 */
+    buyer_cnt          int,  /* 购买人数 */
+    sales_qty_30d      int,  /* 近30天销量 */
+    /* 审计字段 */
+    del_flag           NVARCHAR(1),
+    crt_cycle_id       BIGINT,
+    last_upd_cycle_id  BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_sales_tmp1 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.total_sales_qty IS '累计销量';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.buyer_cnt IS '购买人数';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.sales_qty_30d IS '近30天销量';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   规则号: R0001
+   规则名: 商品销售汇总中间表
+   目标表: slprd.dwb_product_sales_tmp1（中间表）
+   粒度: 多行/商品(订单明细) → 一行/商品(按 product_id 收敛)
+   设计意图: 把订单明细按 product_id 聚合到商品粒度，
+            产出累计销量/累计销售额/购买人数/近30天销量，
+            供 R0003 按 product_id 安全关联宽表，避免主表行数发散。
+   源表: sdord.dwd_order_detail_f (别名 dod)
+   关联安全: GROUP BY product_id 收敛后聚合，product_id 唯一
+   ===================================================== */
+/* 过滤说明:
+   - design_logic 明确为"全量订单"，故不臆造业务状态过滤
+     (源表订单状态字段名/枚举值未在切片中确认，保持全量聚合)。
+   - 仅保留数仓标准软删除过滤(del_flag='N')，属技术层面，
+     不改变业务"全量有效订单"口径。
+   - 源字段假设(切片 source_fields 为空，按 design_logic 推断):
+     qty=销售数量, real_price=实付单价, user_id=买家ID, order_time=下单时间。
+*/
+SELECT
+    dod.product_id AS product_id,
+    COALESCE(SUM(dod.qty), 0) AS total_sales_qty,
+    COALESCE(SUM(dod.real_price * dod.qty), 0) AS total_sales_amount,
+    COUNT(DISTINCT dod.user_id) AS buyer_cnt,
+    COALESCE(
+        SUM(
+            CASE
+                WHEN dod.order_time &gt;= CURRENT_DATE - INTERVAL '30 day'
+                    THEN dod.qty
+                ELSE 0
+            END
+        ), 0
+    ) AS sales_qty_30d,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_detail_f dod
+WHERE COALESCE(dod.del_flag, 'N') = 'N'
+GROUP BY dod.product_id;
 档案来源：../10_project_deliver/009_dwb_product_center_f</t>
         </is>
       </c>
@@ -1089,7 +2285,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -1109,10 +2306,252 @@
 | 3 | dim.dim_region_d | 地区维度表 | drd |
 | 4 | dim.dim_user_source_d | 用户来源维度表 | dus |
 ---
-产物清单：
-- ddl/create_table_dwb_user_profile_f.sql
-- select/R0001_select.sql
-档案来源：../10_project_deliver/010_dwb_user_profile_f</t>
+——ddl/create_table_dwb_user_profile_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_profile_f
+   规则: R0001 - 用户画像宽表全量装载
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 ods.ods_user_basic_f 为主表（一行=一个用户），LEFT JOIN 等级/地区/来源三张维度表 补齐画像属性，行内完成脱敏/翻译/日期拆解/VIP 判定等轻加工，全量覆盖目标宽表所有字段。 关联表数量少、无粒度变化、无聚合，单条 INSERT 即可，无需分段或建中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_profile_f (
+    user_id                    bigint,  /* 用户ID */
+    user_name                  varchar(100),  /* 用户姓名 */
+    user_phone_processed       varchar(20),  /* 手机号 */
+    user_phone_masked          varchar(20),  /* 手机号(脱敏) */
+    email                      varchar(100),  /* 电子邮箱 */
+    gender_processed           varchar(10),  /* 性别 */
+    birthday                   date,  /* 出生日期 */
+    age_processed              int,  /* 年龄 */
+    id_card                    varchar(20),  /* 身份证号 */
+    id_card_masked_processed   varchar(20),  /* 身份证号(脱敏) */
+    real_name                  varchar(50),  /* 真实姓名 */
+    nick_name                  varchar(50),  /* 昵称 */
+    avatar_url                 varchar(500),  /* 头像URL */
+    user_status                varchar(20),  /* 用户状态 */
+    user_status_name_processed varchar(20),  /* 用户状态名称 */
+    register_time              timestamp,  /* 注册时间 */
+    register_date_processed    date,  /* 注册日期 */
+    register_hour_processed    int,  /* 注册小时 */
+    register_weekday_processed int,  /* 注册星期 */
+    last_login_time            timestamp,  /* 最后登录时间 */
+    last_login_date_processed  date,  /* 最后登录日期 */
+    login_count                int,  /* 登录次数 */
+    province_code              varchar(20),  /* 省份代码 */
+    province_name              varchar(50),  /* 省份名称 */
+    city_code                  varchar(20),  /* 城市代码 */
+    city_name                  varchar(50),  /* 城市名称 */
+    district_code              varchar(20),  /* 区县代码 */
+    district_name              varchar(50),  /* 区县名称 */
+    address                    varchar(500),  /* 详细地址 */
+    zip_code                   varchar(10),  /* 邮政编码 */
+    source_id                  int,  /* 来源渠道ID */
+    source_name                varchar(50),  /* 来源渠道名称 */
+    source_type                varchar(20),  /* 来源类型 */
+    device_type                varchar(20),  /* 设备类型 */
+    os_type                    varchar(20),  /* 操作系统 */
+    app_version                varchar(20),  /* APP版本 */
+    ip_address                 varchar(50),  /* IP地址 */
+    longitude                  decimal(10,6),  /* 经度 */
+    latitude                   decimal(10,6),  /* 纬度 */
+    language                   varchar(20),  /* 语言 */
+    timezone                   varchar(50),  /* 时区 */
+    currency                   varchar(10),  /* 货币 */
+    vip_level                  int,  /* VIP等级 */
+    vip_expire_time            timestamp,  /* VIP到期时间 */
+    is_vip_processed           int,  /* 是否VIP */
+    member_points              int,  /* 会员积分 */
+    balance                    decimal(18,2),  /* 账户余额 */
+    credit_score               int,  /* 信用分 */
+    risk_level                 varchar(20),  /* 风险等级 */
+    verify_status              varchar(20),  /* 认证状态 */
+    level_id                   int,  /* 等级ID */
+    level_name                 varchar(50),  /* 等级名称 */
+    level_code                 varchar(20),  /* 等级代码 */
+    level_rank                 int,  /* 等级排序 */
+    min_points                 int,  /* 最小积分 */
+    max_points                 int,  /* 最大积分 */
+    level_icon                 varchar(500),  /* 等级图标 */
+    level_color                varchar(20),  /* 等级颜色 */
+    upgrade_points             int,  /* 升级所需积分 */
+    current_level_points       int,  /* 当前等级积分 */
+    next_level_points          int,  /* 下一等级积分 */
+    progress_percentage        decimal(5,2),  /* 升级进度百分比 */
+    privilege_list             varchar(1000),  /* 权限列表 */
+    discount_rate              decimal(5,2),  /* 折扣率 */
+    points_rate                decimal(5,2),  /* 积分倍率 */
+    free_shipping              int,  /* 免费配送 */
+    exclusive_products         int,  /* 专属商品 */
+    priority_support           int,  /* 优先客服 */
+    birthday_bonus             int,  /* 生日礼金 */
+    monthly_coupon             int,  /* 月度优惠券 */
+    annual_gift                int,  /* 年度礼品 */
+    vip_service                int,  /* VIP服务 */
+    invite_quota               int,  /* 邀请名额 */
+    max_orders_per_day         int,  /* 每日最大订单数 */
+    max_return_days            int,  /* 最大退货天数 */
+    level_benefits             varchar(1000),  /* 等级权益 */
+    upgrade_time               timestamp,  /* 升级时间 */
+    downgrade_time             timestamp,  /* 降级时间 */
+    maintain_days              int,  /* 维持天数 */
+    level_status               varchar(20),  /* 等级状态 */
+    create_time                timestamp,  /* 创建时间 */
+    update_time                timestamp,  /* 更新时间 */
+    valid_from                 timestamp,  /* 生效开始时间 */
+    valid_to                   timestamp,  /* 生效结束时间 */
+    is_active                  int,  /* 是否激活 */
+    level_tier                 int,  /* 等级层级 */
+    level_group                varchar(50),  /* 等级分组 */
+    level_category             varchar(50),  /* 等级分类 */
+    points_required            int,  /* 所需积分 */
+    orders_required            int,  /* 所需订单数 */
+    amount_required            decimal(18,2),  /* 所需金额 */
+    days_required              int,  /* 所需天数 */
+    growth_value               int,  /* 成长值 */
+    experience_value           int,  /* 经验值 */
+    contribution_value         int,  /* 贡献值 */
+    activity_value             int,  /* 活跃值 */
+    loyalty_score              decimal(5,2),  /* 忠诚度分数 */
+    engagement_score           decimal(5,2),  /* 参与度分数 */
+    satisfaction_score         decimal(5,2),  /* 满意度分数 */
+    retention_score            decimal(5,2),  /* 留存率分数 */
+    region_id                  int,  /* 地区ID */
+    region_code                varchar(20),  /* 地区代码 */
+    region_name                varchar(100),  /* 地区名称 */
+    parent_id                  int,  /* 父级ID */
+    region_level               int,  /* 地区层级 */
+    region_path                varchar(500),  /* 地区路径 */
+    province_id                int,  /* 省份ID */
+    province_abbr              varchar(20),  /* 省份简称 */
+    city_id                    int,  /* 城市ID */
+    city_abbr                  varchar(20),  /* 城市简称 */
+    district_id                int,  /* 区县ID */
+    district_abbr              varchar(20),  /* 区县简称 */
+    street_id                  int,  /* 街道ID */
+    street_code                varchar(20),  /* 街道代码 */
+    street_name                varchar(50),  /* 街道名称 */
+    center_longitude           decimal(10,6),  /* 中心经度 */
+    center_latitude            decimal(10,6),  /* 中心纬度 */
+    area_size                  decimal(18,2),  /* 区域面积 */
+    population                 int,  /* 人口数量 */
+    gdp                        decimal(18,2),  /* GDP */
+    gdp_per_capita             decimal(18,2),  /* 人均GDP */
+    climate_type               varchar(50),  /* 气候类型 */
+    economy_level              varchar(50),  /* 经济水平 */
+    development_level          varchar(50),  /* 发展水平 */
+    urban_rate                 decimal(5,2),  /* 城镇化率 */
+    region_type                varchar(50),  /* 地区类型 */
+    is_coastal                 int,  /* 是否沿海 */
+    is_border                  int,  /* 是否边境 */
+    is_capital                 int,  /* 是否省会 */
+    is_special                 int,  /* 是否特区 */
+    postal_code_prefix         varchar(10),  /* 邮编前缀 */
+    phone_area_code            varchar(20),  /* 电话区号 */
+    car_plate_prefix           varchar(10),  /* 车牌前缀 */
+    airport_code               varchar(10),  /* 机场代码 */
+    railway_station_code       varchar(20),  /* 火车站代码 */
+    port_code                  varchar(20),  /* 港口代码 */
+    weather_station_code       varchar(20),  /* 气象站代码 */
+    customs_code               varchar(20),  /* 海关代码 */
+    statistical_code           varchar(20),  /* 统计代码 */
+    iso_code                   varchar(20),  /* ISO代码 */
+    source_code                varchar(50),  /* 来源代码 */
+    source_category         …（截断）
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 用户画像宽表全量装载
+   目标表: slusr.dwb_user_profile_f
+   主表: ods.ods_user_basic_f (oub) 全量
+   关联:
+     - dim.dim_user_level_d (dul): SCD2 收敛,取当前有效行
+       (is_active=1 且 valid_from&lt;=当前时间&lt;valid_to),保证 level_id 唯一
+     - dim.dim_region_d (drd): 限定 region_level=1(省份层级)收敛,
+       保证 region_code 唯一
+     - dim.dim_user_source_d (dus): source_id 唯一,直接 LEFT JOIN
+   粒度: 无变化 (用户 -&gt; 用户),无聚合
+   说明: 多个 _processed 字段 TS 的 source_fields 与 design_logic 不一致,
+        按 skill 约定以 design_logic 口径为准翻译(详见回报)。
+   ===================================================== */
+SELECT
+    /* ---------- 主表 ods_user_basic_f 基础属性 ---------- */
+    oub.user_id AS user_id,                                                       /* 用户ID */
+    COALESCE(oub.user_name, '') AS user_name,                                     /* 用户姓名 */
+    COALESCE(LEFT(oub.user_phone, 3) || '****' || RIGHT(oub.user_phone, 4), '') AS user_phone_processed,  /* 手机号(脱敏:前3+****+后4) */
+    COALESCE(oub.user_phone_masked, '') AS user_phone_masked,                     /* 手机号(脱敏) */
+    COALESCE(oub.email, '') AS email,                                             /* 电子邮箱 */
+    CASE oub.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_processed,                                                      /* 性别(M男/F女/其它未知) */
+    oub.birthday AS birthday,                                                     /* 出生日期 */
+    COALESCE((DATE_PART('YEAR', CURRENT_DATE) - DATE_PART('YEAR', oub.birthday))::INT, 0) AS age_processed,  /* 年龄(当前年-出生年) */
+    COALESCE(oub.id_card, '') AS id_card,                                         /* 身份证号 */
+    COALESCE(LEFT(oub.id_card_masked, 6) || '********' || RIGHT(oub.id_card_masked, 4), '') AS id_card_masked_processed,  /* 身份证号(脱敏:前6+********+后4) */
+    COALESCE(oub.real_name, '') AS real_name,                                     /* 真实姓名 */
+    COALESCE(oub.nick_name, '') AS nick_name,                                     /* 昵称 */
+    COALESCE(oub.avatar_url, '') AS avatar_url,                                   /* 头像URL */
+    COALESCE(oub.user_status, '') AS user_status,                                 /* 用户状态 */
+    CASE oub.user_status
+        WHEN 'ACTIVE' THEN '正常'
+        WHEN 'INACTIVE' THEN '未激活'
+        WHEN 'BANNED' THEN '封禁'
+        ELSE '未知'
+    END AS user_status_name_processed,                                            /* 用户状态名称(ACTIVE正常/INACTIVE未激活/BANNED封禁/其它未知) */
+    oub.register_time AS register_time,                                           /* 注册时间 */
+    oub.register_time::DATE AS register_date_processed,                           /* 注册日期(取注册时间日期部分) */
+    COALESCE(DATE_PART('HOUR', oub.register_time)::INT, 0) AS register_hour_processed,  /* 注册小时(0~23) */
+    COALESCE(DATE_PART('ISODOW', oub.register_time)::INT, 0) AS register_weekday_processed,  /* 注册星期(1周一~7周日) */
+    oub.last_login_time AS last_login_time,                                       /* 最后登录时间 */
+    oub.last_login_time::DATE AS last_login_date_processed,                       /* 最后登录日期(取最后登录时间日期部分) */
+    COALESCE(oub.login_count, 0) AS login_count,                                  /* 登录次数 */
+    COALESCE(oub.province_code, '') AS province_code,                             /* 省份代码 */
+    COALESCE(oub.province_name, '') AS province_name,                             /* 省份名称 */
+    COALESCE(oub.city_code, '') AS city_code,                                     /* 城市代码 */
+    COALESCE(oub.city_name, '') AS city_name,                                     /* 城市名称 */
+    COALESCE(oub.district_code, '') AS district_code,                             /* 区县代码 */
+    COALESCE(oub.district_name, '') AS district_name,                             /* 区县名称 */
+    COALESCE(oub.address, '') AS address,                                         /* 详细地址 */
+    COALESCE(oub.zip_code, '') AS zip_code,                                       /* 邮政编码 */
+    COALESCE(oub.source_id, 0) AS source_id,                                      /* 来源渠道ID */
+    COALESCE(oub.source_name, '') AS source_name,                                 /* 来源渠道名称 */
+    COALESCE(oub.source_type, '') AS source_type,                                 /* 来源类型 */
+    COALESCE(oub.device_type, '') AS device_type,                                 /* 设备类型 */
+    COALESCE(oub.os_type, '') AS os_type,                                         /* 操作系统 */
+    COALESCE(oub.app_version, '') AS app_version,                                 /* APP版本 */
+    COALESCE(oub.ip_address, '') AS ip_address,                                   /* IP地址 */
+    COALESCE(oub.longitude, 0) AS longitude,                                      /* 经度 */
+    COALESCE(oub.latitude, 0) AS latitude,                                        /* 纬度 */
+    COALESCE(oub.language, '') AS language,                                       /* 语言 */
+    COALESCE(oub.timezone, '') AS timezone,                                       /* 时区 */
+    COALESCE(oub.currency, '') AS currency,                                       /* 货币 */
+    COALESCE(oub.vip_level, 0) AS vip_level,                                      /* VIP等级 */
+    oub.vip_expire_time AS vip_expire_time,                                       /* VIP到期时间 */
+    CASE WHEN oub.vip_expire_time &gt; CURRENT_TIMESTAMP THEN 1 ELSE 0 END AS is_vip_processed,  /* 是否VIP(到期时间晚于当前时间取1,否则0) */
+    COALESCE(oub.member_points, 0) AS member_points,                              /* 会员积分 */
+    COALESCE(oub.balance, 0) AS balance,                                          /* 账户余额 */
+    COALESCE(oub.credit_score, 0) AS credit_score,                                /* 信用分 */
+    COALESCE(oub.risk_level, '') AS risk_level,                                   /* 风险等级 */
+    COALESCE(oub.verify_status, '') AS verify_status,                             /* 认证状态 */
+    /* ---------- dim_user_level_d 等级维度(SCD2 取当前有效行) ---------- */
+    dul.level_id AS level_id,                                                     /* 等级ID */
+    COALESCE(dul.level_name, '') AS level_name,                                   /* 等级名称 */
+    COALESCE(dul.level_code, '') AS level_code,                                   /* 等级代码 */
+    COALESCE(dul.level_rank, 0) AS level_rank,                                    /* 等级排序 */
+    COALESCE(dul.min_points, 0) AS min_points,                                    /* 最小积分 */
+    COALESCE(dul.max_points, 0) AS max_points,                                    /* 最大积分 */
+    COALESCE(dul.level_icon, '') AS level_icon,                                   /* 等级图标 */
+    COALESCE(dul.level_color, '') AS level_color,                                 /* 等级颜色 */
+    COALESCE(dul.upgrade_points, 0) AS upgrade_points,                            /* 升级所需积分 */
+    COALESCE(dul.current_level_points, 0) AS current_level_points,                /* 当前等级积分 */
+    COALESCE(dul.next_level_points, 0) AS next_level_points,                      /* 下一等级积分 */
+    CASE
+        WHEN COALESCE(dul.upgrade_points, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(dul.current_level_points, 0)::NUMERIC * 100.0 / dul.upgrade_points, 2)
+    END AS progress_percentage,                                                   /* 升级进度百分比(当前等级积分/升级所需积分*100,除0保护) */
+    COALESCE(dul.privilege_list, '') AS privilege_list,                           /* 权限列表 */
+    COALESCE(dul.discount_rate, 0) AS discount_…（截断）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1163,7 +2602,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -1184,10 +2624,184 @@
 | 4 | sdmar.dwd_coupon_use_f | 优惠券使用事实表 | dcu |
 | 5 | sdord.dwd_order_f | 订单明细事实表 | dof |
 ---
-产物清单：
-- ddl/create_table_dwb_marketing_center_f.sql
-- ddl/create_table_dwb_marketing_order_tmp.sql
-- select/R0001_select.sql
+——ddl/create_table_dwb_marketing_center_f.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_center_f
+   规则: R0002 - 营销中心宽表组装
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以活动事实表为主表，LEFT JOIN 活动类型维、优惠券维、优惠券使用成本CTE、订单指标中间表，装配全部宽表字段（活动直取+字典翻译+日期差+优惠券直取与派生+订单派生指标+ROI+审计）
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_center_f (
+    activity_id          bigint,  /* 活动ID */
+    activity_name        varchar(100),  /* 活动名称 */
+    start_time           datetime,  /* 开始时间 */
+    end_time             datetime,  /* 结束时间 */
+    create_time          datetime,  /* 创建时间 */
+    min_amount           decimal(18,2),  /* 最低消费金额 */
+    discount_rate        decimal(5,2),  /* 折扣率(%) */
+    max_discount         decimal(18,2),  /* 最高优惠金额 */
+    activity_type_name   varchar(50),  /* 活动类型 */
+    activity_status_name varchar(50),  /* 活动状态 */
+    activity_days        int,  /* 活动天数 */
+    activity_type_desc   varchar(500),  /* 活动类型说明 */
+    coupon_id            bigint,  /* 优惠券ID */
+    coupon_name          varchar(100),  /* 优惠券名称 */
+    coupon_total_qty     int,  /* 优惠券发放总量 */
+    coupon_used_qty      int,  /* 优惠券已使用量 */
+    coupon_type_name     varchar(50),  /* 优惠券类型 */
+    coupon_use_rate      decimal(5,2),  /* 优惠券使用率(%) */
+    avg_order_amount     decimal(18,2),  /* 人均消费 */
+    activity_roi         decimal(8,2),  /* 活动ROI(%) */
+    del_flag             NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id         BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id    BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_center_f IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_id IS '活动ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_name IS '活动名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.start_time IS '开始时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.end_time IS '结束时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.min_amount IS '最低消费金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.max_discount IS '最高优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_type_name IS '活动类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_status_name IS '活动状态';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_days IS '活动天数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_type_desc IS '活动类型说明';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_id IS '优惠券ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_name IS '优惠券名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_total_qty IS '优惠券发放总量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_used_qty IS '优惠券已使用量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_type_name IS '优惠券类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_use_rate IS '优惠券使用率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.avg_order_amount IS '人均消费';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_roi IS '活动ROI(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_marketing_order_tmp.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_order_tmp
+   规则: R0001 - 活动订单指标中间表
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将订单明细事实表按活动ID聚合收口到活动粒度，产出订单域核心指标（订单数/GMV/参与人数/优惠金额/新客占比），为最终宽表提供订单指标输入
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_order_tmp (
+    order_cnt             int,  /* 活动订单数 */
+    gmv_amount            decimal(18,2),  /* 活动GMV */
+    participant_cnt       int,  /* 参与人数 */
+    total_discount_amount decimal(18,2),  /* 活动优惠金额 */
+    new_user_rate         decimal(5,2),  /* 新客占比(%) */
+    /* 审计字段 */
+    del_flag              NVARCHAR(1),
+    crt_cycle_id          BIGINT,
+    last_upd_cycle_id     BIGINT,
+    dw_last_update_date   TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_order_tmp IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.order_cnt IS '活动订单数';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.gmv_amount IS '活动GMV';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.participant_cnt IS '参与人数';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.total_discount_amount IS '活动优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.new_user_rate IS '新客占比(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 活动订单指标中间表
+   目标表: slmar.dwb_marketing_order_tmp
+   源表:   sdord.dwd_order_f (dof)
+   设计意图: 将订单明细事实表按 activity_id 聚合收口到活动粒度，
+             产出订单域核心指标（订单数/GMV/参与人数/优惠金额/新客占比），
+             为最终宽表（R0002）提供订单指标输入。
+   粒度变化: 订单明细（多行）→ 活动（一行），GROUP BY activity_id
+   过滤口径: order_status NOT IN ('CANCELLED','DELETED')，仅计入有效订单
+   ===================================================== */
+/* ⚠️ new_user_rate 语义待人工确认（项目红线：语义判断不自主，coder 不拍板口径）
+   -----------------------------------------------------------------------
+   design_logic 原口径:
+     "活动期间新用户订单数 / 总订单数 × 100"
+     "新用户 = 用户全表首次下单时间落在【活动起止时间】(start_time~end_time) 内"
+   -----------------------------------------------------------------------
+   实现障碍:
+     R0001 源表 dwd_order_f 仅含订单明细，不含活动起止时间(start_time/end_time)，
+     无法按原口径严格判定"新用户"。
+   -----------------------------------------------------------------------
+   本规则采用的【订单表内自洽近似口径】(可执行实现，需人工确认后定案):
+     1. 取每个用户在全表有效订单中的【首单活动】(最早有效订单所在的 activity_id)；
+     2. 若某用户的首单活动 == 当前活动，则该用户在此活动产生的所有订单计为"新客订单"；
+     3. new_user_rate = 新客订单数 / 活动总有效订单数 × 100，分母为 0 返回 NULL。
+   -----------------------------------------------------------------------
+   字段假设(待确认):
+     - 首单判定排序字段: create_time（订单创建时间）。若源表实际字段名不同需调整。
+     - 首单时间兜底: COALESCE(create_time, pay_time)。
+   -----------------------------------------------------------------------
+   若需严格按活动起止时间判定新客，应在 R0002 关联活动维表后重新计算此字段。
+*/
+SELECT
+    dof.activity_id AS activity_id,
+    COUNT(1) AS order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS gmv_amount,
+    COUNT(DISTINCT dof.user_id) AS participant_cnt,
+    COALESCE(SUM(dof.discount_amount), 0) AS total_discount_amount,
+    CASE
+        WHEN COUNT(1) = 0 THEN NULL
+        ELSE ROUND(
+            COUNT(
+                CASE WHEN ufa._first_activity_id IS NOT NULL
+                      AND ufa._first_activity_id = dof.activity_id
+                     THEN 1 END
+            ) * 100.0 / COUNT(1),
+            2
+        )
+    END AS new_user_rate,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+LEFT JOIN (
+    /* 每个有效订单用户的全表首单活动（rn=1 即该用户最早有效订单所在活动） */
+    SELECT
+        _user_id,
+        _first_activity_id
+    FROM (
+        SELECT
+            user_id AS _user_id,
+            activity_id AS _first_activity_id,
+            ROW_NUMBER() OVER (
+                PARTITION BY user_id
+                ORDER BY COALESCE(create_time, pay_time) ASC
+            ) AS _rn
+        FROM sdord.dwd_order_f
+        WHERE order_status NOT IN ('CANCELLED', 'DELETED')
+          AND user_id IS NOT NULL
+    ) _x
+    WHERE _rn = 1
+) ufa ON dof.user_id = ufa._user_id
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.activity_id;
 档案来源：../10_project_deliver/011_dwb_marketing_center_f</t>
         </is>
       </c>
@@ -1239,7 +2853,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>设计摘要（ts.md §1 概述，真实运行档案摘录）：
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
 ## 1. 概述
 | 项目 | 内容 |
 |------|------|
@@ -1273,13 +2888,303 @@
 | 17 | dim.dim_activity_f | 营销活动维度表 | daf |
 | 18 | sdref.dwd_refund_f | 退款事实表 | drf17 |
 ---
-产物清单：
-- ddl/create_table_dwb_order_center_f.sql
-- ddl/create_table_dwb_order_center_prod_tmp2.sql
-- ddl/create_table_dwb_order_center_shop_tmp3.sql
-- ddl/create_table_dwb_order_center_user_tmp1.sql
-- select/R0001_select.sql
-档案来源：../10_project_deliver/012_dwb_order_center_f</t>
+——ddl/create_table_dwb_order_center_f.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_f
+   规则: R0004 - 订单中心宽表主组装
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 dwd_order_f(订单主事实，order_id 粒度)为骨架，LEFT JOIN 订单明细(取第一条主商品)、 支付(取最新成功)、物流(取最新)、优惠券(取一条)、退款(取最新成功退款)及全部维度表， 并关联 R0001/R0002/R0003 三张画像中间表，一次性组装出订单中心宽表全部字段。 所有直取维度字段、码值翻译、脱敏、地址拼接、时长计算、订单级标识均在此规则产出。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_f (
+    order_id               bigint,  /* 订单ID */
+    order_no               varchar(64),  /* 订单号 */
+    order_status           varchar(20),  /* 订单状态 */
+    order_status_name      varchar(50),  /* 订单状态名称 */
+    order_time             datetime,  /* 下单时间 */
+    order_date             date,  /* 下单日期 */
+    order_source_name      varchar(50),  /* 订单来源 */
+    order_type_name        varchar(50),  /* 订单类型 */
+    order_remark           varchar(500),  /* 订单备注 */
+    total_amount           decimal(18,2),  /* 订单总金额 */
+    product_amount         decimal(18,2),  /* 商品金额 */
+    pay_amount             decimal(18,2),  /* 实付金额 */
+    discount_amount        decimal(18,2),  /* 优惠金额 */
+    freight_amount         decimal(18,2),  /* 运费金额 */
+    product_cnt            int,  /* 商品种类数 */
+    product_qty            int,  /* 商品总件数 */
+    ship_time              datetime,  /* 发货时间 */
+    receive_time           datetime,  /* 签收时间 */
+    delivery_days          int,  /* 物流时长(天) */
+    user_id                bigint,  /* 用户ID */
+    user_name              varchar(100),  /* 用户姓名 */
+    user_phone_masked      varchar(20),  /* 用户手机(脱敏) */
+    user_email_masked      varchar(100),  /* 用户邮箱(脱敏) */
+    gender_name            varchar(10),  /* 用户性别 */
+    user_birthday          date,  /* 用户生日 */
+    user_age               int,  /* 用户年龄 */
+    user_register_time     datetime,  /* 注册时间 */
+    user_level_id          int,  /* 用户等级ID */
+    user_level_name        varchar(50),  /* 用户等级名称 */
+    member_points          int,  /* 会员积分 */
+    member_balance         decimal(18,2),  /* 会员余额 */
+    user_tag               varchar(500),  /* 用户标签 */
+    user_source_name       varchar(50),  /* 用户来源 */
+    user_province_code     varchar(20),  /* 用户省份编码 */
+    user_city_code         varchar(20),  /* 用户城市编码 */
+    user_days              int,  /* 用户注册天数 */
+    product_id             bigint,  /* 商品ID */
+    product_name           varchar(200),  /* 商品名称 */
+    product_code           varchar(50),  /* 商品编码 */
+    sku_code               varchar(50),  /* SKU编码 */
+    category_l1_id         bigint,  /* 一级类目ID */
+    category_l1_name       varchar(100),  /* 一级类目名称 */
+    category_l2_id         bigint,  /* 二级类目ID */
+    category_l2_name       varchar(100),  /* 二级类目名称 */
+    category_l3_id         bigint,  /* 三级类目ID */
+    category_l3_name       varchar(100),  /* 三级类目名称 */
+    brand_id               bigint,  /* 品牌ID */
+    brand_name             varchar(100),  /* 品牌名称 */
+    brand_origin           varchar(50),  /* 品牌产地 */
+    product_attr           varchar(500),  /* 商品属性 */
+    product_spec           varchar(200),  /* 商品规格 */
+    product_weight         decimal(10,2),  /* 商品重量(kg) */
+    product_volume         decimal(10,4),  /* 商品体积(m³) */
+    cost_price             decimal(18,2),  /* 商品成本价 */
+    sale_price             decimal(18,2),  /* 商品售价 */
+    real_price             decimal(18,2),  /* 商品实付单价 */
+    product_tag            varchar(200),  /* 商品标签 */
+    product_status_name    varchar(20),  /* 商品状态 */
+    product_profit         decimal(18,2),  /* 单品毛利 */
+    shop_id                bigint,  /* 店铺ID */
+    shop_name              varchar(200),  /* 店铺名称 */
+    shop_type_name         varchar(50),  /* 店铺类型 */
+    shop_level_name        varchar(20),  /* 店铺等级 */
+    shop_score             decimal(3,2),  /* 店铺评分 */
+    company_name           varchar(200),  /* 店铺所属公司 */
+    shop_province_code     varchar(20),  /* 店铺省份编码 */
+    shop_province_name     varchar(50),  /* 店铺省份名称 */
+    shop_city_code         varchar(20),  /* 店铺城市编码 */
+    shop_city_name         varchar(50),  /* 店铺城市名称 */
+    shop_open_time         datetime,  /* 开店时间 */
+    receiver_name          varchar(100),  /* 收货人姓名 */
+    receiver_phone_masked  varchar(20),  /* 收货人手机(脱敏) */
+    receiver_province_code varchar(20),  /* 收货省份编码 */
+    receiver_province_name varchar(50),  /* 收货省份名称 */
+    receiver_city_code     varchar(20),  /* 收货城市编码 */
+    receiver_city_name     varchar(50),  /* 收货城市名称 */
+    receiver_district_code varchar(20),  /* 收货区县编码 */
+    receiver_district_name varchar(50),  /* 收货区县名称 */
+    receiver_street        varchar(200),  /* 收货街道 */
+    receiver_address       varchar(500),  /* 详细地址 */
+    full_address           varchar(1000),  /* 完整收货地址 */
+    postal_code            varchar(10),  /* 邮政编码 */
+    address_tag_name       varchar(50),  /* 地址标签 */
+    longitude              decimal(10,6),  /* 经度 */
+    latitude               decimal(10,6),  /* 纬度 */
+    pay_time               datetime,  /* 支付时间 */
+    pay_id                 bigint,  /* 支付ID */
+    pay_no                 varchar(64),  /* 支付流水号 */
+    pay_method_code        varchar(20),  /* 支付方式编码 */
+    pay_method_name        varchar(50),  /* 支付方式名称 */
+    pay_channel_name       varchar(50),  /* 支付渠道名称 */
+    pay_status_name        varchar(20),  /* 支付状态 */
+    bank_card_masked       varchar(20),  /* 银行卡号(脱敏) */
+    bank_name              varchar(50),  /* 支付银行 */
+    installment_num        int,  /* 分期期数 */
+    pay_service_fee        decimal(10,2),  /* 支付手续费 */
+    pay_duration_minutes   int,  /* 下单到支付时长(分钟) */
+    logistics_id           bigint,  /* 物流ID */
+    logistics_no           varchar(50),  /* 物流单号 */
+    logistics_company_code varchar(20),  /* 物流公司编码 */
+    logistics_company_name varchar(100),  /* 物流公司名称 */
+    logistics_type_name    varchar(50),  /* 物流类型 */
+    warehouse_id           bigint,  /* 发货仓库ID */
+    warehouse_name         varchar(100),  /* 发货仓库名称 */
+    warehouse_address      varchar(200),  /* 发货仓库地址 */
+    logistics_status_name  varchar(50),  /* 物流状态 */
+    pickup_time            datetime,  /* 揽收时间 */
+    sign_receiver_name     varchar(100),  /* 签收人 */
+    ship_duration_hours    int,  /* 支付到发货时长(小时) */
+    coupon_id              bigint,  /* 优惠券ID */
+    coupon_name            varchar(100),  /* 优惠券名称 */
+    coupon_type_name       varchar(50),  /* 优惠券类型 */
+    coupon_amount          decimal(10,2),  /* 优惠券金额 */
+    activity_id            bigint,  /* 活动ID */
+    activity_name          varchar(100),  /* 活动名称 */
+    activity_type_name     varchar(50),  /* 活动类型 */
+    activity_discount_rate decimal(5,2),  /* 活动折扣率(%) */
+    full_reduce_amount     decimal(10,2),  /* 满减金额 */
+    points_deduct_amount   decimal(10,2),  /* 积分抵扣金额 */
+    points_used            int,  /* 使用积分数 */
+    is_marketing_order     varchar(1),  /* 是否营销订单 */
+    total_discount_amount  decimal(18,2),  /* 总优惠金额 */
+    refund_id              bigint,  /* 退款ID */
+    refund_no              varchar(64),  /* 退款单号 */
+    refund_type_name       varchar(50),  /* 退款类型 */
+    refund_reason          varchar(200),  /* 退款原因 */
+    refund_amount          decimal(18,2),  /* 退款金额 */
+    refund_status_name     varchar(50),  /* 退款状态 */
+    refund_apply_time      datetime,  /* 退款申请时间 */
+    refund_complete_time   datetime,  /* 退款完成时间 */
+    is_refund_order        varchar(1),  /* 是否退款订单 */
+    del_flag               NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id           BIGINT,  /* 创建批次 */
+    last_upd_cycle_id      BIGINT,  /* 更新批次 */
+    dw_last_update_date    TIMESTAMP(0)  /* 更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_f IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_status IS '订单状态';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_status_name IS '订单状态名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_time IS '下单时间';
+COMMENT ON C…（截断）
+——ddl/create_table_dwb_order_center_prod_tmp2.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_prod_tmp2
+   规则: R0002 - 商品画像聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 收口按 product_id 聚合的商品级累计销量与销售额指标。中间表粒度=一个商品一行， 以 product_id 为关联键供主规则 JOIN。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_prod_tmp2 (
+    product_sales_cnt    int,  /* 商品累计销量 */
+    product_sales_amount decimal(18,2),  /* 商品累计销售额 */
+    /* 审计字段 */
+    del_flag             NVARCHAR(1),
+    crt_cycle_id         BIGINT,
+    last_upd_cycle_id    BIGINT,
+    dw_last_update_date  TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_prod_tmp2 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.product_sales_cnt IS '商品累计销量';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.product_sales_amount IS '商品累计销售额';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_prod_tmp2.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_order_center_shop_tmp3.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_shop_tmp3
+   规则: R0003 - 店铺画像聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 收口按 shop_id 聚合的店铺历史订单数指标。中间表粒度=一个店铺一行， 以 shop_id 为关联键供主规则 JOIN。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_shop_tmp3 (
+    shop_history_order_cnt int,  /* 店铺历史订单数 */
+    /* 审计字段 */
+    del_flag               NVARCHAR(1),
+    crt_cycle_id           BIGINT,
+    last_upd_cycle_id      BIGINT,
+    dw_last_update_date    TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_shop_tmp3 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_shop_tmp3.shop_history_order_cnt IS '店铺历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_shop_tmp3.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_shop_tmp3.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_shop_tmp3.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_shop_tmp3.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_order_center_user_tmp1.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_user_tmp1
+   规则: R0001 - 用户画像聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 收口所有按 user_id 聚合的用户级指标（历史订单统计、消费金额、RFM 分层、 常用支付方式、优惠券使用、退款次数、偏好活动类型等），避免在主 INSERT 中 混入聚合后关联逻辑。中间表粒度=一个用户一行，以 user_id 为关联键供主规则 JOIN。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_user_tmp1 (
+    first_order_time        datetime,  /* 首次下单时间 */
+    last_order_time         datetime,  /* 最近下单时间 */
+    history_order_cnt       int,  /* 历史订单数 */
+    history_pay_amount      decimal(18,2),  /* 历史消费金额 */
+    history_discount_amount decimal(18,2),  /* 历史优惠金额 */
+    avg_order_amount        decimal(18,2),  /* 平均客单价 */
+    rfm_segment             varchar(20),  /* 用户RFM分层 */
+    is_repeat_user          varchar(1),  /* 是否复购用户 */
+    fav_pay_method          varchar(20),  /* 用户常用支付方式 */
+    user_coupon_used_cnt    int,  /* 用户优惠券使用次数 */
+    user_refund_cnt         int,  /* 用户历史退款次数 */
+    user_fav_activity_type  varchar(50),  /* 用户偏好活动类型 */
+    /* 审计字段 */
+    del_flag                NVARCHAR(1),
+    crt_cycle_id            BIGINT,
+    last_upd_cycle_id       BIGINT,
+    dw_last_update_date     TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_user_tmp1 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_discount_amount IS '历史优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.rfm_segment IS '用户RFM分层';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.is_repeat_user IS '是否复购用户';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.fav_pay_method IS '用户常用支付方式';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_coupon_used_cnt IS '用户优惠券使用次数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_refund_cnt IS '用户历史退款次数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_fav_activity_type IS '用户偏好活动类型';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——select/R0001_select.sql——
+/* =====================================================
+   R0001: 用户画像聚合（收口所有按 user_id 聚合的用户级指标）
+   目标表: slord.dwb_order_center_user_tmp1（中间表，一行=一个用户）
+   来源表:
+     - sdord.dwd_order_f       (dof)  订单事实，过滤 order_status NOT IN ('CANCELLED','DELETED')
+     - sdpay.dwd_payment_f     (dpf)  支付事实，过滤 pay_status='SUCCESS'
+     - sdmar.dwd_coupon_use_f  (dcu)  优惠券使用，过滤 use_status='USED'
+     - sdref.dwd_refund_f      (drf17)退款事实，过滤 refund_status='SUCCESS'
+   关联安全: 4 个源表各自 GROUP BY user_id 收敛后聚合天然唯一，再 LEFT JOIN 组装
+   ===================================================== */
+WITH
+/* CTE 1: 订单基础聚合（按用户收敛） */
+order_agg AS (
+    SELECT
+        dof.user_id                                                    AS user_id,
+        MIN(dof.order_time)                                            AS first_order_time,
+        MAX(dof.order_time)                                            AS last_order_time,
+        COUNT(1)                                                       AS history_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0)                               AS history_pay_amount,
+        COALESCE(SUM(dof.discount_amount), 0)                          AS history_discount_amount
+    FROM sdord.dwd_order_f dof
+    WHERE COALESCE(dof.del_flag, 'N') = 'N'
+      AND dof.order_status NOT IN ('CANCELLED', 'DELETED')
+    GROUP BY dof.user_id
+),
+/* CTE 2: 在订单聚合基础上…（截断）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">

--- a/eval-suite/out/platform_dataset_intranet.xlsx
+++ b/eval-suite/out/platform_dataset_intranet.xlsx
@@ -551,10 +551,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 ，粒度：每行一个订单
-- 覆盖全部 7 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 ，粒度：每行一个订单
+- 目标字段 7 项：order_id, cust_id, total_amount, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 1 张：ods_trade_order_di
+- 建表 DDL（create_table_.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -732,10 +733,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 dws.dwb_trade_wide_f，粒度：每行一个订单
-- 覆盖全部 15 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_trade_wide_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 dws.dwb_trade_wide_f，粒度：每行一个订单
+- 目标字段 15 项：order_id, cust_id, product_id, order_amt, order_qty, cust_name, cust_level, product_name, category_code, total_pay_amt, total_ship_fee, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：ods_trade_order_di, dim_cust_d, dim_product_d, ods_payment_di, ods_logistics_di
+- 建表 DDL（create_table_dwb_trade_wide_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -932,10 +934,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slshp.dwb_shop_center_f，粒度：每行一个店铺记录
-- 覆盖全部 20 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_shop_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slshp.dwb_shop_center_f，粒度：每行一个店铺记录
+- 目标字段 20 项：shop_id, shop_name, shop_type_name, shop_status_name, company_name, open_time, open_days, province_code, province_name, shop_score, service_score, logistics_score, total_order_cnt, total_sales_amount, total_buyer_cnt, review_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 4 张：dim_shop_f, dim_region_f, dwd_order_f, dwd_review_f
+- 建表 DDL（create_table_dwb_shop_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -1192,10 +1195,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slusr.dwb_user_center_f，粒度：每行一个用户记录
-- 覆盖全部 46 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_user_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slusr.dwb_user_center_f，粒度：每行一个用户记录
+- 目标字段 46 项：user_id, user_name, user_phone_masked, gender_name, birthday, age, register_time, register_days, last_login_time, level_id, level_name, level_min_points, province_code, province_name, city_code, city_name, source_name, member_points, member_balance, user_status_name, total_order_cnt, total_pay_amount, avg_order_amount, last_order_time, first_order_time, rfm_r_score, rfm_f_score, rfm_m_score, rfm_segment, total_pv_cnt, total_collect_cnt, total_cart_cnt, pv_to_order_rate, pv_to_cart_rate, coupon_used_cnt, coupon_total_amount, refund_cnt, refund_rate, cart_product_cnt, cart_total_amount, order_freq_label, consume_level_label, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 9 张：dim_user_f, dim_user_level_f, dim_region_f, dim_user_source_f, dwd_order_f, dwd_user_behavior_f, dwd_coupon_use_f, dwd_refund_f, dwd_cart_f
+- 建表 DDL（create_table_dwb_user_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -1509,10 +1513,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slord.dwb_user_behavior_f，粒度：每行一个用户行为记录
-- 覆盖全部 264 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_user_behavior_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slord.dwb_user_behavior_f，粒度：每行一个用户行为记录
+- 目标字段 184 项：user_user_id, user_user_name, user_user_phone, user_gender, user_age, user_birthday, user_province_name, user_city_name, user_user_level, user_user_level_name, user_vip_status, user_register_time, user_register_date, user_user_status, user_user_status_name, user_source_channel, user_source_type, user_first_active_time, user_last_active_time, user_active_days, user_total_score, user_credit_score, user_risk_level, user_device_type, user_os_type, user_app_version, user_ip_address, user_network_type, user_is_real_name, user_verify_status, behavior_id, behavior_time, behavior_date, behavior_hour, behavior_weekday, behavior_month, behavior_quarter, behavior_year, is_weekend, time_period, order_order_id, order_order_no, order_order_status, order_order_status_name, order_order_amount, order_discount_amount, order_actual_amount, order_payment_method, order_payment_time, order_shipping_fee, order_product_count, order_sku_count, order_is_first_order, order_coupon_id, order_coupon_name, order_points_used, order_points_earned, order_complete_time, order_cancel_time, order_cancel_reason, order_merchant_id, order_merchant_name, order_delivery_type, order_delivery_time, order_receive_time, order_receive_status, order_order_source, order_remark, order_invoice_type, order_invoice_title, prod_product_id, prod_product_name, prod_product_code, prod_sku_id, prod_sku_name, prod_brand_id, prod_brand_name, prod_category_id, prod_category_name, prod_category_level1, prod_category_level2, prod_category_level3, prod_price, prod_cost_price, prod_profit_rate, prod_stock_status, prod_sale_status, prod_product_type, prod_is_virtual, prod_supplier_id, content_interaction_id, content_content_id, content_interaction_type, content_interaction_type_name, content_duration_seconds, content_duration_minutes, content_comment_content, content_comment_word_count, content_share_platform, content_share_count, content_like_count, content_comment_count, content_collect_count, content_forward_count, content_is_original, content_source_type, content_browse_depth, content_scroll_percentage, content_click_count, content_stay_time, content_bounce_flag, content_exit_page, content_session_id, content_page_view_count, content_unique_visitor, content_referer_url, content_utm_source, content_utm_medium, content_utm_campaign, content_interaction_device, content_content_title, content_content_type, content_content_category, content_author_id, content_author_name, content_publish_time, content_publish_date, content_content_length, content_word_count, content_read_count, content_content_like_count, content_content_comment_count, content_content_share_count, content_content_collect_count, content_topic_id, content_topic_name, content_is_hot, content_is_recommend, content_content_status, content_content_score, social_relation_id, social_target_user_id, social_relation_type, social_relation_type_name, social_is_mutual, social_interaction_count, social_last_interaction_time, social_relation_status, social_source, social_group_id, social_group_name, social_remark, social_intimacy_level, social_chat_count, social_call_count, social_video_call_count, social_gift_count, social_follow_days, social_interaction_frequency, social_common_friends, social_common_groups, social_social_distance, social_relationship_strength, social_trust_level, social_contact_importance, profile_avatar_url, profile_profession, profile_education, profile_interests, profile_active_level, profile_influence_score, profile_social_value, profile_user_tags, profile_fans_count, profile_follow_count, profile_friend_count, profile_social_activity_score, profile_content_creation_score, profile_engagement_score, profile_social_influence_rank, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 7 张：ods_order_main_f, dim_product_d, dim_user_base_d, ods_content_interaction_f, dim_content_d, ods_social_relation_f, dim_user_profile_d
+- 建表 DDL（create_table_dwb_user_behavior_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -1739,10 +1744,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slscc.dwb_supply_chain_center_f，粒度：每行一个供应链记录
-- 覆盖全部 23 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_supply_chain_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slscc.dwb_supply_chain_center_f，粒度：每行一个供应链记录
+- 目标字段 23 项：purchase_id, purchase_no, purchase_status_name, create_time, supplier_id, supplier_name, supplier_level_name, cooperation_years, product_id, product_name, purchase_qty, purchase_price, purchase_amount, warehouse_id, warehouse_name, warehouse_type_name, current_stock_qty, locked_qty, stock_days, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：dwd_purchase_f, dim_supplier_f, dim_product_f, dim_warehouse_f, dwd_inventory_f
+- 建表 DDL（create_table_dwb_supply_chain_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -1970,10 +1976,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slas.dwb_after_sale_center_f，粒度：每行一个售后服务记录
-- 覆盖全部 24 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_after_sale_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slas.dwb_after_sale_center_f，粒度：每行一个售后服务记录
+- 目标字段 24 项：refund_id, refund_no, refund_type_name, refund_status_name, apply_time, complete_time, process_days, refund_amount, refund_reason, order_id, order_no, order_pay_amount, refund_rate, user_id, user_name, product_id, product_name, ticket_id, ticket_status_name, handler_name, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：dwd_refund_f, dwd_order_f, dim_user_f, dim_product_f, dwd_service_ticket_f
+- 建表 DDL（create_table_dwb_after_sale_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -2238,10 +2245,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slprd.dwb_product_center_f，粒度：每行一个商品记录
-- 覆盖全部 39 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_product_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slprd.dwb_product_center_f，粒度：每行一个商品记录
+- 目标字段 39 项：product_id, product_name, product_code, product_status_name, create_time, on_shelf_time, cost_price, sale_price, market_price, discount_rate, gross_profit, gross_profit_rate, category_id, category_name, category_path, brand_id, brand_name, brand_origin, shop_id, shop_name, stock_qty, locked_qty, available_qty, warning_qty, stock_status, total_sales_qty, total_sales_amount, buyer_cnt, sales_qty_30d, review_cnt, avg_rating, good_review_rate, weight, volume, product_tag, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 7 张：dim_product_f, dim_product_category_f, dim_brand_f, dim_shop_f, dwd_inventory_f, dwd_order_detail_f, dwd_review_f
+- 建表 DDL（create_table_dwb_product_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -2556,10 +2564,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slusr.dwb_user_profile_f，粒度：每行一个用户画像记录
-- 覆盖全部 187 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_user_profile_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slusr.dwb_user_profile_f，粒度：每行一个用户画像记录
+- 目标字段 187 项：user_id, user_name, user_phone_processed, user_phone_masked, email, gender_processed, birthday, age_processed, id_card, id_card_masked_processed, real_name, nick_name, avatar_url, user_status, user_status_name_processed, register_time, register_date_processed, register_hour_processed, register_weekday_processed, last_login_time, last_login_date_processed, login_count, province_code, province_name, city_code, city_name, district_code, district_name, address, zip_code, source_id, source_name, source_type, device_type, os_type, app_version, ip_address, longitude, latitude, language, timezone, currency, vip_level, vip_expire_time, is_vip_processed, member_points, balance, credit_score, risk_level, verify_status, level_id, level_name, level_code, level_rank, min_points, max_points, level_icon, level_color, upgrade_points, current_level_points, next_level_points, progress_percentage, privilege_list, discount_rate, points_rate, free_shipping, exclusive_products, priority_support, birthday_bonus, monthly_coupon, annual_gift, vip_service, invite_quota, max_orders_per_day, max_return_days, level_benefits, upgrade_time, downgrade_time, maintain_days, level_status, create_time, update_time, valid_from, valid_to, is_active, level_tier, level_group, level_category, points_required, orders_required, amount_required, days_required, growth_value, experience_value, contribution_value, activity_value, loyalty_score, engagement_score, satisfaction_score, retention_score, region_id, region_code, region_name, parent_id, region_level, region_path, province_id, province_abbr, city_id, city_abbr, district_id, district_abbr, street_id, street_code, street_name, center_longitude, center_latitude, area_size, population, gdp, gdp_per_capita, climate_type, economy_level, development_level, urban_rate, region_type, is_coastal, is_border, is_capital, is_special, postal_code_prefix, phone_area_code, car_plate_prefix, airport_code, railway_station_code, port_code, weather_station_code, customs_code, statistical_code, iso_code, source_code, source_category, channel_id, channel_code, channel_name, channel_type, channel_category, campaign_id, campaign_code, campaign_name, campaign_type, medium_id, medium_code, medium_name, medium_type, term_id, term_keyword, content_id, content_name, referral_url, landing_page, utm_source, utm_medium, utm_campaign, utm_term, utm_content, cost_per_acquisition, conversion_rate, quality_score, retention_rate_7d, retention_rate_30d, lifetime_value, first_order_amount, first_order_days, register_device, register_os, register_browser, register_network, register_location, attribution_model, lookback_days, priority, is_paid, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 4 张：ods_user_basic_f, dim_user_level_d, dim_region_d, dim_user_source_d
+- 建表 DDL（create_table_dwb_user_profile_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -2807,10 +2816,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slmar.dwb_marketing_center_f，粒度：每行一个营销记录
-- 覆盖全部 29 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_marketing_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slmar.dwb_marketing_center_f，粒度：每行一个营销记录
+- 目标字段 29 项：activity_id, activity_name, activity_type_name, activity_type_desc, activity_status_name, start_time, end_time, activity_days, create_time, min_amount, discount_rate, max_discount, coupon_id, coupon_name, coupon_type_name, coupon_total_qty, coupon_used_qty, coupon_use_rate, order_cnt, gmv_amount, participant_cnt, total_discount_amount, avg_order_amount, new_user_rate, activity_roi, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：dwd_activity_f, dim_activity_type_f, dim_coupon_f, dwd_coupon_use_f, dwd_order_f
+- 建表 DDL（create_table_dwb_marketing_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -3189,10 +3199,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>任务完成标准（自 RS 派生）：
-- 产出 TS 设计（ts.md/ts.json），目标表 slord.dwb_order_center_f，粒度：每行一个订单
-- 覆盖全部 150 个映射字段的加工口径，无遗漏无幻觉字段
-- 建表 DDL（create_table_dwb_order_center_f.sql）与结构一致；ETL 每规则一个 SELECT 文件
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slord.dwb_order_center_f，粒度：每行一个订单
+- 目标字段 150 项：order_id, order_no, order_status, order_status_name, order_time, pay_time, ship_time, receive_time, delivery_days, total_amount, product_amount, pay_amount, discount_amount, freight_amount, product_cnt, product_qty, order_source_name, order_type_name, order_remark, order_date, user_id, user_name, user_phone_masked, user_email_masked, gender_name, user_birthday, user_age, user_register_time, user_level_id, user_level_name, member_points, member_balance, first_order_time, last_order_time, history_order_cnt, history_pay_amount, history_discount_amount, avg_order_amount, rfm_segment, user_tag, user_source_name, user_province_code, user_city_code, user_days, is_repeat_user, product_id, product_name, product_code, sku_code, category_l1_id, category_l1_name, category_l2_id, category_l2_name, category_l3_id, category_l3_name, brand_id, brand_name, brand_origin, product_attr, product_spec, product_weight, product_volume, cost_price, sale_price, real_price, product_tag, product_status_name, product_sales_cnt, product_sales_amount, product_profit, shop_id, shop_name, shop_type_name, shop_level_name, shop_score, company_name, shop_province_code, shop_province_name, shop_city_code, shop_city_name, shop_open_time, shop_history_order_cnt, receiver_name, receiver_phone_masked, receiver_province_code, receiver_province_name, receiver_city_code, receiver_city_name, receiver_district_code, receiver_district_name, receiver_street, receiver_address, full_address, postal_code, address_tag_name, longitude, latitude, pay_id, pay_no, pay_method_code, pay_method_name, pay_channel_name, pay_status_name, bank_card_masked, bank_name, installment_num, pay_service_fee, fav_pay_method, pay_duration_minutes, logistics_id, logistics_no, logistics_company_code, logistics_company_name, logistics_type_name, warehouse_id, warehouse_name, warehouse_address, logistics_status_name, pickup_time, sign_receiver_name, ship_duration_hours, coupon_id, coupon_name, coupon_type_name, coupon_amount, activity_id, activity_name, activity_type_name, activity_discount_rate, full_reduce_amount, points_deduct_amount, points_used, is_marketing_order, total_discount_amount, user_coupon_used_cnt, user_fav_activity_type, refund_id, refund_no, refund_type_name, refund_reason, refund_amount, refund_status_name, refund_apply_time, refund_complete_time, is_refund_order, user_refund_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 18 张：dwd_order_f, dwd_order_detail_f, dwd_payment_f, dwd_logistics_f, dwd_coupon_use_f, dim_user_f, dim_user_level_f, dim_product_f, dim_product_category_f, dim_brand_f, dim_shop_f, dim_region_f, dim_warehouse_f, dim_payment_method_f, dim_logistics_company_f, dim_coupon_f, dim_activity_f, dwd_refund_f
+- 建表 DDL（create_table_dwb_order_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>

--- a/eval-suite/out/platform_dataset_intranet.xlsx
+++ b/eval-suite/out/platform_dataset_intranet.xlsx
@@ -1224,7 +1224,34 @@
 dim_region_f.region_name --[数据加工]--&gt; city_name(城市名称)
 dim_user_source_f.source_name --[直接复制]--&gt; source_name(注册来源)
 dim_user_f.member_points --[直接复制]--&gt; member_points(会员积分)
-dim_user_f.member_balance --[直接…（截断）</t>
+dim_user_f.member_balance --[直接复制]--&gt; member_balance(会员余额)
+dim_user_f.user_status --[数据加工]--&gt; user_status_name(用户状态)
+（无源声明） --[数据加工]--&gt; total_order_cnt(历史订单数)
+（无源声明） --[数据加工]--&gt; total_pay_amount(历史消费金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f.create_time --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f.create_time --[数据加工]--&gt; first_order_time(首次下单时间)
+（无源声明） --[数据加工]--&gt; rfm_r_score(RFM-R值)
+（无源声明） --[数据加工]--&gt; rfm_f_score(RFM-F值)
+（无源声明） --[数据加工]--&gt; rfm_m_score(RFM-M值)
+（无源声明） --[数据加工]--&gt; rfm_segment(用户价值分层)
+dwd_user_behavior_f.pv_cnt --[数据加工]--&gt; total_pv_cnt(浏览次数)
+dwd_user_behavior_f.collect_cnt --[数据加工]--&gt; total_collect_cnt(收藏次数)
+dwd_user_behavior_f.cart_cnt --[数据加工]--&gt; total_cart_cnt(加购次数)
+（无源声明） --[数据加工]--&gt; pv_to_order_rate(浏览-下单转化率(%))
+（无源声明） --[数据加工]--&gt; pv_to_cart_rate(浏览-加购转化率(%))
+（无源声明） --[数据加工]--&gt; coupon_used_cnt(优惠券使用次数)
+（无源声明） --[数据加工]--&gt; coupon_total_amount(优惠券使用金额)
+（无源声明） --[数据加工]--&gt; refund_cnt(退款次数)
+（无源声明） --[数据加工]--&gt; refund_rate(退款率(%))
+（无源声明） --[数据加工]--&gt; cart_product_cnt(购物车商品数)
+（无源声明） --[数据加工]--&gt; cart_total_amount(购物车金额)
+（无源声明） --[数据加工]--&gt; order_freq_label(下单频率标签)
+（无源声明） --[数据加工]--&gt; consume_level_label(消费能力标签)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1411,7 +1438,79 @@
     content_word_count             int,  /* 字数 */
     content_read_count             int,  /* 阅读数 */
     content_content_like_count     int,  /* 内容点赞数 */
-    content_cont…（截断）
+    content_content_comment_count  int,  /* 内容评论数 */
+    content_content_share_count    int,  /* 内容分享数 */
+    content_content_collect_count  int,  /* 内容收藏数 */
+    content_topic_id               int,  /* 话题ID */
+    content_topic_name             varchar(100),  /* 话题名称 */
+    content_is_hot                 int,  /* 是否热门 */
+    content_is_recommend           int,  /* 是否推荐 */
+    content_content_status         varchar(20),  /* 内容状态 */
+    content_content_score          decimal(5,2),  /* 内容评分 */
+    social_relation_id             bigint,  /* 关系ID */
+    social_target_user_id          bigint,  /* 目标用户ID */
+    social_relation_type           varchar(50),  /* 关系类型 */
+    social_relation_type_name      varchar(50),  /* 关系类型名称 */
+    social_is_mutual               int,  /* 是否互相关注 */
+    social_interaction_count       int,  /* 互动次数 */
+    social_last_interaction_time   timestamp,  /* 最后互动时间 */
+    social_relation_status         varchar(20),  /* 关系状态 */
+    social_source                  varchar(50),  /* 来源 */
+    social_group_id                int,  /* 分组ID */
+    social_group_name              varchar(100),  /* 分组名称 */
+    social_remark                  varchar(100),  /* 备注名 */
+    social_intimacy_level          int,  /* 亲密度等级 */
+    social_chat_count              int,  /* 聊天次数 */
+    social_call_count              int,  /* 通话次数 */
+    social_video_call_count        int,  /* 视频通话次数 */
+    social_gift_count              int,  /* 礼物次数 */
+    social_follow_days             int,  /* 关注天数 */
+    social_interaction_frequency   decimal(5,2),  /* 互动频率 */
+    social_common_friends          int,  /* 共同好友数 */
+    social_common_groups           int,  /* 共同群组数 */
+    social_social_distance         int,  /* 社交距离 */
+    social_relationship_strength   decimal(5,2),  /* 关系强度 */
+    social_trust_level             int,  /* 信任等级 */
+    social_contact_importance      decimal(5,2),  /* 联系人重要性 */
+    profile_avatar_url             varchar(500),  /* 头像URL */
+    profile_profession             varchar(50),  /* 职业 */
+    profile_education              varchar(50),  /* 学历 */
+    profile_interests              varchar(500),  /* 兴趣标签 */
+    profile_active_level           varchar(20),  /* 活跃等级 */
+    profile_influence_score        decimal(5,2),  /* 影响力分数 */
+    profile_social_value           decimal(18,2),  /* 社交价值 */
+    profile_user_tags              varchar(500),  /* 用户标签 */
+    profile_fans_count             int,  /* 粉丝数 */
+    profile_follow_count           int,  /* 关注数 */
+    profile_friend_count           int,  /* 好友数 */
+    profile_social_activity_score  decimal(5,2),  /* 社交活跃度 */
+    profile_content_creation_score decimal(5,2),  /* 内容创作力 */
+    profile_engagement_score       decimal(5,2),  /* 参与度分数 */
+    profile_social_influence_rank  int,  /* 社交影响力排名 */
+    del_flag                       NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id                   BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id              BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date            TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(behavior_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_user_behavior_f IS '用户行为宽表';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_id IS '用户ID';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_name IS '用户姓名';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_phone IS '手机号';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_gender IS '性别';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_age IS '年龄';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_birthday IS '出生日期';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_province_name IS '省份';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_city_name IS '城市';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_level IS '用户等级';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_level_name IS '用户等级名称';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_vip_status IS 'VIP状态';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_…（截断）
 ——select/R0001_select.sql——
 /* =========================================================================
  * 规则编号: R0001
@@ -1508,7 +1607,60 @@
   oom.payment_method                                                     AS order_payment_method,
   oom.payment_time                                                       AS order_payment_time,
   oom.shipping_fee                                                       AS order_shipping_fee,
-  oom.product_count                                                      AS order_p…（截断）</t>
+  oom.product_count                                                      AS order_product_count,
+  oom.sku_count                                                          AS order_sku_count,
+  oom.is_first_order                                                     AS order_is_first_order,
+  oom.coupon_id                                                          AS order_coupon_id,
+  oom.coupon_name                                                        AS order_coupon_name,
+  oom.points_used                                                        AS order_points_used,
+  oom.points_earned                                                      AS order_points_earned,
+  oom.complete_time                                                      AS order_complete_time,
+  oom.cancel_time                                                        AS order_cancel_time,
+  oom.cancel_reason                                                      AS order_cancel_reason,
+  oom.merchant_id                                                        AS order_merchant_id,
+  oom.merchant_name                                                      AS order_merchant_name,
+  oom.delivery_type                                                      AS order_delivery_type,
+  oom.delivery_time                                                      AS order_delivery_time,
+  oom.receive_time                                                       AS order_receive_time,
+  oom.receive_status                                                     AS order_receive_status,
+  oom.order_source                                                       AS order_order_source,
+  oom.remark                                                             AS order_remark,
+  oom.invoice_type                                                       AS order_invoice_type,
+  oom.invoice_title                                                      AS order_invoice_title,
+  -- ========== prod_* (20) ==========
+  dpd.product_id                                                         AS prod_product_id,
+  COALESCE(dpd.product_name, '')                                         AS prod_product_name,
+  COALESCE(dpd.product_code, '')                                         AS prod_product_code,
+  dpd.sku_id                                                             AS prod_sku_id,
+  COALESCE(dpd.sku_name, '')                                             AS prod_sku_name,
+  COALESCE(dpd.brand_id, 0)                                              AS prod_brand_id,
+  COALESCE(dpd.brand_name, '')                                           AS prod_brand_name,
+  COALESCE(dpd.category_id, 0)                                           AS prod_category_id,
+  COALESCE(dpd.category_name, '')                                        AS prod_category_name,
+  COALESCE(dpd.category_level1, '')                                      AS prod_category_level1,
+  COALESCE(dpd.category_level2, '')                                      AS prod_category_level2,
+  COALESCE(dpd.category_level3, '')                                      AS prod_category_level3,
+  COALESCE(dpd.price, 0)                                                 AS prod_price,
+  COALESCE(dpd.cost_price, 0)                                            AS prod_cost_price,
+  CASE WHEN dpd.price &gt; 0 THEN (dpd.price - dpd.cost_price) / dpd.price * 100
+       ELSE 0 END                                                        AS prod_profit_rate,
+  COALESCE(dpd.stock_status, '')                                         AS prod_stock_status,
+  COALESCE(dpd.sale_status, '')                                          AS prod_sale_status,
+  COALESCE(dpd.product_type, '')                                         AS prod_product_type,
+  COALESCE(dpd.is_virtual, 0)                                            AS prod_is_virtual,
+  COALESCE(dpd.supplier_id, 0)                                           AS prod_supplier_id,
+  -- ========== content_* (50) — 场景1 不适用 ==========
+  CAST(NULL AS BIGINT)                                                   AS content_interaction_id,
+  CAST(NULL AS BIGINT)                                                   AS content_content_id,
+  CAST(NULL AS VARCHAR(50))                                              AS content_interaction_type,
+  CAST(NULL AS VARCHAR(50))                                              AS content_interaction_type_name,
+  CAST(NULL AS INTEGER)                                                  AS content_duration_seconds,
+  CAST(NULL AS NUMERIC(5,2))                                             AS content_duration_minutes,
+  CAST(NULL AS VARCHAR(1000))                                            AS content_comment_content,
+  CAST(NULL AS INTEGER)                                                  AS content_comment_word_count,
+  CAST(NULL AS VARCHAR(50))                                              AS content_share_platform,
+  CAST(NULL AS INTEGER)                                                  AS content_share_count,…（截断）
+档案来源：../10_project_deliver/006_dwb_user_behavior_f</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1541,7 +1693,69 @@
 dim_user_base_d.age --[数据加工]--&gt; user_age(年龄)
 dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
 dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
-dim_user_base_d.birthday --[直接复制]--&gt; user_…（截断）</t>
+dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.ip_address --[直接复制]--&gt; user_ip_address(IP地址)
+dim_us…（截断）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1770,7 +1984,14 @@
 （无源声明） --[数据加工]--&gt; purchase_amount(采购金额)
 dwd_purchase_f.warehouse_id --[直接复制]--&gt; warehouse_id(仓库ID)
 dim_warehouse_f.warehouse_name --[直接复制]--&gt; warehouse_name(仓库名称)
-dim_warehouse_f.warehouse_type --[数据加工]--&gt; warehouse_type_name(仓库类型)…（截断）</t>
+dim_warehouse_f.warehouse_type --[数据加工]--&gt; warehouse_type_name(仓库类型)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; current_stock_qty(当前库存)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定库存)
+（无源声明） --[数据加工]--&gt; stock_days(库存周转天数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -2005,7 +2226,12 @@
 dwd_refund_f.product_id --[直接复制]--&gt; product_id(商品ID)
 dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
 dwd_service_ticket_f.ticket_id --[直接复制]--&gt; ticket_id(工单ID)
-dwd_service…（截断）</t>
+dwd_service_ticket_f.ticket_status --[数据加工]--&gt; ticket_status_name(工单状态)
+dwd_service_ticket_f.handler_name --[直接复制]--&gt; handler_name(处理人)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2273,7 +2499,28 @@
 dim_product_category_f.category_path --[直接复制]--&gt; category_path(分类路径)
 dim_product_f.brand_id --[直接复制]--&gt; brand_id(品牌ID)
 dim_brand_f.brand_name --[直接复制]--&gt; brand_name(品牌名称)
-dim_brand_f.brand_origin --[直接复…（截断）</t>
+dim_brand_f.brand_origin --[直接复制]--&gt; brand_origin(品牌产地)
+dim_product_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; stock_qty(库存数量)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定数量)
+（无源声明） --[数据加工]--&gt; available_qty(可售数量)
+dwd_inventory_f.warning_qty --[直接复制]--&gt; warning_qty(库存预警值)
+（无源声明） --[数据加工]--&gt; stock_status(库存状态)
+（无源声明） --[数据加工]--&gt; total_sales_qty(累计销量)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; buyer_cnt(购买人数)
+（无源声明） --[数据加工]--&gt; sales_qty_30d(近30天销量)
+（无源声明） --[数据加工]--&gt; review_cnt(评价数)
+（无源声明） --[数据加工]--&gt; avg_rating(平均评分)
+（无源声明） --[数据加工]--&gt; good_review_rate(好评率(%))
+dim_product_f.weight --[直接复制]--&gt; weight(重量(kg))
+dim_product_f.volume --[直接复制]--&gt; volume(体积(m³))
+dim_product_f.product_tag --[直接复制]--&gt; product_tag(商品标签)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2465,7 +2712,79 @@
     statistical_code           varchar(20),  /* 统计代码 */
     iso_code                   varchar(20),  /* ISO代码 */
     source_code                varchar(50),  /* 来源代码 */
-    source_category         …（截断）
+    source_category            varchar(50),  /* 来源分类 */
+    channel_id                 int,  /* 渠道ID */
+    channel_code               varchar(50),  /* 渠道代码 */
+    channel_name               varchar(100),  /* 渠道名称 */
+    channel_type               varchar(50),  /* 渠道类型 */
+    channel_category           varchar(50),  /* 渠道分类 */
+    campaign_id                int,  /* 活动ID */
+    campaign_code              varchar(50),  /* 活动代码 */
+    campaign_name              varchar(100),  /* 活动名称 */
+    campaign_type              varchar(50),  /* 活动类型 */
+    medium_id                  int,  /* 媒介ID */
+    medium_code                varchar(50),  /* 媒介代码 */
+    medium_name                varchar(100),  /* 媒介名称 */
+    medium_type                varchar(50),  /* 媒介类型 */
+    term_id                    int,  /* 搜索词ID */
+    term_keyword               varchar(200),  /* 搜索关键词 */
+    content_id                 int,  /* 内容ID */
+    content_name               varchar(200),  /* 内容名称 */
+    referral_url               varchar(500),  /* 来源URL */
+    landing_page               varchar(500),  /* 落地页 */
+    utm_source                 varchar(100),  /* UTM来源 */
+    utm_medium                 varchar(100),  /* UTM媒介 */
+    utm_campaign               varchar(100),  /* UTM活动 */
+    utm_term                   varchar(100),  /* UTM关键词 */
+    utm_content                varchar(100),  /* UTM内容 */
+    cost_per_acquisition       decimal(18,2),  /* 获客成本 */
+    conversion_rate            decimal(5,2),  /* 转化率 */
+    quality_score              decimal(5,2),  /* 质量分数 */
+    retention_rate_7d          decimal(5,2),  /* 7日留存率 */
+    retention_rate_30d         decimal(5,2),  /* 30日留存率 */
+    lifetime_value             decimal(18,2),  /* 生命周期价值 */
+    first_order_amount         decimal(18,2),  /* 首单金额 */
+    first_order_days           int,  /* 首单天数 */
+    register_device            varchar(50),  /* 注册设备 */
+    register_os                varchar(50),  /* 注册系统 */
+    register_browser           varchar(50),  /* 注册浏览器 */
+    register_network           varchar(50),  /* 注册网络 */
+    register_location          varchar(200),  /* 注册地点 */
+    attribution_model          varchar(50),  /* 归因模型 */
+    lookback_days              int,  /* 回溯天数 */
+    priority                   int,  /* 优先级 */
+    is_paid                    int,  /* 是否付费 */
+    del_flag                   NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id               BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id          BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date        TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_profile_f IS '用户画像宽表';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_processed IS '手机号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.email IS '电子邮箱';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.gender_processed IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.age_processed IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card IS '身份证号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card_masked_processed IS '身份证号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.real_name IS '真实姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.nick_name IS '昵称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.avatar_url IS '头像URL';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status_name_processed IS '用户状态名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_date_processed IS '注册日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_hour_processed IS '注册小时';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_weekday_proce…（截断）
 ——select/R0001_select.sql——
 /* =====================================================
    R0001: 用户画像宽表全量装载
@@ -2559,7 +2878,58 @@
         ELSE ROUND(COALESCE(dul.current_level_points, 0)::NUMERIC * 100.0 / dul.upgrade_points, 2)
     END AS progress_percentage,                                                   /* 升级进度百分比(当前等级积分/升级所需积分*100,除0保护) */
     COALESCE(dul.privilege_list, '') AS privilege_list,                           /* 权限列表 */
-    COALESCE(dul.discount_rate, 0) AS discount_…（截断）</t>
+    COALESCE(dul.discount_rate, 0) AS discount_rate,                              /* 折扣率 */
+    COALESCE(dul.points_rate, 0) AS points_rate,                                  /* 积分倍率 */
+    COALESCE(dul.free_shipping, 0) AS free_shipping,                              /* 免费配送 */
+    COALESCE(dul.exclusive_products, 0) AS exclusive_products,                    /* 专属商品 */
+    COALESCE(dul.priority_support, 0) AS priority_support,                        /* 优先客服 */
+    COALESCE(dul.birthday_bonus, 0) AS birthday_bonus,                            /* 生日礼金 */
+    COALESCE(dul.monthly_coupon, 0) AS monthly_coupon,                            /* 月度优惠券 */
+    COALESCE(dul.annual_gift, 0) AS annual_gift,                                  /* 年度礼品 */
+    COALESCE(dul.vip_service, 0) AS vip_service,                                  /* VIP服务 */
+    COALESCE(dul.invite_quota, 0) AS invite_quota,                                /* 邀请名额 */
+    COALESCE(dul.max_orders_per_day, 0) AS max_orders_per_day,                    /* 每日最大订单数 */
+    COALESCE(dul.max_return_days, 0) AS max_return_days,                          /* 最大退货天数 */
+    COALESCE(dul.level_benefits, '') AS level_benefits,                           /* 等级权益 */
+    dul.upgrade_time AS upgrade_time,                                             /* 升级时间 */
+    dul.downgrade_time AS downgrade_time,                                         /* 降级时间 */
+    COALESCE(dul.maintain_days, 0) AS maintain_days,                              /* 维持天数 */
+    COALESCE(dul.level_status, '') AS level_status,                               /* 等级状态 */
+    dul.create_time AS create_time,                                               /* 创建时间 */
+    dul.update_time AS update_time,                                               /* 更新时间 */
+    dul.valid_from AS valid_from,                                                 /* 生效开始时间 */
+    dul.valid_to AS valid_to,                                                     /* 生效结束时间 */
+    COALESCE(dul.is_active, 0) AS is_active,                                      /* 是否激活 */
+    COALESCE(dul.level_tier, 0) AS level_tier,                                    /* 等级层级 */
+    COALESCE(dul.level_group, '') AS level_group,                                 /* 等级分组 */
+    COALESCE(dul.level_category, '') AS level_category,                           /* 等级分类 */
+    COALESCE(dul.points_required, 0) AS points_required,                          /* 所需积分 */
+    COALESCE(dul.orders_required, 0) AS orders_required,                          /* 所需订单数 */
+    COALESCE(dul.amount_required, 0) AS amount_required,                          /* 所需金额 */
+    COALESCE(dul.days_required, 0) AS days_required,                              /* 所需天数 */
+    COALESCE(dul.growth_value, 0) AS growth_value,                                /* 成长值 */
+    COALESCE(dul.experience_value, 0) AS experience_value,                        /* 经验值 */
+    COALESCE(dul.contribution_value, 0) AS contribution_value,                    /* 贡献值 */
+    COALESCE(dul.activity_value, 0) AS activity_value,                            /* 活跃值 */
+    COALESCE(dul.loyalty_score, 0) AS loyalty_score,                              /* 忠诚度分数 */
+    COALESCE(dul.engagement_score, 0) AS engagement_score,                        /* 参与度分数 */
+    COALESCE(dul.satisfaction_score, 0) AS satisfaction_score,                    /* 满意度分数 */
+    COALESCE(dul.retention_score, 0) AS retention_score,                          /* 留存率分数 */
+    /* ---------- dim_region_d 地区维度(限定 region_level=1 省份层级) ---------- */
+    COALESCE(drd.region_id, 0) AS region_id,                                      /* 地区ID */
+    COALESCE(drd.region_code, '') AS region_code,                                 /* 地区代码 */
+    COALESCE(drd.region_name, '') AS region_name,                                 /* 地区名称 */
+    COALESCE(drd.parent_id, 0) AS parent_id,                                      /* 父级ID */
+    COALESCE(drd.region_level, 0) AS region_level,                                /* 地区层级 */
+    COALESCE(drd.region_path, '') AS region_path,                                 /* 地区路径 */
+    COALESCE(drd.province_id, 0) AS province_id,                                  /* 省份ID */
+    COALESCE(drd.province_abbr, '') AS province_abbr,                             /* 省份简称 */
+    COALESCE(drd.city_id, 0) AS city_id,                                          /* 城市ID */
+    COALESCE(drd.city_abbr, '') AS city_abbr,                                     /* 城市简称 */
+    COALESCE(drd.district_id, 0) AS district_id,                                  /* 区县ID */
+    COALESCE(drd.district_abbr, '') AS district_abbr,                             /* 区县简称 */
+    COALESCE(drd.street_id, 0) AS street_id,             …（截断）
+档案来源：../10_project_deliver/010_dwb_user_profile_f</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2591,7 +2961,72 @@
 ods_user_basic_f.user_status --[直接复制]--&gt; user_status(用户状态)
 ods_user_basic_f.user_status_name --[数据加工]--&gt; user_status_name_processed(用户状态名称)
 ods_user_basic_f.register_time --[直接复制]--&gt; register_time(注册时间)
-ods_user_basi…（截断）</t>
+ods_user_basic_f.register_date --[数据加工]--&gt; register_date_processed(注册日期)
+ods_user_basic_f.register_hour --[数据加工]--&gt; register_hour_processed(注册小时)
+ods_user_basic_f.register_weekday --[数据加工]--&gt; register_weekday_processed(注册星期)
+ods_user_basic_f.last_login_time --[直接复制]--&gt; last_login_time(最后登录时间)
+ods_user_basic_f.last_login_date --[数据加工]--&gt; last_login_date_processed(最后登录日期)
+ods_user_basic_f.login_count --[直接复制]--&gt; login_count(登录次数)
+ods_user_basic_f.province_code --[直接复制]--&gt; province_code(省份代码)
+ods_user_basic_f.province_name --[直接复制]--&gt; province_name(省份名称)
+ods_user_basic_f.city_code --[直接复制]--&gt; city_code(城市代码)
+ods_user_basic_f.city_name --[直接复制]--&gt; city_name(城市名称)
+ods_user_basic_f.district_code --[直接复制]--&gt; district_code(区县代码)
+ods_user_basic_f.district_name --[直接复制]--&gt; district_name(区县名称)
+ods_user_basic_f.address --[直接复制]--&gt; address(详细地址)
+ods_user_basic_f.zip_code --[直接复制]--&gt; zip_code(邮政编码)
+ods_user_basic_f.source_id --[直接复制]--&gt; source_id(来源渠道ID)
+ods_user_basic_f.source_name --[直接复制]--&gt; source_name(来源渠道名称)
+ods_user_basic_f.source_type --[直接复制]--&gt; source_type(来源类型)
+ods_user_basic_f.device_type --[直接复制]--&gt; device_type(设备类型)
+ods_user_basic_f.os_type --[直接复制]--&gt; os_type(操作系统)
+ods_user_basic_f.app_version --[直接复制]--&gt; app_version(APP版本)
+ods_user_basic_f.ip_address --[直接复制]--&gt; ip_address(IP地址)
+ods_user_basic_f.longitude --[直接复制]--&gt; longitude(经度)
+ods_user_basic_f.latitude --[直接复制]--&gt; latitude(纬度)
+ods_user_basic_f.language --[直接复制]--&gt; language(语言)
+ods_user_basic_f.timezone --[直接复制]--&gt; timezone(时区)
+ods_user_basic_f.currency --[直接复制]--&gt; currency(货币)
+ods_user_basic_f.vip_level --[直接复制]--&gt; vip_level(VIP等级)
+ods_user_basic_f.vip_expire_time --[直接复制]--&gt; vip_expire_time(VIP到期时间)
+ods_user_basic_f.is_vip --[数据加工]--&gt; is_vip_processed(是否VIP)
+ods_user_basic_f.member_points --[直接复制]--&gt; member_points(会员积分)
+ods_user_basic_f.balance --[直接复制]--&gt; balance(账户余额)
+ods_user_basic_f.credit_score --[直接复制]--&gt; credit_score(信用分)
+ods_user_basic_f.risk_level --[直接复制]--&gt; risk_level(风险等级)
+ods_user_basic_f.verify_status --[直接复制]--&gt; verify_status(认证状态)
+dim_user_level_d.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_d.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_d.level_code --[直接复制]--&gt; level_code(等级代码)
+dim_user_level_d.level_rank --[直接复制]--&gt; level_rank(等级排序)
+dim_user_level_d.min_points --[直接复制]--&gt; min_points(最小积分)
+dim_user_level_d.max_points --[直接复制]--&gt; max_points(最大积分)
+dim_user_level_d.level_icon --[直接复制]--&gt; level_icon(等级图标)
+dim_user_level_d.level_color --[直接复制]--&gt; level_color(等级颜色)
+dim_user_level_d.upgrade_points --[直接复制]--&gt; upgrade_points(升级所需积分)
+dim_user_level_d.current_level_points --[直接复制]--&gt; current_level_points(当前等级积分)
+dim_user_level_d.next_level_points --[直接复制]--&gt; next_level_points(下一等级积分)
+dim_user_level_d.progress_percentage --[数据加工]--&gt; progress_percentage(升级进度百分比)
+dim_user_level_d.privilege_list --[直接复制]--&gt; privilege_list(权限列表)
+dim_user_level_d.discount_rate --[直接复制]--&gt; discount_rate(折扣率)
+dim_user_level_d.points_rate --[直接复制]--&gt; points_rate(积分倍率)
+dim_user_level_d.free_shipping --[直接复制]--&gt; free_shipping(免费配送)
+dim_user_level_d.exclusive_products --[直接复制]--&gt; exclusive_products(专属商品)
+dim_user_level_d.priority_support --[直接复制]--&gt; priority_support(优先客服)
+dim_user_level_d.birthday_bonus --[直接复制]--&gt; birthday_bonus(生日礼金)
+dim_user_level_d.monthly_coupon --[直接复制]--&gt; monthly_coupon(月度优惠券)
+dim_user_level_d.annual_gift --[直接复制]--&gt; annual_gift(年度礼品)
+dim_user_level_d.vip_service --[直接复制]--&gt; vip_service(VIP服务)
+dim_user_level_d.invite_quota --[直接复制]--&gt; invite_quota(邀请名额)
+dim_user_level_d.max_orders_per_day --[直接复制]--&gt; max_orders_per_day(每日最大订单数)
+dim_user_level_d.max_return_days --[直接复制]--&gt; max_return_days(最大退货天数)
+dim_user_level_d.level_benefits --[直接复制]--&gt; level_benefits(等级权益)
+dim_user_level_d.upgrade_time --[直接复制]--&gt; upgrade_time(升级时间)
+dim_user_level_d.downgrade_time --[直接复制]--&gt; downgrade_time(降级时间)
+dim_user_level_d.maintain_days --[直接复制]--&gt; maintain_days(维持天数)
+dim_user_level_d.level_status --[直接复制]--&gt; level_status(等级状态)
+dim_user_level_d.create_time --[直接复制]--&gt; create_time(创建时间)
+di…（截断）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -2843,7 +3278,19 @@
 dim_coupon_f.coupon_name --[直接复制]--&gt; coupon_name(优惠券名称)
 dim_coupon_f.coupon_type --[数据加工]--&gt; coupon_type_name(优惠券类型)
 dim_coupon_f.total_qty --[直接复制]--&gt; coupon_total_qty(优惠券发放总量)
-dim_coupon_f.used_qty --[直接复制]-…（截断）</t>
+dim_coupon_f.used_qty --[直接复制]--&gt; coupon_used_qty(优惠券已使用量)
+（无源声明） --[数据加工]--&gt; coupon_use_rate(优惠券使用率(%))
+（无源声明） --[数据加工]--&gt; order_cnt(活动订单数)
+（无源声明） --[数据加工]--&gt; gmv_amount(活动GMV)
+（无源声明） --[数据加工]--&gt; participant_cnt(参与人数)
+（无源声明） --[数据加工]--&gt; total_discount_amount(活动优惠金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(人均消费)
+（无源声明） --[数据加工]--&gt; new_user_rate(新客占比(%))
+（无源声明） --[数据加工]--&gt; activity_roi(活动ROI(%))
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -3056,7 +3503,65 @@
 COMMENT ON COLUMN slord.dwb_order_center_f.order_status IS '订单状态';
 COMMENT ON COLUMN slord.dwb_order_center_f.order_status_name IS '订单状态名称';
 COMMENT ON COLUMN slord.dwb_order_center_f.order_time IS '下单时间';
-COMMENT ON C…（截断）
+COMMENT ON COLUMN slord.dwb_order_center_f.order_date IS '下单日期';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_source_name IS '订单来源';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_type_name IS '订单类型';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_remark IS '订单备注';
+COMMENT ON COLUMN slord.dwb_order_center_f.total_amount IS '订单总金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_amount IS '商品金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_amount IS '实付金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.discount_amount IS '优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.freight_amount IS '运费金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_cnt IS '商品种类数';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_qty IS '商品总件数';
+COMMENT ON COLUMN slord.dwb_order_center_f.ship_time IS '发货时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.receive_time IS '签收时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.delivery_days IS '物流时长(天)';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_phone_masked IS '用户手机(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_email_masked IS '用户邮箱(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_f.gender_name IS '用户性别';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_birthday IS '用户生日';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_age IS '用户年龄';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_register_time IS '注册时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_level_id IS '用户等级ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_level_name IS '用户等级名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.member_points IS '会员积分';
+COMMENT ON COLUMN slord.dwb_order_center_f.member_balance IS '会员余额';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_tag IS '用户标签';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_source_name IS '用户来源';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_province_code IS '用户省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_city_code IS '用户城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_days IS '用户注册天数';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_code IS '商品编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.sku_code IS 'SKU编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l1_id IS '一级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l1_name IS '一级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l2_id IS '二级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l2_name IS '二级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l3_id IS '三级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l3_name IS '三级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_id IS '品牌ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_name IS '品牌名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_attr IS '商品属性';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_spec IS '商品规格';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_weight IS '商品重量(kg)';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_volume IS '商品体积(m³)';
+COMMENT ON COLUMN slord.dwb_order_center_f.cost_price IS '商品成本价';
+COMMENT ON COLUMN slord.dwb_order_center_f.sale_price IS '商品售价';
+COMMENT ON COLUMN slord.dwb_order_center_f.real_price IS '商品实付单价';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_tag IS '商品标签';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_status_name IS '商品状态';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_profit IS '单品毛利';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_level_name IS '店铺等级';
+COMMENT ON COLUMN slord.dwb_order_center_f.sho…（截断）
 ——ddl/create_table_dwb_order_center_prod_tmp2.sql——
 /* =====================================================
    表名: slord.dwb_order_center_prod_tmp2
@@ -3194,7 +3699,112 @@
       AND dof.order_status NOT IN ('CANCELLED', 'DELETED')
     GROUP BY dof.user_id
 ),
-/* CTE 2: 在订单聚合基础上…（截断）</t>
+/* CTE 2: 在订单聚合基础上计算 RFM 三项分值（NTILE 5 分位） */
+order_rfm AS (
+    SELECT
+        oa.user_id                                                    AS user_id,
+        oa.first_order_time                                           AS first_order_time,
+        oa.last_order_time                                            AS last_order_time,
+        oa.history_order_cnt                                          AS history_order_cnt,
+        oa.history_pay_amount                                         AS history_pay_amount,
+        oa.history_discount_amount                                    AS history_discount_amount,
+        NTILE(5) OVER (ORDER BY oa.last_order_time ASC)               AS r_score,  /* 越近分越高 */
+        NTILE(5) OVER (ORDER BY oa.history_order_cnt ASC)             AS f_score,  /* 越多分越高 */
+        NTILE(5) OVER (ORDER BY oa.history_pay_amount ASC)            AS m_score   /* 越大分越高 */
+    FROM order_agg oa
+),
+/* CTE 3: 用户参与各活动类型的订单数 */
+activity_cnt AS (
+    SELECT
+        dof.user_id                                                    AS user_id,
+        dof.activity_type                                              AS activity_type,
+        COUNT(1)                                                       AS act_order_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE COALESCE(dof.del_flag, 'N') = 'N'
+      AND dof.order_status NOT IN ('CANCELLED', 'DELETED')
+      AND dof.activity_type IS NOT NULL
+    GROUP BY dof.user_id, dof.activity_type
+),
+/* CTE 4: 取每个用户参与订单数最多的活动类型（ROW_NUMBER rn=1） */
+activity_top AS (
+    SELECT
+        ac.user_id                                                                   AS user_id,
+        ac.activity_type                                                             AS activity_type,
+        ROW_NUMBER() OVER (PARTITION BY ac.user_id
+                           ORDER BY ac.act_order_cnt DESC, ac.activity_type ASC)    AS rn
+    FROM activity_cnt ac
+),
+/* CTE 5: 用户各支付方式成功支付次数 */
+payment_cnt AS (
+    SELECT
+        dpf.user_id                                                   AS user_id,
+        dpf.pay_method                                                AS pay_method,
+        COUNT(1)                                                      AS pay_cnt
+    FROM sdpay.dwd_payment_f dpf
+    WHERE COALESCE(dpf.del_flag, 'N') = 'N'
+      AND dpf.pay_status = 'SUCCESS'
+    GROUP BY dpf.user_id, dpf.pay_method
+),
+/* CTE 6: 取每个用户使用频次最高的支付方式（ROW_NUMBER rn=1） */
+payment_top AS (
+    SELECT
+        pc.user_id                                                                AS user_id,
+        pc.pay_method                                                             AS pay_method,
+        ROW_NUMBER() OVER (PARTITION BY pc.user_id
+                           ORDER BY pc.pay_cnt DESC, pc.pay_method ASC)         AS rn
+    FROM payment_cnt pc
+),
+/* CTE 7: 用户已使用优惠券去重计数 */
+coupon_agg AS (
+    SELECT
+        dcu.user_id                                 AS user_id,
+        COUNT(DISTINCT dcu.coupon_id)               AS user_coupon_used_cnt
+    FROM sdmar.dwd_coupon_use_f dcu
+    WHERE COALESCE(dcu.del_flag, 'N') = 'N'
+      AND dcu.use_status = 'USED'
+    GROUP BY dcu.user_id
+),
+/* CTE 8: 用户历史成功退款次数 */
+refund_agg AS (
+    SELECT
+        drf17.user_id                               AS user_id,
+        COUNT(1)                                    AS user_refund_cnt
+    FROM sdref.dwd_refund_f drf17
+    WHERE COALESCE(drf17.del_flag, 'N') = 'N'
+      AND drf17.refund_status = 'SUCCESS'
+    GROUP BY drf17.user_id
+)
+/* 最终组装：以 order_rfm 为主表，LEFT JOIN 各源收敛后的用户级结果 */
+SELECT
+    orf.user_id                                                                      AS user_id,
+    orf.first_order_time                                                             AS first_order_time,
+    orf.last_order_time                                                              AS last_order_time,
+    COALESCE(orf.history_order_cnt, 0)                                               AS history_order_cnt,
+    COALESCE(orf.history_pay_amount, 0)                                              AS history_pay_amount,
+    COALESCE(orf.history_discount_amount, 0)                                         AS history_discount_amount,
+    CASE
+        WHEN COALESCE(orf.history_order_cnt, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(orf.history_pay_amount, 0) / orf.history_order_cnt, 2)
+    END                                                                              AS avg_order_amount,
+    (orf.r_score::TEXT || orf.f_score::TEXT || orf.m_score::TEXT)                     AS rfm_segment,
+    CASE
+        WHEN COALESCE(orf.history_order_cnt, 0) &gt;= 2 THEN 'Y'
+        ELSE 'N'
+    END                                                                              AS is_repeat_user,
+    COALESCE(ptp.pay_method, '')                                                     AS fav_pay_method,
+    COALESCE(ca.user_coupon_used_cnt, 0)                                             AS user_coupon_used_cnt,
+    COALESCE(ra.user_refund_cnt, 0)                                                  AS user_refund_cnt,
+    COALESCE(atp.activity_type, '')                                                  AS user_fav_activity_type,
+    'N'                                                                              AS del_flag,
+    '${P_CYCLE_ID}'                                                                  AS crt_cycle_id,
+    '${P_CYCLE_ID}'                                                                  AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP                                                                AS dw_last_update_date
+FROM order_rfm orf
+LEFT JOIN activity_top atp ON orf.user_id = atp.user_id AND atp.rn = 1
+LEFT JOIN payment_top  ptp ON orf.user_id = ptp.user_id AND ptp.rn = 1
+LEFT JOIN coupon_agg   ca  ON orf.user_id = ca.user_id
+LEFT JOIN refund_agg   ra  ON orf.user_id = ra.user_id;
+档案来源：../10_project_deliver/012_dwb_order_center_f</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3227,7 +3837,78 @@
 dwd_order_f.product_cnt --[直接复制]--&gt; product_cnt(商品种类数)
 dwd_order_f.product_qty --[直接复制]--&gt; product_qty(商品总件数)
 dwd_order_f.order_source --[数据加工]--&gt; order_source_name(订单来源)
-dwd_order_f.order_typ…（截断）</t>
+dwd_order_f.order_type --[数据加工]--&gt; order_type_name(订单类型)
+dwd_order_f.remark --[直接复制]--&gt; order_remark(订单备注)
+dwd_order_f.create_time --[数据加工]--&gt; order_date(下单日期)
+dwd_order_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dim_user_f.user_phone --[数据加工]--&gt; user_phone_masked(用户手机(脱敏))
+dim_user_f.user_email --[数据加工]--&gt; user_email_masked(用户邮箱(脱敏))
+dim_user_f.gender --[数据加工]--&gt; gender_name(用户性别)
+dim_user_f.birthday --[直接复制]--&gt; user_birthday(用户生日)
+dim_user_f. --[数据加工]--&gt; user_age(用户年龄)
+dim_user_f.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_f.level_id --[直接复制]--&gt; user_level_id(用户等级ID)
+dim_user_level_f.level_name --[直接复制]--&gt; user_level_name(用户等级名称)
+dim_user_f.member_points --[直接复制]--&gt; member_points(会员积分)
+dim_user_f.member_balance --[直接复制]--&gt; member_balance(会员余额)
+dwd_order_f. --[数据加工]--&gt; first_order_time(首次下单时间)
+dwd_order_f. --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f. --[数据加工]--&gt; history_order_cnt(历史订单数)
+dwd_order_f. --[数据加工]--&gt; history_pay_amount(历史消费金额)
+dwd_order_f. --[数据加工]--&gt; history_discount_amount(历史优惠金额)
+dwd_order_f. --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f. --[数据加工]--&gt; rfm_segment(用户RFM分层)
+dim_user_f.user_tag --[直接复制]--&gt; user_tag(用户标签)
+dim_user_f.user_source --[数据加工]--&gt; user_source_name(用户来源)
+dim_user_f.province_code --[直接复制]--&gt; user_province_code(用户省份编码)
+dim_user_f.city_code --[直接复制]--&gt; user_city_code(用户城市编码)
+dim_user_f. --[数据加工]--&gt; user_days(用户注册天数)
+dwd_order_f. --[数据加工]--&gt; is_repeat_user(是否复购用户)
+dwd_order_detail_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dim_product_f.product_code --[直接复制]--&gt; product_code(商品编码)
+dwd_order_detail_f.sku_code --[直接复制]--&gt; sku_code(SKU编码)
+dim_product_f.category_id --[直接复制]--&gt; category_l1_id(一级类目ID)
+dim_product_category_f.category_name --[直接复制]--&gt; category_l1_name(一级类目名称)
+dim_product_category_f. --[数据加工]--&gt; category_l2_id(二级类目ID)
+dim_product_category_f. --[数据加工]--&gt; category_l2_name(二级类目名称)
+dim_product_category_f. --[数据加工]--&gt; category_l3_id(三级类目ID)
+dim_product_category_f. --[数据加工]--&gt; category_l3_name(三级类目名称)
+dim_product_f.brand_id --[直接复制]--&gt; brand_id(品牌ID)
+dim_brand_f.brand_name --[直接复制]--&gt; brand_name(品牌名称)
+dim_brand_f.brand_origin --[直接复制]--&gt; brand_origin(品牌产地)
+dim_product_f.product_attr --[直接复制]--&gt; product_attr(商品属性)
+dim_product_f.product_spec --[直接复制]--&gt; product_spec(商品规格)
+dim_product_f.weight --[直接复制]--&gt; product_weight(商品重量(kg))
+dim_product_f.volume --[直接复制]--&gt; product_volume(商品体积(m³))
+dwd_order_detail_f.cost_price --[直接复制]--&gt; cost_price(商品成本价)
+dwd_order_detail_f.sale_price --[直接复制]--&gt; sale_price(商品售价)
+dwd_order_detail_f.real_price --[直接复制]--&gt; real_price(商品实付单价)
+dim_product_f.product_tag --[直接复制]--&gt; product_tag(商品标签)
+dim_product_f.product_status --[数据加工]--&gt; product_status_name(商品状态)
+dwd_order_detail_f. --[数据加工]--&gt; product_sales_cnt(商品累计销量)
+dwd_order_detail_f. --[数据加工]--&gt; product_sales_amount(商品累计销售额)
+dwd_order_detail_f. --[数据加工]--&gt; product_profit(单品毛利)
+dwd_order_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dim_shop_f.shop_type --[数据加工]--&gt; shop_type_name(店铺类型)
+dim_shop_f.shop_level --[数据加工]--&gt; shop_level_name(店铺等级)
+dim_shop_f.shop_score --[直接复制]--&gt; shop_score(店铺评分)
+dim_shop_f.company_name --[直接复制]--&gt; company_name(店铺所属公司)
+dim_shop_f.province_code --[直接复制]--&gt; shop_province_code(店铺省份编码)
+dim_region_f. --[数据加工]--&gt; shop_province_name(店铺省份名称)
+dim_shop_f.city_code --[直接复制]--&gt; shop_city_code(店铺城市编码)
+dim_region_f. --[数据加工]--&gt; shop_city_name(店铺城市名称)
+dim_shop_f.open_time --[直接复制]--&gt; shop_open_time(开店时间)
+dwd_order_f. --[数据加工]--&gt; shop_history_order_cnt(店铺历史订单数)
+dwd_order_f.receiver_name --[直接复制]--&gt; receiver_name(收货人姓名)
+dwd_order_f.receiver_phone --[数据加工]--&gt; receiver_phone_masked(收货人手机(脱敏))
+dwd_order_f.province_code --[直接复制]--&gt; receiver_province_code(收货省份编码)
+dim_region_f.region_name --[直接复制]--&gt; receiver_province_name(收货省份名称)
+dwd_order_f.city_code --[直接复制]--&gt; receiver_city_code(收货城市编码)
+dim_region_f. --[数据加工]--&gt; receiver_city_name(收货城市名称)
+dwd_order_f.district_code --[直接复制]--&gt; r…（截断）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>

--- a/eval-suite/out/platform_dataset_intranet.xlsx
+++ b/eval-suite/out/platform_dataset_intranet.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -475,8 +475,8 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>任务：为  完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
-表说明：
+          <t>任务：为 dws.dwb_trade_order_d 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单汇总表
 粒度：每行一个订单
 调度：全量调度 / T+1，一天一调
 映射字段 7 项，来源表 1 张。</t>
@@ -552,10 +552,10 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
-- 目标表 ，粒度：每行一个订单
+- 目标表 dws.dwb_trade_order_d，粒度：每行一个订单
 - 目标字段 7 项：order_id, cust_id, total_amount, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
 - 来源表 1 张：ods_trade_order_di
-- 建表 DDL（create_table_.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 建表 DDL（create_table_dwb_trade_order_d.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
 - 调度方案：全量调度</t>
         </is>
       </c>
@@ -579,6 +579,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>任务：为 dws.dwb_trade_order_d 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单汇总表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 7 项，来源表 1 张。
+本规则：R0001（订单汇总主加工），step_type=full，目标表 dwb_trade_order_d——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* R0001: 订单汇总主加工（单源表 ods_trade_order_di 按 订单ID(order_id)+客户ID(cust_id) 分组聚合，对金额求和(SUM)，收敛到"一行=一个订单+客户组合"的目标粒度，直产目标 F 表。单表无 JOIN、仅 1 个聚合字段，复杂度低，无需分段建中间表。） */
+SELECT
+    a."订单ID" AS order_id,
+    a."客户ID" AS cust_id,
+    COALESCE(SUM(a."金额"), 0) AS total_amount,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di a
+GROUP BY a."订单ID", a."客户ID"
+——ddl/create_table_dwb_trade_order_d.sql——
+/* =====================================================
+   表名: dws.dwb_trade_order_d
+   规则: R0001 - 订单汇总主加工
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-06
+   说明: 单源表 ods_trade_order_di 按 订单ID(order_id)+客户ID(cust_id) 分组聚合， 对金额求和(SUM)，收敛到"一行=一个订单+客户组合"的目标粒度，直产目标 F 表。 单表无 JOIN、仅 1 个聚合字段，复杂度低，无需分段建中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_order_d (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    total_amount        DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_order_d IS '订单汇总表';
+COMMENT ON COLUMN dws.dwb_trade_order_d.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.total_amount IS '订单总额';
+COMMENT ON COLUMN dws.dwb_trade_order_d.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_order_d.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_order_d.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_order_d.dw_last_update_date IS '更新时间';
+档案来源：../10_project_deliver/002_dwb_trade_order_d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 7 项：order_id, cust_id, total_amount, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_trade_order_d 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 7 项）（源→规则→目标）：
+ods_trade_order_di.order_id --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.cust_id --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.amount --[数据加工]--&gt; total_amount(订单总额)
+ods_trade_order_di. --[赋值]--&gt; del_flag(删除标识)
+ods_trade_order_di. --[赋值]--&gt; crt_cycle_id(创建批次ID)
+ods_trade_order_di. --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+ods_trade_order_di. --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>任务：为 dws.dwb_trade_wide_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：交易宽表
 粒度：每行一个订单
@@ -586,7 +671,7 @@
 映射字段 15 项，来源表 5 张。</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -731,7 +816,7 @@
 档案来源：../10_project_deliver/003_dwb_trade_wide_f</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 dws.dwb_trade_wide_f，粒度：每行一个订单
@@ -741,7 +826,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 15 项（源→规则→目标）：
 ods_trade_order_di.订单ID --[直接复制]--&gt; order_id(订单ID)
@@ -761,13 +846,180 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(更新时间)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>任务：为 dws.dwb_trade_wide_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：交易宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 15 项，来源表 5 张。
+本规则：R0001（交易宽表全量装配），step_type=full，目标表 dwb_trade_wide_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 交易宽表全量装配
+   设计意图: 5表JOIN宽表，复杂度未达分段阈值，
+             pay/log 收敛用 CTE 内联处理，
+             商品维取最新有效行，单条 SELECT 直产目标 F 表
+   粒度: 一行=一个订单（输入输出无变化）
+   目标表: dws.dwb_trade_wide_f
+   ===================================================== */
+WITH
+/* CTE 1: pay_agg - 支付明细按 order_id 收敛（一个订单可有多笔支付，GROUP BY 收敛到每订单一行） */
+pay_agg AS (
+    SELECT
+        "订单ID" AS order_id,
+        COALESCE(SUM("支付金额"), 0) AS total_pay_amt
+    FROM ods.ods_payment_di
+    WHERE COALESCE(del_flag, 'N') = 'N'
+    GROUP BY "订单ID"
+),
+/* CTE 2: log_agg - 物流明细按 order_id 收敛（一个订单可有多条物流，GROUP BY 收敛到每订单一行） */
+log_agg AS (
+    SELECT
+        "订单ID" AS order_id,
+        COALESCE(SUM("运费"), 0) AS total_ship_fee
+    FROM ods.ods_logistics_di
+    WHERE COALESCE(del_flag, 'N') = 'N'
+    GROUP BY "订单ID"
+),
+/* CTE 3: prod_latest - 商品维取最新有效行（消除多版本历史行，ROW_NUMBER 按 product_id 取最新） */
+prod_latest AS (
+    SELECT
+        "商品ID" AS product_id,
+        "商品名称" AS product_name,
+        "商品分类" AS category_code,
+        ROW_NUMBER() OVER (
+            PARTITION BY "商品ID"
+            ORDER BY dw_last_update_date DESC NULLS LAST
+        ) AS _rn
+    FROM dwrdim.dim_product_d
+    WHERE COALESCE(del_flag, 'N') = 'N'
+)
+/* 主查询: 5 表 JOIN 组装宽表（粒度=订单，无变化；LEFT JOIN 右侧字段 COALESCE 兜底） */
+SELECT
+    o."订单ID" AS order_id,
+    o."客户ID" AS cust_id,
+    o."商品ID" AS product_id,
+    o."订单金额" AS order_amt,
+    o."订单数量" AS order_qty,
+    COALESCE(c."客户名称", '') AS cust_name,
+    COALESCE(c."客户等级", '') AS cust_level,
+    COALESCE(pl.product_name, '') AS product_name,
+    COALESCE(pl.category_code, '') AS category_code,
+    COALESCE(pay.total_pay_amt, 0) AS total_pay_amt,
+    COALESCE(log.total_ship_fee, 0) AS total_ship_fee,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di o
+LEFT JOIN dwrdim.dim_cust_d c
+    ON o."客户ID" = c."客户ID"
+    AND COALESCE(c.del_flag, 'N') = 'N'
+LEFT JOIN prod_latest pl
+    ON o."商品ID" = pl.product_id
+    AND pl._rn = 1
+LEFT JOIN pay_agg pay
+    ON o."订单ID" = pay.order_id
+LEFT JOIN log_agg log
+    ON o."订单ID" = log.order_id
+WHERE COALESCE(o.del_flag, 'N') = 'N';
+——ddl/create_table_dwb_trade_wide_f.sql——
+/* =====================================================
+   表名: dws.dwb_trade_wide_f
+   规则: R0001 - 交易宽表全量装配
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 5表JOIN宽表，复杂度未达分段阈值，pay/log收敛用CTE内联处理，商品维取最新有效行，单条INSERT直产目标F表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_wide_f (
+    order_id            VARCHAR(64),  /* 订单ID */
+    cust_id             VARCHAR(64),  /* 客户ID */
+    product_id          VARCHAR(64),  /* 商品ID */
+    order_amt           DECIMAL(18,2),  /* 订单金额 */
+    order_qty           DECIMAL(18,4),  /* 订单数量 */
+    cust_name           VARCHAR(200),  /* 客户名称 */
+    cust_level          VARCHAR(10),  /* 客户等级 */
+    product_name        VARCHAR(200),  /* 商品名称 */
+    category_code       VARCHAR(50),  /* 商品分类 */
+    total_pay_amt       DECIMAL(18,2),  /* 支付总额 */
+    total_ship_fee      DECIMAL(18,2),  /* 运费总额 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次 */
+    last_upd_cycle_id   BIGINT,  /* 更新批次 */
+    dw_last_update_date TIMESTAMP(0)  /* 更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_wide_f IS '交易宽表';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_id IS '商品ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_amt IS '订单金额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_qty IS '订单数量';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_name IS '客户名称';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_level IS '客户等级';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_name IS '商品名称';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.category_code IS '商品分类';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.total_pay_amt IS '支付总额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.total_ship_fee IS '运费总额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.dw_last_update_date IS '更新时间';
+档案来源：../10_project_deliver/003_dwb_trade_wide_f</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 15 项：order_id, cust_id, product_id, order_amt, order_qty, cust_name, cust_level, product_name, category_code, total_pay_amt, total_ship_fee, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_trade_wide_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 15 项）（源→规则→目标）：
+ods_trade_order_di.订单ID --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.客户ID --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.商品ID --[直接复制]--&gt; product_id(商品ID)
+ods_trade_order_di.订单金额 --[直接复制]--&gt; order_amt(订单金额)
+ods_trade_order_di.订单数量 --[直接复制]--&gt; order_qty(订单数量)
+dim_cust_d.客户名称 --[直接复制]--&gt; cust_name(客户名称)
+dim_cust_d.客户等级 --[直接复制]--&gt; cust_level(客户等级)
+dim_product_d.商品名称 --[直接复制]--&gt; product_name(商品名称)
+dim_product_d.商品分类 --[直接复制]--&gt; category_code(商品分类)
+ods_payment_di.支付金额 --[数据加工]--&gt; total_pay_amt(支付总额)
+ods_logistics_di.运费 --[数据加工]--&gt; total_ship_fee(运费总额)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(更新批次)
+（无源声明） --[赋值]--&gt; dw_last_update_date(更新时间)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>任务：为 slshp.dwb_shop_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：店铺中心宽表
@@ -776,7 +1028,7 @@
 映射字段 20 项，来源表 4 张。</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -932,7 +1184,7 @@
 档案来源：../10_project_deliver/004_dwb_shop_center_f</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slshp.dwb_shop_center_f，粒度：每行一个店铺记录
@@ -942,7 +1194,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 20 项（源→规则→目标）：
 dim_shop_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
@@ -967,13 +1219,197 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>任务：为 slshp.dwb_shop_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：店铺中心宽表
+粒度：每行一个店铺记录
+调度：全量调度 / T+1，一天一调
+映射字段 20 项，来源表 4 张。
+本规则：R0001（店铺中心宽表装配），step_type=full，目标表 dwb_shop_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* R0001: 店铺中心宽表装配
+   以 dim_shop_f 为主表，LEFT JOIN 地区维度取省份名，并通过两个 CTE 把订单/评价事实表
+   预聚合到店铺粒度后关联，一次产出店铺中心宽表全量字段。
+   字段命名假设（dwd_order_f 的实付金额/购买用户字段名 ts 切片未给出，按常见命名推断）：
+     - 实付金额列假设为 pay_amount（最符合"实付金额"语义）
+     - 购买用户列假设为 user_id
+   若源表 DDL 字段名不同，需同步调整 order_agg CTE 内引用。 */
+WITH
+/* CTE 1: order_agg — 按 shop_id 预聚合订单（累计订单数、累计销售额、累计去重购买人数） */
+order_agg AS (
+    SELECT
+        dof.shop_id AS shop_id,
+        COUNT(1) AS total_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0) AS total_sales_amount,
+        COUNT(DISTINCT dof.user_id) AS total_buyer_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE dof.del_flag = 'N'
+    GROUP BY dof.shop_id
+),
+/* CTE 2: review_agg — 按 shop_id 预聚合评价（评价数） */
+review_agg AS (
+    SELECT
+        drf5.shop_id AS shop_id,
+        COUNT(1) AS review_cnt
+    FROM sdrev.dwd_review_f drf5
+    WHERE drf5.del_flag = 'N'
+    GROUP BY drf5.shop_id
+)
+/* 主查询：dim_shop_f 主表
+   → LEFT JOIN dim_region_f 取省份名（region_code 唯一，不膨胀）
+   → LEFT JOIN order_agg / review_agg（CTE 已按 shop_id 收敛，不膨胀）取店铺度量 */
+SELECT
+    dsf.shop_id AS shop_id,
+    dsf.shop_name AS shop_name,
+    dsf.company_name AS company_name,
+    dsf.open_time AS open_time,
+    dsf.province_code AS province_code,
+    COALESCE(dsf.shop_score, 0) AS shop_score,
+    COALESCE(dsf.service_score, 0) AS service_score,
+    COALESCE(dsf.logistics_score, 0) AS logistics_score,
+    CASE dsf.shop_type
+        WHEN 'FLAGSHIP' THEN '旗舰店'
+        WHEN 'SPECIALTY' THEN '专卖店'
+        WHEN 'FRANCHISE' THEN '专营店'
+        ELSE '其他'
+    END AS shop_type_name,
+    CASE dsf.shop_status
+        WHEN 'OPEN' THEN '营业中'
+        WHEN 'CLOSED' THEN '已关闭'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS shop_status_name,
+    COALESCE(CURRENT_DATE - dsf.open_time::date, 0)::int AS open_days,
+    COALESCE(drf.region_name, '') AS province_name,
+    COALESCE(order_agg.total_order_cnt, 0) AS total_order_cnt,
+    COALESCE(order_agg.total_sales_amount, 0) AS total_sales_amount,
+    COALESCE(order_agg.total_buyer_cnt, 0) AS total_buyer_cnt,
+    COALESCE(review_agg.review_cnt, 0) AS review_cnt,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_shop_f dsf
+LEFT JOIN dim.dim_region_f drf
+    ON dsf.province_code = drf.region_code
+    AND drf.del_flag = 'N'
+LEFT JOIN order_agg
+    ON dsf.shop_id = order_agg.shop_id
+LEFT JOIN review_agg
+    ON dsf.shop_id = review_agg.shop_id
+WHERE dsf.del_flag = 'N';
+——ddl/create_table_dwb_shop_center_f.sql——
+/* =====================================================
+   表名: slshp.dwb_shop_center_f
+   规则: R0001 - 店铺中心宽表装配
+   分布键: shop_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 dim_shop_f 为主表，LEFT JOIN 地区维度取省份名，并通过两个 CTE 把订单/评价事实表预聚合到店铺粒度后关联，一次产出店铺中心宽表全量字段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slshp.dwb_shop_center_f (
+    shop_id             bigint,  /* 店铺ID */
+    shop_name           varchar(200),  /* 店铺名称 */
+    company_name        varchar(200),  /* 公司名称 */
+    open_time           datetime,  /* 开店时间 */
+    province_code       varchar(20),  /* 省份编码 */
+    shop_score          decimal(3,2),  /* 店铺评分 */
+    service_score       decimal(3,2),  /* 服务评分 */
+    logistics_score     decimal(3,2),  /* 物流评分 */
+    shop_type_name      varchar(50),  /* 店铺类型 */
+    shop_status_name    varchar(50),  /* 店铺状态 */
+    open_days           int,  /* 营业天数 */
+    province_name       varchar(50),  /* 省份名称 */
+    total_order_cnt     int,  /* 累计订单数 */
+    total_sales_amount  decimal(18,2),  /* 累计销售额 */
+    total_buyer_cnt     int,  /* 累计购买人数 */
+    review_cnt          int,  /* 评价数 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(shop_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slshp.dwb_shop_center_f IS '店铺中心宽表';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.company_name IS '公司名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_time IS '开店时间';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_score IS '店铺评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.service_score IS '服务评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.logistics_score IS '物流评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_status_name IS '店铺状态';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_days IS '营业天数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_order_cnt IS '累计订单数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_buyer_cnt IS '累计购买人数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.review_cnt IS '评价数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/004_dwb_shop_center_f</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 20 项：shop_id, shop_name, company_name, open_time, province_code, shop_score, service_score, logistics_score, shop_type_name, shop_status_name, open_days, province_name, total_order_cnt, total_sales_amount, total_buyer_cnt, review_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_shop_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 20 项）（源→规则→目标）：
+dim_shop_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dim_shop_f.shop_type --[数据加工]--&gt; shop_type_name(店铺类型)
+dim_shop_f.shop_status --[数据加工]--&gt; shop_status_name(店铺状态)
+dim_shop_f.company_name --[直接复制]--&gt; company_name(公司名称)
+dim_shop_f.open_time --[直接复制]--&gt; open_time(开店时间)
+（无源声明） --[数据加工]--&gt; open_days(营业天数)
+dim_shop_f.province_code --[直接复制]--&gt; province_code(省份编码)
+dim_region_f.region_name --[直接复制]--&gt; province_name(省份名称)
+dim_shop_f.shop_score --[直接复制]--&gt; shop_score(店铺评分)
+dim_shop_f.service_score --[直接复制]--&gt; service_score(服务评分)
+dim_shop_f.logistics_score --[直接复制]--&gt; logistics_score(物流评分)
+（无源声明） --[数据加工]--&gt; total_order_cnt(累计订单数)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; total_buyer_cnt(累计购买人数)
+（无源声明） --[数据加工]--&gt; review_cnt(评价数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：用户中心宽表
@@ -982,7 +1418,7 @@
 映射字段 46 项，来源表 9 张。</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -1193,7 +1629,7 @@
 档案来源：../10_project_deliver/005_dwb_user_center_f</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slusr.dwb_user_center_f，粒度：每行一个用户记录
@@ -1203,7 +1639,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 46 项（源→规则→目标）：
 dim_user_f.user_id --[直接复制]--&gt; user_id(用户ID)
@@ -1254,13 +1690,105 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户中心宽表
+粒度：每行一个用户记录
+调度：全量调度 / T+1，一天一调
+映射字段 46 项，来源表 9 张。
+本规则：R0001（订单聚合中间表），step_type=full，目标表 dwb_user_center_f_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* R0001: 订单聚合中间表（将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用） */
+SELECT
+    dof.user_id AS user_id,
+    COUNT(1) AS total_order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS total_pay_amount,
+    SUM(dof.pay_amount) / NULLIF(COUNT(1), 0) AS avg_order_amount,
+    MAX(dof.create_time) AS last_order_time,
+    MIN(dof.create_time) AS first_order_time,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.user_id;
+——ddl/create_table_dwb_user_center_f_tmp1.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp1
+   规则: R0001 - 订单聚合中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp1 (
+    total_order_cnt  int,  /* 历史订单数 */
+    total_pay_amount decimal(18,2),  /* 历史消费金额 */
+    avg_order_amount decimal(18,2),  /* 平均客单价 */
+    last_order_time  datetime,  /* 最近下单时间 */
+    first_order_time datetime,  /* 首次下单时间 */
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp1 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/005_dwb_user_center_f</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 5 项：total_order_cnt, total_pay_amount, avg_order_amount, last_order_time, first_order_time（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_center_f_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 5 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; total_order_cnt(历史订单数)
+（无源声明） --[数据加工]--&gt; total_pay_amount(历史消费金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f.create_time --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f.create_time --[数据加工]--&gt; first_order_time(首次下单时间)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>任务：为 slord.dwb_user_behavior_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：用户行为宽表
@@ -1269,7 +1797,7 @@
 映射字段 264 项，来源表 9 张。</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -1663,7 +2191,7 @@
 档案来源：../10_project_deliver/006_dwb_user_behavior_f</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slord.dwb_user_behavior_f，粒度：每行一个用户行为记录
@@ -1673,7 +2201,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 264 项（源→规则→目标）：
 dim_user_base_d.user_id --[直接复制]--&gt; user_user_id(用户ID)
@@ -1758,13 +2286,490 @@
 dim_us…（截断）</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>任务：为 slord.dwb_user_behavior_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户行为宽表
+粒度：每行一个用户行为记录
+调度：全量调度 / T+1，一天一调
+映射字段 264 项，来源表 9 张。
+本规则：R0001（用户行为宽表三场景 UNION ALL 加工），step_type=full，目标表 dwb_user_behavior_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =========================================================================
+ * 规则编号: R0001
+ * 规则名称: 用户行为宽表三场景 UNION ALL 加工
+ * 目标表:   dwb_user_behavior_f
+ * 设计意图:
+ *   将三类互斥的用户行为事件流（电商交易 / 内容互动 / 社交关系）按统一的
+ *   用户 + 行为 + 领域扩展 字段模型 UNION ALL 合并到一张行为宽表。
+ *   因 user_* 与通用行为字段在三场景物理上同属每一行，无法分配到多条场景规则，
+ *   故用单条 SELECT 承载全部 184 个目标字段（含 4 审计字段），三场景作为
+ *   并联 JOIN 子图在同一 SQL 内并行产出，最终 UNION ALL。
+ * 三场景说明:
+ *   场景1 电商交易: 主表 ods.ods_order_main_f(oom)
+ *                   + dim.dim_product_d(dpd, oom.product_id=dpd.product_id)
+ *                   + dim.dim_user_base_d(dub, oom.user_id=dub.user_id)
+ *                   → order_*/prod_* 取真值, 其余领域字段 NULL
+ *   场景2 内容互动: 主表 ods.ods_content_interaction_f(oci)
+ *                   + dim.dim_content_d(dcd, oci.content_id=dcd.content_id)
+ *                   + dim.dim_user_base_d(dub7, oci.user_id=dub7.user_id)
+ *                   → content_* 取真值, 其余领域字段 NULL
+ *   场景3 社交关系: 主表 ods.ods_social_relation_f(osr)
+ *                   + dim.dim_user_profile_d(dup, osr.user_id=dup.user_id)
+ *                   + dim.dim_user_base_d(dub10, osr.user_id=dub10.user_id)
+ *                   → social_*/profile_* 取真值, 其余领域字段 NULL
+ * 通用字段:
+ *   user_* (30个) — 三场景分别取各自 JOIN 的 dub/dub7/dub10
+ *   behavior_time/日期/时间派生 — S1/S3 用 create_time, S2 用 interaction_time
+ * 粒度: 无变化（行级追加，无聚合无展开）
+ * ========================================================================= */
+-- =======================================================
+-- 场景1: 电商交易 (oom + dpd + dub)
+-- =======================================================
+SELECT
+  -- ========== user_* (30) ==========
+  dub.user_id                                                            AS user_user_id,
+  COALESCE(dub.user_name, '')                                            AS user_user_name,
+  CONCAT(LEFT(COALESCE(dub.user_phone, ''), 3), '****',
+         RIGHT(COALESCE(dub.user_phone, ''), 4))                         AS user_user_phone,
+  CASE dub.gender WHEN 'M' THEN '男' WHEN 'F' THEN '女'
+       ELSE '未知' END                                                   AS user_gender,
+  CAST(EXTRACT(YEAR FROM CURRENT_DATE) AS INTEGER)
+    - CAST(EXTRACT(YEAR FROM dub.birthday) AS INTEGER)                   AS user_age,
+  dub.birthday                                                           AS user_birthday,
+  COALESCE(dub.province_name, '')                                        AS user_province_name,
+  COALESCE(dub.city_name, '')                                            AS user_city_name,
+  COALESCE(dub.user_level, 0)                                            AS user_user_level,
+  COALESCE(dub.user_level_name, '')                                      AS user_user_level_name,
+  COALESCE(dub.vip_status, 0)                                            AS user_vip_status,
+  dub.register_time                                                      AS user_register_time,
+  CAST(dub.register_time AS DATE)                                        AS user_register_date,
+  COALESCE(dub.user_status, '')                                          AS user_user_status,
+  CASE dub.user_status WHEN 'ACTIVE' THEN '正常' WHEN 'INACTIVE' THEN '未激活'
+       WHEN 'BANNED' THEN '封禁' ELSE '未知' END                         AS user_user_status_name,
+  COALESCE(dub.source_channel, '')                                       AS user_source_channel,
+  COALESCE(dub.source_type, '')                                          AS user_source_type,
+  dub.first_active_time                                                  AS user_first_active_time,
+  dub.last_active_time                                                   AS user_last_active_time,
+  COALESCE(dub.active_days, 0)                                           AS user_active_days,
+  COALESCE(dub.total_score, 0)                                           AS user_total_score,
+  COALESCE(dub.credit_score, 0)                                          AS user_credit_score,
+  COALESCE(dub.risk_level, '')                                           AS user_risk_level,
+  COALESCE(dub.device_type, '')                                          AS user_device_type,
+  COALESCE(dub.os_type, '')                                              AS user_os_type,
+  COALESCE(dub.app_version, '')                                          AS user_app_version,
+  COALESCE(dub.ip_address, '')                                           AS user_ip_address,
+  COALESCE(dub.network_type, '')                                         AS user_network_type,
+  COALESCE(dub.is_real_name, 0)                                          AS user_is_real_name,
+  COALESCE(dub.verify_status, '')                                        AS user_verify_status,
+  -- ========== behavior_* (10) ==========
+  CAST(NULL AS BIGINT)                                                   AS behavior_id,
+  oom.create_time                                                        AS behavior_time,
+  CAST(oom.create_time AS DATE)                                          AS behavior_date,
+  CAST(EXTRACT(HOUR FROM oom.create_time) AS INTEGER)                    AS behavior_hour,
+  CAST(EXTRACT(DOW FROM oom.create_time) + 1 AS INTEGER)                 AS behavior_weekday,
+  CAST(EXTRACT(MONTH FROM oom.create_time) AS INTEGER)                   AS behavior_month,
+  CAST(EXTRACT(QUARTER FROM oom.create_time) AS INTEGER)                 AS behavior_quarter,
+  CAST(EXTRACT(YEAR FROM oom.create_time) AS INTEGER)                    AS behavior_year,
+  CASE WHEN EXTRACT(DOW FROM oom.create_time) IN (0, 6) THEN 1 ELSE 0 END AS is_weekend,
+  CASE WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 0 AND 5 THEN '凌晨'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 6 AND 11 THEN '上午'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 12 AND 13 THEN '中午'
+       WHEN EXTRACT(HOUR FROM oom.create_time) BETWEEN 14 AND 17 THEN '下午'
+       ELSE '晚上' END                                                   AS time_period,
+  -- ========== order_* (30) ==========
+  oom.order_id                                                           AS order_order_id,
+  oom.order_no                                                           AS order_order_no,
+  oom.order_status                                                       AS order_order_status,
+  CASE oom.order_status WHEN 'PENDING' THEN '待支付' WHEN 'PAID' THEN '已支付'
+       WHEN 'SHIPPED' THEN '已发货' WHEN 'COMPLETED' THEN '已完成'
+       WHEN 'CANCELLED' THEN '已取消' ELSE '未知' END                    AS order_order_status_name,
+  oom.order_amount                                                       AS order_order_amount,
+  oom.discount_amount                                                    AS order_discount_amount,
+  oom.actual_amount                                                      AS order_actual_amount,
+  oom.payment_method                                                     AS order_payment_method,
+  oom.payment_time                                                       AS order_payment_time,
+  oom.shipping_fee                                                       AS order_shipping_fee,
+  oom.product_count                                                      AS order_product_count,
+  oom.sku_count                                                          AS order_sku_count,
+  oom.is_first_order                                                     AS order_is_first_order,
+  oom.coupon_id                                                          AS order_coupon_id,
+  oom.coupon_name                                                        AS order_coupon_name,
+  oom.points_used                                                        AS order_points_used,
+  oom.points_earned                                                      AS order_points_earned,
+  oom.complete_time                                                      AS order_complete_time,
+  oom.cancel_time                                                        AS order_cancel_time,
+  oom.cancel_reason                                                      AS order_cancel_reason,
+  oom.merchant_id                                                        AS order_merchant_id,
+  oom.merchant_name                                                      AS order_merchant_name,
+  oom.delivery_type                                                      AS order_delivery_type,
+  oom.delivery_time                                                      AS order_delivery_time,
+  oom.receive_time                                                       AS order_receive_time,
+  oom.receive_status                                                     AS order_receive_status,
+  oom.order_source                                                       AS order_order_source,
+  oom.remark                                                             AS order_remark,
+  oom.invoice_type                                                       AS order_invoice_type,
+  oom.invoice_title                                                      AS order_invoice_title,
+  -- ========== prod_* (20) ==========
+  dpd.product_id                                                         AS prod_product_id,
+  COALESCE(dpd.product_name, '')                                         AS prod_product_name,
+  COALESCE(dpd.product_code, '')                                         AS prod_product_code,
+  dpd.sku_id                                                             AS prod_sku_id,
+  COALESCE(dpd.sku_name, '')                                             AS prod_sku_name,
+  COALESCE(dpd.brand_id, 0)                                              AS prod_brand_id,
+  COALESCE(dpd.brand_name, '')                                           AS prod_brand_name,
+  COALESCE(dpd.category_id, 0)                                           AS prod_category_id,
+  COALESCE(dpd.category_name, '')                                        AS prod_category_name,
+  COALESCE(dpd.category_level1, '')                                      AS prod_category_level1,
+  COALESCE(dpd.category_level2, '')                                      AS prod_category_level2,
+  COALESCE(dpd.category_level3, '')                                      AS prod_category_level3,
+  COALESCE(dpd.price, 0)                                                 AS prod_price,
+  COALESCE(dpd.cost_price, 0)                                            AS prod_cost_price,
+  CASE WHEN dpd.price &gt; 0 THEN (dpd.price - dpd.cost_price) / dpd.price * 100
+       ELSE 0 END                                                        AS prod_profit_rate,
+  COALESCE(dpd.stock_status, '')                                         AS prod_stock_status,
+  COALESCE(dpd.sale_status, '')                                          AS prod_sale_status,
+  COALESCE(dpd.product_type, '')                                         AS prod_product_type,
+  COALESCE(dpd.is_virtual, 0)                                            AS prod_is_virtual,
+  COALESCE(dpd.supplier_id, 0)                                           AS prod_supplier_id,
+  -- ========== content_* (50) — 场景1 不适用 ==========
+  CAST(NULL AS BIGINT)                                                   AS content_interaction_id,
+  CAST(NULL AS BIGINT)                                                   AS content_content_id,
+  CAST(NULL AS VARCHAR(50))                                              AS content_interaction_type,
+  CAST(NULL AS VARCHAR(50))                                              AS content_interaction_type_name,
+  CAST(NULL AS INTEGER)                                                  AS content_duration_seconds,
+  CAST(NULL AS NUMERIC(5,2))                                             AS content_duration_minutes,
+  CAST(NULL AS VARCHAR(1000))                                            AS content_comment_content,
+  CAST(NULL AS INTEGER)                                                  AS content_comment_word_count,
+  CAST(NULL AS VARCHAR(50))                                              AS content_share_platform,
+  CAST(NULL AS INTEGER)                                                  AS content_share_count,…（截断）
+——ddl/create_table_dwb_user_behavior_f.sql——
+/* =====================================================
+   表名: slord.dwb_user_behavior_f
+   规则: R0001 - 用户行为宽表三场景 UNION ALL 加工
+   分布键: behavior_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将三类互斥的用户行为事件流（电商交易、内容互动、社交关系）按统一的 用户+行为+领域扩展 字段模型 UNION ALL 合并到一张行为宽表。 因 user_* 与通用行为字段在三场景物理上同属每一行，无法分配到多条场景规则， 故用单条 INSERT 承载全部 184 个目标字段，三场景作为并联 JOIN 子图 在同一规则的 SQL 内并行产出，最终 UNION ALL。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_user_behavior_f (
+    user_user_id                   bigint,  /* 用户ID */
+    user_user_name                 varchar(100),  /* 用户姓名 */
+    user_user_phone                varchar(20),  /* 手机号 */
+    user_gender                    varchar(10),  /* 性别 */
+    user_age                       int,  /* 年龄 */
+    user_birthday                  date,  /* 出生日期 */
+    user_province_name             varchar(50),  /* 省份 */
+    user_city_name                 varchar(50),  /* 城市 */
+    user_user_level                int,  /* 用户等级 */
+    user_user_level_name           varchar(50),  /* 用户等级名称 */
+    user_vip_status                int,  /* VIP状态 */
+    user_register_time             timestamp,  /* 注册时间 */
+    user_register_date             date,  /* 注册日期 */
+    user_user_status               varchar(20),  /* 用户状态 */
+    user_user_status_name          varchar(50),  /* 用户状态名称 */
+    user_source_channel            varchar(50),  /* 来源渠道 */
+    user_source_type               varchar(50),  /* 来源类型 */
+    user_first_active_time         timestamp,  /* 首次活跃时间 */
+    user_last_active_time          timestamp,  /* 最后活跃时间 */
+    user_active_days               int,  /* 活跃天数 */
+    user_total_score               int,  /* 总积分 */
+    user_credit_score              int,  /* 信用分 */
+    user_risk_level                varchar(20),  /* 风险等级 */
+    user_device_type               varchar(50),  /* 设备类型 */
+    user_os_type                   varchar(50),  /* 操作系统 */
+    user_app_version               varchar(20),  /* APP版本 */
+    user_ip_address                varchar(50),  /* IP地址 */
+    user_network_type              varchar(20),  /* 网络类型 */
+    user_is_real_name              int,  /* 是否实名 */
+    user_verify_status             varchar(20),  /* 认证状态 */
+    behavior_id                    bigint,  /* 行为ID */
+    behavior_time                  timestamp,  /* 行为时间 */
+    behavior_date                  date,  /* 行为日期 */
+    behavior_hour                  int,  /* 行为小时 */
+    behavior_weekday               int,  /* 行为星期 */
+    behavior_month                 int,  /* 行为月份 */
+    behavior_quarter               int,  /* 行为季度 */
+    behavior_year                  int,  /* 行为年份 */
+    is_weekend                     int,  /* 是否周末 */
+    time_period                    varchar(20),  /* 时间段 */
+    order_order_id                 bigint,  /* 订单ID */
+    order_order_no                 varchar(50),  /* 订单编号 */
+    order_order_status             varchar(20),  /* 订单状态 */
+    order_order_status_name        varchar(50),  /* 订单状态名称 */
+    order_order_amount             decimal(18,2),  /* 订单金额 */
+    order_discount_amount          decimal(18,2),  /* 优惠金额 */
+    order_actual_amount            decimal(18,2),  /* 实付金额 */
+    order_payment_method           varchar(50),  /* 支付方式 */
+    order_payment_time             timestamp,  /* 支付时间 */
+    order_shipping_fee             decimal(18,2),  /* 运费 */
+    order_product_count            int,  /* 商品数量 */
+    order_sku_count                int,  /* SKU数量 */
+    order_is_first_order           int,  /* 是否首单 */
+    order_coupon_id                int,  /* 优惠券ID */
+    order_coupon_name              varchar(100),  /* 优惠券名称 */
+    order_points_used              int,  /* 使用积分 */
+    order_points_earned            int,  /* 获得积分 */
+    order_complete_time            timestamp,  /* 完成时间 */
+    order_cancel_time              timestamp,  /* 取消时间 */
+    order_cancel_reason            varchar(200),  /* 取消原因 */
+    order_merchant_id              int,  /* 商家ID */
+    order_merchant_name            varchar(200),  /* 商家名称 */
+    order_delivery_type            varchar(50),  /* 配送方式 */
+    order_delivery_time            timestamp,  /* 配送时间 */
+    order_receive_time             timestamp,  /* 收货时间 */
+    order_receive_status           varchar(20),  /* 收货状态 */
+    order_order_source             varchar(50),  /* 订单来源 */
+    order_remark                   varchar(500),  /* 订单备注 */
+    order_invoice_type             varchar(20),  /* 发票类型 */
+    order_invoice_title            varchar(200),  /* 发票抬头 */
+    prod_product_id                bigint,  /* 商品ID */
+    prod_product_name              varchar(200),  /* 商品名称 */
+    prod_product_code              varchar(50),  /* 商品编码 */
+    prod_sku_id                    bigint,  /* SKU_ID */
+    prod_sku_name                  varchar(200),  /* SKU名称 */
+    prod_brand_id                  int,  /* 品牌ID */
+    prod_brand_name                varchar(100),  /* 品牌名称 */
+    prod_category_id               int,  /* 类目ID */
+    prod_category_name             varchar(100),  /* 类目名称 */
+    prod_category_level1           varchar(100),  /* 一级类目 */
+    prod_category_level2           varchar(100),  /* 二级类目 */
+    prod_category_level3           varchar(100),  /* 三级类目 */
+    prod_price                     decimal(18,2),  /* 商品价格 */
+    prod_cost_price                decimal(18,2),  /* 成本价 */
+    prod_profit_rate               decimal(5,2),  /* 利润率 */
+    prod_stock_status              varchar(20),  /* 库存状态 */
+    prod_sale_status               varchar(20),  /* 销售状态 */
+    prod_product_type              varchar(50),  /* 商品类型 */
+    prod_is_virtual                int,  /* 是否虚拟商品 */
+    prod_supplier_id               int,  /* 供应商ID */
+    content_interaction_id         bigint,  /* 互动ID */
+    content_content_id             bigint,  /* 内容ID */
+    content_interaction_type       varchar(50),  /* 互动类型 */
+    content_interaction_type_name  varchar(50),  /* 互动类型名称 */
+    content_duration_seconds       int,  /* 浏览时长(秒) */
+    content_duration_minutes       decimal(5,2),  /* 浏览时长(分) */
+    content_comment_content        varchar(1000),  /* 评论内容 */
+    content_comment_word_count     int,  /* 评论字数 */
+    content_share_platform         varchar(50),  /* 分享平台 */
+    content_share_count            int,  /* 分享次数 */
+    content_like_count             int,  /* 点赞数 */
+    content_comment_count          int,  /* 评论数 */
+    content_collect_count          int,  /* 收藏数 */
+    content_forward_count          int,  /* 转发数 */
+    content_is_original            int,  /* 是否原创 */
+    content_source_type            varchar(50),  /* 来源类型 */
+    content_browse_depth           int,  /* 浏览深度 */
+    content_scroll_percentage      decimal(5,2),  /* 滚动百分比 */
+    content_click_count            int,  /* 点击次数 */
+    content_stay_time              int,  /* 停留时长 */
+    content_bounce_flag            int,  /* 是否跳出 */
+    content_exit_page              varchar(200),  /* 退出页面 */
+    content_session_id             varchar(100),  /* 会话ID */
+    content_page_view_count        int,  /* 页面浏览数 */
+    content_unique_visitor         int,  /* 独立访客标识 */
+    content_referer_url            varchar(500),  /* 来源URL */
+    content_utm_source             varchar(100),  /* UTM来源 */
+    content_utm_medium             varchar(100),  /* UTM媒介 */
+    content_utm_campaign           varchar(100),  /* UTM活动 */
+    content_interaction_device     varchar(50),  /* 互动设备 */
+    content_content_title          varchar(200),  /* 内容标题 */
+    content_content_type           varchar(50),  /* 内容类型 */
+    content_content_category       varchar(50),  /* 内容分类 */
+    content_author_id              bigint,  /* 作者ID */
+    content_author_name            varchar(100),  /* 作者名称 */
+    content_publish_time           timestamp,  /* 发布时间 */
+    content_publish_date           date,  /* 发布日期 */
+    content_content_length         int,  /* 内容长度 */
+    content_word_count             int,  /* 字数 */
+    content_read_count             int,  /* 阅读数 */
+    content_content_like_count     int,  /* 内容点赞数 */
+    content_content_comment_count  int,  /* 内容评论数 */
+    content_content_share_count    int,  /* 内容分享数 */
+    content_content_collect_count  int,  /* 内容收藏数 */
+    content_topic_id               int,  /* 话题ID */
+    content_topic_name             varchar(100),  /* 话题名称 */
+    content_is_hot                 int,  /* 是否热门 */
+    content_is_recommend           int,  /* 是否推荐 */
+    content_content_status         varchar(20),  /* 内容状态 */
+    content_content_score          decimal(5,2),  /* 内容评分 */
+    social_relation_id             bigint,  /* 关系ID */
+    social_target_user_id          bigint,  /* 目标用户ID */
+    social_relation_type           varchar(50),  /* 关系类型 */
+    social_relation_type_name      varchar(50),  /* 关系类型名称 */
+    social_is_mutual               int,  /* 是否互相关注 */
+    social_interaction_count       int,  /* 互动次数 */
+    social_last_interaction_time   timestamp,  /* 最后互动时间 */
+    social_relation_status         varchar(20),  /* 关系状态 */
+    social_source                  varchar(50),  /* 来源 */
+    social_group_id                int,  /* 分组ID */
+    social_group_name              varchar(100),  /* 分组名称 */
+    social_remark                  varchar(100),  /* 备注名 */
+    social_intimacy_level          int,  /* 亲密度等级 */
+    social_chat_count              int,  /* 聊天次数 */
+    social_call_count              int,  /* 通话次数 */
+    social_video_call_count        int,  /* 视频通话次数 */
+    social_gift_count              int,  /* 礼物次数 */
+    social_follow_days             int,  /* 关注天数 */
+    social_interaction_frequency   decimal(5,2),  /* 互动频率 */
+    social_common_friends          int,  /* 共同好友数 */
+    social_common_groups           int,  /* 共同群组数 */
+    social_social_distance         int,  /* 社交距离 */
+    social_relationship_strength   decimal(5,2),  /* 关系强度 */
+    social_trust_level             int,  /* 信任等级 */
+    social_contact_importance      decimal(5,2),  /* 联系人重要性 */
+    profile_avatar_url             varchar(500),  /* 头像URL */
+    profile_profession             varchar(50),  /* 职业 */
+    profile_education              varchar(50),  /* 学历 */
+    profile_interests              varchar(500),  /* 兴趣标签 */
+    profile_active_level           varchar(20),  /* 活跃等级 */
+    profile_influence_score        decimal(5,2),  /* 影响力分数 */
+    profile_social_value           decimal(18,2),  /* 社交价值 */
+    profile_user_tags              varchar(500),  /* 用户标签 */
+    profile_fans_count             int,  /* 粉丝数 */
+    profile_follow_count           int,  /* 关注数 */
+    profile_friend_count           int,  /* 好友数 */
+    profile_social_activity_score  decimal(5,2),  /* 社交活跃度 */
+    profile_content_creation_score decimal(5,2),  /* 内容创作力 */
+    profile_engagement_score       decimal(5,2),  /* 参与度分数 */
+    profile_social_influence_rank  int,  /* 社交影响力排名 */
+    del_flag                       NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id                   BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id              BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date            TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(behavior_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_user_behavior_f IS '用户行为宽表';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_id IS '用户ID';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_name IS '用户姓名';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_phone IS '手机号';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_gender IS '性别';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_age IS '年龄';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_birthday IS '出生日期';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_province_name IS '省份';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_city_name IS '城市';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_level IS '用户等级';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_user_level_name IS '用户等级名称';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_vip_status IS 'VIP状态';
+COMMENT ON COLUMN slord.dwb_user_behavior_f.user_…（截断）
+档案来源：../10_project_deliver/006_dwb_user_behavior_f</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 184 项：user_user_id, user_user_name, user_user_phone, user_gender, user_age, user_birthday, user_province_name, user_city_name, user_user_level, user_user_level_name, user_vip_status, user_register_time, user_register_date, user_user_status, user_user_status_name, user_source_channel, user_source_type, user_first_active_time, user_last_active_time, user_active_days, user_total_score, user_credit_score, user_risk_level, user_device_type, user_os_type, user_app_version, user_ip_address, user_network_type, user_is_real_name, user_verify_status, behavior_id, behavior_time, behavior_date, behavior_hour, behavior_weekday, behavior_month, behavior_quarter, behavior_year, is_weekend, time_period, order_order_id, order_order_no, order_order_status, order_order_status_name, order_order_amount, order_discount_amount, order_actual_amount, order_payment_method, order_payment_time, order_shipping_fee, order_product_count, order_sku_count, order_is_first_order, order_coupon_id, order_coupon_name, order_points_used, order_points_earned, order_complete_time, order_cancel_time, order_cancel_reason, order_merchant_id, order_merchant_name, order_delivery_type, order_delivery_time, order_receive_time, order_receive_status, order_order_source, order_remark, order_invoice_type, order_invoice_title, prod_product_id, prod_product_name, prod_product_code, prod_sku_id, prod_sku_name, prod_brand_id, prod_brand_name, prod_category_id, prod_category_name, prod_category_level1, prod_category_level2, prod_category_level3, prod_price, prod_cost_price, prod_profit_rate, prod_stock_status, prod_sale_status, prod_product_type, prod_is_virtual, prod_supplier_id, content_interaction_id, content_content_id, content_interaction_type, content_interaction_type_name, content_duration_seconds, content_duration_minutes, content_comment_content, content_comment_word_count, content_share_platform, content_share_count, content_like_count, content_comment_count, content_collect_count, content_forward_count, content_is_original, content_source_type, content_browse_depth, content_scroll_percentage, content_click_count, content_stay_time, content_bounce_flag, content_exit_page, content_session_id, content_page_view_count, content_unique_visitor, content_referer_url, content_utm_source, content_utm_medium, content_utm_campaign, content_interaction_device, content_content_title, content_content_type, content_content_category, content_author_id, content_author_name, content_publish_time, content_publish_date, content_content_length, content_word_count, content_read_count, content_content_like_count, content_content_comment_count, content_content_share_count, content_content_collect_count, content_topic_id, content_topic_name, content_is_hot, content_is_recommend, content_content_status, content_content_score, social_relation_id, social_target_user_id, social_relation_type, social_relation_type_name, social_is_mutual, social_interaction_count, social_last_interaction_time, social_relation_status, social_source, social_group_id, social_group_name, social_remark, social_intimacy_level, social_chat_count, social_call_count, social_video_call_count, social_gift_count, social_follow_days, social_interaction_frequency, social_common_friends, social_common_groups, social_social_distance, social_relationship_strength, social_trust_level, social_contact_importance, profile_avatar_url, profile_profession, profile_education, profile_interests, profile_active_level, profile_influence_score, profile_social_value, profile_user_tags, profile_fans_count, profile_follow_count, profile_friend_count, profile_social_activity_score, profile_content_creation_score, profile_engagement_score, profile_social_influence_rank, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_behavior_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 264 项）（源→规则→目标）：
+dim_user_base_d.user_id --[直接复制]--&gt; user_user_id(用户ID)
+dim_user_base_d.user_id --[直接复制]--&gt; user_user_id(用户ID)
+dim_user_base_d.user_id --[直接复制]--&gt; user_user_id(用户ID)
+dim_user_base_d.user_name --[直接复制]--&gt; user_user_name(用户姓名)
+dim_user_base_d.user_name --[直接复制]--&gt; user_user_name(用户姓名)
+dim_user_base_d.user_name --[直接复制]--&gt; user_user_name(用户姓名)
+dim_user_base_d.user_phone --[数据加工]--&gt; user_user_phone(手机号)
+dim_user_base_d.user_phone --[数据加工]--&gt; user_user_phone(手机号)
+dim_user_base_d.user_phone --[数据加工]--&gt; user_user_phone(手机号)
+dim_user_base_d.gender --[数据加工]--&gt; user_gender(性别)
+dim_user_base_d.gender --[数据加工]--&gt; user_gender(性别)
+dim_user_base_d.gender --[数据加工]--&gt; user_gender(性别)
+dim_user_base_d.age --[数据加工]--&gt; user_age(年龄)
+dim_user_base_d.age --[数据加工]--&gt; user_age(年龄)
+dim_user_base_d.age --[数据加工]--&gt; user_age(年龄)
+dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
+dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
+dim_user_base_d.birthday --[直接复制]--&gt; user_birthday(出生日期)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.province_name --[直接复制]--&gt; user_province_name(省份)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.city_name --[直接复制]--&gt; user_city_name(城市)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level --[直接复制]--&gt; user_user_level(用户等级)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.user_level_name --[直接复制]--&gt; user_user_level_name(用户等级名称)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.vip_status --[直接复制]--&gt; user_vip_status(VIP状态)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.register_date --[数据加工]--&gt; user_register_date(注册日期)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status --[直接复制]--&gt; user_user_status(用户状态)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.user_status_name --[数据加工]--&gt; user_user_status_name(用户状态名称)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_channel --[直接复制]--&gt; user_source_channel(来源渠道)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.source_type --[直接复制]--&gt; user_source_type(来源类型)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.first_active_time --[直接复制]--&gt; user_first_active_time(首次活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.last_active_time --[直接复制]--&gt; user_last_active_time(最后活跃时间)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.active_days --[直接复制]--&gt; user_active_days(活跃天数)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.total_score --[直接复制]--&gt; user_total_score(总积分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.credit_score --[直接复制]--&gt; user_credit_score(信用分)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.risk_level --[直接复制]--&gt; user_risk_level(风险等级)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.device_type --[直接复制]--&gt; user_device_type(设备类型)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.os_type --[直接复制]--&gt; user_os_type(操作系统)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.app_version --[直接复制]--&gt; user_app_version(APP版本)
+dim_user_base_d.ip_address --[直接复制]--&gt; user_ip_address(IP地址)
+d…（截断）</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>任务：为 slscc.dwb_supply_chain_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：供应链中心宽表
@@ -1773,7 +2778,7 @@
 映射字段 23 项，来源表 5 张。</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -1956,7 +2961,7 @@
 档案来源：../10_project_deliver/007_dwb_supply_chain_f</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slscc.dwb_supply_chain_center_f，粒度：每行一个供应链记录
@@ -1966,7 +2971,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 23 项（源→规则→目标）：
 dwd_purchase_f.purchase_id --[直接复制]--&gt; purchase_id(采购单ID)
@@ -1994,13 +2999,226 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>任务：为 slscc.dwb_supply_chain_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：供应链中心宽表
+粒度：每行一个供应链记录
+调度：全量调度 / T+1，一天一调
+映射字段 23 项，来源表 5 张。
+本规则：R0001（供应链中心宽表主加工），step_type=full，目标表 dwb_supply_chain_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 供应链中心宽表主加工
+   目标表: slscc.dwb_supply_chain_center_f
+   设计意图: 以采购事实表为主表，左关联供应商/商品/仓库维度及库存事实表，
+             加工状态/等级/类型映射与金额/周转天数，产出供应链中心宽表 F 表
+   粒度: 一行 = 一条供应链中心记录 (按 purchase_id)
+   加载策略: 全量调度
+   来源表:
+     - sdinv.dwd_purchase_f (dpf, 主表)
+     - dim.dim_supplier_f (dsf)
+     - dim.dim_product_f (dpf4)
+     - dim.dim_warehouse_f (dwf)
+     - sdinv.dwd_inventory_f (dif, 需收敛)
+   ===================================================== */
+SELECT
+    dpf.purchase_id AS purchase_id,
+    dpf.purchase_no AS purchase_no,
+    /* 采购状态码转中文 (源字段 dpf.purchase_status) */
+    CASE dpf.purchase_status
+        WHEN 'DRAFT'     THEN '草稿'
+        WHEN 'SUBMITTED' THEN '已提交'
+        WHEN 'APPROVED'  THEN '已审批'
+        WHEN 'RECEIVED'  THEN '已入库'
+        WHEN 'CLOSED'    THEN '已关闭'
+        ELSE '其他'
+    END AS purchase_status_name,
+    dpf.create_time AS create_time,
+    dpf.supplier_id AS supplier_id,
+    COALESCE(dsf.supplier_name, '') AS supplier_name,
+    /* 供应商等级码转中文 (源字段 dsf.supplier_level) */
+    CASE dsf.supplier_level
+        WHEN 'A' THEN 'A级供应商'
+        WHEN 'B' THEN 'B级供应商'
+        WHEN 'C' THEN 'C级供应商'
+        ELSE '其他'
+    END AS supplier_level_name,
+    COALESCE(dsf.cooperation_years, 0) AS cooperation_years,
+    dpf.product_id AS product_id,
+    COALESCE(dpf4.product_name, '') AS product_name,
+    COALESCE(dpf.purchase_qty, 0) AS purchase_qty,
+    COALESCE(dpf.purchase_price, 0) AS purchase_price,
+    /* 采购金额 = 采购数量 × 采购单价 */
+    COALESCE(dpf.purchase_qty, 0) * COALESCE(dpf.purchase_price, 0) AS purchase_amount,
+    dpf.warehouse_id AS warehouse_id,
+    COALESCE(dwf.warehouse_name, '') AS warehouse_name,
+    /* 仓库类型码转中文 (源字段 dwf.warehouse_type) */
+    CASE dwf.warehouse_type
+        WHEN 'SELF'         THEN '自营仓'
+        WHEN 'THIRD_PARTY'  THEN '第三方仓'
+        ELSE '其他'
+    END AS warehouse_type_name,
+    COALESCE(inv.stock_qty, 0) AS current_stock_qty,
+    COALESCE(inv.locked_qty, 0) AS locked_qty,
+    /* ⚠️ 上游缺口: 库存周转天数依赖销量源表 (近30天销量),
+       该源表不在 source_tables 中 (见 ts.json design_logic 待补源说明),
+       暂输出 NULL, 待销量事实表接入后补全计算逻辑 */
+    NULL::int AS stock_days,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdinv.dwd_purchase_f dpf
+LEFT JOIN dim.dim_supplier_f dsf
+    ON dpf.supplier_id = dsf.supplier_id
+    AND dsf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf4
+    ON dpf.product_id = dpf4.product_id
+    AND dpf4.del_flag = 'N'
+LEFT JOIN dim.dim_warehouse_f dwf
+    ON dpf.warehouse_id = dwf.warehouse_id
+    AND dwf.del_flag = 'N'
+/* 库存收敛 (关联安全策略): dwd_inventory_f 按 (product_id, warehouse_id) 可能有多行,
+   取每个组合的最新有效库存行 (_rn=1), 避免 LEFT JOIN 导致主表放大.
+   实现 join_safety strategy: GROUP BY (product_id, warehouse_id) 收敛 + 取当前有效库存行 */
+LEFT JOIN (
+    SELECT
+        product_id,
+        warehouse_id,
+        stock_qty,
+        locked_qty,
+        ROW_NUMBER() OVER (
+            PARTITION BY product_id, warehouse_id
+            ORDER BY update_time DESC NULLS LAST
+        ) AS _rn
+    FROM sdinv.dwd_inventory_f
+    WHERE del_flag = 'N'
+) inv
+    ON dpf.product_id = inv.product_id
+    AND dpf.warehouse_id = inv.warehouse_id
+    AND inv._rn = 1
+WHERE dpf.del_flag = 'N';
+——ddl/create_table_dwb_supply_chain_center_f.sql——
+/* =====================================================
+   表名: slscc.dwb_supply_chain_center_f
+   规则: R0001 - 供应链中心宽表主加工
+   分布键: purchase_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以采购事实表为主表，左关联供应商/商品/仓库维度及库存事实表，加工状态/等级/类型映射与金额/周转天数，产出供应链中心宽表 F 表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slscc.dwb_supply_chain_center_f (
+    purchase_id          bigint,  /* 采购单ID */
+    purchase_no          varchar(64),  /* 采购单号 */
+    purchase_status_name varchar(50),  /* 采购状态 */
+    create_time          datetime,  /* 创建时间 */
+    supplier_id          bigint,  /* 供应商ID */
+    supplier_name        varchar(200),  /* 供应商名称 */
+    supplier_level_name  varchar(50),  /* 供应商等级 */
+    cooperation_years    int,  /* 合作年限 */
+    product_id           bigint,  /* 商品ID */
+    product_name         varchar(200),  /* 商品名称 */
+    purchase_qty         int,  /* 采购数量 */
+    purchase_price       decimal(18,2),  /* 采购单价 */
+    purchase_amount      decimal(18,2),  /* 采购金额 */
+    warehouse_id         bigint,  /* 仓库ID */
+    warehouse_name       varchar(100),  /* 仓库名称 */
+    warehouse_type_name  varchar(50),  /* 仓库类型 */
+    current_stock_qty    int,  /* 当前库存 */
+    locked_qty           int,  /* 锁定库存 */
+    stock_days           int,  /* 库存周转天数 */
+    del_flag             NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id         BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id    BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(purchase_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slscc.dwb_supply_chain_center_f IS '供应链中心宽表';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_id IS '采购单ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_no IS '采购单号';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_status_name IS '采购状态';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_id IS '供应商ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_name IS '供应商名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_level_name IS '供应商等级';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.cooperation_years IS '合作年限';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_qty IS '采购数量';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_price IS '采购单价';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_amount IS '采购金额';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_id IS '仓库ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_name IS '仓库名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_type_name IS '仓库类型';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.current_stock_qty IS '当前库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.locked_qty IS '锁定库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.stock_days IS '库存周转天数';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/007_dwb_supply_chain_f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 23 项：purchase_id, purchase_no, purchase_status_name, create_time, supplier_id, supplier_name, supplier_level_name, cooperation_years, product_id, product_name, purchase_qty, purchase_price, purchase_amount, warehouse_id, warehouse_name, warehouse_type_name, current_stock_qty, locked_qty, stock_days, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_supply_chain_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 23 项）（源→规则→目标）：
+dwd_purchase_f.purchase_id --[直接复制]--&gt; purchase_id(采购单ID)
+dwd_purchase_f.purchase_no --[直接复制]--&gt; purchase_no(采购单号)
+dwd_purchase_f.purchase_status --[数据加工]--&gt; purchase_status_name(采购状态)
+dwd_purchase_f.create_time --[直接复制]--&gt; create_time(创建时间)
+dwd_purchase_f.supplier_id --[直接复制]--&gt; supplier_id(供应商ID)
+dim_supplier_f.supplier_name --[直接复制]--&gt; supplier_name(供应商名称)
+dim_supplier_f.supplier_level --[数据加工]--&gt; supplier_level_name(供应商等级)
+dim_supplier_f.cooperation_years --[直接复制]--&gt; cooperation_years(合作年限)
+dwd_purchase_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_purchase_f.purchase_qty --[直接复制]--&gt; purchase_qty(采购数量)
+dwd_purchase_f.purchase_price --[直接复制]--&gt; purchase_price(采购单价)
+（无源声明） --[数据加工]--&gt; purchase_amount(采购金额)
+dwd_purchase_f.warehouse_id --[直接复制]--&gt; warehouse_id(仓库ID)
+dim_warehouse_f.warehouse_name --[直接复制]--&gt; warehouse_name(仓库名称)
+dim_warehouse_f.warehouse_type --[数据加工]--&gt; warehouse_type_name(仓库类型)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; current_stock_qty(当前库存)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定库存)
+（无源声明） --[数据加工]--&gt; stock_days(库存周转天数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>任务：为 slas.dwb_after_sale_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：售后服务中心宽表
@@ -2009,7 +3227,7 @@
 映射字段 24 项，来源表 5 张。</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -2195,7 +3413,7 @@
 档案来源：../10_project_deliver/008_dwb_after_sale_center_f</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slas.dwb_after_sale_center_f，粒度：每行一个售后服务记录
@@ -2205,7 +3423,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 24 项（源→规则→目标）：
 dwd_refund_f.refund_id --[直接复制]--&gt; refund_id(退款ID)
@@ -2234,13 +3452,230 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>任务：为 slas.dwb_after_sale_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：售后服务中心宽表
+粒度：每行一个售后服务记录
+调度：全量调度 / T+1，一天一调
+映射字段 24 项，来源表 5 张。
+本规则：R0001（售后服务中心宽表组装），step_type=full，目标表 slas.dwb_after_sale_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 售后服务中心宽表组装
+   目标表: slas.dwb_after_sale_center_f
+   粒度:   一行 = 一个售后服务记录（业务键/distribution_key = refund_id）
+   设计意图: 以退款事实表 dwd_refund_f 为主表，左关联订单/用户/商品/工单四表
+             拼装售后中心宽表。关联安全：dof(订单事实表)、dst(工单事实表)
+             关联前需收敛至 order_id / refund_id 唯一粒度，防止 fan-out；
+             duf(用户维表)、dpf(商品维表) join_key 唯一，直接关联。
+   ===================================================== */
+SELECT
+    drf.refund_id                                                  AS refund_id,
+    COALESCE(drf.refund_no, '')                                    AS refund_no,
+    CASE drf.refund_type
+        WHEN 'ONLY_REFUND'   THEN '仅退款'
+        WHEN 'RETURN_REFUND' THEN '退货退款'
+        WHEN 'EXCHANGE'      THEN '换货'
+        ELSE '其他'
+    END                                                            AS refund_type_name,
+    CASE drf.refund_status
+        WHEN 'APPLYING' THEN '申请中'
+        WHEN 'APPROVED' THEN '已同意'
+        WHEN 'SUCCESS'  THEN '退款成功'
+        WHEN 'REJECTED' THEN '已拒绝'
+        ELSE '其他'
+    END                                                            AS refund_status_name,
+    drf.apply_time                                                 AS apply_time,
+    drf.complete_time                                              AS complete_time,
+    /* 处理天数 = 完成日期 - 申请日期；完成时间为空时用当前日期替代，申请时间为空记为 0 */
+    COALESCE(
+        (COALESCE(drf.complete_time, CURRENT_TIMESTAMP)::date - drf.apply_time::date),
+        0
+    )                                                              AS process_days,
+    COALESCE(drf.refund_amount, 0)                                 AS refund_amount,
+    COALESCE(drf.refund_reason, '')                                AS refund_reason,
+    drf.order_id                                                   AS order_id,
+    drf.user_id                                                    AS user_id,
+    drf.product_id                                                 AS product_id,
+    COALESCE(dof.order_no, '')                                     AS order_no,
+    COALESCE(dof._pay_amount, 0)                                   AS order_pay_amount,
+    /* 退款比例(%) = 退款金额 / 订单实付金额 * 100，保留两位小数；实付金额为零或空记为 0 */
+    CASE
+        WHEN COALESCE(dof._pay_amount, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(drf.refund_amount, 0) / dof._pay_amount * 100, 2)
+    END                                                            AS refund_rate,
+    COALESCE(duf.user_name, '')                                    AS user_name,
+    COALESCE(dpf.product_name, '')                                 AS product_name,
+    dst.ticket_id                                                  AS ticket_id,
+    CASE dst.ticket_status
+        WHEN 'PENDING'    THEN '待处理'
+        WHEN 'PROCESSING' THEN '处理中'
+        WHEN 'RESOLVED'   THEN '已解决'
+        WHEN 'CLOSED'     THEN '已关闭'
+        ELSE '其他'
+    END                                                            AS ticket_status_name,
+    COALESCE(dst.handler_name, '')                                 AS handler_name,
+    'N'                                                            AS del_flag,
+    '${P_CYCLE_ID}'                                                AS crt_cycle_id,
+    '${P_CYCLE_ID}'                                                AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP                                              AS dw_last_update_date
+FROM sdref.dwd_refund_f drf
+/* dof(订单事实表)按 order_id 收敛至订单粒度：order_no 取唯一值、pay_amount 取订单实付金额，
+   保证每个 order_id 只出一行，避免订单明细一对多造成退款记录 fan-out */
+LEFT JOIN (
+    SELECT
+        order_id,
+        MAX(order_no)   AS order_no,
+        MAX(pay_amount) AS _pay_amount
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY order_id
+) dof ON drf.order_id = dof.order_id
+/* duf(用户维表) user_id 唯一，直接关联 */
+LEFT JOIN dim.dim_user_f duf
+    ON drf.user_id = duf.user_id
+    AND duf.del_flag = 'N'
+/* dpf(商品维表) product_id 唯一，直接关联 */
+LEFT JOIN dim.dim_product_f dpf
+    ON drf.product_id = dpf.product_id
+    AND dpf.del_flag = 'N'
+/* dst(工单事实表)按 refund_id 收敛：一个退款对应多张工单时取最新一条工单
+   (ORDER BY ticket_id DESC 取 rn=1)，保证每个 refund_id 只出一行 */
+LEFT JOIN (
+    SELECT
+        refund_id,
+        ticket_id,
+        ticket_status,
+        handler_name,
+        ROW_NUMBER() OVER (PARTITION BY refund_id ORDER BY ticket_id DESC) AS _rn
+    FROM sdcs.dwd_service_ticket_f
+    WHERE del_flag = 'N'
+) dst ON drf.refund_id = dst.refund_id AND dst._rn = 1
+WHERE drf.del_flag = 'N';
+——ddl/create_table_dwb_after_sale_center_f.sql——
+/* =====================================================
+   表名: slas.dwb_after_sale_center_f
+   规则: R0001 - 售后服务中心宽表组装
+   分布键: refund_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以退款事实表 dwd_refund_f 为主表，左关联订单、用户、商品、工单四表拼装售后中心宽表， 保持输出粒度=一个售后服务记录；对所有加工类字段做枚举值中文化与派生指标计算， 直取字段透传，审计字段按标准赋值，单条 INSERT 完成，无需物理中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slas.dwb_after_sale_center_f (
+    refund_id           bigint,  /* 退款ID */
+    refund_no           varchar(64),  /* 退款单号 */
+    refund_type_name    varchar(50),  /* 退款类型 */
+    refund_status_name  varchar(50),  /* 退款状态 */
+    apply_time          datetime,  /* 申请时间 */
+    complete_time       datetime,  /* 完成时间 */
+    process_days        int,  /* 处理天数 */
+    refund_amount       decimal(18,2),  /* 退款金额 */
+    refund_reason       varchar(200),  /* 退款原因 */
+    order_id            bigint,  /* 订单ID */
+    user_id             bigint,  /* 用户ID */
+    product_id          bigint,  /* 商品ID */
+    order_no            varchar(64),  /* 订单号 */
+    order_pay_amount    decimal(18,2),  /* 订单实付金额 */
+    refund_rate         decimal(5,2),  /* 退款比例(%) */
+    user_name           varchar(100),  /* 用户姓名 */
+    product_name        varchar(200),  /* 商品名称 */
+    ticket_id           bigint,  /* 工单ID */
+    ticket_status_name  varchar(50),  /* 工单状态 */
+    handler_name        varchar(50),  /* 处理人 */
+    del_flag            NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id        BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id   BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(refund_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slas.dwb_after_sale_center_f IS '售后服务中心宽表';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_id IS '退款ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_no IS '退款单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_type_name IS '退款类型';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_status_name IS '退款状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.apply_time IS '申请时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.complete_time IS '完成时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.process_days IS '处理天数';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_amount IS '退款金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_reason IS '退款原因';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_pay_amount IS '订单实付金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_rate IS '退款比例(%)';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_id IS '工单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_status_name IS '工单状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.handler_name IS '处理人';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/008_dwb_after_sale_center_f</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 24 项：refund_id, refund_no, refund_type_name, refund_status_name, apply_time, complete_time, process_days, refund_amount, refund_reason, order_id, user_id, product_id, order_no, order_pay_amount, refund_rate, user_name, product_name, ticket_id, ticket_status_name, handler_name, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 slas.dwb_after_sale_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 24 项）（源→规则→目标）：
+dwd_refund_f.refund_id --[直接复制]--&gt; refund_id(退款ID)
+dwd_refund_f.refund_no --[直接复制]--&gt; refund_no(退款单号)
+dwd_refund_f.refund_type --[数据加工]--&gt; refund_type_name(退款类型)
+dwd_refund_f.refund_status --[数据加工]--&gt; refund_status_name(退款状态)
+dwd_refund_f.apply_time --[直接复制]--&gt; apply_time(申请时间)
+dwd_refund_f.complete_time --[直接复制]--&gt; complete_time(完成时间)
+（无源声明） --[数据加工]--&gt; process_days(处理天数)
+dwd_refund_f.refund_amount --[直接复制]--&gt; refund_amount(退款金额)
+dwd_refund_f.refund_reason --[直接复制]--&gt; refund_reason(退款原因)
+dwd_refund_f.order_id --[直接复制]--&gt; order_id(订单ID)
+dwd_order_f.order_no --[直接复制]--&gt; order_no(订单号)
+dwd_order_f.pay_amount --[直接复制]--&gt; order_pay_amount(订单实付金额)
+（无源声明） --[数据加工]--&gt; refund_rate(退款比例(%))
+dwd_refund_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dwd_refund_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_service_ticket_f.ticket_id --[直接复制]--&gt; ticket_id(工单ID)
+dwd_service_ticket_f.ticket_status --[数据加工]--&gt; ticket_status_name(工单状态)
+dwd_service_ticket_f.handler_name --[直接复制]--&gt; handler_name(处理人)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>任务：为 slprd.dwb_product_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：商品中心宽表
@@ -2249,7 +3684,7 @@
 映射字段 39 项，来源表 7 张。</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -2469,7 +3904,7 @@
 档案来源：../10_project_deliver/009_dwb_product_center_f</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slprd.dwb_product_center_f，粒度：每行一个商品记录
@@ -2479,7 +3914,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 39 项（源→规则→目标）：
 dim_product_f.product_id --[直接复制]--&gt; product_id(商品ID)
@@ -2523,13 +3958,127 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>任务：为 slprd.dwb_product_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：商品中心宽表
+粒度：每行一个商品记录
+调度：全量调度 / T+1，一天一调
+映射字段 39 项，来源表 7 张。
+本规则：R0001（商品销售汇总中间表），step_type=full，目标表 dwb_product_sales_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   规则号: R0001
+   规则名: 商品销售汇总中间表
+   目标表: slprd.dwb_product_sales_tmp1（中间表）
+   粒度: 多行/商品(订单明细) → 一行/商品(按 product_id 收敛)
+   设计意图: 把订单明细按 product_id 聚合到商品粒度，
+            产出累计销量/累计销售额/购买人数/近30天销量，
+            供 R0003 按 product_id 安全关联宽表，避免主表行数发散。
+   源表: sdord.dwd_order_detail_f (别名 dod)
+   关联安全: GROUP BY product_id 收敛后聚合，product_id 唯一
+   ===================================================== */
+/* 过滤说明:
+   - design_logic 明确为"全量订单"，故不臆造业务状态过滤
+     (源表订单状态字段名/枚举值未在切片中确认，保持全量聚合)。
+   - 仅保留数仓标准软删除过滤(del_flag='N')，属技术层面，
+     不改变业务"全量有效订单"口径。
+   - 源字段假设(切片 source_fields 为空，按 design_logic 推断):
+     qty=销售数量, real_price=实付单价, user_id=买家ID, order_time=下单时间。
+*/
+SELECT
+    dod.product_id AS product_id,
+    COALESCE(SUM(dod.qty), 0) AS total_sales_qty,
+    COALESCE(SUM(dod.real_price * dod.qty), 0) AS total_sales_amount,
+    COUNT(DISTINCT dod.user_id) AS buyer_cnt,
+    COALESCE(
+        SUM(
+            CASE
+                WHEN dod.order_time &gt;= CURRENT_DATE - INTERVAL '30 day'
+                    THEN dod.qty
+                ELSE 0
+            END
+        ), 0
+    ) AS sales_qty_30d,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_detail_f dod
+WHERE COALESCE(dod.del_flag, 'N') = 'N'
+GROUP BY dod.product_id;
+——ddl/create_table_dwb_product_sales_tmp1.sql——
+/* =====================================================
+   表名: slprd.dwb_product_sales_tmp1
+   规则: R0001 - 商品销售汇总中间表
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 把订单明细(多行/商品)按 product_id 聚合到商品粒度，产出销量/销售额/买家数/近30天销量，供 R0003 关联，避免主表行数发散
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_sales_tmp1 (
+    total_sales_qty    int,  /* 累计销量 */
+    total_sales_amount decimal(18,2),  /* 累计销售额 */
+    buyer_cnt          int,  /* 购买人数 */
+    sales_qty_30d      int,  /* 近30天销量 */
+    /* 审计字段 */
+    del_flag           NVARCHAR(1),
+    crt_cycle_id       BIGINT,
+    last_upd_cycle_id  BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_sales_tmp1 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.total_sales_qty IS '累计销量';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.buyer_cnt IS '购买人数';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.sales_qty_30d IS '近30天销量';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_sales_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/009_dwb_product_center_f</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 4 项：total_sales_qty, total_sales_amount, buyer_cnt, sales_qty_30d（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_product_sales_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 4 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; total_sales_qty(累计销量)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; buyer_cnt(购买人数)
+（无源声明） --[数据加工]--&gt; sales_qty_30d(近30天销量)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>任务：为 slusr.dwb_user_profile_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：用户画像宽表
@@ -2538,7 +4087,7 @@
 映射字段 187 项，来源表 4 张。</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -2932,7 +4481,7 @@
 档案来源：../10_project_deliver/010_dwb_user_profile_f</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slusr.dwb_user_profile_f，粒度：每行一个用户画像记录
@@ -2942,7 +4491,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 187 项（源→规则→目标）：
 ods_user_basic_f.user_id --[直接复制]--&gt; user_id(用户ID)
@@ -3029,13 +4578,496 @@
 di…（截断）</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_profile_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户画像宽表
+粒度：每行一个用户画像记录
+调度：全量调度 / T+1，一天一调
+映射字段 187 项，来源表 4 张。
+本规则：R0001（用户画像宽表全量装载），step_type=full，目标表 dwb_user_profile_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 用户画像宽表全量装载
+   目标表: slusr.dwb_user_profile_f
+   主表: ods.ods_user_basic_f (oub) 全量
+   关联:
+     - dim.dim_user_level_d (dul): SCD2 收敛,取当前有效行
+       (is_active=1 且 valid_from&lt;=当前时间&lt;valid_to),保证 level_id 唯一
+     - dim.dim_region_d (drd): 限定 region_level=1(省份层级)收敛,
+       保证 region_code 唯一
+     - dim.dim_user_source_d (dus): source_id 唯一,直接 LEFT JOIN
+   粒度: 无变化 (用户 -&gt; 用户),无聚合
+   说明: 多个 _processed 字段 TS 的 source_fields 与 design_logic 不一致,
+        按 skill 约定以 design_logic 口径为准翻译(详见回报)。
+   ===================================================== */
+SELECT
+    /* ---------- 主表 ods_user_basic_f 基础属性 ---------- */
+    oub.user_id AS user_id,                                                       /* 用户ID */
+    COALESCE(oub.user_name, '') AS user_name,                                     /* 用户姓名 */
+    COALESCE(LEFT(oub.user_phone, 3) || '****' || RIGHT(oub.user_phone, 4), '') AS user_phone_processed,  /* 手机号(脱敏:前3+****+后4) */
+    COALESCE(oub.user_phone_masked, '') AS user_phone_masked,                     /* 手机号(脱敏) */
+    COALESCE(oub.email, '') AS email,                                             /* 电子邮箱 */
+    CASE oub.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_processed,                                                      /* 性别(M男/F女/其它未知) */
+    oub.birthday AS birthday,                                                     /* 出生日期 */
+    COALESCE((DATE_PART('YEAR', CURRENT_DATE) - DATE_PART('YEAR', oub.birthday))::INT, 0) AS age_processed,  /* 年龄(当前年-出生年) */
+    COALESCE(oub.id_card, '') AS id_card,                                         /* 身份证号 */
+    COALESCE(LEFT(oub.id_card_masked, 6) || '********' || RIGHT(oub.id_card_masked, 4), '') AS id_card_masked_processed,  /* 身份证号(脱敏:前6+********+后4) */
+    COALESCE(oub.real_name, '') AS real_name,                                     /* 真实姓名 */
+    COALESCE(oub.nick_name, '') AS nick_name,                                     /* 昵称 */
+    COALESCE(oub.avatar_url, '') AS avatar_url,                                   /* 头像URL */
+    COALESCE(oub.user_status, '') AS user_status,                                 /* 用户状态 */
+    CASE oub.user_status
+        WHEN 'ACTIVE' THEN '正常'
+        WHEN 'INACTIVE' THEN '未激活'
+        WHEN 'BANNED' THEN '封禁'
+        ELSE '未知'
+    END AS user_status_name_processed,                                            /* 用户状态名称(ACTIVE正常/INACTIVE未激活/BANNED封禁/其它未知) */
+    oub.register_time AS register_time,                                           /* 注册时间 */
+    oub.register_time::DATE AS register_date_processed,                           /* 注册日期(取注册时间日期部分) */
+    COALESCE(DATE_PART('HOUR', oub.register_time)::INT, 0) AS register_hour_processed,  /* 注册小时(0~23) */
+    COALESCE(DATE_PART('ISODOW', oub.register_time)::INT, 0) AS register_weekday_processed,  /* 注册星期(1周一~7周日) */
+    oub.last_login_time AS last_login_time,                                       /* 最后登录时间 */
+    oub.last_login_time::DATE AS last_login_date_processed,                       /* 最后登录日期(取最后登录时间日期部分) */
+    COALESCE(oub.login_count, 0) AS login_count,                                  /* 登录次数 */
+    COALESCE(oub.province_code, '') AS province_code,                             /* 省份代码 */
+    COALESCE(oub.province_name, '') AS province_name,                             /* 省份名称 */
+    COALESCE(oub.city_code, '') AS city_code,                                     /* 城市代码 */
+    COALESCE(oub.city_name, '') AS city_name,                                     /* 城市名称 */
+    COALESCE(oub.district_code, '') AS district_code,                             /* 区县代码 */
+    COALESCE(oub.district_name, '') AS district_name,                             /* 区县名称 */
+    COALESCE(oub.address, '') AS address,                                         /* 详细地址 */
+    COALESCE(oub.zip_code, '') AS zip_code,                                       /* 邮政编码 */
+    COALESCE(oub.source_id, 0) AS source_id,                                      /* 来源渠道ID */
+    COALESCE(oub.source_name, '') AS source_name,                                 /* 来源渠道名称 */
+    COALESCE(oub.source_type, '') AS source_type,                                 /* 来源类型 */
+    COALESCE(oub.device_type, '') AS device_type,                                 /* 设备类型 */
+    COALESCE(oub.os_type, '') AS os_type,                                         /* 操作系统 */
+    COALESCE(oub.app_version, '') AS app_version,                                 /* APP版本 */
+    COALESCE(oub.ip_address, '') AS ip_address,                                   /* IP地址 */
+    COALESCE(oub.longitude, 0) AS longitude,                                      /* 经度 */
+    COALESCE(oub.latitude, 0) AS latitude,                                        /* 纬度 */
+    COALESCE(oub.language, '') AS language,                                       /* 语言 */
+    COALESCE(oub.timezone, '') AS timezone,                                       /* 时区 */
+    COALESCE(oub.currency, '') AS currency,                                       /* 货币 */
+    COALESCE(oub.vip_level, 0) AS vip_level,                                      /* VIP等级 */
+    oub.vip_expire_time AS vip_expire_time,                                       /* VIP到期时间 */
+    CASE WHEN oub.vip_expire_time &gt; CURRENT_TIMESTAMP THEN 1 ELSE 0 END AS is_vip_processed,  /* 是否VIP(到期时间晚于当前时间取1,否则0) */
+    COALESCE(oub.member_points, 0) AS member_points,                              /* 会员积分 */
+    COALESCE(oub.balance, 0) AS balance,                                          /* 账户余额 */
+    COALESCE(oub.credit_score, 0) AS credit_score,                                /* 信用分 */
+    COALESCE(oub.risk_level, '') AS risk_level,                                   /* 风险等级 */
+    COALESCE(oub.verify_status, '') AS verify_status,                             /* 认证状态 */
+    /* ---------- dim_user_level_d 等级维度(SCD2 取当前有效行) ---------- */
+    dul.level_id AS level_id,                                                     /* 等级ID */
+    COALESCE(dul.level_name, '') AS level_name,                                   /* 等级名称 */
+    COALESCE(dul.level_code, '') AS level_code,                                   /* 等级代码 */
+    COALESCE(dul.level_rank, 0) AS level_rank,                                    /* 等级排序 */
+    COALESCE(dul.min_points, 0) AS min_points,                                    /* 最小积分 */
+    COALESCE(dul.max_points, 0) AS max_points,                                    /* 最大积分 */
+    COALESCE(dul.level_icon, '') AS level_icon,                                   /* 等级图标 */
+    COALESCE(dul.level_color, '') AS level_color,                                 /* 等级颜色 */
+    COALESCE(dul.upgrade_points, 0) AS upgrade_points,                            /* 升级所需积分 */
+    COALESCE(dul.current_level_points, 0) AS current_level_points,                /* 当前等级积分 */
+    COALESCE(dul.next_level_points, 0) AS next_level_points,                      /* 下一等级积分 */
+    CASE
+        WHEN COALESCE(dul.upgrade_points, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(dul.current_level_points, 0)::NUMERIC * 100.0 / dul.upgrade_points, 2)
+    END AS progress_percentage,                                                   /* 升级进度百分比(当前等级积分/升级所需积分*100,除0保护) */
+    COALESCE(dul.privilege_list, '') AS privilege_list,                           /* 权限列表 */
+    COALESCE(dul.discount_rate, 0) AS discount_rate,                              /* 折扣率 */
+    COALESCE(dul.points_rate, 0) AS points_rate,                                  /* 积分倍率 */
+    COALESCE(dul.free_shipping, 0) AS free_shipping,                              /* 免费配送 */
+    COALESCE(dul.exclusive_products, 0) AS exclusive_products,                    /* 专属商品 */
+    COALESCE(dul.priority_support, 0) AS priority_support,                        /* 优先客服 */
+    COALESCE(dul.birthday_bonus, 0) AS birthday_bonus,                            /* 生日礼金 */
+    COALESCE(dul.monthly_coupon, 0) AS monthly_coupon,                            /* 月度优惠券 */
+    COALESCE(dul.annual_gift, 0) AS annual_gift,                                  /* 年度礼品 */
+    COALESCE(dul.vip_service, 0) AS vip_service,                                  /* VIP服务 */
+    COALESCE(dul.invite_quota, 0) AS invite_quota,                                /* 邀请名额 */
+    COALESCE(dul.max_orders_per_day, 0) AS max_orders_per_day,                    /* 每日最大订单数 */
+    COALESCE(dul.max_return_days, 0) AS max_return_days,                          /* 最大退货天数 */
+    COALESCE(dul.level_benefits, '') AS level_benefits,                           /* 等级权益 */
+    dul.upgrade_time AS upgrade_time,                                             /* 升级时间 */
+    dul.downgrade_time AS downgrade_time,                                         /* 降级时间 */
+    COALESCE(dul.maintain_days, 0) AS maintain_days,                              /* 维持天数 */
+    COALESCE(dul.level_status, '') AS level_status,                               /* 等级状态 */
+    dul.create_time AS create_time,                                               /* 创建时间 */
+    dul.update_time AS update_time,                                               /* 更新时间 */
+    dul.valid_from AS valid_from,                                                 /* 生效开始时间 */
+    dul.valid_to AS valid_to,                                                     /* 生效结束时间 */
+    COALESCE(dul.is_active, 0) AS is_active,                                      /* 是否激活 */
+    COALESCE(dul.level_tier, 0) AS level_tier,                                    /* 等级层级 */
+    COALESCE(dul.level_group, '') AS level_group,                                 /* 等级分组 */
+    COALESCE(dul.level_category, '') AS level_category,                           /* 等级分类 */
+    COALESCE(dul.points_required, 0) AS points_required,                          /* 所需积分 */
+    COALESCE(dul.orders_required, 0) AS orders_required,                          /* 所需订单数 */
+    COALESCE(dul.amount_required, 0) AS amount_required,                          /* 所需金额 */
+    COALESCE(dul.days_required, 0) AS days_required,                              /* 所需天数 */
+    COALESCE(dul.growth_value, 0) AS growth_value,                                /* 成长值 */
+    COALESCE(dul.experience_value, 0) AS experience_value,                        /* 经验值 */
+    COALESCE(dul.contribution_value, 0) AS contribution_value,                    /* 贡献值 */
+    COALESCE(dul.activity_value, 0) AS activity_value,                            /* 活跃值 */
+    COALESCE(dul.loyalty_score, 0) AS loyalty_score,                              /* 忠诚度分数 */
+    COALESCE(dul.engagement_score, 0) AS engagement_score,                        /* 参与度分数 */
+    COALESCE(dul.satisfaction_score, 0) AS satisfaction_score,                    /* 满意度分数 */
+    COALESCE(dul.retention_score, 0) AS retention_score,                          /* 留存率分数 */
+    /* ---------- dim_region_d 地区维度(限定 region_level=1 省份层级) ---------- */
+    COALESCE(drd.region_id, 0) AS region_id,                                      /* 地区ID */
+    COALESCE(drd.region_code, '') AS region_code,                                 /* 地区代码 */
+    COALESCE(drd.region_name, '') AS region_name,                                 /* 地区名称 */
+    COALESCE(drd.parent_id, 0) AS parent_id,                                      /* 父级ID */
+    COALESCE(drd.region_level, 0) AS region_level,                                /* 地区层级 */
+    COALESCE(drd.region_path, '') AS region_path,                                 /* 地区路径 */
+    COALESCE(drd.province_id, 0) AS province_id,                                  /* 省份ID */
+    COALESCE(drd.province_abbr, '') AS province_abbr,                             /* 省份简称 */
+    COALESCE(drd.city_id, 0) AS city_id,                                          /* 城市ID */
+    COALESCE(drd.city_abbr, '') AS city_abbr,                                     /* 城市简称 */
+    COALESCE(drd.district_id, 0) AS district_id,                                  /* 区县ID */
+    COALESCE(drd.district_abbr, '') AS district_abbr,                             /* 区县简称 */
+    COALESCE(drd.street_id, 0) AS street_id,             …（截断）
+——ddl/create_table_dwb_user_profile_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_profile_f
+   规则: R0001 - 用户画像宽表全量装载
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 以 ods.ods_user_basic_f 为主表（一行=一个用户），LEFT JOIN 等级/地区/来源三张维度表 补齐画像属性，行内完成脱敏/翻译/日期拆解/VIP 判定等轻加工，全量覆盖目标宽表所有字段。 关联表数量少、无粒度变化、无聚合，单条 INSERT 即可，无需分段或建中间表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_profile_f (
+    user_id                    bigint,  /* 用户ID */
+    user_name                  varchar(100),  /* 用户姓名 */
+    user_phone_processed       varchar(20),  /* 手机号 */
+    user_phone_masked          varchar(20),  /* 手机号(脱敏) */
+    email                      varchar(100),  /* 电子邮箱 */
+    gender_processed           varchar(10),  /* 性别 */
+    birthday                   date,  /* 出生日期 */
+    age_processed              int,  /* 年龄 */
+    id_card                    varchar(20),  /* 身份证号 */
+    id_card_masked_processed   varchar(20),  /* 身份证号(脱敏) */
+    real_name                  varchar(50),  /* 真实姓名 */
+    nick_name                  varchar(50),  /* 昵称 */
+    avatar_url                 varchar(500),  /* 头像URL */
+    user_status                varchar(20),  /* 用户状态 */
+    user_status_name_processed varchar(20),  /* 用户状态名称 */
+    register_time              timestamp,  /* 注册时间 */
+    register_date_processed    date,  /* 注册日期 */
+    register_hour_processed    int,  /* 注册小时 */
+    register_weekday_processed int,  /* 注册星期 */
+    last_login_time            timestamp,  /* 最后登录时间 */
+    last_login_date_processed  date,  /* 最后登录日期 */
+    login_count                int,  /* 登录次数 */
+    province_code              varchar(20),  /* 省份代码 */
+    province_name              varchar(50),  /* 省份名称 */
+    city_code                  varchar(20),  /* 城市代码 */
+    city_name                  varchar(50),  /* 城市名称 */
+    district_code              varchar(20),  /* 区县代码 */
+    district_name              varchar(50),  /* 区县名称 */
+    address                    varchar(500),  /* 详细地址 */
+    zip_code                   varchar(10),  /* 邮政编码 */
+    source_id                  int,  /* 来源渠道ID */
+    source_name                varchar(50),  /* 来源渠道名称 */
+    source_type                varchar(20),  /* 来源类型 */
+    device_type                varchar(20),  /* 设备类型 */
+    os_type                    varchar(20),  /* 操作系统 */
+    app_version                varchar(20),  /* APP版本 */
+    ip_address                 varchar(50),  /* IP地址 */
+    longitude                  decimal(10,6),  /* 经度 */
+    latitude                   decimal(10,6),  /* 纬度 */
+    language                   varchar(20),  /* 语言 */
+    timezone                   varchar(50),  /* 时区 */
+    currency                   varchar(10),  /* 货币 */
+    vip_level                  int,  /* VIP等级 */
+    vip_expire_time            timestamp,  /* VIP到期时间 */
+    is_vip_processed           int,  /* 是否VIP */
+    member_points              int,  /* 会员积分 */
+    balance                    decimal(18,2),  /* 账户余额 */
+    credit_score               int,  /* 信用分 */
+    risk_level                 varchar(20),  /* 风险等级 */
+    verify_status              varchar(20),  /* 认证状态 */
+    level_id                   int,  /* 等级ID */
+    level_name                 varchar(50),  /* 等级名称 */
+    level_code                 varchar(20),  /* 等级代码 */
+    level_rank                 int,  /* 等级排序 */
+    min_points                 int,  /* 最小积分 */
+    max_points                 int,  /* 最大积分 */
+    level_icon                 varchar(500),  /* 等级图标 */
+    level_color                varchar(20),  /* 等级颜色 */
+    upgrade_points             int,  /* 升级所需积分 */
+    current_level_points       int,  /* 当前等级积分 */
+    next_level_points          int,  /* 下一等级积分 */
+    progress_percentage        decimal(5,2),  /* 升级进度百分比 */
+    privilege_list             varchar(1000),  /* 权限列表 */
+    discount_rate              decimal(5,2),  /* 折扣率 */
+    points_rate                decimal(5,2),  /* 积分倍率 */
+    free_shipping              int,  /* 免费配送 */
+    exclusive_products         int,  /* 专属商品 */
+    priority_support           int,  /* 优先客服 */
+    birthday_bonus             int,  /* 生日礼金 */
+    monthly_coupon             int,  /* 月度优惠券 */
+    annual_gift                int,  /* 年度礼品 */
+    vip_service                int,  /* VIP服务 */
+    invite_quota               int,  /* 邀请名额 */
+    max_orders_per_day         int,  /* 每日最大订单数 */
+    max_return_days            int,  /* 最大退货天数 */
+    level_benefits             varchar(1000),  /* 等级权益 */
+    upgrade_time               timestamp,  /* 升级时间 */
+    downgrade_time             timestamp,  /* 降级时间 */
+    maintain_days              int,  /* 维持天数 */
+    level_status               varchar(20),  /* 等级状态 */
+    create_time                timestamp,  /* 创建时间 */
+    update_time                timestamp,  /* 更新时间 */
+    valid_from                 timestamp,  /* 生效开始时间 */
+    valid_to                   timestamp,  /* 生效结束时间 */
+    is_active                  int,  /* 是否激活 */
+    level_tier                 int,  /* 等级层级 */
+    level_group                varchar(50),  /* 等级分组 */
+    level_category             varchar(50),  /* 等级分类 */
+    points_required            int,  /* 所需积分 */
+    orders_required            int,  /* 所需订单数 */
+    amount_required            decimal(18,2),  /* 所需金额 */
+    days_required              int,  /* 所需天数 */
+    growth_value               int,  /* 成长值 */
+    experience_value           int,  /* 经验值 */
+    contribution_value         int,  /* 贡献值 */
+    activity_value             int,  /* 活跃值 */
+    loyalty_score              decimal(5,2),  /* 忠诚度分数 */
+    engagement_score           decimal(5,2),  /* 参与度分数 */
+    satisfaction_score         decimal(5,2),  /* 满意度分数 */
+    retention_score            decimal(5,2),  /* 留存率分数 */
+    region_id                  int,  /* 地区ID */
+    region_code                varchar(20),  /* 地区代码 */
+    region_name                varchar(100),  /* 地区名称 */
+    parent_id                  int,  /* 父级ID */
+    region_level               int,  /* 地区层级 */
+    region_path                varchar(500),  /* 地区路径 */
+    province_id                int,  /* 省份ID */
+    province_abbr              varchar(20),  /* 省份简称 */
+    city_id                    int,  /* 城市ID */
+    city_abbr                  varchar(20),  /* 城市简称 */
+    district_id                int,  /* 区县ID */
+    district_abbr              varchar(20),  /* 区县简称 */
+    street_id                  int,  /* 街道ID */
+    street_code                varchar(20),  /* 街道代码 */
+    street_name                varchar(50),  /* 街道名称 */
+    center_longitude           decimal(10,6),  /* 中心经度 */
+    center_latitude            decimal(10,6),  /* 中心纬度 */
+    area_size                  decimal(18,2),  /* 区域面积 */
+    population                 int,  /* 人口数量 */
+    gdp                        decimal(18,2),  /* GDP */
+    gdp_per_capita             decimal(18,2),  /* 人均GDP */
+    climate_type               varchar(50),  /* 气候类型 */
+    economy_level              varchar(50),  /* 经济水平 */
+    development_level          varchar(50),  /* 发展水平 */
+    urban_rate                 decimal(5,2),  /* 城镇化率 */
+    region_type                varchar(50),  /* 地区类型 */
+    is_coastal                 int,  /* 是否沿海 */
+    is_border                  int,  /* 是否边境 */
+    is_capital                 int,  /* 是否省会 */
+    is_special                 int,  /* 是否特区 */
+    postal_code_prefix         varchar(10),  /* 邮编前缀 */
+    phone_area_code            varchar(20),  /* 电话区号 */
+    car_plate_prefix           varchar(10),  /* 车牌前缀 */
+    airport_code               varchar(10),  /* 机场代码 */
+    railway_station_code       varchar(20),  /* 火车站代码 */
+    port_code                  varchar(20),  /* 港口代码 */
+    weather_station_code       varchar(20),  /* 气象站代码 */
+    customs_code               varchar(20),  /* 海关代码 */
+    statistical_code           varchar(20),  /* 统计代码 */
+    iso_code                   varchar(20),  /* ISO代码 */
+    source_code                varchar(50),  /* 来源代码 */
+    source_category            varchar(50),  /* 来源分类 */
+    channel_id                 int,  /* 渠道ID */
+    channel_code               varchar(50),  /* 渠道代码 */
+    channel_name               varchar(100),  /* 渠道名称 */
+    channel_type               varchar(50),  /* 渠道类型 */
+    channel_category           varchar(50),  /* 渠道分类 */
+    campaign_id                int,  /* 活动ID */
+    campaign_code              varchar(50),  /* 活动代码 */
+    campaign_name              varchar(100),  /* 活动名称 */
+    campaign_type              varchar(50),  /* 活动类型 */
+    medium_id                  int,  /* 媒介ID */
+    medium_code                varchar(50),  /* 媒介代码 */
+    medium_name                varchar(100),  /* 媒介名称 */
+    medium_type                varchar(50),  /* 媒介类型 */
+    term_id                    int,  /* 搜索词ID */
+    term_keyword               varchar(200),  /* 搜索关键词 */
+    content_id                 int,  /* 内容ID */
+    content_name               varchar(200),  /* 内容名称 */
+    referral_url               varchar(500),  /* 来源URL */
+    landing_page               varchar(500),  /* 落地页 */
+    utm_source                 varchar(100),  /* UTM来源 */
+    utm_medium                 varchar(100),  /* UTM媒介 */
+    utm_campaign               varchar(100),  /* UTM活动 */
+    utm_term                   varchar(100),  /* UTM关键词 */
+    utm_content                varchar(100),  /* UTM内容 */
+    cost_per_acquisition       decimal(18,2),  /* 获客成本 */
+    conversion_rate            decimal(5,2),  /* 转化率 */
+    quality_score              decimal(5,2),  /* 质量分数 */
+    retention_rate_7d          decimal(5,2),  /* 7日留存率 */
+    retention_rate_30d         decimal(5,2),  /* 30日留存率 */
+    lifetime_value             decimal(18,2),  /* 生命周期价值 */
+    first_order_amount         decimal(18,2),  /* 首单金额 */
+    first_order_days           int,  /* 首单天数 */
+    register_device            varchar(50),  /* 注册设备 */
+    register_os                varchar(50),  /* 注册系统 */
+    register_browser           varchar(50),  /* 注册浏览器 */
+    register_network           varchar(50),  /* 注册网络 */
+    register_location          varchar(200),  /* 注册地点 */
+    attribution_model          varchar(50),  /* 归因模型 */
+    lookback_days              int,  /* 回溯天数 */
+    priority                   int,  /* 优先级 */
+    is_paid                    int,  /* 是否付费 */
+    del_flag                   NVARCHAR(1),  /* 删除标识 */
+    crt_cycle_id               BIGINT,  /* 创建批次ID */
+    last_upd_cycle_id          BIGINT,  /* 最后更新批次ID */
+    dw_last_update_date        TIMESTAMP(0) WITHOUT TIME ZONE  /* 数仓最后更新时间 */
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_profile_f IS '用户画像宽表';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_processed IS '手机号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.email IS '电子邮箱';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.gender_processed IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.age_processed IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card IS '身份证号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card_masked_processed IS '身份证号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.real_name IS '真实姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.nick_name IS '昵称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.avatar_url IS '头像URL';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status_name_processed IS '用户状态名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_date_processed IS '注册日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_hour_processed IS '注册小时';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_weekday_proce…（截断）
+档案来源：../10_project_deliver/010_dwb_user_profile_f</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 187 项：user_id, user_name, user_phone_processed, user_phone_masked, email, gender_processed, birthday, age_processed, id_card, id_card_masked_processed, real_name, nick_name, avatar_url, user_status, user_status_name_processed, register_time, register_date_processed, register_hour_processed, register_weekday_processed, last_login_time, last_login_date_processed, login_count, province_code, province_name, city_code, city_name, district_code, district_name, address, zip_code, source_id, source_name, source_type, device_type, os_type, app_version, ip_address, longitude, latitude, language, timezone, currency, vip_level, vip_expire_time, is_vip_processed, member_points, balance, credit_score, risk_level, verify_status, level_id, level_name, level_code, level_rank, min_points, max_points, level_icon, level_color, upgrade_points, current_level_points, next_level_points, progress_percentage, privilege_list, discount_rate, points_rate, free_shipping, exclusive_products, priority_support, birthday_bonus, monthly_coupon, annual_gift, vip_service, invite_quota, max_orders_per_day, max_return_days, level_benefits, upgrade_time, downgrade_time, maintain_days, level_status, create_time, update_time, valid_from, valid_to, is_active, level_tier, level_group, level_category, points_required, orders_required, amount_required, days_required, growth_value, experience_value, contribution_value, activity_value, loyalty_score, engagement_score, satisfaction_score, retention_score, region_id, region_code, region_name, parent_id, region_level, region_path, province_id, province_abbr, city_id, city_abbr, district_id, district_abbr, street_id, street_code, street_name, center_longitude, center_latitude, area_size, population, gdp, gdp_per_capita, climate_type, economy_level, development_level, urban_rate, region_type, is_coastal, is_border, is_capital, is_special, postal_code_prefix, phone_area_code, car_plate_prefix, airport_code, railway_station_code, port_code, weather_station_code, customs_code, statistical_code, iso_code, source_code, source_category, channel_id, channel_code, channel_name, channel_type, channel_category, campaign_id, campaign_code, campaign_name, campaign_type, medium_id, medium_code, medium_name, medium_type, term_id, term_keyword, content_id, content_name, referral_url, landing_page, utm_source, utm_medium, utm_campaign, utm_term, utm_content, cost_per_acquisition, conversion_rate, quality_score, retention_rate_7d, retention_rate_30d, lifetime_value, first_order_amount, first_order_days, register_device, register_os, register_browser, register_network, register_location, attribution_model, lookback_days, priority, is_paid, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_profile_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 187 项）（源→规则→目标）：
+ods_user_basic_f.user_id --[直接复制]--&gt; user_id(用户ID)
+ods_user_basic_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+ods_user_basic_f.user_phone --[数据加工]--&gt; user_phone_processed(手机号)
+ods_user_basic_f.user_phone_masked --[直接复制]--&gt; user_phone_masked(手机号(脱敏))
+ods_user_basic_f.email --[直接复制]--&gt; email(电子邮箱)
+ods_user_basic_f.gender --[数据加工]--&gt; gender_processed(性别)
+ods_user_basic_f.birthday --[直接复制]--&gt; birthday(出生日期)
+ods_user_basic_f.age --[数据加工]--&gt; age_processed(年龄)
+ods_user_basic_f.id_card --[直接复制]--&gt; id_card(身份证号)
+ods_user_basic_f.id_card_masked --[数据加工]--&gt; id_card_masked_processed(身份证号(脱敏))
+ods_user_basic_f.real_name --[直接复制]--&gt; real_name(真实姓名)
+ods_user_basic_f.nick_name --[直接复制]--&gt; nick_name(昵称)
+ods_user_basic_f.avatar_url --[直接复制]--&gt; avatar_url(头像URL)
+ods_user_basic_f.user_status --[直接复制]--&gt; user_status(用户状态)
+ods_user_basic_f.user_status_name --[数据加工]--&gt; user_status_name_processed(用户状态名称)
+ods_user_basic_f.register_time --[直接复制]--&gt; register_time(注册时间)
+ods_user_basic_f.register_date --[数据加工]--&gt; register_date_processed(注册日期)
+ods_user_basic_f.register_hour --[数据加工]--&gt; register_hour_processed(注册小时)
+ods_user_basic_f.register_weekday --[数据加工]--&gt; register_weekday_processed(注册星期)
+ods_user_basic_f.last_login_time --[直接复制]--&gt; last_login_time(最后登录时间)
+ods_user_basic_f.last_login_date --[数据加工]--&gt; last_login_date_processed(最后登录日期)
+ods_user_basic_f.login_count --[直接复制]--&gt; login_count(登录次数)
+ods_user_basic_f.province_code --[直接复制]--&gt; province_code(省份代码)
+ods_user_basic_f.province_name --[直接复制]--&gt; province_name(省份名称)
+ods_user_basic_f.city_code --[直接复制]--&gt; city_code(城市代码)
+ods_user_basic_f.city_name --[直接复制]--&gt; city_name(城市名称)
+ods_user_basic_f.district_code --[直接复制]--&gt; district_code(区县代码)
+ods_user_basic_f.district_name --[直接复制]--&gt; district_name(区县名称)
+ods_user_basic_f.address --[直接复制]--&gt; address(详细地址)
+ods_user_basic_f.zip_code --[直接复制]--&gt; zip_code(邮政编码)
+ods_user_basic_f.source_id --[直接复制]--&gt; source_id(来源渠道ID)
+ods_user_basic_f.source_name --[直接复制]--&gt; source_name(来源渠道名称)
+ods_user_basic_f.source_type --[直接复制]--&gt; source_type(来源类型)
+ods_user_basic_f.device_type --[直接复制]--&gt; device_type(设备类型)
+ods_user_basic_f.os_type --[直接复制]--&gt; os_type(操作系统)
+ods_user_basic_f.app_version --[直接复制]--&gt; app_version(APP版本)
+ods_user_basic_f.ip_address --[直接复制]--&gt; ip_address(IP地址)
+ods_user_basic_f.longitude --[直接复制]--&gt; longitude(经度)
+ods_user_basic_f.latitude --[直接复制]--&gt; latitude(纬度)
+ods_user_basic_f.language --[直接复制]--&gt; language(语言)
+ods_user_basic_f.timezone --[直接复制]--&gt; timezone(时区)
+ods_user_basic_f.currency --[直接复制]--&gt; currency(货币)
+ods_user_basic_f.vip_level --[直接复制]--&gt; vip_level(VIP等级)
+ods_user_basic_f.vip_expire_time --[直接复制]--&gt; vip_expire_time(VIP到期时间)
+ods_user_basic_f.is_vip --[数据加工]--&gt; is_vip_processed(是否VIP)
+ods_user_basic_f.member_points --[直接复制]--&gt; member_points(会员积分)
+ods_user_basic_f.balance --[直接复制]--&gt; balance(账户余额)
+ods_user_basic_f.credit_score --[直接复制]--&gt; credit_score(信用分)
+ods_user_basic_f.risk_level --[直接复制]--&gt; risk_level(风险等级)
+ods_user_basic_f.verify_status --[直接复制]--&gt; verify_status(认证状态)
+dim_user_level_d.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_d.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_d.level_code --[直接复制]--&gt; level_code(等级代码)
+dim_user_level_d.level_rank --[直接复制]--&gt; level_rank(等级排序)
+dim_user_level_d.min_points --[直接复制]--&gt; min_points(最小积分)
+dim_user_level_d.max_points --[直接复制]--&gt; max_points(最大积分)
+dim_user_level_d.level_icon --[直接复制]--&gt; level_icon(等级图标)
+dim_user_level_d.level_color --[直接复制]--&gt; level_color(等级颜色)
+dim_user_level_d.upgrade_points --[直接复制]--&gt; upgrade_points(升级所需积分)
+dim_user_level_d.current_level_points --[直接复制]--&gt; current_level_points(当前等级积分)
+dim_user_level_d.next_level_points --[直接复制]--&gt; next_level_points(下一等级积分)
+dim_user_level_d.progress_percentage --[数据加工]--&gt; progress_percentage(升级进度百分比)
+dim_user_level_d.privilege_list --[直接复制]--&gt; privilege_list(权限列表)
+dim_user_level_d.discount_rate --[直接复制]--&gt; discount_rate(折扣率)
+dim_user_level_d.points_rate --[直接复制]--&gt; points_rate(积分倍率)
+dim_user_level_d.free_shipping --[直接复制]--&gt; free_shipping(免费配送)
+dim_user_level_d.exclusive_products --[直接复制]--&gt; exclusive_products(专属商品)
+dim_user_level_d.priority_support --[直接复制]--&gt; priority_support(优先客服)
+dim_user_level_d.birthday_bonus --[直接复制]--&gt; birthday_bonus(生日礼金)
+dim_user_level_d.monthly_coupon --[直接复制]--&gt; monthly_coupon(月度优惠券)
+dim_user_level_d.annual_gift --[直接复制]--&gt; annual_gift(年度礼品)
+dim_user_level_d.vip_service --[直接复制]--&gt; vip_service(VIP服务)
+dim_user_level_d.invite_quota --[直接复制]--&gt; invite_quota(邀请名额)
+dim_user_level_d.max_orders_per_day --[直接复制]--&gt; max_orders_per_day(每日最大订单数)
+dim_user_level_d.max_return_days --[直接复制]--&gt; max_return_days(最大退货天数)
+dim_user_level_d.level_benefits --[直接复制]--&gt; level_benefits(等级权益)
+dim_user_level_d.upgrade_time --[直接复制]--&gt; upgrade_time(升级时间)
+dim_user_level_d.downgrade_time --[直接复制]--&gt; downgrade_time(降级时间)
+dim_user_level_d.maintain_days --[直接复制]--&gt; maintain_days(维持天数)
+dim_user_level_d.level_status --[直接复制]--&gt; level_status(等级状态)
+dim_user_level_d.create_time --[直接复制]--&gt; create_time(创建时…（截断）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>任务：为 slmar.dwb_marketing_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：营销中心宽表
@@ -3044,7 +5076,7 @@
 映射字段 29 项，来源表 5 张。</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -3249,7 +5281,7 @@
 档案来源：../10_project_deliver/011_dwb_marketing_center_f</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slmar.dwb_marketing_center_f，粒度：每行一个营销记录
@@ -3259,7 +5291,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 29 项（源→规则→目标）：
 dwd_activity_f.activity_id --[直接复制]--&gt; activity_id(活动ID)
@@ -3293,13 +5325,164 @@
 （无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>任务：为 slmar.dwb_marketing_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：营销中心宽表
+粒度：每行一个营销记录
+调度：全量调度 / T+1，一天一调
+映射字段 29 项，来源表 5 张。
+本规则：R0001（活动订单指标中间表），step_type=full，目标表 dwb_marketing_order_tmp——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 活动订单指标中间表
+   目标表: slmar.dwb_marketing_order_tmp
+   源表:   sdord.dwd_order_f (dof)
+   设计意图: 将订单明细事实表按 activity_id 聚合收口到活动粒度，
+             产出订单域核心指标（订单数/GMV/参与人数/优惠金额/新客占比），
+             为最终宽表（R0002）提供订单指标输入。
+   粒度变化: 订单明细（多行）→ 活动（一行），GROUP BY activity_id
+   过滤口径: order_status NOT IN ('CANCELLED','DELETED')，仅计入有效订单
+   ===================================================== */
+/* ⚠️ new_user_rate 语义待人工确认（项目红线：语义判断不自主，coder 不拍板口径）
+   -----------------------------------------------------------------------
+   design_logic 原口径:
+     "活动期间新用户订单数 / 总订单数 × 100"
+     "新用户 = 用户全表首次下单时间落在【活动起止时间】(start_time~end_time) 内"
+   -----------------------------------------------------------------------
+   实现障碍:
+     R0001 源表 dwd_order_f 仅含订单明细，不含活动起止时间(start_time/end_time)，
+     无法按原口径严格判定"新用户"。
+   -----------------------------------------------------------------------
+   本规则采用的【订单表内自洽近似口径】(可执行实现，需人工确认后定案):
+     1. 取每个用户在全表有效订单中的【首单活动】(最早有效订单所在的 activity_id)；
+     2. 若某用户的首单活动 == 当前活动，则该用户在此活动产生的所有订单计为"新客订单"；
+     3. new_user_rate = 新客订单数 / 活动总有效订单数 × 100，分母为 0 返回 NULL。
+   -----------------------------------------------------------------------
+   字段假设(待确认):
+     - 首单判定排序字段: create_time（订单创建时间）。若源表实际字段名不同需调整。
+     - 首单时间兜底: COALESCE(create_time, pay_time)。
+   -----------------------------------------------------------------------
+   若需严格按活动起止时间判定新客，应在 R0002 关联活动维表后重新计算此字段。
+*/
+SELECT
+    dof.activity_id AS activity_id,
+    COUNT(1) AS order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS gmv_amount,
+    COUNT(DISTINCT dof.user_id) AS participant_cnt,
+    COALESCE(SUM(dof.discount_amount), 0) AS total_discount_amount,
+    CASE
+        WHEN COUNT(1) = 0 THEN NULL
+        ELSE ROUND(
+            COUNT(
+                CASE WHEN ufa._first_activity_id IS NOT NULL
+                      AND ufa._first_activity_id = dof.activity_id
+                     THEN 1 END
+            ) * 100.0 / COUNT(1),
+            2
+        )
+    END AS new_user_rate,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+LEFT JOIN (
+    /* 每个有效订单用户的全表首单活动（rn=1 即该用户最早有效订单所在活动） */
+    SELECT
+        _user_id,
+        _first_activity_id
+    FROM (
+        SELECT
+            user_id AS _user_id,
+            activity_id AS _first_activity_id,
+            ROW_NUMBER() OVER (
+                PARTITION BY user_id
+                ORDER BY COALESCE(create_time, pay_time) ASC
+            ) AS _rn
+        FROM sdord.dwd_order_f
+        WHERE order_status NOT IN ('CANCELLED', 'DELETED')
+          AND user_id IS NOT NULL
+    ) _x
+    WHERE _rn = 1
+) ufa ON dof.user_id = ufa._user_id
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.activity_id;
+——ddl/create_table_dwb_marketing_order_tmp.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_order_tmp
+   规则: R0001 - 活动订单指标中间表
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 将订单明细事实表按活动ID聚合收口到活动粒度，产出订单域核心指标（订单数/GMV/参与人数/优惠金额/新客占比），为最终宽表提供订单指标输入
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_order_tmp (
+    order_cnt             int,  /* 活动订单数 */
+    gmv_amount            decimal(18,2),  /* 活动GMV */
+    participant_cnt       int,  /* 参与人数 */
+    total_discount_amount decimal(18,2),  /* 活动优惠金额 */
+    new_user_rate         decimal(5,2),  /* 新客占比(%) */
+    /* 审计字段 */
+    del_flag              NVARCHAR(1),
+    crt_cycle_id          BIGINT,
+    last_upd_cycle_id     BIGINT,
+    dw_last_update_date   TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_order_tmp IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.order_cnt IS '活动订单数';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.gmv_amount IS '活动GMV';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.participant_cnt IS '参与人数';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.total_discount_amount IS '活动优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.new_user_rate IS '新客占比(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_order_tmp.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/011_dwb_marketing_center_f</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 5 项：order_cnt, gmv_amount, participant_cnt, total_discount_amount, new_user_rate（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_marketing_order_tmp 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 5 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; order_cnt(活动订单数)
+（无源声明） --[数据加工]--&gt; gmv_amount(活动GMV)
+（无源声明） --[数据加工]--&gt; participant_cnt(参与人数)
+（无源声明） --[数据加工]--&gt; total_discount_amount(活动优惠金额)
+（无源声明） --[数据加工]--&gt; new_user_rate(新客占比(%))</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>任务：为 slord.dwb_order_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
 表说明：订单中心宽表
@@ -3308,7 +5491,7 @@
 映射字段 150 项，来源表 18 张。</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>产物内容（真实运行档案，文件原文）：
 ——设计概述（ts.md §1 概述）——
@@ -3807,7 +5990,7 @@
 档案来源：../10_project_deliver/012_dwb_order_center_f</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>任务完成标准（自 RS 派生，逐项可核验）：
 - 目标表 slord.dwb_order_center_f，粒度：每行一个订单
@@ -3817,7 +6000,7 @@
 - 调度方案：全量调度</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>输入材料：mapping 字段映射 150 项（源→规则→目标）：
 dwd_order_f.order_id --[直接复制]--&gt; order_id(订单ID)
@@ -3911,10 +6094,6585 @@
 dwd_order_f.district_code --[直接复制]--&gt; r…（截断）</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>任务：为 slord.dwb_order_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单中心宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 150 项，来源表 18 张。
+本规则：R0001（用户画像聚合），step_type=full，目标表 dwb_order_center_user_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>——select/R0001_select.sql——
+/* =====================================================
+   R0001: 用户画像聚合（收口所有按 user_id 聚合的用户级指标）
+   目标表: slord.dwb_order_center_user_tmp1（中间表，一行=一个用户）
+   来源表:
+     - sdord.dwd_order_f       (dof)  订单事实，过滤 order_status NOT IN ('CANCELLED','DELETED')
+     - sdpay.dwd_payment_f     (dpf)  支付事实，过滤 pay_status='SUCCESS'
+     - sdmar.dwd_coupon_use_f  (dcu)  优惠券使用，过滤 use_status='USED'
+     - sdref.dwd_refund_f      (drf17)退款事实，过滤 refund_status='SUCCESS'
+   关联安全: 4 个源表各自 GROUP BY user_id 收敛后聚合天然唯一，再 LEFT JOIN 组装
+   ===================================================== */
+WITH
+/* CTE 1: 订单基础聚合（按用户收敛） */
+order_agg AS (
+    SELECT
+        dof.user_id                                                    AS user_id,
+        MIN(dof.order_time)                                            AS first_order_time,
+        MAX(dof.order_time)                                            AS last_order_time,
+        COUNT(1)                                                       AS history_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0)                               AS history_pay_amount,
+        COALESCE(SUM(dof.discount_amount), 0)                          AS history_discount_amount
+    FROM sdord.dwd_order_f dof
+    WHERE COALESCE(dof.del_flag, 'N') = 'N'
+      AND dof.order_status NOT IN ('CANCELLED', 'DELETED')
+    GROUP BY dof.user_id
+),
+/* CTE 2: 在订单聚合基础上计算 RFM 三项分值（NTILE 5 分位） */
+order_rfm AS (
+    SELECT
+        oa.user_id                                                    AS user_id,
+        oa.first_order_time                                           AS first_order_time,
+        oa.last_order_time                                            AS last_order_time,
+        oa.history_order_cnt                                          AS history_order_cnt,
+        oa.history_pay_amount                                         AS history_pay_amount,
+        oa.history_discount_amount                                    AS history_discount_amount,
+        NTILE(5) OVER (ORDER BY oa.last_order_time ASC)               AS r_score,  /* 越近分越高 */
+        NTILE(5) OVER (ORDER BY oa.history_order_cnt ASC)             AS f_score,  /* 越多分越高 */
+        NTILE(5) OVER (ORDER BY oa.history_pay_amount ASC)            AS m_score   /* 越大分越高 */
+    FROM order_agg oa
+),
+/* CTE 3: 用户参与各活动类型的订单数 */
+activity_cnt AS (
+    SELECT
+        dof.user_id                                                    AS user_id,
+        dof.activity_type                                              AS activity_type,
+        COUNT(1)                                                       AS act_order_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE COALESCE(dof.del_flag, 'N') = 'N'
+      AND dof.order_status NOT IN ('CANCELLED', 'DELETED')
+      AND dof.activity_type IS NOT NULL
+    GROUP BY dof.user_id, dof.activity_type
+),
+/* CTE 4: 取每个用户参与订单数最多的活动类型（ROW_NUMBER rn=1） */
+activity_top AS (
+    SELECT
+        ac.user_id                                                                   AS user_id,
+        ac.activity_type                                                             AS activity_type,
+        ROW_NUMBER() OVER (PARTITION BY ac.user_id
+                           ORDER BY ac.act_order_cnt DESC, ac.activity_type ASC)    AS rn
+    FROM activity_cnt ac
+),
+/* CTE 5: 用户各支付方式成功支付次数 */
+payment_cnt AS (
+    SELECT
+        dpf.user_id                                                   AS user_id,
+        dpf.pay_method                                                AS pay_method,
+        COUNT(1)                                                      AS pay_cnt
+    FROM sdpay.dwd_payment_f dpf
+    WHERE COALESCE(dpf.del_flag, 'N') = 'N'
+      AND dpf.pay_status = 'SUCCESS'
+    GROUP BY dpf.user_id, dpf.pay_method
+),
+/* CTE 6: 取每个用户使用频次最高的支付方式（ROW_NUMBER rn=1） */
+payment_top AS (
+    SELECT
+        pc.user_id                                                                AS user_id,
+        pc.pay_method                                                             AS pay_method,
+        ROW_NUMBER() OVER (PARTITION BY pc.user_id
+                           ORDER BY pc.pay_cnt DESC, pc.pay_method ASC)         AS rn
+    FROM payment_cnt pc
+),
+/* CTE 7: 用户已使用优惠券去重计数 */
+coupon_agg AS (
+    SELECT
+        dcu.user_id                                 AS user_id,
+        COUNT(DISTINCT dcu.coupon_id)               AS user_coupon_used_cnt
+    FROM sdmar.dwd_coupon_use_f dcu
+    WHERE COALESCE(dcu.del_flag, 'N') = 'N'
+      AND dcu.use_status = 'USED'
+    GROUP BY dcu.user_id
+),
+/* CTE 8: 用户历史成功退款次数 */
+refund_agg AS (
+    SELECT
+        drf17.user_id                               AS user_id,
+        COUNT(1)                                    AS user_refund_cnt
+    FROM sdref.dwd_refund_f drf17
+    WHERE COALESCE(drf17.del_flag, 'N') = 'N'
+      AND drf17.refund_status = 'SUCCESS'
+    GROUP BY drf17.user_id
+)
+/* 最终组装：以 order_rfm 为主表，LEFT JOIN 各源收敛后的用户级结果 */
+SELECT
+    orf.user_id                                                                      AS user_id,
+    orf.first_order_time                                                             AS first_order_time,
+    orf.last_order_time                                                              AS last_order_time,
+    COALESCE(orf.history_order_cnt, 0)                                               AS history_order_cnt,
+    COALESCE(orf.history_pay_amount, 0)                                              AS history_pay_amount,
+    COALESCE(orf.history_discount_amount, 0)                                         AS history_discount_amount,
+    CASE
+        WHEN COALESCE(orf.history_order_cnt, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(orf.history_pay_amount, 0) / orf.history_order_cnt, 2)
+    END                                                                              AS avg_order_amount,
+    (orf.r_score::TEXT || orf.f_score::TEXT || orf.m_score::TEXT)                     AS rfm_segment,
+    CASE
+        WHEN COALESCE(orf.history_order_cnt, 0) &gt;= 2 THEN 'Y'
+        ELSE 'N'
+    END                                                                              AS is_repeat_user,
+    COALESCE(ptp.pay_method, '')                                                     AS fav_pay_method,
+    COALESCE(ca.user_coupon_used_cnt, 0)                                             AS user_coupon_used_cnt,
+    COALESCE(ra.user_refund_cnt, 0)                                                  AS user_refund_cnt,
+    COALESCE(atp.activity_type, '')                                                  AS user_fav_activity_type,
+    'N'                                                                              AS del_flag,
+    '${P_CYCLE_ID}'                                                                  AS crt_cycle_id,
+    '${P_CYCLE_ID}'                                                                  AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP                                                                AS dw_last_update_date
+FROM order_rfm orf
+LEFT JOIN activity_top atp ON orf.user_id = atp.user_id AND atp.rn = 1
+LEFT JOIN payment_top  ptp ON orf.user_id = ptp.user_id AND ptp.rn = 1
+LEFT JOIN coupon_agg   ca  ON orf.user_id = ca.user_id
+LEFT JOIN refund_agg   ra  ON orf.user_id = ra.user_id;
+——ddl/create_table_dwb_order_center_user_tmp1.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_user_tmp1
+   规则: R0001 - 用户画像聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-02
+   说明: 收口所有按 user_id 聚合的用户级指标（历史订单统计、消费金额、RFM 分层、 常用支付方式、优惠券使用、退款次数、偏好活动类型等），避免在主 INSERT 中 混入聚合后关联逻辑。中间表粒度=一个用户一行，以 user_id 为关联键供主规则 JOIN。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_user_tmp1 (
+    first_order_time        datetime,  /* 首次下单时间 */
+    last_order_time         datetime,  /* 最近下单时间 */
+    history_order_cnt       int,  /* 历史订单数 */
+    history_pay_amount      decimal(18,2),  /* 历史消费金额 */
+    history_discount_amount decimal(18,2),  /* 历史优惠金额 */
+    avg_order_amount        decimal(18,2),  /* 平均客单价 */
+    rfm_segment             varchar(20),  /* 用户RFM分层 */
+    is_repeat_user          varchar(1),  /* 是否复购用户 */
+    fav_pay_method          varchar(20),  /* 用户常用支付方式 */
+    user_coupon_used_cnt    int,  /* 用户优惠券使用次数 */
+    user_refund_cnt         int,  /* 用户历史退款次数 */
+    user_fav_activity_type  varchar(50),  /* 用户偏好活动类型 */
+    /* 审计字段 */
+    del_flag                NVARCHAR(1),
+    crt_cycle_id            BIGINT,
+    last_upd_cycle_id       BIGINT,
+    dw_last_update_date     TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_user_tmp1 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.history_discount_amount IS '历史优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.rfm_segment IS '用户RFM分层';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.is_repeat_user IS '是否复购用户';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.fav_pay_method IS '用户常用支付方式';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_coupon_used_cnt IS '用户优惠券使用次数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_refund_cnt IS '用户历史退款次数';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.user_fav_activity_type IS '用户偏好活动类型';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_user_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/012_dwb_order_center_f</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 12 项：first_order_time, last_order_time, history_order_cnt, history_pay_amount, history_discount_amount, avg_order_amount, rfm_segment, is_repeat_user, fav_pay_method, user_coupon_used_cnt, user_refund_cnt, user_fav_activity_type（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001_select.sql），加工口径与 mapping 一致
+- 与目标表 dwb_order_center_user_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 12 项）（源→规则→目标）：
+dwd_order_f. --[数据加工]--&gt; first_order_time(首次下单时间)
+dwd_order_f. --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f. --[数据加工]--&gt; history_order_cnt(历史订单数)
+dwd_order_f. --[数据加工]--&gt; history_pay_amount(历史消费金额)
+dwd_order_f. --[数据加工]--&gt; history_discount_amount(历史优惠金额)
+dwd_order_f. --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f. --[数据加工]--&gt; rfm_segment(用户RFM分层)
+dwd_order_f. --[数据加工]--&gt; is_repeat_user(是否复购用户)
+dwd_payment_f. --[数据加工]--&gt; fav_pay_method(用户常用支付方式)
+dwd_coupon_use_f. --[数据加工]--&gt; user_coupon_used_cnt(用户优惠券使用次数)
+dwd_order_f. --[数据加工]--&gt; user_fav_activity_type(用户偏好活动类型)
+dwd_refund_f. --[数据加工]--&gt; user_refund_cnt(用户历史退款次数)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>任务：为 slas.dwb_after_sale_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：售后服务中心宽表
+粒度：每行一个售后服务记录
+调度：全量调度 / T+1，一天一调
+映射字段 24 项，来源表 5 张。</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slas.dwb_after_sale_center_f`（售后服务中心宽表） |
+| **I 视图** | `slas.dwb_after_sale_center_i`（F表镜像，对外查询） |
+| **业务主键** | refund_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 24 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | sdref.dwd_refund_f | 退款事实表 | drf |
+| 2 | sdord.dwd_order_f | 订单明细事实表 | dof |
+| 3 | dim.dim_user_f | 用户维度表 | duf |
+| 4 | dim.dim_product_f | 商品维度表 | dpf |
+| 5 | sdcs.dwd_service_ticket_f | 工单事实表 | dst |
+---
+——ddl/create_table_dwb_after_sale_center_f.sql——
+/* =====================================================
+   表名: slas.dwb_after_sale_center_f
+   规则: R0001 - 售后服务中心宽表装配
+   分布键: refund_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以退款事实表为主表，左关联订单/用户/商品/工单四表，一次性拼装售后服务中心宽表全量字段；单场景全量覆盖，无分段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slas.dwb_after_sale_center_f (
+    refund_id           bigint,
+    refund_no           varchar(64),
+    apply_time          datetime,
+    complete_time       datetime,
+    refund_amount       decimal(18,2),
+    refund_reason       varchar(200),
+    order_id            bigint,
+    user_id             bigint,
+    product_id          bigint,
+    order_no            varchar(64),
+    order_pay_amount    decimal(18,2),
+    user_name           varchar(100),
+    product_name        varchar(200),
+    ticket_id           bigint,
+    handler_name        varchar(50),
+    refund_type_name    varchar(50),
+    refund_status_name  varchar(50),
+    ticket_status_name  varchar(50),
+    process_days        int,
+    refund_rate         decimal(5,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(refund_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slas.dwb_after_sale_center_f IS '售后服务中心宽表';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_id IS '退款ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_no IS '退款单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.apply_time IS '申请时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.complete_time IS '完成时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_amount IS '退款金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_reason IS '退款原因';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_pay_amount IS '订单实付金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_id IS '工单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.handler_name IS '处理人';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_type_name IS '退款类型';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_status_name IS '退款状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_status_name IS '工单状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.process_days IS '处理天数';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_rate IS '退款比例(%)';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_after_sale_center_i.sql——
+/* I视图: slas.dwb_after_sale_center_i（售后服务中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slas.dwb_after_sale_center_i AS
+SELECT
+    refund_id,
+    refund_no,
+    apply_time,
+    complete_time,
+    refund_amount,
+    refund_reason,
+    order_id,
+    user_id,
+    product_id,
+    order_no,
+    order_pay_amount,
+    user_name,
+    product_name,
+    ticket_id,
+    handler_name,
+    refund_type_name,
+    refund_status_name,
+    ticket_status_name,
+    process_days,
+    refund_rate,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slas.dwb_after_sale_center_f;
+COMMENT ON TABLE slas.dwb_after_sale_center_i IS '售后服务中心宽表（视图）';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_id IS '退款ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_no IS '退款单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.apply_time IS '申请时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.complete_time IS '完成时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_amount IS '退款金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_reason IS '退款原因';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.order_id IS '订单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.user_id IS '用户ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.product_id IS '商品ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.order_no IS '订单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.order_pay_amount IS '订单实付金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.user_name IS '用户姓名';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.product_name IS '商品名称';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.ticket_id IS '工单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.handler_name IS '处理人';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_type_name IS '退款类型';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_status_name IS '退款状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.ticket_status_name IS '工单状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.process_days IS '处理天数';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.refund_rate IS '退款比例(%)';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_i.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* R0001: 售后服务中心宽表装配（以退款事实表为主表，左关联订单/用户/商品/工单四表，一次性拼装售后服务中心宽表全量字段；单场景全量覆盖，无分段） */
+/* CTE 1: dwd_order_f 按 order_id 聚合到订单粒度（取订单号、汇总实付金额），避免退款行发散 */
+WITH dof_agg AS (
+    SELECT
+        order_id,
+        MAX(order_no) AS order_no,
+        COALESCE(SUM(pay_amount), 0) AS pay_amount
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY order_id
+),
+/* CTE 2: dwd_service_ticket_f 按 refund_id 取最新一条有效工单（创建时间倒序取首条），保证每个退款 1:1 关联 */
+dst_latest AS (
+    SELECT
+        refund_id,
+        ticket_id,
+        handler_name,
+        ticket_status,
+        ROW_NUMBER() OVER (PARTITION BY refund_id ORDER BY create_time DESC NULLS LAST) AS rn
+    FROM sdcs.dwd_service_ticket_f
+    WHERE del_flag = 'N'
+)
+/* 主查询: 退款粒度装配（1:1，无外层 GROUP BY） */
+SELECT
+    drf.refund_id AS refund_id,
+    drf.refund_no AS refund_no,
+    drf.apply_time AS apply_time,
+    drf.complete_time AS complete_time,
+    COALESCE(drf.refund_amount, 0) AS refund_amount,
+    COALESCE(drf.refund_reason, '') AS refund_reason,
+    drf.order_id AS order_id,
+    drf.user_id AS user_id,
+    drf.product_id AS product_id,
+    COALESCE(dof_agg.order_no, '') AS order_no,
+    COALESCE(dof_agg.pay_amount, 0) AS order_pay_amount,
+    COALESCE(duf.user_name, '') AS user_name,
+    COALESCE(dpf.product_name, '') AS product_name,
+    dst.ticket_id AS ticket_id,
+    COALESCE(dst.handler_name, '') AS handler_name,
+    /* 退款类型码值转换: ONLY_REFUND→仅退款, RETURN_REFUND→退货退款, EXCHANGE→换货, 其余→其他 */
+    CASE drf.refund_type
+        WHEN 'ONLY_REFUND' THEN '仅退款'
+        WHEN 'RETURN_REFUND' THEN '退货退款'
+        WHEN 'EXCHANGE' THEN '换货'
+        ELSE '其他'
+    END AS refund_type_name,
+    /* 退款状态码值转换: APPLYING→申请中, APPROVED→已同意, SUCCESS→退款成功, REJECTED→已拒绝, 其余→其他 */
+    CASE drf.refund_status
+        WHEN 'APPLYING' THEN '申请中'
+        WHEN 'APPROVED' THEN '已同意'
+        WHEN 'SUCCESS' THEN '退款成功'
+        WHEN 'REJECTED' THEN '已拒绝'
+        ELSE '其他'
+    END AS refund_status_name,
+    /* 工单状态码值转换: PENDING→待处理, PROCESSING→处理中, RESOLVED→已解决, CLOSED→已关闭, 其余→其他 */
+    CASE dst.ticket_status
+        WHEN 'PENDING' THEN '待处理'
+        WHEN 'PROCESSING' THEN '处理中'
+        WHEN 'RESOLVED' THEN '已解决'
+        WHEN 'CLOSED' THEN '已关闭'
+        ELSE '其他'
+    END AS ticket_status_name,
+    /* 处理天数=完成时间与申请时间相差天数；完成时间为空时按当天计算（COALESCE 兜底当前日期） */
+    COALESCE(CAST(drf.complete_time AS DATE), CURRENT_DATE) - CAST(drf.apply_time AS DATE) AS process_days,
+    /* 退款比例(%)=退款金额/订单实付金额×100；订单实付金额为空或为0时防除零 */
+    CASE
+        WHEN COALESCE(dof_agg.pay_amount, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(drf.refund_amount, 0) * 100.0 / dof_agg.pay_amount, 2)
+    END AS refund_rate,
+    /* 审计字段 */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdref.dwd_refund_f drf
+LEFT JOIN dof_agg ON drf.order_id = dof_agg.order_id
+LEFT JOIN dim.dim_user_f duf ON drf.user_id = duf.user_id AND duf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf ON drf.product_id = dpf.product_id AND dpf.del_flag = 'N'
+LEFT JOIN dst_latest dst ON drf.refund_id = dst.refund_id AND dst.rn = 1
+WHERE drf.del_flag = 'N';
+——dq/dq_dwb_after_sale_center_f.sql——
+-- ============================================================
+-- DQ 检查: slas.dwb_after_sale_center_f
+-- 规则: R0001
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: refund_id）
+SELECT refund_id, COUNT(*) AS cnt
+FROM slas.dwb_after_sale_center_f
+GROUP BY refund_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slas.dwb_after_sale_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slas.dwb_after_sale_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slas.dwb_after_sale_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slas.dwb_after_sale_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slas.dwb_after_sale_center_f;
+档案来源：../10_project_deliver/dwb_after_sale_center_f</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slas.dwb_after_sale_center_f，粒度：每行一个售后服务记录
+- 目标字段 24 项：refund_id, refund_no, refund_type_name, refund_status_name, apply_time, complete_time, process_days, refund_amount, refund_reason, order_id, order_no, order_pay_amount, refund_rate, user_id, user_name, product_id, product_name, ticket_id, ticket_status_name, handler_name, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：dwd_refund_f, dwd_order_f, dim_user_f, dim_product_f, dwd_service_ticket_f
+- 建表 DDL（create_table_dwb_after_sale_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 24 项（源→规则→目标）：
+dwd_refund_f.refund_id --[直接复制]--&gt; refund_id(退款ID)
+dwd_refund_f.refund_no --[直接复制]--&gt; refund_no(退款单号)
+dwd_refund_f.refund_type --[数据加工]--&gt; refund_type_name(退款类型)
+dwd_refund_f.refund_status --[数据加工]--&gt; refund_status_name(退款状态)
+dwd_refund_f.apply_time --[直接复制]--&gt; apply_time(申请时间)
+dwd_refund_f.complete_time --[直接复制]--&gt; complete_time(完成时间)
+（无源声明） --[数据加工]--&gt; process_days(处理天数)
+dwd_refund_f.refund_amount --[直接复制]--&gt; refund_amount(退款金额)
+dwd_refund_f.refund_reason --[直接复制]--&gt; refund_reason(退款原因)
+dwd_refund_f.order_id --[直接复制]--&gt; order_id(订单ID)
+dwd_order_f.order_no --[直接复制]--&gt; order_no(订单号)
+dwd_order_f.pay_amount --[直接复制]--&gt; order_pay_amount(订单实付金额)
+（无源声明） --[数据加工]--&gt; refund_rate(退款比例(%))
+dwd_refund_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dwd_refund_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_service_ticket_f.ticket_id --[直接复制]--&gt; ticket_id(工单ID)
+dwd_service_ticket_f.ticket_status --[数据加工]--&gt; ticket_status_name(工单状态)
+dwd_service_ticket_f.handler_name --[直接复制]--&gt; handler_name(处理人)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>任务：为 slas.dwb_after_sale_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：售后服务中心宽表
+粒度：每行一个售后服务记录
+调度：全量调度 / T+1，一天一调
+映射字段 24 项，来源表 5 张。
+本规则：R0001（售后服务中心宽表装配），step_type=full，目标表 dwb_after_sale_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* R0001: 售后服务中心宽表装配（以退款事实表为主表，左关联订单/用户/商品/工单四表，一次性拼装售后服务中心宽表全量字段；单场景全量覆盖，无分段） */
+/* CTE 1: dwd_order_f 按 order_id 聚合到订单粒度（取订单号、汇总实付金额），避免退款行发散 */
+WITH dof_agg AS (
+    SELECT
+        order_id,
+        MAX(order_no) AS order_no,
+        COALESCE(SUM(pay_amount), 0) AS pay_amount
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY order_id
+),
+/* CTE 2: dwd_service_ticket_f 按 refund_id 取最新一条有效工单（创建时间倒序取首条），保证每个退款 1:1 关联 */
+dst_latest AS (
+    SELECT
+        refund_id,
+        ticket_id,
+        handler_name,
+        ticket_status,
+        ROW_NUMBER() OVER (PARTITION BY refund_id ORDER BY create_time DESC NULLS LAST) AS rn
+    FROM sdcs.dwd_service_ticket_f
+    WHERE del_flag = 'N'
+)
+/* 主查询: 退款粒度装配（1:1，无外层 GROUP BY） */
+SELECT
+    drf.refund_id AS refund_id,
+    drf.refund_no AS refund_no,
+    drf.apply_time AS apply_time,
+    drf.complete_time AS complete_time,
+    COALESCE(drf.refund_amount, 0) AS refund_amount,
+    COALESCE(drf.refund_reason, '') AS refund_reason,
+    drf.order_id AS order_id,
+    drf.user_id AS user_id,
+    drf.product_id AS product_id,
+    COALESCE(dof_agg.order_no, '') AS order_no,
+    COALESCE(dof_agg.pay_amount, 0) AS order_pay_amount,
+    COALESCE(duf.user_name, '') AS user_name,
+    COALESCE(dpf.product_name, '') AS product_name,
+    dst.ticket_id AS ticket_id,
+    COALESCE(dst.handler_name, '') AS handler_name,
+    /* 退款类型码值转换: ONLY_REFUND→仅退款, RETURN_REFUND→退货退款, EXCHANGE→换货, 其余→其他 */
+    CASE drf.refund_type
+        WHEN 'ONLY_REFUND' THEN '仅退款'
+        WHEN 'RETURN_REFUND' THEN '退货退款'
+        WHEN 'EXCHANGE' THEN '换货'
+        ELSE '其他'
+    END AS refund_type_name,
+    /* 退款状态码值转换: APPLYING→申请中, APPROVED→已同意, SUCCESS→退款成功, REJECTED→已拒绝, 其余→其他 */
+    CASE drf.refund_status
+        WHEN 'APPLYING' THEN '申请中'
+        WHEN 'APPROVED' THEN '已同意'
+        WHEN 'SUCCESS' THEN '退款成功'
+        WHEN 'REJECTED' THEN '已拒绝'
+        ELSE '其他'
+    END AS refund_status_name,
+    /* 工单状态码值转换: PENDING→待处理, PROCESSING→处理中, RESOLVED→已解决, CLOSED→已关闭, 其余→其他 */
+    CASE dst.ticket_status
+        WHEN 'PENDING' THEN '待处理'
+        WHEN 'PROCESSING' THEN '处理中'
+        WHEN 'RESOLVED' THEN '已解决'
+        WHEN 'CLOSED' THEN '已关闭'
+        ELSE '其他'
+    END AS ticket_status_name,
+    /* 处理天数=完成时间与申请时间相差天数；完成时间为空时按当天计算（COALESCE 兜底当前日期） */
+    COALESCE(CAST(drf.complete_time AS DATE), CURRENT_DATE) - CAST(drf.apply_time AS DATE) AS process_days,
+    /* 退款比例(%)=退款金额/订单实付金额×100；订单实付金额为空或为0时防除零 */
+    CASE
+        WHEN COALESCE(dof_agg.pay_amount, 0) = 0 THEN 0
+        ELSE ROUND(COALESCE(drf.refund_amount, 0) * 100.0 / dof_agg.pay_amount, 2)
+    END AS refund_rate,
+    /* 审计字段 */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdref.dwd_refund_f drf
+LEFT JOIN dof_agg ON drf.order_id = dof_agg.order_id
+LEFT JOIN dim.dim_user_f duf ON drf.user_id = duf.user_id AND duf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf ON drf.product_id = dpf.product_id AND dpf.del_flag = 'N'
+LEFT JOIN dst_latest dst ON drf.refund_id = dst.refund_id AND dst.rn = 1
+WHERE drf.del_flag = 'N';
+——ddl/create_table_dwb_after_sale_center_f.sql——
+/* =====================================================
+   表名: slas.dwb_after_sale_center_f
+   规则: R0001 - 售后服务中心宽表装配
+   分布键: refund_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以退款事实表为主表，左关联订单/用户/商品/工单四表，一次性拼装售后服务中心宽表全量字段；单场景全量覆盖，无分段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slas.dwb_after_sale_center_f (
+    refund_id           bigint,
+    refund_no           varchar(64),
+    apply_time          datetime,
+    complete_time       datetime,
+    refund_amount       decimal(18,2),
+    refund_reason       varchar(200),
+    order_id            bigint,
+    user_id             bigint,
+    product_id          bigint,
+    order_no            varchar(64),
+    order_pay_amount    decimal(18,2),
+    user_name           varchar(100),
+    product_name        varchar(200),
+    ticket_id           bigint,
+    handler_name        varchar(50),
+    refund_type_name    varchar(50),
+    refund_status_name  varchar(50),
+    ticket_status_name  varchar(50),
+    process_days        int,
+    refund_rate         decimal(5,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(refund_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slas.dwb_after_sale_center_f IS '售后服务中心宽表';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_id IS '退款ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_no IS '退款单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.apply_time IS '申请时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.complete_time IS '完成时间';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_amount IS '退款金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_reason IS '退款原因';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.order_pay_amount IS '订单实付金额';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_id IS '工单ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.handler_name IS '处理人';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_type_name IS '退款类型';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_status_name IS '退款状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.ticket_status_name IS '工单状态';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.process_days IS '处理天数';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.refund_rate IS '退款比例(%)';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slas.dwb_after_sale_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_after_sale_center_f</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 24 项：refund_id, refund_no, apply_time, complete_time, refund_amount, refund_reason, order_id, user_id, product_id, order_no, order_pay_amount, user_name, product_name, ticket_id, handler_name, refund_type_name, refund_status_name, ticket_status_name, process_days, refund_rate, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 dwb_after_sale_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 24 项）（源→规则→目标）：
+dwd_refund_f.refund_id --[直接复制]--&gt; refund_id(退款ID)
+dwd_refund_f.refund_no --[直接复制]--&gt; refund_no(退款单号)
+dwd_refund_f.refund_type --[数据加工]--&gt; refund_type_name(退款类型)
+dwd_refund_f.refund_status --[数据加工]--&gt; refund_status_name(退款状态)
+dwd_refund_f.apply_time --[直接复制]--&gt; apply_time(申请时间)
+dwd_refund_f.complete_time --[直接复制]--&gt; complete_time(完成时间)
+（无源声明） --[数据加工]--&gt; process_days(处理天数)
+dwd_refund_f.refund_amount --[直接复制]--&gt; refund_amount(退款金额)
+dwd_refund_f.refund_reason --[直接复制]--&gt; refund_reason(退款原因)
+dwd_refund_f.order_id --[直接复制]--&gt; order_id(订单ID)
+dwd_order_f.order_no --[直接复制]--&gt; order_no(订单号)
+dwd_order_f.pay_amount --[直接复制]--&gt; order_pay_amount(订单实付金额)
+（无源声明） --[数据加工]--&gt; refund_rate(退款比例(%))
+dwd_refund_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dwd_refund_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_service_ticket_f.ticket_id --[直接复制]--&gt; ticket_id(工单ID)
+dwd_service_ticket_f.ticket_status --[数据加工]--&gt; ticket_status_name(工单状态)
+dwd_service_ticket_f.handler_name --[直接复制]--&gt; handler_name(处理人)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>任务：为 slmar.dwb_marketing_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：营销中心宽表
+粒度：每行一个营销记录
+调度：全量调度 / T+1，一天一调
+映射字段 29 项，来源表 5 张。</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slmar.dwb_marketing_center_f`（营销中心宽表） |
+| **I 视图** | `slmar.dwb_marketing_center_i`（F表镜像，对外查询） |
+| **业务主键** | activity_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 29 |
+| **规则数** | 2 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | sdmar.dwd_activity_f | 活动事实表 | daf |
+| 2 | dim.dim_activity_type_f | 活动类型维度表 | dat |
+| 3 | dim.dim_coupon_f | 优惠券维度表 | dcf |
+| 4 | sdmar.dwd_coupon_use_f | 优惠券使用事实表 | dcu |
+| 5 | sdord.dwd_order_f | 订单明细事实表 | dof |
+---
+——ddl/create_table_dwb_marketing_center_f.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_center_f
+   规则: R0002 - 营销中心宽表组装
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以活动事实表(dwd_activity_f)为主表, LEFT JOIN 活动类型维度、优惠券维度和订单聚合中间表, 组装营销中心宽表全部字段。枚举翻译、比率指标、人均消费、ROI 在此规则完成。 订单相关指标全部取自 R0001 中间表, 不再直接关联订单明细表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_center_f (
+    activity_id          bigint,
+    activity_name        varchar(100),
+    activity_type_desc   varchar(500),
+    start_time           datetime,
+    end_time             datetime,
+    create_time          datetime,
+    min_amount           decimal(18,2),
+    discount_rate        decimal(5,2),
+    max_discount         decimal(18,2),
+    coupon_id            bigint,
+    coupon_name          varchar(100),
+    coupon_total_qty     int,
+    coupon_used_qty      int,
+    activity_type_name   varchar(50),
+    activity_status_name varchar(50),
+    activity_days        int,
+    coupon_type_name     varchar(50),
+    coupon_use_rate      decimal(5,2),
+    avg_order_amount     decimal(18,2),
+    activity_roi         decimal(8,2),
+    del_flag             NVARCHAR(1),
+    crt_cycle_id         BIGINT,
+    last_upd_cycle_id    BIGINT,
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_center_f IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_id IS '活动ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_name IS '活动名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_type_desc IS '活动类型说明';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.start_time IS '开始时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.end_time IS '结束时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.min_amount IS '最低消费金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.max_discount IS '最高优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_id IS '优惠券ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_name IS '优惠券名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_total_qty IS '优惠券发放总量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_used_qty IS '优惠券已使用量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_type_name IS '活动类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_status_name IS '活动状态';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_days IS '活动天数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_type_name IS '优惠券类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.coupon_use_rate IS '优惠券使用率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.avg_order_amount IS '人均消费';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.activity_roi IS '活动ROI(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_marketing_center_order_mid_f.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_center_order_mid_f
+   规则: R0001 - 订单指标预聚合
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 按 activity_id 预聚合订单指标(订单数/GMV/参与人数/优惠金额/新客占比), 将 dwd_order_f 多行(每笔订单)收敛为一行(每个活动), 防止主查询关联订单表时发散。中间表粒度=每行一个活动, 以 activity_id 为聚合键(隐式粒度键, 非 field_targets 所属)。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_center_order_mid_f (
+    order_cnt             int,
+    gmv_amount            decimal(18,2),
+    participant_cnt       int,
+    total_discount_amount decimal(18,2),
+    new_user_rate         decimal(5,2),
+    /* 审计字段 */
+    del_flag              NVARCHAR(1),
+    crt_cycle_id          BIGINT,
+    last_upd_cycle_id     BIGINT,
+    dw_last_update_date   TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_center_order_mid_f IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.order_cnt IS '活动订单数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.gmv_amount IS '活动GMV';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.participant_cnt IS '参与人数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.total_discount_amount IS '活动优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.new_user_rate IS '新客占比(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_marketing_center_i.sql——
+/* I视图: slmar.dwb_marketing_center_i（营销中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slmar.dwb_marketing_center_i AS
+SELECT
+    activity_id,
+    activity_name,
+    activity_type_desc,
+    start_time,
+    end_time,
+    create_time,
+    min_amount,
+    discount_rate,
+    max_discount,
+    coupon_id,
+    coupon_name,
+    coupon_total_qty,
+    coupon_used_qty,
+    activity_type_name,
+    activity_status_name,
+    activity_days,
+    coupon_type_name,
+    coupon_use_rate,
+    avg_order_amount,
+    activity_roi,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slmar.dwb_marketing_center_f;
+COMMENT ON TABLE slmar.dwb_marketing_center_i IS '营销中心宽表（视图）';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_id IS '活动ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_name IS '活动名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_type_desc IS '活动类型说明';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.start_time IS '开始时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.end_time IS '结束时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.create_time IS '创建时间';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.min_amount IS '最低消费金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.max_discount IS '最高优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_id IS '优惠券ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_name IS '优惠券名称';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_total_qty IS '优惠券发放总量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_used_qty IS '优惠券已使用量';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_type_name IS '活动类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_status_name IS '活动状态';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_days IS '活动天数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_type_name IS '优惠券类型';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.coupon_use_rate IS '优惠券使用率(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.avg_order_amount IS '人均消费';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.activity_roi IS '活动ROI(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_i.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_marketing_center_order_mid_i.sql——
+/* I视图: slmar.dwb_marketing_center_order_mid_i（营销中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slmar.dwb_marketing_center_order_mid_i AS
+SELECT
+    order_cnt,
+    gmv_amount,
+    participant_cnt,
+    total_discount_amount,
+    new_user_rate
+FROM slmar.dwb_marketing_center_order_mid_f;
+COMMENT ON TABLE slmar.dwb_marketing_center_order_mid_i IS '营销中心宽表（视图）';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_i.order_cnt IS '活动订单数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_i.gmv_amount IS '活动GMV';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_i.participant_cnt IS '参与人数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_i.total_discount_amount IS '活动优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_i.new_user_rate IS '新客占比(%)';
+——etl/R0001.sql——
+/* =====================================================
+   R0001: 订单指标预聚合
+   目标表: slmar.dwb_marketing_center_order_mid_f (中间表)
+   设计意图: 按 activity_id 预聚合订单指标(订单数/GMV/参与人数/优惠金额/新客占比),
+            将 dwd_order_f 多行(每笔订单)收敛为一行(每个活动),
+            防止主查询关联订单表时发散。
+   粒度: 一行=一笔订单 → 一行=一个活动(按 activity_id 聚合)
+   来源表:
+     - sdord.dwd_order_f dof (订单事实表)
+     - sdmar.dwd_activity_f daf (活动事实表, INNER JOIN on activity_id, 取活动时间窗口)
+   ===================================================== */
+WITH
+/* CTE: 用户历史首单时间(扫描 dwd_order_f 全量, 按 user_id 取 MIN 下单时间),
+       用于判定该用户是否为某活动期间的新用户 */
+user_first_order AS (
+    SELECT
+        user_id,
+        MIN(order_time) AS first_order_time
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY user_id
+)
+SELECT
+    /* 业务主键/分组键: activity_id (也是分布键和下游 JOIN 关联键) */
+    dof.activity_id AS activity_id,
+    /* 活动订单数: 按 activity_id 计数活动下的订单行 */
+    COUNT(1) AS order_cnt,
+    /* 活动GMV: 按 activity_id 汇总活动下所有订单的 pay_amount */
+    COALESCE(SUM(dof.pay_amount), 0) AS gmv_amount,
+    /* 参与人数: 按 activity_id 对 user_id 去重计数 */
+    COUNT(DISTINCT dof.user_id) AS participant_cnt,
+    /* 活动优惠金额: 按 activity_id 汇总活动下所有订单的 discount_amount */
+    COALESCE(SUM(dof.discount_amount), 0) AS total_discount_amount,
+    /* 新客占比(%): 分子=首单时间落在活动[start_time,end_time]窗口内的用户产生的订单数,
+       分母=活动总订单数(order_cnt), 比值×100; 分母为0时返回NULL */
+    CAST(
+        SUM(CASE WHEN ufo.first_order_time BETWEEN daf.start_time AND daf.end_time THEN 1 ELSE 0 END) * 100.0
+            / NULLIF(COUNT(1), 0)
+        AS NUMERIC(5,2)
+    ) AS new_user_rate,
+    /* 审计字段 */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+INNER JOIN sdmar.dwd_activity_f daf
+    ON dof.activity_id = daf.activity_id
+    AND daf.del_flag = 'N'
+LEFT JOIN user_first_order ufo
+    ON dof.user_id = ufo.user_id
+WHERE dof.del_flag = 'N'
+GROUP BY dof.activity_id, daf.start_time, daf.end_time;
+——dq/dq_dwb_marketing_center_f.sql——
+-- ============================================================
+-- DQ 检查: slmar.dwb_marketing_center_f
+-- 规则: R0002
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: activity_id）
+SELECT activity_id, COUNT(*) AS cnt
+FROM slmar.dwb_marketing_center_f
+GROUP BY activity_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slmar.dwb_marketing_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slmar.dwb_marketing_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slmar.dwb_marketing_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slmar.dwb_marketing_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slmar.dwb_marketing_center_f;
+档案来源：../10_project_deliver/dwb_marketing_center_f</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slmar.dwb_marketing_center_f，粒度：每行一个营销记录
+- 目标字段 29 项：activity_id, activity_name, activity_type_name, activity_type_desc, activity_status_name, start_time, end_time, activity_days, create_time, min_amount, discount_rate, max_discount, coupon_id, coupon_name, coupon_type_name, coupon_total_qty, coupon_used_qty, coupon_use_rate, order_cnt, gmv_amount, participant_cnt, total_discount_amount, avg_order_amount, new_user_rate, activity_roi, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 5 张：dwd_activity_f, dim_activity_type_f, dim_coupon_f, dwd_coupon_use_f, dwd_order_f
+- 建表 DDL（create_table_dwb_marketing_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 29 项（源→规则→目标）：
+dwd_activity_f.activity_id --[直接复制]--&gt; activity_id(活动ID)
+dwd_activity_f.activity_name --[直接复制]--&gt; activity_name(活动名称)
+dwd_activity_f.activity_type --[数据加工]--&gt; activity_type_name(活动类型)
+dim_activity_type_f.type_desc --[直接复制]--&gt; activity_type_desc(活动类型说明)
+dwd_activity_f.activity_status --[数据加工]--&gt; activity_status_name(活动状态)
+dwd_activity_f.start_time --[直接复制]--&gt; start_time(开始时间)
+dwd_activity_f.end_time --[直接复制]--&gt; end_time(结束时间)
+（无源声明） --[数据加工]--&gt; activity_days(活动天数)
+dwd_activity_f.create_time --[直接复制]--&gt; create_time(创建时间)
+dwd_activity_f.min_amount --[直接复制]--&gt; min_amount(最低消费金额)
+dwd_activity_f.discount_rate --[直接复制]--&gt; discount_rate(折扣率(%))
+dwd_activity_f.max_discount --[直接复制]--&gt; max_discount(最高优惠金额)
+dim_coupon_f.coupon_id --[直接复制]--&gt; coupon_id(优惠券ID)
+dim_coupon_f.coupon_name --[直接复制]--&gt; coupon_name(优惠券名称)
+dim_coupon_f.coupon_type --[数据加工]--&gt; coupon_type_name(优惠券类型)
+dim_coupon_f.total_qty --[直接复制]--&gt; coupon_total_qty(优惠券发放总量)
+dim_coupon_f.used_qty --[直接复制]--&gt; coupon_used_qty(优惠券已使用量)
+（无源声明） --[数据加工]--&gt; coupon_use_rate(优惠券使用率(%))
+（无源声明） --[数据加工]--&gt; order_cnt(活动订单数)
+（无源声明） --[数据加工]--&gt; gmv_amount(活动GMV)
+（无源声明） --[数据加工]--&gt; participant_cnt(参与人数)
+（无源声明） --[数据加工]--&gt; total_discount_amount(活动优惠金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(人均消费)
+（无源声明） --[数据加工]--&gt; new_user_rate(新客占比(%))
+（无源声明） --[数据加工]--&gt; activity_roi(活动ROI(%))
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>任务：为 slmar.dwb_marketing_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：营销中心宽表
+粒度：每行一个营销记录
+调度：全量调度 / T+1，一天一调
+映射字段 29 项，来源表 5 张。
+本规则：R0001（订单指标预聚合），step_type=full，目标表 slmar.dwb_marketing_center_order_mid_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* =====================================================
+   R0001: 订单指标预聚合
+   目标表: slmar.dwb_marketing_center_order_mid_f (中间表)
+   设计意图: 按 activity_id 预聚合订单指标(订单数/GMV/参与人数/优惠金额/新客占比),
+            将 dwd_order_f 多行(每笔订单)收敛为一行(每个活动),
+            防止主查询关联订单表时发散。
+   粒度: 一行=一笔订单 → 一行=一个活动(按 activity_id 聚合)
+   来源表:
+     - sdord.dwd_order_f dof (订单事实表)
+     - sdmar.dwd_activity_f daf (活动事实表, INNER JOIN on activity_id, 取活动时间窗口)
+   ===================================================== */
+WITH
+/* CTE: 用户历史首单时间(扫描 dwd_order_f 全量, 按 user_id 取 MIN 下单时间),
+       用于判定该用户是否为某活动期间的新用户 */
+user_first_order AS (
+    SELECT
+        user_id,
+        MIN(order_time) AS first_order_time
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+    GROUP BY user_id
+)
+SELECT
+    /* 业务主键/分组键: activity_id (也是分布键和下游 JOIN 关联键) */
+    dof.activity_id AS activity_id,
+    /* 活动订单数: 按 activity_id 计数活动下的订单行 */
+    COUNT(1) AS order_cnt,
+    /* 活动GMV: 按 activity_id 汇总活动下所有订单的 pay_amount */
+    COALESCE(SUM(dof.pay_amount), 0) AS gmv_amount,
+    /* 参与人数: 按 activity_id 对 user_id 去重计数 */
+    COUNT(DISTINCT dof.user_id) AS participant_cnt,
+    /* 活动优惠金额: 按 activity_id 汇总活动下所有订单的 discount_amount */
+    COALESCE(SUM(dof.discount_amount), 0) AS total_discount_amount,
+    /* 新客占比(%): 分子=首单时间落在活动[start_time,end_time]窗口内的用户产生的订单数,
+       分母=活动总订单数(order_cnt), 比值×100; 分母为0时返回NULL */
+    CAST(
+        SUM(CASE WHEN ufo.first_order_time BETWEEN daf.start_time AND daf.end_time THEN 1 ELSE 0 END) * 100.0
+            / NULLIF(COUNT(1), 0)
+        AS NUMERIC(5,2)
+    ) AS new_user_rate,
+    /* 审计字段 */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+INNER JOIN sdmar.dwd_activity_f daf
+    ON dof.activity_id = daf.activity_id
+    AND daf.del_flag = 'N'
+LEFT JOIN user_first_order ufo
+    ON dof.user_id = ufo.user_id
+WHERE dof.del_flag = 'N'
+GROUP BY dof.activity_id, daf.start_time, daf.end_time;
+——ddl/create_table_dwb_marketing_center_order_mid_f.sql——
+/* =====================================================
+   表名: slmar.dwb_marketing_center_order_mid_f
+   规则: R0001 - 订单指标预聚合
+   分布键: activity_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 按 activity_id 预聚合订单指标(订单数/GMV/参与人数/优惠金额/新客占比), 将 dwd_order_f 多行(每笔订单)收敛为一行(每个活动), 防止主查询关联订单表时发散。中间表粒度=每行一个活动, 以 activity_id 为聚合键(隐式粒度键, 非 field_targets 所属)。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slmar.dwb_marketing_center_order_mid_f (
+    order_cnt             int,
+    gmv_amount            decimal(18,2),
+    participant_cnt       int,
+    total_discount_amount decimal(18,2),
+    new_user_rate         decimal(5,2),
+    /* 审计字段 */
+    del_flag              NVARCHAR(1),
+    crt_cycle_id          BIGINT,
+    last_upd_cycle_id     BIGINT,
+    dw_last_update_date   TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(activity_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slmar.dwb_marketing_center_order_mid_f IS '营销中心宽表';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.order_cnt IS '活动订单数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.gmv_amount IS '活动GMV';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.participant_cnt IS '参与人数';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.total_discount_amount IS '活动优惠金额';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.new_user_rate IS '新客占比(%)';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slmar.dwb_marketing_center_order_mid_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_marketing_center_f</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 5 项：order_cnt, gmv_amount, participant_cnt, total_discount_amount, new_user_rate（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 slmar.dwb_marketing_center_order_mid_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 5 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; order_cnt(活动订单数)
+（无源声明） --[数据加工]--&gt; gmv_amount(活动GMV)
+（无源声明） --[数据加工]--&gt; participant_cnt(参与人数)
+（无源声明） --[数据加工]--&gt; total_discount_amount(活动优惠金额)
+（无源声明） --[数据加工]--&gt; new_user_rate(新客占比(%))</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>任务：为 slord.dwb_order_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单中心宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 150 项，来源表 18 张。</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slord.dwb_order_center_f`（订单中心宽表） |
+| **I 视图** | `slord.dwb_order_center_i`（F表镜像，对外查询） |
+| **业务主键** | order_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 150 |
+| **规则数** | 3 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | sdord.dwd_order_f | 订单明细事实表 | dof |
+| 2 | sdord.dwd_order_detail_f | 订单商品明细事实表 | dod |
+| 3 | sdpay.dwd_payment_f | 支付事实表 | dpf |
+| 4 | sdlog.dwd_logistics_f | 物流事实表 | dlf |
+| 5 | sdmar.dwd_coupon_use_f | 优惠券使用事实表 | dcu |
+| 6 | dim.dim_user_f | 用户维度表 | duf |
+| 7 | dim.dim_user_level_f | 用户等级维度表 | dul |
+| 8 | dim.dim_product_f | 商品维度表 | dpf7 |
+| 9 | dim.dim_product_category_f | 商品分类维度表 | dpc |
+| 10 | dim.dim_brand_f | 品牌维度表 | dbf |
+| 11 | dim.dim_shop_f | 店铺维度表 | dsf |
+| 12 | dim.dim_region_f | 地区维度表 | drf |
+| 13 | dim.dim_warehouse_f | 仓库维度表 | dwf |
+| 14 | dim.dim_payment_method_f | 支付方式维度表 | dpm |
+| 15 | dim.dim_logistics_company_f | 物流公司维度表 | dlc |
+| 16 | dim.dim_coupon_f | 优惠券维度表 | dcf |
+| 17 | dim.dim_activity_f | 营销活动维度表 | daf |
+| 18 | sdref.dwd_refund_f | 退款事实表 | drf17 |
+---
+——ddl/create_table_dwb_order_center_f.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_f
+   规则: R0003 - 订单中心宽表装配
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以 dwd_order_f 为驱动表，LEFT JOIN 订单明细/支付/物流/优惠券/退款事实表（各取一条有效记录）+ 全部维表 + tmp1用户画像 + tmp2商品画像，一次性装配宽表全部字段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_f (
+    order_id               bigint,
+    order_no               varchar(64),
+    order_status           varchar(20),
+    order_status_name      varchar(50),
+    order_time             datetime,
+    total_amount           decimal(18,2),
+    product_amount         decimal(18,2),
+    pay_amount             decimal(18,2),
+    discount_amount        decimal(18,2),
+    freight_amount         decimal(18,2),
+    product_cnt            int,
+    product_qty            int,
+    order_source_name      varchar(50),
+    order_type_name        varchar(50),
+    order_remark           varchar(500),
+    order_date             date,
+    user_id                bigint,
+    user_name              varchar(100),
+    user_phone_masked      varchar(20),
+    user_email_masked      varchar(100),
+    gender_name            varchar(10),
+    user_birthday          date,
+    user_age               int,
+    user_register_time     datetime,
+    user_level_id          int,
+    user_level_name        varchar(50),
+    member_points          int,
+    member_balance         decimal(18,2),
+    user_tag               varchar(500),
+    user_source_name       varchar(50),
+    user_province_code     varchar(20),
+    user_city_code         varchar(20),
+    user_days              int,
+    product_id             bigint,
+    product_name           varchar(200),
+    product_code           varchar(50),
+    sku_code               varchar(50),
+    category_l1_id         bigint,
+    category_l1_name       varchar(100),
+    category_l2_id         bigint,
+    category_l2_name       varchar(100),
+    category_l3_id         bigint,
+    category_l3_name       varchar(100),
+    brand_id               bigint,
+    brand_name             varchar(100),
+    brand_origin           varchar(50),
+    product_attr           varchar(500),
+    product_spec           varchar(200),
+    product_weight         decimal(10,2),
+    product_volume         decimal(10,4),
+    cost_price             decimal(18,2),
+    sale_price             decimal(18,2),
+    real_price             decimal(18,2),
+    product_tag            varchar(200),
+    product_status_name    varchar(20),
+    product_profit         decimal(18,2),
+    shop_id                bigint,
+    shop_name              varchar(200),
+    shop_type_name         varchar(50),
+    shop_level_name        varchar(20),
+    shop_score             decimal(3,2),
+    company_name           varchar(200),
+    shop_province_code     varchar(20),
+    shop_province_name     varchar(50),
+    shop_city_code         varchar(20),
+    shop_city_name         varchar(50),
+    shop_open_time         datetime,
+    shop_history_order_cnt int,
+    receiver_name          varchar(100),
+    receiver_phone_masked  varchar(20),
+    receiver_province_code varchar(20),
+    receiver_province_name varchar(50),
+    receiver_city_code     varchar(20),
+    receiver_city_name     varchar(50),
+    receiver_district_code varchar(20),
+    receiver_district_name varchar(50),
+    receiver_street        varchar(200),
+    receiver_address       varchar(500),
+    full_address           varchar(1000),
+    postal_code            varchar(10),
+    address_tag_name       varchar(50),
+    longitude              decimal(10,6),
+    latitude               decimal(10,6),
+    pay_time               datetime,
+    pay_id                 bigint,
+    pay_no                 varchar(64),
+    pay_method_code        varchar(20),
+    pay_method_name        varchar(50),
+    pay_channel_name       varchar(50),
+    pay_status_name        varchar(20),
+    bank_card_masked       varchar(20),
+    bank_name              varchar(50),
+    installment_num        int,
+    pay_service_fee        decimal(10,2),
+    pay_duration_minutes   int,
+    ship_time              datetime,
+    receive_time           datetime,
+    delivery_days          int,
+    logistics_id           bigint,
+    logistics_no           varchar(50),
+    logistics_company_code varchar(20),
+    logistics_company_name varchar(100),
+    logistics_type_name    varchar(50),
+    warehouse_id           bigint,
+    warehouse_name         varchar(100),
+    warehouse_address      varchar(200),
+    logistics_status_name  varchar(50),
+    pickup_time            datetime,
+    sign_receiver_name     varchar(100),
+    ship_duration_hours    int,
+    coupon_id              bigint,
+    coupon_name            varchar(100),
+    coupon_type_name       varchar(50),
+    coupon_amount          decimal(10,2),
+    activity_id            bigint,
+    activity_name          varchar(100),
+    activity_type_name     varchar(50),
+    activity_discount_rate decimal(5,2),
+    full_reduce_amount     decimal(10,2),
+    points_deduct_amount   decimal(10,2),
+    points_used            int,
+    is_marketing_order     varchar(1),
+    total_discount_amount  decimal(18,2),
+    refund_id              bigint,
+    refund_no              varchar(64),
+    refund_type_name       varchar(50),
+    refund_reason          varchar(200),
+    refund_amount          decimal(18,2),
+    refund_status_name     varchar(50),
+    refund_apply_time      datetime,
+    refund_complete_time   datetime,
+    is_refund_order        varchar(1),
+    del_flag               NVARCHAR(1),
+    crt_cycle_id           BIGINT,
+    last_upd_cycle_id      BIGINT,
+    dw_last_update_date    TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_f IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_id IS '订单ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_no IS '订单号';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_status IS '订单状态';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_status_name IS '订单状态名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_time IS '下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.total_amount IS '订单总金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_amount IS '商品金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_amount IS '实付金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.discount_amount IS '优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.freight_amount IS '运费金额';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_cnt IS '商品种类数';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_qty IS '商品总件数';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_source_name IS '订单来源';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_type_name IS '订单类型';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_remark IS '订单备注';
+COMMENT ON COLUMN slord.dwb_order_center_f.order_date IS '下单日期';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_phone_masked IS '用户手机(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_email_masked IS '用户邮箱(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_f.gender_name IS '用户性别';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_birthday IS '用户生日';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_age IS '用户年龄';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_register_time IS '注册时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_level_id IS '用户等级ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_level_name IS '用户等级名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.member_points IS '会员积分';
+COMMENT ON COLUMN slord.dwb_order_center_f.member_balance IS '会员余额';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_tag IS '用户标签';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_source_name IS '用户来源';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_province_code IS '用户省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_city_code IS '用户城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.user_days IS '用户注册天数';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_code IS '商品编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.sku_code IS 'SKU编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l1_id IS '一级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l1_name IS '一级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l2_id IS '二级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l2_name IS '二级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l3_id IS '三级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.category_l3_name IS '三级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_id IS '品牌ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_name IS '品牌名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_attr IS '商品属性';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_spec IS '商品规格';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_weight IS '商品重量(kg)';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_volume IS '商品体积(m³)';
+COMMENT ON COLUMN slord.dwb_order_center_f.cost_price IS '商品成本价';
+COMMENT ON COLUMN slord.dwb_order_center_f.sale_price IS '商品售价';
+COMMENT ON COLUMN slord.dwb_order_center_f.real_price IS '商品实付单价';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_tag IS '商品标签';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_status_name IS '商品状态';
+COMMENT ON COLUMN slord.dwb_order_center_f.product_profit IS '单品毛利';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_level_name IS '店铺等级';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_score IS '店铺评分';
+COMMENT ON COLUMN slord.dwb_order_center_f.company_name IS '店铺所属公司';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_province_code IS '店铺省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_province_name IS '店铺省份名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_city_code IS '店铺城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_city_name IS '店铺城市名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_open_time IS '开店时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.shop_history_order_cnt IS '店铺历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_name IS '收货人姓名';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_phone_masked IS '收货人手机(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_province_code IS '收货省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_province_name IS '收货省份名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_city_code IS '收货城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_city_name IS '收货城市名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_district_code IS '收货区县编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_district_name IS '收货区县名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_street IS '收货街道';
+COMMENT ON COLUMN slord.dwb_order_center_f.receiver_address IS '详细地址';
+COMMENT ON COLUMN slord.dwb_order_center_f.full_address IS '完整收货地址';
+COMMENT ON COLUMN slord.dwb_order_center_f.postal_code IS '邮政编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.address_tag_name IS '地址标签';
+COMMENT ON COLUMN slord.dwb_order_center_f.longitude IS '经度';
+COMMENT ON COLUMN slord.dwb_order_center_f.latitude IS '纬度';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_time IS '支付时间';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_id IS '支付ID';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_no IS '支付流水号';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_method_code IS '支付方式编码';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_method_name IS '支付方式名称';
+COMMENT ON COLUMN slord.dwb_order_center_f.pay_channel_name IS '支付渠道名称';
+…（截断）
+——ddl/create_table_dwb_order_center_tmp1.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_tmp1
+   规则: R0001 - 用户画像汇总
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将订单、支付、优惠券、退款四类事实表按 user_id 聚合，产出用户级画像指标（首次/最近下单、历史消费、RFM分层、复购、偏好），避免主装配阶段聚合导致粒度发散
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_tmp1 (
+    first_order_time        datetime,
+    last_order_time         datetime,
+    history_order_cnt       int,
+    history_pay_amount      decimal(18,2),
+    history_discount_amount decimal(18,2),
+    avg_order_amount        decimal(18,2),
+    rfm_segment             varchar(20),
+    is_repeat_user          varchar(1),
+    fav_pay_method          varchar(20),
+    user_coupon_used_cnt    int,
+    user_fav_activity_type  varchar(50),
+    user_refund_cnt         int,
+    /* 审计字段 */
+    del_flag                NVARCHAR(1),
+    crt_cycle_id            BIGINT,
+    last_upd_cycle_id       BIGINT,
+    dw_last_update_date     TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_tmp1 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_discount_amount IS '历史优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.rfm_segment IS '用户RFM分层';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.is_repeat_user IS '是否复购用户';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.fav_pay_method IS '用户常用支付方式';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_coupon_used_cnt IS '用户优惠券使用次数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_fav_activity_type IS '用户偏好活动类型';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_refund_cnt IS '用户历史退款次数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_order_center_tmp2.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_tmp2
+   规则: R0002 - 商品画像汇总
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将订单商品明细按 product_id 聚合，产出商品累计销量和销售额，供主表装配时 LEFT JOIN
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_tmp2 (
+    product_sales_cnt    int,
+    product_sales_amount decimal(18,2),
+    /* 审计字段 */
+    del_flag             NVARCHAR(1),
+    crt_cycle_id         BIGINT,
+    last_upd_cycle_id    BIGINT,
+    dw_last_update_date  TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_tmp2 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.product_sales_cnt IS '商品累计销量';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.product_sales_amount IS '商品累计销售额';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp2.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_order_center_i.sql——
+/* I视图: slord.dwb_order_center_i（订单中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slord.dwb_order_center_i AS
+SELECT
+    order_id,
+    order_no,
+    order_status,
+    order_status_name,
+    order_time,
+    total_amount,
+    product_amount,
+    pay_amount,
+    discount_amount,
+    freight_amount,
+    product_cnt,
+    product_qty,
+    order_source_name,
+    order_type_name,
+    order_remark,
+    order_date,
+    user_id,
+    user_name,
+    user_phone_masked,
+    user_email_masked,
+    gender_name,
+    user_birthday,
+    user_age,
+    user_register_time,
+    user_level_id,
+    user_level_name,
+    member_points,
+    member_balance,
+    user_tag,
+    user_source_name,
+    user_province_code,
+    user_city_code,
+    user_days,
+    product_id,
+    product_name,
+    product_code,
+    sku_code,
+    category_l1_id,
+    category_l1_name,
+    category_l2_id,
+    category_l2_name,
+    category_l3_id,
+    category_l3_name,
+    brand_id,
+    brand_name,
+    brand_origin,
+    product_attr,
+    product_spec,
+    product_weight,
+    product_volume,
+    cost_price,
+    sale_price,
+    real_price,
+    product_tag,
+    product_status_name,
+    product_profit,
+    shop_id,
+    shop_name,
+    shop_type_name,
+    shop_level_name,
+    shop_score,
+    company_name,
+    shop_province_code,
+    shop_province_name,
+    shop_city_code,
+    shop_city_name,
+    shop_open_time,
+    shop_history_order_cnt,
+    receiver_name,
+    receiver_phone_masked,
+    receiver_province_code,
+    receiver_province_name,
+    receiver_city_code,
+    receiver_city_name,
+    receiver_district_code,
+    receiver_district_name,
+    receiver_street,
+    receiver_address,
+    full_address,
+    postal_code,
+    address_tag_name,
+    longitude,
+    latitude,
+    pay_time,
+    pay_id,
+    pay_no,
+    pay_method_code,
+    pay_method_name,
+    pay_channel_name,
+    pay_status_name,
+    bank_card_masked,
+    bank_name,
+    installment_num,
+    pay_service_fee,
+    pay_duration_minutes,
+    ship_time,
+    receive_time,
+    delivery_days,
+    logistics_id,
+    logistics_no,
+    logistics_company_code,
+    logistics_company_name,
+    logistics_type_name,
+    warehouse_id,
+    warehouse_name,
+    warehouse_address,
+    logistics_status_name,
+    pickup_time,
+    sign_receiver_name,
+    ship_duration_hours,
+    coupon_id,
+    coupon_name,
+    coupon_type_name,
+    coupon_amount,
+    activity_id,
+    activity_name,
+    activity_type_name,
+    activity_discount_rate,
+    full_reduce_amount,
+    points_deduct_amount,
+    points_used,
+    is_marketing_order,
+    total_discount_amount,
+    refund_id,
+    refund_no,
+    refund_type_name,
+    refund_reason,
+    refund_amount,
+    refund_status_name,
+    refund_apply_time,
+    refund_complete_time,
+    is_refund_order,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slord.dwb_order_center_f;
+COMMENT ON TABLE slord.dwb_order_center_i IS '订单中心宽表（视图）';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_id IS '订单ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_no IS '订单号';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_status IS '订单状态';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_status_name IS '订单状态名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_time IS '下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_i.total_amount IS '订单总金额';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_amount IS '商品金额';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_amount IS '实付金额';
+COMMENT ON COLUMN slord.dwb_order_center_i.discount_amount IS '优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_i.freight_amount IS '运费金额';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_cnt IS '商品种类数';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_qty IS '商品总件数';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_source_name IS '订单来源';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_type_name IS '订单类型';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_remark IS '订单备注';
+COMMENT ON COLUMN slord.dwb_order_center_i.order_date IS '下单日期';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_id IS '用户ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_name IS '用户姓名';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_phone_masked IS '用户手机(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_email_masked IS '用户邮箱(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_i.gender_name IS '用户性别';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_birthday IS '用户生日';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_age IS '用户年龄';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_register_time IS '注册时间';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_level_id IS '用户等级ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_level_name IS '用户等级名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.member_points IS '会员积分';
+COMMENT ON COLUMN slord.dwb_order_center_i.member_balance IS '会员余额';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_tag IS '用户标签';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_source_name IS '用户来源';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_province_code IS '用户省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_city_code IS '用户城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.user_days IS '用户注册天数';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_id IS '商品ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_name IS '商品名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_code IS '商品编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.sku_code IS 'SKU编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l1_id IS '一级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l1_name IS '一级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l2_id IS '二级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l2_name IS '二级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l3_id IS '三级类目ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.category_l3_name IS '三级类目名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.brand_id IS '品牌ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.brand_name IS '品牌名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_attr IS '商品属性';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_spec IS '商品规格';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_weight IS '商品重量(kg)';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_volume IS '商品体积(m³)';
+COMMENT ON COLUMN slord.dwb_order_center_i.cost_price IS '商品成本价';
+COMMENT ON COLUMN slord.dwb_order_center_i.sale_price IS '商品售价';
+COMMENT ON COLUMN slord.dwb_order_center_i.real_price IS '商品实付单价';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_tag IS '商品标签';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_status_name IS '商品状态';
+COMMENT ON COLUMN slord.dwb_order_center_i.product_profit IS '单品毛利';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_id IS '店铺ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_name IS '店铺名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_level_name IS '店铺等级';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_score IS '店铺评分';
+COMMENT ON COLUMN slord.dwb_order_center_i.company_name IS '店铺所属公司';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_province_code IS '店铺省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_province_name IS '店铺省份名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_city_code IS '店铺城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_city_name IS '店铺城市名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_open_time IS '开店时间';
+COMMENT ON COLUMN slord.dwb_order_center_i.shop_history_order_cnt IS '店铺历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_name IS '收货人姓名';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_phone_masked IS '收货人手机(脱敏)';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_province_code IS '收货省份编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_province_name IS '收货省份名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_city_code IS '收货城市编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_city_name IS '收货城市名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_district_code IS '收货区县编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_district_name IS '收货区县名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_street IS '收货街道';
+COMMENT ON COLUMN slord.dwb_order_center_i.receiver_address IS '详细地址';
+COMMENT ON COLUMN slord.dwb_order_center_i.full_address IS '完整收货地址';
+COMMENT ON COLUMN slord.dwb_order_center_i.postal_code IS '邮政编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.address_tag_name IS '地址标签';
+COMMENT ON COLUMN slord.dwb_order_center_i.longitude IS '经度';
+COMMENT ON COLUMN slord.dwb_order_center_i.latitude IS '纬度';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_time IS '支付时间';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_id IS '支付ID';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_no IS '支付流水号';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_method_code IS '支付方式编码';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_method_name IS '支付方式名称';
+COMMENT ON COLUMN slord.dwb_order_center_i.pay_channel_na…（截断）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slord.dwb_order_center_f，粒度：每行一个订单
+- 目标字段 150 项：order_id, order_no, order_status, order_status_name, order_time, pay_time, ship_time, receive_time, delivery_days, total_amount, product_amount, pay_amount, discount_amount, freight_amount, product_cnt, product_qty, order_source_name, order_type_name, order_remark, order_date, user_id, user_name, user_phone_masked, user_email_masked, gender_name, user_birthday, user_age, user_register_time, user_level_id, user_level_name, member_points, member_balance, first_order_time, last_order_time, history_order_cnt, history_pay_amount, history_discount_amount, avg_order_amount, rfm_segment, user_tag, user_source_name, user_province_code, user_city_code, user_days, is_repeat_user, product_id, product_name, product_code, sku_code, category_l1_id, category_l1_name, category_l2_id, category_l2_name, category_l3_id, category_l3_name, brand_id, brand_name, brand_origin, product_attr, product_spec, product_weight, product_volume, cost_price, sale_price, real_price, product_tag, product_status_name, product_sales_cnt, product_sales_amount, product_profit, shop_id, shop_name, shop_type_name, shop_level_name, shop_score, company_name, shop_province_code, shop_province_name, shop_city_code, shop_city_name, shop_open_time, shop_history_order_cnt, receiver_name, receiver_phone_masked, receiver_province_code, receiver_province_name, receiver_city_code, receiver_city_name, receiver_district_code, receiver_district_name, receiver_street, receiver_address, full_address, postal_code, address_tag_name, longitude, latitude, pay_id, pay_no, pay_method_code, pay_method_name, pay_channel_name, pay_status_name, bank_card_masked, bank_name, installment_num, pay_service_fee, fav_pay_method, pay_duration_minutes, logistics_id, logistics_no, logistics_company_code, logistics_company_name, logistics_type_name, warehouse_id, warehouse_name, warehouse_address, logistics_status_name, pickup_time, sign_receiver_name, ship_duration_hours, coupon_id, coupon_name, coupon_type_name, coupon_amount, activity_id, activity_name, activity_type_name, activity_discount_rate, full_reduce_amount, points_deduct_amount, points_used, is_marketing_order, total_discount_amount, user_coupon_used_cnt, user_fav_activity_type, refund_id, refund_no, refund_type_name, refund_reason, refund_amount, refund_status_name, refund_apply_time, refund_complete_time, is_refund_order, user_refund_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 18 张：dwd_order_f, dwd_order_detail_f, dwd_payment_f, dwd_logistics_f, dwd_coupon_use_f, dim_user_f, dim_user_level_f, dim_product_f, dim_product_category_f, dim_brand_f, dim_shop_f, dim_region_f, dim_warehouse_f, dim_payment_method_f, dim_logistics_company_f, dim_coupon_f, dim_activity_f, dwd_refund_f
+- 建表 DDL（create_table_dwb_order_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 150 项（源→规则→目标）：
+dwd_order_f.order_id --[直接复制]--&gt; order_id(订单ID)
+dwd_order_f.order_no --[直接复制]--&gt; order_no(订单号)
+dwd_order_f.order_status --[直接复制]--&gt; order_status(订单状态)
+dwd_order_f.order_status --[数据加工]--&gt; order_status_name(订单状态名称)
+dwd_order_f.create_time --[直接复制]--&gt; order_time(下单时间)
+dwd_payment_f.pay_time --[直接复制]--&gt; pay_time(支付时间)
+dwd_logistics_f.ship_time --[直接复制]--&gt; ship_time(发货时间)
+dwd_logistics_f.receive_time --[直接复制]--&gt; receive_time(签收时间)
+dwd_logistics_f. --[数据加工]--&gt; delivery_days(物流时长(天))
+dwd_order_f.total_amount --[直接复制]--&gt; total_amount(订单总金额)
+dwd_order_f.product_amount --[直接复制]--&gt; product_amount(商品金额)
+dwd_order_f.pay_amount --[直接复制]--&gt; pay_amount(实付金额)
+dwd_order_f.discount_amount --[直接复制]--&gt; discount_amount(优惠金额)
+dwd_order_f.freight_amount --[直接复制]--&gt; freight_amount(运费金额)
+dwd_order_f.product_cnt --[直接复制]--&gt; product_cnt(商品种类数)
+dwd_order_f.product_qty --[直接复制]--&gt; product_qty(商品总件数)
+dwd_order_f.order_source --[数据加工]--&gt; order_source_name(订单来源)
+dwd_order_f.order_type --[数据加工]--&gt; order_type_name(订单类型)
+dwd_order_f.remark --[直接复制]--&gt; order_remark(订单备注)
+dwd_order_f.create_time --[数据加工]--&gt; order_date(下单日期)
+dwd_order_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dim_user_f.user_phone --[数据加工]--&gt; user_phone_masked(用户手机(脱敏))
+dim_user_f.user_email --[数据加工]--&gt; user_email_masked(用户邮箱(脱敏))
+dim_user_f.gender --[数据加工]--&gt; gender_name(用户性别)
+dim_user_f.birthday --[直接复制]--&gt; user_birthday(用户生日)
+dim_user_f. --[数据加工]--&gt; user_age(用户年龄)
+dim_user_f.register_time --[直接复制]--&gt; user_register_time(注册时间)
+dim_user_f.level_id --[直接复制]--&gt; user_level_id(用户等级ID)
+dim_user_level_f.level_name --[直接复制]--&gt; user_level_name(用户等级名称)
+dim_user_f.member_points --[直接复制]--&gt; member_points(会员积分)
+dim_user_f.member_balance --[直接复制]--&gt; member_balance(会员余额)
+dwd_order_f. --[数据加工]--&gt; first_order_time(首次下单时间)
+dwd_order_f. --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f. --[数据加工]--&gt; history_order_cnt(历史订单数)
+dwd_order_f. --[数据加工]--&gt; history_pay_amount(历史消费金额)
+dwd_order_f. --[数据加工]--&gt; history_discount_amount(历史优惠金额)
+dwd_order_f. --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f. --[数据加工]--&gt; rfm_segment(用户RFM分层)
+dim_user_f.user_tag --[直接复制]--&gt; user_tag(用户标签)
+dim_user_f.user_source --[数据加工]--&gt; user_source_name(用户来源)
+dim_user_f.province_code --[直接复制]--&gt; user_province_code(用户省份编码)
+dim_user_f.city_code --[直接复制]--&gt; user_city_code(用户城市编码)
+dim_user_f. --[数据加工]--&gt; user_days(用户注册天数)
+dwd_order_f. --[数据加工]--&gt; is_repeat_user(是否复购用户)
+dwd_order_detail_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dim_product_f.product_code --[直接复制]--&gt; product_code(商品编码)
+dwd_order_detail_f.sku_code --[直接复制]--&gt; sku_code(SKU编码)
+dim_product_f.category_id --[直接复制]--&gt; category_l1_id(一级类目ID)
+dim_product_category_f.category_name --[直接复制]--&gt; category_l1_name(一级类目名称)
+dim_product_category_f. --[数据加工]--&gt; category_l2_id(二级类目ID)
+dim_product_category_f. --[数据加工]--&gt; category_l2_name(二级类目名称)
+dim_product_category_f. --[数据加工]--&gt; category_l3_id(三级类目ID)
+dim_product_category_f. --[数据加工]--&gt; category_l3_name(三级类目名称)
+dim_product_f.brand_id --[直接复制]--&gt; brand_id(品牌ID)
+dim_brand_f.brand_name --[直接复制]--&gt; brand_name(品牌名称)
+dim_brand_f.brand_origin --[直接复制]--&gt; brand_origin(品牌产地)
+dim_product_f.product_attr --[直接复制]--&gt; product_attr(商品属性)
+dim_product_f.product_spec --[直接复制]--&gt; product_spec(商品规格)
+dim_product_f.weight --[直接复制]--&gt; product_weight(商品重量(kg))
+dim_product_f.volume --[直接复制]--&gt; product_volume(商品体积(m³))
+dwd_order_detail_f.cost_price --[直接复制]--&gt; cost_price(商品成本价)
+dwd_order_detail_f.sale_price --[直接复制]--&gt; sale_price(商品售价)
+dwd_order_detail_f.real_price --[直接复制]--&gt; real_price(商品实付单价)
+dim_product_f.product_tag --[直接复制]--&gt; product_tag(商品标签)
+dim_product_f.product_status --[数据加工]--&gt; product_status_name(商品状态)
+dwd_order_detail_f. --[数据加工]--&gt; product_sales_cnt(商品累计销量)
+dwd_order_detail_f. --[数据加工]--&gt; product_sales_amount(商品累计销售额)
+dwd_order_detail_f. --[数据加工]--&gt; product_profit(单品毛利)
+dwd_order_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dim_shop_f.shop_type --[数据加工]--&gt; shop_type_name(店铺类型)
+dim_shop_f.shop_level --[数据加工]--&gt; shop_level_name(店铺等级)
+dim_shop_f.shop_score --[直接复制]--&gt; shop_score(店铺评分)
+dim_shop_f.company_name --[直接复制]--&gt; company_name(店铺所属公司)
+dim_shop_f.province_code --[直接复制]--&gt; shop_province_code(店铺省份编码)
+dim_region_f. --[数据加工]--&gt; shop_province_name(店铺省份名称)
+dim_shop_f.city_code --[直接复制]--&gt; shop_city_code(店铺城市编码)
+dim_region_f. --[数据加工]--&gt; shop_city_name(店铺城市名称)
+dim_shop_f.open_time --[直接复制]--&gt; shop_open_time(开店时间)
+dwd_order_f. --[数据加工]--&gt; shop_history_order_cnt(店铺历史订单数)
+dwd_order_f.receiver_name --[直接复制]--&gt; receiver_name(收货人姓名)
+dwd_order_f.receiver_phone --[数据加工]--&gt; receiver_phone_masked(收货人手机(脱敏))
+dwd_order_f.province_code --[直接复制]--&gt; receiver_province_code(收货省份编码)
+dim_region_f.region_name --[直接复制]--&gt; receiver_province_name(收货省份名称)
+dwd_order_f.city_code --[直接复制]--&gt; receiver_city_code(收货城市编码)
+dim_region_f. --[数据加工]--&gt; receiver_city_name(收货城市名称)
+dwd_order_f.district_code --[直接复制]--&gt; r…（截断）</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>任务：为 slord.dwb_order_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单中心宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 150 项，来源表 18 张。
+本规则：R0001（用户画像汇总），step_type=full，目标表 slord.dwb_order_center_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* R0001: 用户画像汇总
+   将订单/支付/优惠券/退款四类事实表按 user_id 聚合，
+   产出用户级画像指标（首次/最近下单、历史消费、RFM分层、复购、偏好），
+   避免主装配阶段聚合导致粒度发散。目标表: slord.dwb_order_center_tmp1 */
+/* CTE 1: 订单核心统计 - 按 user_id 聚合订单时间/订单数/金额汇总 */
+WITH cte_order_stats AS (
+    SELECT
+        user_id,
+        MIN(create_time)                  AS first_order_time,
+        MAX(create_time)                  AS last_order_time,
+        COUNT(*)                          AS history_order_cnt,
+        COALESCE(SUM(pay_amount), 0)      AS history_pay_amount,
+        COALESCE(SUM(discount_amount), 0) AS history_discount_amount
+    FROM sdord.dwd_order_f
+    WHERE del_flag = 'N'
+      AND order_status NOT IN ('CANCELLED', 'DELETED')
+    GROUP BY user_id
+),
+/* CTE 2: 订单衍生指标 - 客单价 / 复购标识 / RFM 三分量(NTILE 自动5等分) */
+cte_order_rfm AS (
+    SELECT
+        os.user_id,
+        os.first_order_time,
+        os.last_order_time,
+        os.history_order_cnt,
+        os.history_pay_amount,
+        os.history_discount_amount,
+        /* 平均客单价 = 历史消费金额 / 历史订单数 (防除零) */
+        CASE
+            WHEN os.history_order_cnt = 0 THEN 0
+            ELSE ROUND(os.history_pay_amount / os.history_order_cnt, 2)
+        END AS avg_order_amount,
+        /* 复购用户: 历史订单数 &gt;= 2 */
+        CASE WHEN os.history_order_cnt &gt;= 2 THEN 'Y' ELSE 'N' END AS is_repeat_user,
+        /* R/F/M 各按数据分布自动5等分 (设计未给阈值, 用 NTILE 兜底) */
+        NTILE(5) OVER (ORDER BY os.last_order_time ASC)     AS r_score,
+        NTILE(5) OVER (ORDER BY os.history_order_cnt ASC)   AS f_score,
+        NTILE(5) OVER (ORDER BY os.history_pay_amount ASC)  AS m_score
+    FROM cte_order_stats os
+),
+/* CTE 3: 活动偏好 - 按 user_id+activity_type 统计参与订单数, 取最多的活动类型 */
+cte_activity_pref AS (
+    SELECT user_id, activity_type
+    FROM (
+        SELECT
+            user_id,
+            activity_type,
+            ROW_NUMBER() OVER (
+                PARTITION BY user_id
+                ORDER BY COUNT(*) DESC, MAX(create_time) DESC
+            ) AS rn
+        FROM sdord.dwd_order_f
+        WHERE del_flag = 'N'
+          AND order_status NOT IN ('CANCELLED', 'DELETED')
+          AND activity_type IS NOT NULL
+        GROUP BY user_id, activity_type
+    ) t
+    WHERE rn = 1
+),
+/* CTE 4: 支付偏好 - 按 user_id+pay_method 统计次数, 取使用最多的支付方式 */
+cte_pay_pref AS (
+    SELECT user_id, pay_method
+    FROM (
+        SELECT
+            user_id,
+            pay_method,
+            ROW_NUMBER() OVER (
+                PARTITION BY user_id
+                ORDER BY COUNT(*) DESC, MAX(create_time) DESC
+            ) AS rn
+        FROM sdpay.dwd_payment_f
+        WHERE del_flag = 'N'
+          AND pay_status = 'SUCCESS'
+        GROUP BY user_id, pay_method
+    ) t
+    WHERE rn = 1
+),
+/* CTE 5: 优惠券统计 - 按 user_id 统计 DISTINCT coupon_id 使用次数 */
+cte_coupon_stats AS (
+    SELECT
+        user_id,
+        COUNT(DISTINCT coupon_id) AS user_coupon_used_cnt
+    FROM sdmar.dwd_coupon_use_f
+    WHERE del_flag = 'N'
+      AND use_status = 'USED'
+    GROUP BY user_id
+),
+/* CTE 6: 退款统计 - 按 user_id 统计退款成功次数 */
+cte_refund_stats AS (
+    SELECT
+        user_id,
+        COUNT(*) AS user_refund_cnt
+    FROM sdref.dwd_refund_f
+    WHERE del_flag = 'N'
+      AND refund_status = 'SUCCESS'
+    GROUP BY user_id
+)
+/* 最终组装: 以 cte_order_rfm 为主表, LEFT JOIN 各 user_id 粒度子聚合 */
+SELECT
+    rf.user_id AS user_id,
+    rf.first_order_time AS first_order_time,
+    rf.last_order_time AS last_order_time,
+    rf.history_order_cnt AS history_order_cnt,
+    rf.history_pay_amount AS history_pay_amount,
+    rf.history_discount_amount AS history_discount_amount,
+    rf.avg_order_amount AS avg_order_amount,
+    /* RFM 三分量组合标签: R{r}F{f}M{m} */
+    CONCAT('R', rf.r_score, 'F', rf.f_score, 'M', rf.m_score) AS rfm_segment,
+    rf.is_repeat_user AS is_repeat_user,
+    /* 常用支付方式, 无支付记录兜底空串 */
+    COALESCE(pp.pay_method, '') AS fav_pay_method,
+    /* 优惠券使用次数, 无记录兜底 0 */
+    COALESCE(cs.user_coupon_used_cnt, 0) AS user_coupon_used_cnt,
+    /* 偏好活动类型, 无活动记录兜底空串 */
+    COALESCE(ap.activity_type, '') AS user_fav_activity_type,
+    /* 历史退款次数, 无退款记录兜底 0 */
+    COALESCE(rs.user_refund_cnt, 0) AS user_refund_cnt,
+    /* 审计字段 (assemble_ddl.py 会给 tmp 表追加审计列, 必带) */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM cte_order_rfm rf
+LEFT JOIN cte_activity_pref ap ON rf.user_id = ap.user_id
+LEFT JOIN cte_pay_pref pp     ON rf.user_id = pp.user_id
+LEFT JOIN cte_coupon_stats cs ON rf.user_id = cs.user_id
+LEFT JOIN cte_refund_stats rs ON rf.user_id = rs.user_id
+——ddl/create_table_dwb_order_center_tmp1.sql——
+/* =====================================================
+   表名: slord.dwb_order_center_tmp1
+   规则: R0001 - 用户画像汇总
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将订单、支付、优惠券、退款四类事实表按 user_id 聚合，产出用户级画像指标（首次/最近下单、历史消费、RFM分层、复购、偏好），避免主装配阶段聚合导致粒度发散
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slord.dwb_order_center_tmp1 (
+    first_order_time        datetime,
+    last_order_time         datetime,
+    history_order_cnt       int,
+    history_pay_amount      decimal(18,2),
+    history_discount_amount decimal(18,2),
+    avg_order_amount        decimal(18,2),
+    rfm_segment             varchar(20),
+    is_repeat_user          varchar(1),
+    fav_pay_method          varchar(20),
+    user_coupon_used_cnt    int,
+    user_fav_activity_type  varchar(50),
+    user_refund_cnt         int,
+    /* 审计字段 */
+    del_flag                NVARCHAR(1),
+    crt_cycle_id            BIGINT,
+    last_upd_cycle_id       BIGINT,
+    dw_last_update_date     TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slord.dwb_order_center_tmp1 IS '订单中心宽表';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.history_discount_amount IS '历史优惠金额';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.rfm_segment IS '用户RFM分层';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.is_repeat_user IS '是否复购用户';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.fav_pay_method IS '用户常用支付方式';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_coupon_used_cnt IS '用户优惠券使用次数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_fav_activity_type IS '用户偏好活动类型';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.user_refund_cnt IS '用户历史退款次数';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slord.dwb_order_center_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_order_center_f</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 12 项：first_order_time, last_order_time, history_order_cnt, history_pay_amount, history_discount_amount, avg_order_amount, rfm_segment, is_repeat_user, fav_pay_method, user_coupon_used_cnt, user_fav_activity_type, user_refund_cnt（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 slord.dwb_order_center_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 12 项）（源→规则→目标）：
+dwd_order_f. --[数据加工]--&gt; first_order_time(首次下单时间)
+dwd_order_f. --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f. --[数据加工]--&gt; history_order_cnt(历史订单数)
+dwd_order_f. --[数据加工]--&gt; history_pay_amount(历史消费金额)
+dwd_order_f. --[数据加工]--&gt; history_discount_amount(历史优惠金额)
+dwd_order_f. --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f. --[数据加工]--&gt; rfm_segment(用户RFM分层)
+dwd_order_f. --[数据加工]--&gt; is_repeat_user(是否复购用户)
+dwd_payment_f. --[数据加工]--&gt; fav_pay_method(用户常用支付方式)
+dwd_coupon_use_f. --[数据加工]--&gt; user_coupon_used_cnt(用户优惠券使用次数)
+dwd_order_f. --[数据加工]--&gt; user_fav_activity_type(用户偏好活动类型)
+dwd_refund_f. --[数据加工]--&gt; user_refund_cnt(用户历史退款次数)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>任务：为 slprd.dwb_product_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：商品中心宽表
+粒度：每行一个商品记录
+调度：全量调度 / T+1，一天一调
+映射字段 39 项，来源表 7 张。</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slprd.dwb_product_center_f`（商品中心宽表） |
+| **I 视图** | `slprd.dwb_product_center_i`（F表镜像，对外查询） |
+| **业务主键** | product_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 39 |
+| **规则数** | 3 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | dim.dim_product_f | 商品维度表 | dpf |
+| 2 | dim.dim_product_category_f | 商品分类维度表 | dpc |
+| 3 | dim.dim_brand_f | 品牌维度表 | dbf |
+| 4 | dim.dim_shop_f | 店铺维度表 | dsf |
+| 5 | sdinv.dwd_inventory_f | 库存事实表 | dif |
+| 6 | sdord.dwd_order_detail_f | 订单商品明细事实表 | dod |
+| 7 | sdrev.dwd_review_f | 评价事实表 | drf |
+---
+——ddl/create_table_dwb_product_center_f.sql——
+/* =====================================================
+   表名: slprd.dwb_product_center_f
+   规则: R0003 - 商品中心宽表组装
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以商品维度表为主表，LEFT JOIN 分类/品牌/店铺/库存 + 中间表汇总指标，组装商品中心宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_center_f (
+    product_id          bigint,
+    product_name        varchar(200),
+    product_code        varchar(50),
+    product_status_name varchar(20),
+    create_time         datetime,
+    on_shelf_time       datetime,
+    cost_price          decimal(18,2),
+    sale_price          decimal(18,2),
+    market_price        decimal(18,2),
+    discount_rate       decimal(5,2),
+    gross_profit        decimal(18,2),
+    gross_profit_rate   decimal(5,2),
+    category_id         bigint,
+    brand_id            bigint,
+    shop_id             bigint,
+    weight              decimal(10,2),
+    volume              decimal(10,4),
+    product_tag         varchar(200),
+    category_name       varchar(100),
+    category_path       varchar(200),
+    brand_name          varchar(100),
+    brand_origin        varchar(50),
+    shop_name           varchar(200),
+    stock_qty           int,
+    locked_qty          int,
+    available_qty       int,
+    warning_qty         int,
+    stock_status        varchar(20),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_center_f IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_code IS '商品编码';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_status_name IS '商品状态';
+COMMENT ON COLUMN slprd.dwb_product_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slprd.dwb_product_center_f.on_shelf_time IS '上架时间';
+COMMENT ON COLUMN slprd.dwb_product_center_f.cost_price IS '成本价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.sale_price IS '销售价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.market_price IS '市场价';
+COMMENT ON COLUMN slprd.dwb_product_center_f.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.gross_profit IS '单品毛利';
+COMMENT ON COLUMN slprd.dwb_product_center_f.gross_profit_rate IS '毛利率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_id IS '分类ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_id IS '品牌ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.weight IS '重量(kg)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.volume IS '体积(m³)';
+COMMENT ON COLUMN slprd.dwb_product_center_f.product_tag IS '商品标签';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_name IS '分类名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.category_path IS '分类路径';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_name IS '品牌名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slprd.dwb_product_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slprd.dwb_product_center_f.stock_qty IS '库存数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.locked_qty IS '锁定数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.available_qty IS '可售数量';
+COMMENT ON COLUMN slprd.dwb_product_center_f.warning_qty IS '库存预警值';
+COMMENT ON COLUMN slprd.dwb_product_center_f.stock_status IS '库存状态';
+COMMENT ON COLUMN slprd.dwb_product_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slprd.dwb_product_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_product_center_tmp1.sql——
+/* =====================================================
+   表名: slprd.dwb_product_center_tmp1
+   规则: R0001 - 订单销售汇总
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将订单明细按商品粒度聚合，收口为每商品一行的销售指标，解耦主规则的聚合复杂度
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_center_tmp1 (
+    total_sales_qty    int,
+    total_sales_amount decimal(18,2),
+    buyer_cnt          int,
+    sales_qty_30d      int,
+    /* 审计字段 */
+    del_flag           NVARCHAR(1),
+    crt_cycle_id       BIGINT,
+    last_upd_cycle_id  BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_center_tmp1 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.total_sales_qty IS '累计销量';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.buyer_cnt IS '购买人数';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.sales_qty_30d IS '近30天销量';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_product_center_tmp2.sql——
+/* =====================================================
+   表名: slprd.dwb_product_center_tmp2
+   规则: R0002 - 评价汇总
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将评价明细按商品粒度聚合，收口为每商品一行的评价指标，与订单汇总并行执行
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_center_tmp2 (
+    review_cnt       int,
+    avg_rating       decimal(2,1),
+    good_review_rate decimal(5,2),
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_center_tmp2 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.review_cnt IS '评价数';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.avg_rating IS '平均评分';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.good_review_rate IS '好评率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp2.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_product_center_i.sql——
+/* I视图: slprd.dwb_product_center_i（商品中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slprd.dwb_product_center_i AS
+SELECT
+    product_id,
+    product_name,
+    product_code,
+    product_status_name,
+    create_time,
+    on_shelf_time,
+    cost_price,
+    sale_price,
+    market_price,
+    discount_rate,
+    gross_profit,
+    gross_profit_rate,
+    category_id,
+    brand_id,
+    shop_id,
+    weight,
+    volume,
+    product_tag,
+    category_name,
+    category_path,
+    brand_name,
+    brand_origin,
+    shop_name,
+    stock_qty,
+    locked_qty,
+    available_qty,
+    warning_qty,
+    stock_status,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slprd.dwb_product_center_f;
+COMMENT ON TABLE slprd.dwb_product_center_i IS '商品中心宽表（视图）';
+COMMENT ON COLUMN slprd.dwb_product_center_i.product_id IS '商品ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.product_name IS '商品名称';
+COMMENT ON COLUMN slprd.dwb_product_center_i.product_code IS '商品编码';
+COMMENT ON COLUMN slprd.dwb_product_center_i.product_status_name IS '商品状态';
+COMMENT ON COLUMN slprd.dwb_product_center_i.create_time IS '创建时间';
+COMMENT ON COLUMN slprd.dwb_product_center_i.on_shelf_time IS '上架时间';
+COMMENT ON COLUMN slprd.dwb_product_center_i.cost_price IS '成本价';
+COMMENT ON COLUMN slprd.dwb_product_center_i.sale_price IS '销售价';
+COMMENT ON COLUMN slprd.dwb_product_center_i.market_price IS '市场价';
+COMMENT ON COLUMN slprd.dwb_product_center_i.discount_rate IS '折扣率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_i.gross_profit IS '单品毛利';
+COMMENT ON COLUMN slprd.dwb_product_center_i.gross_profit_rate IS '毛利率(%)';
+COMMENT ON COLUMN slprd.dwb_product_center_i.category_id IS '分类ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.brand_id IS '品牌ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.shop_id IS '店铺ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.weight IS '重量(kg)';
+COMMENT ON COLUMN slprd.dwb_product_center_i.volume IS '体积(m³)';
+COMMENT ON COLUMN slprd.dwb_product_center_i.product_tag IS '商品标签';
+COMMENT ON COLUMN slprd.dwb_product_center_i.category_name IS '分类名称';
+COMMENT ON COLUMN slprd.dwb_product_center_i.category_path IS '分类路径';
+COMMENT ON COLUMN slprd.dwb_product_center_i.brand_name IS '品牌名称';
+COMMENT ON COLUMN slprd.dwb_product_center_i.brand_origin IS '品牌产地';
+COMMENT ON COLUMN slprd.dwb_product_center_i.shop_name IS '店铺名称';
+COMMENT ON COLUMN slprd.dwb_product_center_i.stock_qty IS '库存数量';
+COMMENT ON COLUMN slprd.dwb_product_center_i.locked_qty IS '锁定数量';
+COMMENT ON COLUMN slprd.dwb_product_center_i.available_qty IS '可售数量';
+COMMENT ON COLUMN slprd.dwb_product_center_i.warning_qty IS '库存预警值';
+COMMENT ON COLUMN slprd.dwb_product_center_i.stock_status IS '库存状态';
+COMMENT ON COLUMN slprd.dwb_product_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slprd.dwb_product_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_i.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* =====================================================
+   ETL 转换脚本（SELECT 部分）
+   规则: R0001 订单销售汇总
+   目标表: slprd.dwb_product_center_tmp1（中间表）
+   来源表:
+     - sdord.dwd_order_detail_f dod
+   粒度: 输入=一条订单商品明细, 输出=一个商品, 多行聚合
+   写入方式: truncate_table
+   设计意图: 将订单明细按商品粒度聚合，收口为每商品一行的销售指标
+   =====================================================
+   假设说明:
+   - 订单日期字段在 ts.json design_logic 中仅写"订单日期"，未给出具体字段名；
+     本脚本按 DWS 字段命名规范（_date 后缀 = DATE 类型）假设为 order_date。
+     若源表实际为 create_time / order_time 等其它字段，请相应替换。
+   ===================================================== */
+SELECT
+    dod.product_id AS product_id,                              /* 分组键/业务主键 */
+    /* 累计销量: 按 product_id 汇总 SUM(qty) */
+    COALESCE(SUM(dod.qty), 0) AS total_sales_qty,
+    /* 累计销售额: 按 product_id 汇总 SUM(real_price * qty) */
+    COALESCE(SUM(dod.real_price * dod.qty), 0) AS total_sales_amount,
+    /* 购买人数: 按 product_id 去重计数 user_id */
+    COUNT(DISTINCT dod.user_id) AS buyer_cnt,
+    /* 近30天销量: 按 product_id 汇总近30天 SUM(qty)，无记录返回0 */
+    COALESCE(
+        SUM(
+            CASE
+                WHEN dod.order_date &gt;= CURRENT_DATE - INTERVAL '30 day'
+                    THEN dod.qty
+                ELSE 0
+            END
+        ),
+        0
+    ) AS sales_qty_30d,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_detail_f dod
+WHERE COALESCE(dod.del_flag, 'N') = 'N'                        /* 排除逻辑删除行 */
+GROUP BY dod.product_id;
+——dq/dq_dwb_product_center_f.sql——
+-- ============================================================
+-- DQ 检查: slprd.dwb_product_center_f
+-- 规则: R0003
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: product_id）
+SELECT product_id, COUNT(*) AS cnt
+FROM slprd.dwb_product_center_f
+GROUP BY product_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slprd.dwb_product_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slprd.dwb_product_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slprd.dwb_product_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slprd.dwb_product_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slprd.dwb_product_center_f;
+档案来源：../10_project_deliver/dwb_product_center_f</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slprd.dwb_product_center_f，粒度：每行一个商品记录
+- 目标字段 39 项：product_id, product_name, product_code, product_status_name, create_time, on_shelf_time, cost_price, sale_price, market_price, discount_rate, gross_profit, gross_profit_rate, category_id, category_name, category_path, brand_id, brand_name, brand_origin, shop_id, shop_name, stock_qty, locked_qty, available_qty, warning_qty, stock_status, total_sales_qty, total_sales_amount, buyer_cnt, sales_qty_30d, review_cnt, avg_rating, good_review_rate, weight, volume, product_tag, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 7 张：dim_product_f, dim_product_category_f, dim_brand_f, dim_shop_f, dwd_inventory_f, dwd_order_detail_f, dwd_review_f
+- 建表 DDL（create_table_dwb_product_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 39 项（源→规则→目标）：
+dim_product_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dim_product_f.product_code --[直接复制]--&gt; product_code(商品编码)
+dim_product_f.product_status --[数据加工]--&gt; product_status_name(商品状态)
+dim_product_f.create_time --[直接复制]--&gt; create_time(创建时间)
+dim_product_f.on_shelf_time --[直接复制]--&gt; on_shelf_time(上架时间)
+dim_product_f.cost_price --[直接复制]--&gt; cost_price(成本价)
+dim_product_f.sale_price --[直接复制]--&gt; sale_price(销售价)
+dim_product_f.market_price --[直接复制]--&gt; market_price(市场价)
+（无源声明） --[数据加工]--&gt; discount_rate(折扣率(%))
+（无源声明） --[数据加工]--&gt; gross_profit(单品毛利)
+（无源声明） --[数据加工]--&gt; gross_profit_rate(毛利率(%))
+dim_product_f.category_id --[直接复制]--&gt; category_id(分类ID)
+dim_product_category_f.category_name --[直接复制]--&gt; category_name(分类名称)
+dim_product_category_f.category_path --[直接复制]--&gt; category_path(分类路径)
+dim_product_f.brand_id --[直接复制]--&gt; brand_id(品牌ID)
+dim_brand_f.brand_name --[直接复制]--&gt; brand_name(品牌名称)
+dim_brand_f.brand_origin --[直接复制]--&gt; brand_origin(品牌产地)
+dim_product_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; stock_qty(库存数量)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定数量)
+（无源声明） --[数据加工]--&gt; available_qty(可售数量)
+dwd_inventory_f.warning_qty --[直接复制]--&gt; warning_qty(库存预警值)
+（无源声明） --[数据加工]--&gt; stock_status(库存状态)
+（无源声明） --[数据加工]--&gt; total_sales_qty(累计销量)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; buyer_cnt(购买人数)
+（无源声明） --[数据加工]--&gt; sales_qty_30d(近30天销量)
+（无源声明） --[数据加工]--&gt; review_cnt(评价数)
+（无源声明） --[数据加工]--&gt; avg_rating(平均评分)
+（无源声明） --[数据加工]--&gt; good_review_rate(好评率(%))
+dim_product_f.weight --[直接复制]--&gt; weight(重量(kg))
+dim_product_f.volume --[直接复制]--&gt; volume(体积(m³))
+dim_product_f.product_tag --[直接复制]--&gt; product_tag(商品标签)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>任务：为 slprd.dwb_product_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：商品中心宽表
+粒度：每行一个商品记录
+调度：全量调度 / T+1，一天一调
+映射字段 39 项，来源表 7 张。
+本规则：R0001（订单销售汇总），step_type=full，目标表 dwb_product_center_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* =====================================================
+   ETL 转换脚本（SELECT 部分）
+   规则: R0001 订单销售汇总
+   目标表: slprd.dwb_product_center_tmp1（中间表）
+   来源表:
+     - sdord.dwd_order_detail_f dod
+   粒度: 输入=一条订单商品明细, 输出=一个商品, 多行聚合
+   写入方式: truncate_table
+   设计意图: 将订单明细按商品粒度聚合，收口为每商品一行的销售指标
+   =====================================================
+   假设说明:
+   - 订单日期字段在 ts.json design_logic 中仅写"订单日期"，未给出具体字段名；
+     本脚本按 DWS 字段命名规范（_date 后缀 = DATE 类型）假设为 order_date。
+     若源表实际为 create_time / order_time 等其它字段，请相应替换。
+   ===================================================== */
+SELECT
+    dod.product_id AS product_id,                              /* 分组键/业务主键 */
+    /* 累计销量: 按 product_id 汇总 SUM(qty) */
+    COALESCE(SUM(dod.qty), 0) AS total_sales_qty,
+    /* 累计销售额: 按 product_id 汇总 SUM(real_price * qty) */
+    COALESCE(SUM(dod.real_price * dod.qty), 0) AS total_sales_amount,
+    /* 购买人数: 按 product_id 去重计数 user_id */
+    COUNT(DISTINCT dod.user_id) AS buyer_cnt,
+    /* 近30天销量: 按 product_id 汇总近30天 SUM(qty)，无记录返回0 */
+    COALESCE(
+        SUM(
+            CASE
+                WHEN dod.order_date &gt;= CURRENT_DATE - INTERVAL '30 day'
+                    THEN dod.qty
+                ELSE 0
+            END
+        ),
+        0
+    ) AS sales_qty_30d,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_detail_f dod
+WHERE COALESCE(dod.del_flag, 'N') = 'N'                        /* 排除逻辑删除行 */
+GROUP BY dod.product_id;
+——ddl/create_table_dwb_product_center_tmp1.sql——
+/* =====================================================
+   表名: slprd.dwb_product_center_tmp1
+   规则: R0001 - 订单销售汇总
+   分布键: product_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 将订单明细按商品粒度聚合，收口为每商品一行的销售指标，解耦主规则的聚合复杂度
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slprd.dwb_product_center_tmp1 (
+    total_sales_qty    int,
+    total_sales_amount decimal(18,2),
+    buyer_cnt          int,
+    sales_qty_30d      int,
+    /* 审计字段 */
+    del_flag           NVARCHAR(1),
+    crt_cycle_id       BIGINT,
+    last_upd_cycle_id  BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(product_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slprd.dwb_product_center_tmp1 IS '商品中心宽表';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.total_sales_qty IS '累计销量';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.buyer_cnt IS '购买人数';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.sales_qty_30d IS '近30天销量';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slprd.dwb_product_center_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_product_center_f</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 4 项：total_sales_qty, total_sales_amount, buyer_cnt, sales_qty_30d（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 dwb_product_center_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 4 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; total_sales_qty(累计销量)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; buyer_cnt(购买人数)
+（无源声明） --[数据加工]--&gt; sales_qty_30d(近30天销量)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>任务：为 slshp.dwb_shop_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：店铺中心宽表
+粒度：每行一个店铺记录
+调度：全量调度 / T+1，一天一调
+映射字段 20 项，来源表 4 张。</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slshp.dwb_shop_center_f`（店铺中心宽表） |
+| **I 视图** | `slshp.dwb_shop_center_i`（F表镜像，对外查询） |
+| **业务主键** | shop_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 20 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | dim.dim_shop_f | 店铺维度表 | dsf |
+| 2 | dim.dim_region_f | 地区维度表 | drf |
+| 3 | sdord.dwd_order_f | 订单明细事实表 | dof |
+| 4 | sdrev.dwd_review_f | 评价事实表 | drf3 |
+---
+——ddl/create_table_dwb_shop_center_f.sql——
+/* =====================================================
+   表名: slshp.dwb_shop_center_f
+   规则: R0001 - 店铺中心宽表组装
+   分布键: shop_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以店铺维度表为主表，LEFT JOIN 地区维度表获取省份名称； 通过 CTE 预聚合订单/评价事实表到店铺粒度，避免多表直接 JOIN 的 fan-out； 标量加工字段（类型/状态映射、营业天数）在主表行内计算。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slshp.dwb_shop_center_f (
+    shop_id             bigint,
+    shop_name           varchar(200),
+    shop_type_name      varchar(50),
+    shop_status_name    varchar(50),
+    company_name        varchar(200),
+    open_time           datetime,
+    open_days           int,
+    province_code       varchar(20),
+    province_name       varchar(50),
+    shop_score          decimal(3,2),
+    service_score       decimal(3,2),
+    logistics_score     decimal(3,2),
+    total_order_cnt     int,
+    total_sales_amount  decimal(18,2),
+    total_buyer_cnt     int,
+    review_cnt          int,
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(shop_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slshp.dwb_shop_center_f IS '店铺中心宽表';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_status_name IS '店铺状态';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.company_name IS '公司名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_time IS '开店时间';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_days IS '营业天数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_score IS '店铺评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.service_score IS '服务评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.logistics_score IS '物流评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_order_cnt IS '累计订单数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_buyer_cnt IS '累计购买人数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.review_cnt IS '评价数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_shop_center_i.sql——
+/* I视图: slshp.dwb_shop_center_i（店铺中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slshp.dwb_shop_center_i AS
+SELECT
+    shop_id,
+    shop_name,
+    shop_type_name,
+    shop_status_name,
+    company_name,
+    open_time,
+    open_days,
+    province_code,
+    province_name,
+    shop_score,
+    service_score,
+    logistics_score,
+    total_order_cnt,
+    total_sales_amount,
+    total_buyer_cnt,
+    review_cnt,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slshp.dwb_shop_center_f;
+COMMENT ON TABLE slshp.dwb_shop_center_i IS '店铺中心宽表（视图）';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.shop_id IS '店铺ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.shop_name IS '店铺名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.shop_status_name IS '店铺状态';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.company_name IS '公司名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.open_time IS '开店时间';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.open_days IS '营业天数';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.province_code IS '省份编码';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.province_name IS '省份名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.shop_score IS '店铺评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.service_score IS '服务评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.logistics_score IS '物流评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.total_order_cnt IS '累计订单数';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.total_buyer_cnt IS '累计购买人数';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.review_cnt IS '评价数';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_i.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* =====================================================
+   R0001: 店铺中心宽表组装
+   目标表: slshp.dwb_shop_center_f
+   设计意图:
+     以店铺维度表为主表，LEFT JOIN 地区维度表获取省份名称；
+     通过 CTE 预聚合订单/评价事实表到店铺粒度，避免多表直接 JOIN 的 fan-out；
+     标量加工字段（类型/状态映射、营业天数）在主表行内计算。
+   来源表:
+     - dim.dim_shop_f   dsf   (主表)
+     - dim.dim_region_f drf   (地区维)
+     - sdord.dwd_order_f dof  (订单事实，经 CTE 收敛)
+     - sdrev.dwd_review_f drf3 (评价事实，经 CTE 收敛)
+   粒度: 一行 = 一个店铺
+   ===================================================== */
+WITH
+/* CTE 1: 订单统计预聚合 —— 从 dwd_order_f 按 shop_id 收敛到店铺粒度
+   关联安全策略: 事实表一对多，GROUP BY shop_id 保证 JOIN 键唯一，避免 fan-out */
+order_stat AS (
+    SELECT
+        dof.shop_id AS shop_id,
+        COUNT(1) AS total_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0) AS total_sales_amount,
+        COUNT(DISTINCT dof.user_id) AS total_buyer_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE dof.del_flag = 'N'
+    GROUP BY dof.shop_id
+),
+/* CTE 2: 评价统计预聚合 —— 从 dwd_review_f 按 shop_id 收敛到店铺粒度 */
+review_stat AS (
+    SELECT
+        drf3.shop_id AS shop_id,
+        COUNT(1) AS review_cnt
+    FROM sdrev.dwd_review_f drf3
+    WHERE drf3.del_flag = 'N'
+    GROUP BY drf3.shop_id
+)
+/* 主查询: 店铺维为主表，LEFT JOIN 地区维 + 两个预聚合 CTE */
+SELECT
+    dsf.shop_id AS shop_id,
+    dsf.shop_name AS shop_name,
+    /* 店铺类型中文映射 */
+    CASE dsf.shop_type
+        WHEN 'FLAGSHIP'  THEN '旗舰店'
+        WHEN 'SPECIALTY' THEN '专卖店'
+        WHEN 'FRANCHISE' THEN '专营店'
+        ELSE '其他'
+    END AS shop_type_name,
+    /* 店铺状态中文映射 */
+    CASE dsf.shop_status
+        WHEN 'OPEN'   THEN '营业中'
+        WHEN 'CLOSED' THEN '已关闭'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS shop_status_name,
+    dsf.company_name AS company_name,
+    dsf.open_time AS open_time,
+    /* 营业天数 = 当前日期 - 开店日期的天数差（DWS: 日期相减得到天数整型） */
+    COALESCE(CAST(CURRENT_DATE - CAST(dsf.open_time AS DATE) AS INT), 0) AS open_days,
+    dsf.province_code AS province_code,
+    drf.region_name AS province_name,
+    dsf.shop_score AS shop_score,
+    dsf.service_score AS service_score,
+    dsf.logistics_score AS logistics_score,
+    /* 订单聚合指标：CTE LEFT JOIN 结果，NULL 兜底为 0 */
+    COALESCE(order_stat.total_order_cnt, 0) AS total_order_cnt,
+    COALESCE(order_stat.total_sales_amount, 0) AS total_sales_amount,
+    COALESCE(order_stat.total_buyer_cnt, 0) AS total_buyer_cnt,
+    /* 评价聚合指标：CTE LEFT JOIN 结果，NULL 兜底为 0 */
+    COALESCE(review_stat.review_cnt, 0) AS review_cnt,
+    /* 审计字段（4个） */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_shop_f dsf
+LEFT JOIN dim.dim_region_f drf
+    ON dsf.province_code = drf.region_code
+    AND drf.del_flag = 'N'
+LEFT JOIN order_stat
+    ON dsf.shop_id = order_stat.shop_id
+LEFT JOIN review_stat
+    ON dsf.shop_id = review_stat.shop_id
+WHERE dsf.del_flag = 'N';
+——dq/dq_dwb_shop_center_f.sql——
+-- ============================================================
+-- DQ 检查: slshp.dwb_shop_center_f
+-- 规则: R0001
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: shop_id）
+SELECT shop_id, COUNT(*) AS cnt
+FROM slshp.dwb_shop_center_f
+GROUP BY shop_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slshp.dwb_shop_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slshp.dwb_shop_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slshp.dwb_shop_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slshp.dwb_shop_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slshp.dwb_shop_center_f;
+档案来源：../10_project_deliver/dwb_shop_center_f</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slshp.dwb_shop_center_f，粒度：每行一个店铺记录
+- 目标字段 20 项：shop_id, shop_name, shop_type_name, shop_status_name, company_name, open_time, open_days, province_code, province_name, shop_score, service_score, logistics_score, total_order_cnt, total_sales_amount, total_buyer_cnt, review_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 4 张：dim_shop_f, dim_region_f, dwd_order_f, dwd_review_f
+- 建表 DDL（create_table_dwb_shop_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 20 项（源→规则→目标）：
+dim_shop_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dim_shop_f.shop_type --[数据加工]--&gt; shop_type_name(店铺类型)
+dim_shop_f.shop_status --[数据加工]--&gt; shop_status_name(店铺状态)
+dim_shop_f.company_name --[直接复制]--&gt; company_name(公司名称)
+dim_shop_f.open_time --[直接复制]--&gt; open_time(开店时间)
+（无源声明） --[数据加工]--&gt; open_days(营业天数)
+dim_shop_f.province_code --[直接复制]--&gt; province_code(省份编码)
+dim_region_f.region_name --[直接复制]--&gt; province_name(省份名称)
+dim_shop_f.shop_score --[直接复制]--&gt; shop_score(店铺评分)
+dim_shop_f.service_score --[直接复制]--&gt; service_score(服务评分)
+dim_shop_f.logistics_score --[直接复制]--&gt; logistics_score(物流评分)
+（无源声明） --[数据加工]--&gt; total_order_cnt(累计订单数)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; total_buyer_cnt(累计购买人数)
+（无源声明） --[数据加工]--&gt; review_cnt(评价数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>任务：为 slshp.dwb_shop_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：店铺中心宽表
+粒度：每行一个店铺记录
+调度：全量调度 / T+1，一天一调
+映射字段 20 项，来源表 4 张。
+本规则：R0001（店铺中心宽表组装），step_type=full，目标表 slshp.dwb_shop_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* =====================================================
+   R0001: 店铺中心宽表组装
+   目标表: slshp.dwb_shop_center_f
+   设计意图:
+     以店铺维度表为主表，LEFT JOIN 地区维度表获取省份名称；
+     通过 CTE 预聚合订单/评价事实表到店铺粒度，避免多表直接 JOIN 的 fan-out；
+     标量加工字段（类型/状态映射、营业天数）在主表行内计算。
+   来源表:
+     - dim.dim_shop_f   dsf   (主表)
+     - dim.dim_region_f drf   (地区维)
+     - sdord.dwd_order_f dof  (订单事实，经 CTE 收敛)
+     - sdrev.dwd_review_f drf3 (评价事实，经 CTE 收敛)
+   粒度: 一行 = 一个店铺
+   ===================================================== */
+WITH
+/* CTE 1: 订单统计预聚合 —— 从 dwd_order_f 按 shop_id 收敛到店铺粒度
+   关联安全策略: 事实表一对多，GROUP BY shop_id 保证 JOIN 键唯一，避免 fan-out */
+order_stat AS (
+    SELECT
+        dof.shop_id AS shop_id,
+        COUNT(1) AS total_order_cnt,
+        COALESCE(SUM(dof.pay_amount), 0) AS total_sales_amount,
+        COUNT(DISTINCT dof.user_id) AS total_buyer_cnt
+    FROM sdord.dwd_order_f dof
+    WHERE dof.del_flag = 'N'
+    GROUP BY dof.shop_id
+),
+/* CTE 2: 评价统计预聚合 —— 从 dwd_review_f 按 shop_id 收敛到店铺粒度 */
+review_stat AS (
+    SELECT
+        drf3.shop_id AS shop_id,
+        COUNT(1) AS review_cnt
+    FROM sdrev.dwd_review_f drf3
+    WHERE drf3.del_flag = 'N'
+    GROUP BY drf3.shop_id
+)
+/* 主查询: 店铺维为主表，LEFT JOIN 地区维 + 两个预聚合 CTE */
+SELECT
+    dsf.shop_id AS shop_id,
+    dsf.shop_name AS shop_name,
+    /* 店铺类型中文映射 */
+    CASE dsf.shop_type
+        WHEN 'FLAGSHIP'  THEN '旗舰店'
+        WHEN 'SPECIALTY' THEN '专卖店'
+        WHEN 'FRANCHISE' THEN '专营店'
+        ELSE '其他'
+    END AS shop_type_name,
+    /* 店铺状态中文映射 */
+    CASE dsf.shop_status
+        WHEN 'OPEN'   THEN '营业中'
+        WHEN 'CLOSED' THEN '已关闭'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS shop_status_name,
+    dsf.company_name AS company_name,
+    dsf.open_time AS open_time,
+    /* 营业天数 = 当前日期 - 开店日期的天数差（DWS: 日期相减得到天数整型） */
+    COALESCE(CAST(CURRENT_DATE - CAST(dsf.open_time AS DATE) AS INT), 0) AS open_days,
+    dsf.province_code AS province_code,
+    drf.region_name AS province_name,
+    dsf.shop_score AS shop_score,
+    dsf.service_score AS service_score,
+    dsf.logistics_score AS logistics_score,
+    /* 订单聚合指标：CTE LEFT JOIN 结果，NULL 兜底为 0 */
+    COALESCE(order_stat.total_order_cnt, 0) AS total_order_cnt,
+    COALESCE(order_stat.total_sales_amount, 0) AS total_sales_amount,
+    COALESCE(order_stat.total_buyer_cnt, 0) AS total_buyer_cnt,
+    /* 评价聚合指标：CTE LEFT JOIN 结果，NULL 兜底为 0 */
+    COALESCE(review_stat.review_cnt, 0) AS review_cnt,
+    /* 审计字段（4个） */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_shop_f dsf
+LEFT JOIN dim.dim_region_f drf
+    ON dsf.province_code = drf.region_code
+    AND drf.del_flag = 'N'
+LEFT JOIN order_stat
+    ON dsf.shop_id = order_stat.shop_id
+LEFT JOIN review_stat
+    ON dsf.shop_id = review_stat.shop_id
+WHERE dsf.del_flag = 'N';
+——ddl/create_table_dwb_shop_center_f.sql——
+/* =====================================================
+   表名: slshp.dwb_shop_center_f
+   规则: R0001 - 店铺中心宽表组装
+   分布键: shop_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以店铺维度表为主表，LEFT JOIN 地区维度表获取省份名称； 通过 CTE 预聚合订单/评价事实表到店铺粒度，避免多表直接 JOIN 的 fan-out； 标量加工字段（类型/状态映射、营业天数）在主表行内计算。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slshp.dwb_shop_center_f (
+    shop_id             bigint,
+    shop_name           varchar(200),
+    shop_type_name      varchar(50),
+    shop_status_name    varchar(50),
+    company_name        varchar(200),
+    open_time           datetime,
+    open_days           int,
+    province_code       varchar(20),
+    province_name       varchar(50),
+    shop_score          decimal(3,2),
+    service_score       decimal(3,2),
+    logistics_score     decimal(3,2),
+    total_order_cnt     int,
+    total_sales_amount  decimal(18,2),
+    total_buyer_cnt     int,
+    review_cnt          int,
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(shop_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slshp.dwb_shop_center_f IS '店铺中心宽表';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_id IS '店铺ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_name IS '店铺名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_type_name IS '店铺类型';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_status_name IS '店铺状态';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.company_name IS '公司名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_time IS '开店时间';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.open_days IS '营业天数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.shop_score IS '店铺评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.service_score IS '服务评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.logistics_score IS '物流评分';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_order_cnt IS '累计订单数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_sales_amount IS '累计销售额';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.total_buyer_cnt IS '累计购买人数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.review_cnt IS '评价数';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slshp.dwb_shop_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_shop_center_f</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 20 项：shop_id, shop_name, shop_type_name, shop_status_name, company_name, open_time, open_days, province_code, province_name, shop_score, service_score, logistics_score, total_order_cnt, total_sales_amount, total_buyer_cnt, review_cnt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 slshp.dwb_shop_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 20 项）（源→规则→目标）：
+dim_shop_f.shop_id --[直接复制]--&gt; shop_id(店铺ID)
+dim_shop_f.shop_name --[直接复制]--&gt; shop_name(店铺名称)
+dim_shop_f.shop_type --[数据加工]--&gt; shop_type_name(店铺类型)
+dim_shop_f.shop_status --[数据加工]--&gt; shop_status_name(店铺状态)
+dim_shop_f.company_name --[直接复制]--&gt; company_name(公司名称)
+dim_shop_f.open_time --[直接复制]--&gt; open_time(开店时间)
+（无源声明） --[数据加工]--&gt; open_days(营业天数)
+dim_shop_f.province_code --[直接复制]--&gt; province_code(省份编码)
+dim_region_f.region_name --[直接复制]--&gt; province_name(省份名称)
+dim_shop_f.shop_score --[直接复制]--&gt; shop_score(店铺评分)
+dim_shop_f.service_score --[直接复制]--&gt; service_score(服务评分)
+dim_shop_f.logistics_score --[直接复制]--&gt; logistics_score(物流评分)
+（无源声明） --[数据加工]--&gt; total_order_cnt(累计订单数)
+（无源声明） --[数据加工]--&gt; total_sales_amount(累计销售额)
+（无源声明） --[数据加工]--&gt; total_buyer_cnt(累计购买人数)
+（无源声明） --[数据加工]--&gt; review_cnt(评价数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>任务：为 slscc.dwb_supply_chain_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：供应链中心宽表
+粒度：每行一个供应链记录
+调度：全量调度 / T+1，一天一调
+映射字段 23 项，来源表 6 张。</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slscc.dwb_supply_chain_center_f`（供应链中心宽表） |
+| **I 视图** | `slscc.dwb_supply_chain_center_i`（F表镜像，对外查询） |
+| **业务主键** | purchase_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 23 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | sdinv.dwd_purchase_f | 采购事实表 | dpf |
+| 2 | dim.dim_supplier_f | 供应商维度表 | dsf |
+| 3 | dim.dim_product_f | 商品维度表 | dpf2 |
+| 4 | dim.dim_warehouse_f | 仓库维度表 | dwf |
+| 5 | sdinv.dwd_inventory_f | 库存事实表 | dif |
+| 6 | sdinv.dwd_sales_f | 销售事实表 | dsales |
+---
+——ddl/create_table_dwb_supply_chain_center_f.sql——
+/* =====================================================
+   表名: slscc.dwb_supply_chain_center_f
+   规则: R0001 - 供应链中心宽表写入
+   分布键: purchase_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以采购事实表(dp)为主表锚定粒度，LEFT JOIN 供应商/商品/仓库维度表补充属性，LEFT JOIN 库存事实表取当前库存与锁定库存，通过CTE预聚合销售表按product_id统计近30天销量后关联，计算库存周转天数，写入供应链中心宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slscc.dwb_supply_chain_center_f (
+    purchase_id          bigint,
+    purchase_no          varchar(64),
+    purchase_status_name varchar(50),
+    create_time          datetime,
+    supplier_id          bigint,
+    product_id           bigint,
+    purchase_qty         int,
+    purchase_price       decimal(18,2),
+    purchase_amount      decimal(18,2),
+    warehouse_id         bigint,
+    supplier_name        varchar(200),
+    supplier_level_name  varchar(50),
+    cooperation_years    int,
+    product_name         varchar(200),
+    warehouse_name       varchar(100),
+    warehouse_type_name  varchar(50),
+    current_stock_qty    int,
+    locked_qty           int,
+    stock_days           int,
+    del_flag             NVARCHAR(1),
+    crt_cycle_id         BIGINT,
+    last_upd_cycle_id    BIGINT,
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(purchase_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slscc.dwb_supply_chain_center_f IS '供应链中心宽表';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_id IS '采购单ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_no IS '采购单号';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_status_name IS '采购状态';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_id IS '供应商ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_qty IS '采购数量';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_price IS '采购单价';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_amount IS '采购金额';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_id IS '仓库ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_name IS '供应商名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_level_name IS '供应商等级';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.cooperation_years IS '合作年限';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_name IS '仓库名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_type_name IS '仓库类型';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.current_stock_qty IS '当前库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.locked_qty IS '锁定库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.stock_days IS '库存周转天数';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_supply_chain_center_i.sql——
+/* I视图: slscc.dwb_supply_chain_center_i（供应链中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slscc.dwb_supply_chain_center_i AS
+SELECT
+    purchase_id,
+    purchase_no,
+    purchase_status_name,
+    create_time,
+    supplier_id,
+    product_id,
+    purchase_qty,
+    purchase_price,
+    purchase_amount,
+    warehouse_id,
+    supplier_name,
+    supplier_level_name,
+    cooperation_years,
+    product_name,
+    warehouse_name,
+    warehouse_type_name,
+    current_stock_qty,
+    locked_qty,
+    stock_days,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slscc.dwb_supply_chain_center_f;
+COMMENT ON TABLE slscc.dwb_supply_chain_center_i IS '供应链中心宽表（视图）';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_id IS '采购单ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_no IS '采购单号';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_status_name IS '采购状态';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.create_time IS '创建时间';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.supplier_id IS '供应商ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.product_id IS '商品ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_qty IS '采购数量';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_price IS '采购单价';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.purchase_amount IS '采购金额';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.warehouse_id IS '仓库ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.supplier_name IS '供应商名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.supplier_level_name IS '供应商等级';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.cooperation_years IS '合作年限';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.product_name IS '商品名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.warehouse_name IS '仓库名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.warehouse_type_name IS '仓库类型';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.current_stock_qty IS '当前库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.locked_qty IS '锁定库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.stock_days IS '库存周转天数';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_i.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* =====================================================
+   R0001: 供应链中心宽表写入
+   目标表: slscc.dwb_supply_chain_center_f
+   设计意图: 以采购事实表(dpf)为主表锚定粒度，LEFT JOIN 供应商/商品/仓库
+             维度表补充属性，LEFT JOIN 库存事实表取当前库存与锁定库存，
+             通过CTE预聚合销售表按product_id统计近30天销量后关联，
+             计算库存周转天数，写入供应链中心宽表
+   ===================================================== */
+/* CTE: 销售事实表按product_id预聚合近30天销量，收敛到商品粒度避免JOIN发散 */
+WITH sales_agg AS (
+    SELECT
+        dsales.product_id AS product_id,
+        COALESCE(SUM(dsales.sales_qty_30d), 0) AS sales_qty_30d_sum
+    FROM sdinv.dwd_sales_f dsales
+    WHERE dsales.del_flag = 'N'
+    GROUP BY dsales.product_id
+)
+SELECT
+    dpf.purchase_id AS purchase_id,
+    dpf.purchase_no AS purchase_no,
+    /* 采购状态码转中文映射 */
+    CASE dpf.purchase_status
+        WHEN 'DRAFT' THEN '草稿'
+        WHEN 'SUBMITTED' THEN '已提交'
+        WHEN 'APPROVED' THEN '已审批'
+        WHEN 'RECEIVED' THEN '已入库'
+        WHEN 'CLOSED' THEN '已关闭'
+        ELSE '其他'
+    END AS purchase_status_name,
+    dpf.create_time AS create_time,
+    dpf.supplier_id AS supplier_id,
+    dpf.product_id AS product_id,
+    dpf.purchase_qty AS purchase_qty,
+    dpf.purchase_price AS purchase_price,
+    /* 采购金额 = 采购数量 × 采购单价 */
+    COALESCE(dpf.purchase_qty, 0) * COALESCE(dpf.purchase_price, 0) AS purchase_amount,
+    dpf.warehouse_id AS warehouse_id,
+    COALESCE(dsf.supplier_name, '') AS supplier_name,
+    /* 供应商等级码转中文映射 */
+    CASE dsf.supplier_level
+        WHEN 'A' THEN 'A级供应商'
+        WHEN 'B' THEN 'B级供应商'
+        WHEN 'C' THEN 'C级供应商'
+        ELSE '其他'
+    END AS supplier_level_name,
+    COALESCE(dsf.cooperation_years, 0) AS cooperation_years,
+    COALESCE(dpf2.product_name, '') AS product_name,
+    COALESCE(dwf.warehouse_name, '') AS warehouse_name,
+    /* 仓库类型码转中文映射 */
+    CASE dwf.warehouse_type
+        WHEN 'SELF' THEN '自营仓'
+        WHEN 'THIRD_PARTY' THEN '第三方仓'
+        ELSE '其他'
+    END AS warehouse_type_name,
+    COALESCE(dif.stock_qty, 0) AS current_stock_qty,
+    COALESCE(dif.locked_qty, 0) AS locked_qty,
+    /* 库存周转天数 = (当前库存 - 锁定库存) / 近30天销量，除零保护用NULLIF */
+    (COALESCE(dif.stock_qty, 0) - COALESCE(dif.locked_qty, 0))
+        / NULLIF(sales_agg.sales_qty_30d_sum, 0) AS stock_days,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdinv.dwd_purchase_f dpf
+LEFT JOIN dim.dim_supplier_f dsf
+    ON dpf.supplier_id = dsf.supplier_id
+    AND dsf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf2
+    ON dpf.product_id = dpf2.product_id
+    AND dpf2.del_flag = 'N'
+LEFT JOIN dim.dim_warehouse_f dwf
+    ON dpf.warehouse_id = dwf.warehouse_id
+    AND dwf.del_flag = 'N'
+LEFT JOIN sdinv.dwd_inventory_f dif
+    ON dpf.product_id = dif.product_id
+    AND dpf.warehouse_id = dif.warehouse_id
+    AND dif.del_flag = 'N'
+LEFT JOIN sales_agg
+    ON dpf.product_id = sales_agg.product_id
+WHERE dpf.del_flag = 'N';
+——dq/dq_dwb_supply_chain_center_f.sql——
+-- ============================================================
+-- DQ 检查: slscc.dwb_supply_chain_center_f
+-- 规则: R0001
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: purchase_id）
+SELECT purchase_id, COUNT(*) AS cnt
+FROM slscc.dwb_supply_chain_center_f
+GROUP BY purchase_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slscc.dwb_supply_chain_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slscc.dwb_supply_chain_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slscc.dwb_supply_chain_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slscc.dwb_supply_chain_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slscc.dwb_supply_chain_center_f;
+档案来源：../10_project_deliver/dwb_supply_chain_f</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slscc.dwb_supply_chain_center_f，粒度：每行一个供应链记录
+- 目标字段 23 项：purchase_id, purchase_no, purchase_status_name, create_time, supplier_id, supplier_name, supplier_level_name, cooperation_years, product_id, product_name, purchase_qty, purchase_price, purchase_amount, warehouse_id, warehouse_name, warehouse_type_name, current_stock_qty, locked_qty, stock_days, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 6 张：dwd_purchase_f, dim_supplier_f, dim_product_f, dim_warehouse_f, dwd_inventory_f, dwd_sales_f
+- 建表 DDL（create_table_dwb_supply_chain_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 23 项（源→规则→目标）：
+dwd_purchase_f.purchase_id --[直接复制]--&gt; purchase_id(采购单ID)
+dwd_purchase_f.purchase_no --[直接复制]--&gt; purchase_no(采购单号)
+dwd_purchase_f.purchase_status --[数据加工]--&gt; purchase_status_name(采购状态)
+dwd_purchase_f.create_time --[直接复制]--&gt; create_time(创建时间)
+dwd_purchase_f.supplier_id --[直接复制]--&gt; supplier_id(供应商ID)
+dim_supplier_f.supplier_name --[直接复制]--&gt; supplier_name(供应商名称)
+dim_supplier_f.supplier_level --[数据加工]--&gt; supplier_level_name(供应商等级)
+dim_supplier_f.cooperation_years --[直接复制]--&gt; cooperation_years(合作年限)
+dwd_purchase_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_purchase_f.purchase_qty --[直接复制]--&gt; purchase_qty(采购数量)
+dwd_purchase_f.purchase_price --[直接复制]--&gt; purchase_price(采购单价)
+（无源声明） --[数据加工]--&gt; purchase_amount(采购金额)
+dwd_purchase_f.warehouse_id --[直接复制]--&gt; warehouse_id(仓库ID)
+dim_warehouse_f.warehouse_name --[直接复制]--&gt; warehouse_name(仓库名称)
+dim_warehouse_f.warehouse_type --[数据加工]--&gt; warehouse_type_name(仓库类型)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; current_stock_qty(当前库存)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定库存)
+dwd_sales_f.sales_qty_30d --[数据加工]--&gt; stock_days(库存周转天数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>任务：为 slscc.dwb_supply_chain_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：供应链中心宽表
+粒度：每行一个供应链记录
+调度：全量调度 / T+1，一天一调
+映射字段 23 项，来源表 6 张。
+本规则：R0001（供应链中心宽表写入），step_type=full，目标表 slscc.dwb_supply_chain_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* =====================================================
+   R0001: 供应链中心宽表写入
+   目标表: slscc.dwb_supply_chain_center_f
+   设计意图: 以采购事实表(dpf)为主表锚定粒度，LEFT JOIN 供应商/商品/仓库
+             维度表补充属性，LEFT JOIN 库存事实表取当前库存与锁定库存，
+             通过CTE预聚合销售表按product_id统计近30天销量后关联，
+             计算库存周转天数，写入供应链中心宽表
+   ===================================================== */
+/* CTE: 销售事实表按product_id预聚合近30天销量，收敛到商品粒度避免JOIN发散 */
+WITH sales_agg AS (
+    SELECT
+        dsales.product_id AS product_id,
+        COALESCE(SUM(dsales.sales_qty_30d), 0) AS sales_qty_30d_sum
+    FROM sdinv.dwd_sales_f dsales
+    WHERE dsales.del_flag = 'N'
+    GROUP BY dsales.product_id
+)
+SELECT
+    dpf.purchase_id AS purchase_id,
+    dpf.purchase_no AS purchase_no,
+    /* 采购状态码转中文映射 */
+    CASE dpf.purchase_status
+        WHEN 'DRAFT' THEN '草稿'
+        WHEN 'SUBMITTED' THEN '已提交'
+        WHEN 'APPROVED' THEN '已审批'
+        WHEN 'RECEIVED' THEN '已入库'
+        WHEN 'CLOSED' THEN '已关闭'
+        ELSE '其他'
+    END AS purchase_status_name,
+    dpf.create_time AS create_time,
+    dpf.supplier_id AS supplier_id,
+    dpf.product_id AS product_id,
+    dpf.purchase_qty AS purchase_qty,
+    dpf.purchase_price AS purchase_price,
+    /* 采购金额 = 采购数量 × 采购单价 */
+    COALESCE(dpf.purchase_qty, 0) * COALESCE(dpf.purchase_price, 0) AS purchase_amount,
+    dpf.warehouse_id AS warehouse_id,
+    COALESCE(dsf.supplier_name, '') AS supplier_name,
+    /* 供应商等级码转中文映射 */
+    CASE dsf.supplier_level
+        WHEN 'A' THEN 'A级供应商'
+        WHEN 'B' THEN 'B级供应商'
+        WHEN 'C' THEN 'C级供应商'
+        ELSE '其他'
+    END AS supplier_level_name,
+    COALESCE(dsf.cooperation_years, 0) AS cooperation_years,
+    COALESCE(dpf2.product_name, '') AS product_name,
+    COALESCE(dwf.warehouse_name, '') AS warehouse_name,
+    /* 仓库类型码转中文映射 */
+    CASE dwf.warehouse_type
+        WHEN 'SELF' THEN '自营仓'
+        WHEN 'THIRD_PARTY' THEN '第三方仓'
+        ELSE '其他'
+    END AS warehouse_type_name,
+    COALESCE(dif.stock_qty, 0) AS current_stock_qty,
+    COALESCE(dif.locked_qty, 0) AS locked_qty,
+    /* 库存周转天数 = (当前库存 - 锁定库存) / 近30天销量，除零保护用NULLIF */
+    (COALESCE(dif.stock_qty, 0) - COALESCE(dif.locked_qty, 0))
+        / NULLIF(sales_agg.sales_qty_30d_sum, 0) AS stock_days,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdinv.dwd_purchase_f dpf
+LEFT JOIN dim.dim_supplier_f dsf
+    ON dpf.supplier_id = dsf.supplier_id
+    AND dsf.del_flag = 'N'
+LEFT JOIN dim.dim_product_f dpf2
+    ON dpf.product_id = dpf2.product_id
+    AND dpf2.del_flag = 'N'
+LEFT JOIN dim.dim_warehouse_f dwf
+    ON dpf.warehouse_id = dwf.warehouse_id
+    AND dwf.del_flag = 'N'
+LEFT JOIN sdinv.dwd_inventory_f dif
+    ON dpf.product_id = dif.product_id
+    AND dpf.warehouse_id = dif.warehouse_id
+    AND dif.del_flag = 'N'
+LEFT JOIN sales_agg
+    ON dpf.product_id = sales_agg.product_id
+WHERE dpf.del_flag = 'N';
+——ddl/create_table_dwb_supply_chain_center_f.sql——
+/* =====================================================
+   表名: slscc.dwb_supply_chain_center_f
+   规则: R0001 - 供应链中心宽表写入
+   分布键: purchase_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 以采购事实表(dp)为主表锚定粒度，LEFT JOIN 供应商/商品/仓库维度表补充属性，LEFT JOIN 库存事实表取当前库存与锁定库存，通过CTE预聚合销售表按product_id统计近30天销量后关联，计算库存周转天数，写入供应链中心宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slscc.dwb_supply_chain_center_f (
+    purchase_id          bigint,
+    purchase_no          varchar(64),
+    purchase_status_name varchar(50),
+    create_time          datetime,
+    supplier_id          bigint,
+    product_id           bigint,
+    purchase_qty         int,
+    purchase_price       decimal(18,2),
+    purchase_amount      decimal(18,2),
+    warehouse_id         bigint,
+    supplier_name        varchar(200),
+    supplier_level_name  varchar(50),
+    cooperation_years    int,
+    product_name         varchar(200),
+    warehouse_name       varchar(100),
+    warehouse_type_name  varchar(50),
+    current_stock_qty    int,
+    locked_qty           int,
+    stock_days           int,
+    del_flag             NVARCHAR(1),
+    crt_cycle_id         BIGINT,
+    last_upd_cycle_id    BIGINT,
+    dw_last_update_date  TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(purchase_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slscc.dwb_supply_chain_center_f IS '供应链中心宽表';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_id IS '采购单ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_no IS '采购单号';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_status_name IS '采购状态';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.create_time IS '创建时间';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_id IS '供应商ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_id IS '商品ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_qty IS '采购数量';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_price IS '采购单价';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.purchase_amount IS '采购金额';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_id IS '仓库ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_name IS '供应商名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.supplier_level_name IS '供应商等级';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.cooperation_years IS '合作年限';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.product_name IS '商品名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_name IS '仓库名称';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.warehouse_type_name IS '仓库类型';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.current_stock_qty IS '当前库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.locked_qty IS '锁定库存';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.stock_days IS '库存周转天数';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slscc.dwb_supply_chain_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_supply_chain_f</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 23 项：purchase_id, purchase_no, purchase_status_name, create_time, supplier_id, product_id, purchase_qty, purchase_price, purchase_amount, warehouse_id, supplier_name, supplier_level_name, cooperation_years, product_name, warehouse_name, warehouse_type_name, current_stock_qty, locked_qty, stock_days, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 slscc.dwb_supply_chain_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 23 项）（源→规则→目标）：
+dwd_purchase_f.purchase_id --[直接复制]--&gt; purchase_id(采购单ID)
+dwd_purchase_f.purchase_no --[直接复制]--&gt; purchase_no(采购单号)
+dwd_purchase_f.purchase_status --[数据加工]--&gt; purchase_status_name(采购状态)
+dwd_purchase_f.create_time --[直接复制]--&gt; create_time(创建时间)
+dwd_purchase_f.supplier_id --[直接复制]--&gt; supplier_id(供应商ID)
+dim_supplier_f.supplier_name --[直接复制]--&gt; supplier_name(供应商名称)
+dim_supplier_f.supplier_level --[数据加工]--&gt; supplier_level_name(供应商等级)
+dim_supplier_f.cooperation_years --[直接复制]--&gt; cooperation_years(合作年限)
+dwd_purchase_f.product_id --[直接复制]--&gt; product_id(商品ID)
+dim_product_f.product_name --[直接复制]--&gt; product_name(商品名称)
+dwd_purchase_f.purchase_qty --[直接复制]--&gt; purchase_qty(采购数量)
+dwd_purchase_f.purchase_price --[直接复制]--&gt; purchase_price(采购单价)
+（无源声明） --[数据加工]--&gt; purchase_amount(采购金额)
+dwd_purchase_f.warehouse_id --[直接复制]--&gt; warehouse_id(仓库ID)
+dim_warehouse_f.warehouse_name --[直接复制]--&gt; warehouse_name(仓库名称)
+dim_warehouse_f.warehouse_type --[数据加工]--&gt; warehouse_type_name(仓库类型)
+dwd_inventory_f.stock_qty --[直接复制]--&gt; current_stock_qty(当前库存)
+dwd_inventory_f.locked_qty --[直接复制]--&gt; locked_qty(锁定库存)
+dwd_sales_f.sales_qty_30d --[数据加工]--&gt; stock_days(库存周转天数)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>任务：为 dws.dwb_trade_order_d 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单汇总表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 7 项，来源表 1 张。</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `dws.dwb_trade_order_d`（订单汇总表） |
+| **I 视图** | `dws.dwb_trade_order_d_i`（F表镜像，对外查询） |
+| **业务主键** | order_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 7 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | ods.ods_trade_order_di | 订单明细接入表 | a |
+---
+——ddl/create_table_dwb_trade_order_d.sql——
+/* =====================================================
+   表名: dws.dwb_trade_order_d
+   规则: R0001 - 订单汇总聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 从订单明细接入表按 order_id+cust_id 聚合到订单粒度，汇总金额，直取订单与客户标识，补审计字段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_order_d (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    total_amount        DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_order_d IS '订单汇总表';
+COMMENT ON COLUMN dws.dwb_trade_order_d.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.total_amount IS '订单总额';
+COMMENT ON COLUMN dws.dwb_trade_order_d.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_order_d.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* R0001: 订单汇总聚合（从订单明细接入表按 order_id+cust_id 聚合到订单粒度，汇总金额，直取订单与客户标识，补审计字段） */
+SELECT
+    a.order_id AS order_id,
+    a.cust_id AS cust_id,
+    /* 订单总额：对同一 order_id + cust_id 的 amount 求和汇总 */
+    COALESCE(SUM(a.amount), 0) AS total_amount,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di a
+WHERE a.del_flag = 'N'
+GROUP BY a.order_id, a.cust_id;
+——dq/dq_dwb_trade_order_d.sql——
+-- ============================================================
+-- DQ 检查: dws.dwb_trade_order_d
+-- 规则: R0001
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: order_id）
+SELECT order_id, COUNT(*) AS cnt
+FROM dws.dwb_trade_order_d
+GROUP BY order_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM dws.dwb_trade_order_d
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM dws.dwb_trade_order_d
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM dws.dwb_trade_order_d
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM dws.dwb_trade_order_d
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM dws.dwb_trade_order_d;
+档案来源：../10_project_deliver/dwb_trade_order_d</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 dws.dwb_trade_order_d，粒度：每行一个订单
+- 目标字段 7 项：order_id, cust_id, total_amount, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 1 张：ods_trade_order_di
+- 建表 DDL（create_table_dwb_trade_order_d.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 7 项（源→规则→目标）：
+ods_trade_order_di.order_id --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.cust_id --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.amount --[数据加工]--&gt; total_amount(订单总额)
+ods_trade_order_di. --[赋值]--&gt; del_flag(删除标识)
+ods_trade_order_di. --[赋值]--&gt; crt_cycle_id(创建批次ID)
+ods_trade_order_di. --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+ods_trade_order_di. --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>任务：为 dws.dwb_trade_order_d 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：订单汇总表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 7 项，来源表 1 张。
+本规则：R0001（订单汇总聚合），step_type=full，目标表 dwb_trade_order_d——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* R0001: 订单汇总聚合（从订单明细接入表按 order_id+cust_id 聚合到订单粒度，汇总金额，直取订单与客户标识，补审计字段） */
+SELECT
+    a.order_id AS order_id,
+    a.cust_id AS cust_id,
+    /* 订单总额：对同一 order_id + cust_id 的 amount 求和汇总 */
+    COALESCE(SUM(a.amount), 0) AS total_amount,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_trade_order_di a
+WHERE a.del_flag = 'N'
+GROUP BY a.order_id, a.cust_id;
+——ddl/create_table_dwb_trade_order_d.sql——
+/* =====================================================
+   表名: dws.dwb_trade_order_d
+   规则: R0001 - 订单汇总聚合
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 从订单明细接入表按 order_id+cust_id 聚合到订单粒度，汇总金额，直取订单与客户标识，补审计字段
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_order_d (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    total_amount        DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_order_d IS '订单汇总表';
+COMMENT ON COLUMN dws.dwb_trade_order_d.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.total_amount IS '订单总额';
+COMMENT ON COLUMN dws.dwb_trade_order_d.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_order_d.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN dws.dwb_trade_order_d.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_trade_order_d</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 7 项：order_id, cust_id, total_amount, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 dwb_trade_order_d 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 7 项）（源→规则→目标）：
+ods_trade_order_di.order_id --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.cust_id --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.amount --[数据加工]--&gt; total_amount(订单总额)
+ods_trade_order_di. --[赋值]--&gt; del_flag(删除标识)
+ods_trade_order_di. --[赋值]--&gt; crt_cycle_id(创建批次ID)
+ods_trade_order_di. --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+ods_trade_order_di. --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>任务：为 dws.dwb_trade_wide_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：交易宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 8 项，来源表 1 张。</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `dws.dwb_trade_wide_f`（交易宽表） |
+| **I 视图** | `dws.dwb_trade_wide_i`（F表镜像，对外查询） |
+| **业务主键** | order_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 8 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | ods.ods_trade_order_di | 订单明细 | o |
+---
+——ddl/create_table_dwb_trade_wide_f.sql——
+/* =====================================================
+   表名: dws.dwb_trade_wide_f
+   规则: R0001 - 交易宽表主表加载
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 单源主表直加载，无关联无加工，全量覆盖写入目标F表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_wide_f (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    product_id          VARCHAR(64),
+    order_amt           DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_wide_f IS '交易宽表';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_id IS '商品ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_amt IS '订单金额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.dw_last_update_date IS '更新时间';
+——ddl/create_view_dwb_trade_wide_i.sql——
+/* I视图: dws.dwb_trade_wide_i（交易宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW dws.dwb_trade_wide_i AS
+SELECT
+    order_id,
+    cust_id,
+    product_id,
+    order_amt,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM dws.dwb_trade_wide_f;
+COMMENT ON TABLE dws.dwb_trade_wide_i IS '交易宽表（视图）';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.product_id IS '商品ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.order_amt IS '订单金额';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_i.dw_last_update_date IS '更新时间';
+——etl/R0001.sql——
+/* R0001: 交易宽表主表加载（单源主表直加载，无关联无加工，全量覆盖写入目标F表） */
+SELECT
+    COALESCE(o.order_id, '') AS order_id,
+    COALESCE(o.cust_id, '') AS cust_id,
+    COALESCE(o.product_id, '') AS product_id,
+    COALESCE(o.order_amt, 0) AS order_amt,
+    'N' AS del_flag,                          /* 审计字段：删除标识固定 N */
+    '${P_CYCLE_ID}' AS crt_cycle_id,          /* 审计字段：创建批次号 */
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,     /* 审计字段：最后更新批次号 */
+    CURRENT_TIMESTAMP AS dw_last_update_date  /* 审计字段：数仓最后更新时间 */
+FROM ods.ods_trade_order_di o
+WHERE o.del_flag = 'N';
+——dq/dq_dwb_trade_wide_f.sql——
+-- ============================================================
+-- DQ 检查: dws.dwb_trade_wide_f
+-- 规则: R0001
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: order_id）
+SELECT order_id, COUNT(*) AS cnt
+FROM dws.dwb_trade_wide_f
+GROUP BY order_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM dws.dwb_trade_wide_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM dws.dwb_trade_wide_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM dws.dwb_trade_wide_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM dws.dwb_trade_wide_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM dws.dwb_trade_wide_f;
+档案来源：../10_project_deliver/dwb_trade_wide_f</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 dws.dwb_trade_wide_f，粒度：每行一个订单
+- 目标字段 8 项：order_id, cust_id, product_id, order_amt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 1 张：ods_trade_order_di
+- 建表 DDL（create_table_dwb_trade_wide_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 8 项（源→规则→目标）：
+ods_trade_order_di.order_id --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.cust_id --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.product_id --[直接复制]--&gt; product_id(商品ID)
+ods_trade_order_di.order_amt --[直接复制]--&gt; order_amt(订单金额)
+ods_trade_order_di. --[赋值]--&gt; del_flag(删除标识)
+ods_trade_order_di. --[赋值]--&gt; crt_cycle_id(创建批次)
+ods_trade_order_di. --[赋值]--&gt; last_upd_cycle_id(更新批次)
+ods_trade_order_di. --[赋值]--&gt; dw_last_update_date(更新时间)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>任务：为 dws.dwb_trade_wide_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：交易宽表
+粒度：每行一个订单
+调度：全量调度 / T+1，一天一调
+映射字段 8 项，来源表 1 张。
+本规则：R0001（交易宽表主表加载），step_type=full，目标表 dws.dwb_trade_wide_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* R0001: 交易宽表主表加载（单源主表直加载，无关联无加工，全量覆盖写入目标F表） */
+SELECT
+    COALESCE(o.order_id, '') AS order_id,
+    COALESCE(o.cust_id, '') AS cust_id,
+    COALESCE(o.product_id, '') AS product_id,
+    COALESCE(o.order_amt, 0) AS order_amt,
+    'N' AS del_flag,                          /* 审计字段：删除标识固定 N */
+    '${P_CYCLE_ID}' AS crt_cycle_id,          /* 审计字段：创建批次号 */
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,     /* 审计字段：最后更新批次号 */
+    CURRENT_TIMESTAMP AS dw_last_update_date  /* 审计字段：数仓最后更新时间 */
+FROM ods.ods_trade_order_di o
+WHERE o.del_flag = 'N';
+——ddl/create_table_dwb_trade_wide_f.sql——
+/* =====================================================
+   表名: dws.dwb_trade_wide_f
+   规则: R0001 - 交易宽表主表加载
+   分布键: order_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 单源主表直加载，无关联无加工，全量覆盖写入目标F表。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS dws.dwb_trade_wide_f (
+    order_id            VARCHAR(64),
+    cust_id             VARCHAR(64),
+    product_id          VARCHAR(64),
+    order_amt           DECIMAL(18,2),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0)
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(order_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE dws.dwb_trade_wide_f IS '交易宽表';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_id IS '订单ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.cust_id IS '客户ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.product_id IS '商品ID';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.order_amt IS '订单金额';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.del_flag IS '删除标识';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.crt_cycle_id IS '创建批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.last_upd_cycle_id IS '更新批次';
+COMMENT ON COLUMN dws.dwb_trade_wide_f.dw_last_update_date IS '更新时间';
+档案来源：../10_project_deliver/dwb_trade_wide_f</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 8 项：order_id, cust_id, product_id, order_amt, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 dws.dwb_trade_wide_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 8 项）（源→规则→目标）：
+ods_trade_order_di.order_id --[直接复制]--&gt; order_id(订单ID)
+ods_trade_order_di.cust_id --[直接复制]--&gt; cust_id(客户ID)
+ods_trade_order_di.product_id --[直接复制]--&gt; product_id(商品ID)
+ods_trade_order_di.order_amt --[直接复制]--&gt; order_amt(订单金额)
+ods_trade_order_di. --[赋值]--&gt; del_flag(删除标识)
+ods_trade_order_di. --[赋值]--&gt; crt_cycle_id(创建批次)
+ods_trade_order_di. --[赋值]--&gt; last_upd_cycle_id(更新批次)
+ods_trade_order_di. --[赋值]--&gt; dw_last_update_date(更新时间)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户中心宽表
+粒度：每行一个用户记录
+调度：全量调度 / T+1，一天一调
+映射字段 46 项，来源表 9 张。</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slusr.dwb_user_center_f`（用户中心宽表） |
+| **I 视图** | `slusr.dwb_user_center_i`（F表镜像，对外查询） |
+| **业务主键** | user_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 46 |
+| **规则数** | 3 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | dim.dim_user_f | 用户维度表 | duf |
+| 2 | dim.dim_user_level_f | 用户等级维度表 | dul |
+| 3 | dim.dim_region_f | 地区维度表 | drf |
+| 4 | dim.dim_user_source_f | 用户来源维度表 | dus |
+| 5 | sdord.dwd_order_f | 订单明细事实表 | dof |
+| 6 | sdlog.dwd_user_behavior_f | 用户行为事实表 | dub |
+| 7 | sdmar.dwd_coupon_use_f | 优惠券使用事实表 | dcu |
+| 8 | sdref.dwd_refund_f | 退款事实表 | drf7 |
+| 9 | sdlog.dwd_cart_f | 购物车事实表 | dcf |
+---
+——ddl/create_table_dwb_user_center_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f
+   规则: R0003 - 用户中心宽表装配
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 以 dim_user_f 为主表左联维度表与中间表，CTE 聚合行为/优惠/退款/购物车事实，计算派生转化率与标签，产出最终宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f (
+    user_id             bigint,
+    user_name           varchar(100),
+    user_phone_masked   varchar(20),
+    gender_name         varchar(10),
+    birthday            date,
+    age                 int,
+    register_time       datetime,
+    register_days       int,
+    last_login_time     datetime,
+    level_id            int,
+    level_name          varchar(50),
+    level_min_points    int,
+    province_code       varchar(20),
+    province_name       varchar(50),
+    city_code           varchar(20),
+    city_name           varchar(50),
+    source_name         varchar(50),
+    member_points       int,
+    member_balance      decimal(18,2),
+    user_status_name    varchar(20),
+    total_pv_cnt        int,
+    total_collect_cnt   int,
+    total_cart_cnt      int,
+    pv_to_order_rate    decimal(5,2),
+    pv_to_cart_rate     decimal(5,2),
+    coupon_used_cnt     int,
+    coupon_total_amount decimal(18,2),
+    refund_cnt          int,
+    refund_rate         decimal(5,2),
+    cart_product_cnt    int,
+    cart_total_amount   decimal(18,2),
+    order_freq_label    varchar(20),
+    consume_level_label varchar(20),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.gender_name IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_center_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_center_f.age IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_days IS '注册天数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_login_time IS '最近登录时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_min_points IS '等级所需积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_code IS '城市编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.source_name IS '注册来源';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_balance IS '会员余额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_status_name IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_pv_cnt IS '浏览次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_collect_cnt IS '收藏次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_cart_cnt IS '加购次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_order_rate IS '浏览-下单转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_cart_rate IS '浏览-加购转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_used_cnt IS '优惠券使用次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_total_amount IS '优惠券使用金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_cnt IS '退款次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_rate IS '退款率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_product_cnt IS '购物车商品数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_total_amount IS '购物车金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.order_freq_label IS '下单频率标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.consume_level_label IS '消费能力标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slusr.dwb_user_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_user_center_f_tmp1.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp1
+   规则: R0001 - 订单聚合中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp1 (
+    total_order_cnt  int,
+    total_pay_amount decimal(18,2),
+    avg_order_amount decimal(18,2),
+    last_order_time  datetime,
+    first_order_time datetime,
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp1 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_table_dwb_user_center_f_tmp2.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp2
+   规则: R0002 - RFM 评分中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 基于订单聚合指标用 NTILE(5) 窗口函数跨全量用户打分，产出 RFM 三维分数与价值分层
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp2 (
+    rfm_r_score int,
+    rfm_f_score int,
+    rfm_m_score int,
+    rfm_segment varchar(20),
+    /* 审计字段 */
+    del_flag    NVARCHAR(1),
+    crt_cycle_id BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp2 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_r_score IS 'RFM-R值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_f_score IS 'RFM-F值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_m_score IS 'RFM-M值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_segment IS '用户价值分层';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.dw_last_update_date IS '数仓最后更新时间';
+——ddl/create_view_dwb_user_center_i.sql——
+/* I视图: slusr.dwb_user_center_i（用户中心宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slusr.dwb_user_center_i AS
+SELECT
+    user_id,
+    user_name,
+    user_phone_masked,
+    gender_name,
+    birthday,
+    age,
+    register_time,
+    register_days,
+    last_login_time,
+    level_id,
+    level_name,
+    level_min_points,
+    province_code,
+    province_name,
+    city_code,
+    city_name,
+    source_name,
+    member_points,
+    member_balance,
+    user_status_name,
+    total_pv_cnt,
+    total_collect_cnt,
+    total_cart_cnt,
+    pv_to_order_rate,
+    pv_to_cart_rate,
+    coupon_used_cnt,
+    coupon_total_amount,
+    refund_cnt,
+    refund_rate,
+    cart_product_cnt,
+    cart_total_amount,
+    order_freq_label,
+    consume_level_label,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slusr.dwb_user_center_f;
+COMMENT ON TABLE slusr.dwb_user_center_i IS '用户中心宽表（视图）';
+COMMENT ON COLUMN slusr.dwb_user_center_i.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_center_i.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_center_i.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_center_i.gender_name IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_center_i.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_center_i.age IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_center_i.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_center_i.register_days IS '注册天数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.last_login_time IS '最近登录时间';
+COMMENT ON COLUMN slusr.dwb_user_center_i.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_center_i.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_center_i.level_min_points IS '等级所需积分';
+COMMENT ON COLUMN slusr.dwb_user_center_i.province_code IS '省份编码';
+COMMENT ON COLUMN slusr.dwb_user_center_i.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_center_i.city_code IS '城市编码';
+COMMENT ON COLUMN slusr.dwb_user_center_i.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_center_i.source_name IS '注册来源';
+COMMENT ON COLUMN slusr.dwb_user_center_i.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_center_i.member_balance IS '会员余额';
+COMMENT ON COLUMN slusr.dwb_user_center_i.user_status_name IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_center_i.total_pv_cnt IS '浏览次数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.total_collect_cnt IS '收藏次数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.total_cart_cnt IS '加购次数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.pv_to_order_rate IS '浏览-下单转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_i.pv_to_cart_rate IS '浏览-加购转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_i.coupon_used_cnt IS '优惠券使用次数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.coupon_total_amount IS '优惠券使用金额';
+COMMENT ON COLUMN slusr.dwb_user_center_i.refund_cnt IS '退款次数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.refund_rate IS '退款率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_i.cart_product_cnt IS '购物车商品数';
+COMMENT ON COLUMN slusr.dwb_user_center_i.cart_total_amount IS '购物车金额';
+COMMENT ON COLUMN slusr.dwb_user_center_i.order_freq_label IS '下单频率标签';
+COMMENT ON COLUMN slusr.dwb_user_center_i.consume_level_label IS '消费能力标签';
+COMMENT ON COLUMN slusr.dwb_user_center_i.del_flag IS '删除标识';
+COMMENT ON COLUMN slusr.dwb_user_center_i.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_i.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_i.dw_last_update_date IS '数仓最后更新时间';
+——etl/R0001.sql——
+/* R0001: 订单聚合中间表（将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用） */
+SELECT
+    dof.user_id AS user_id,
+    COUNT(*) AS total_order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS total_pay_amount,
+    /* 平均客单价 = 总消费金额 / 历史订单数；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(SUM(dof.pay_amount), 0) / NULLIF(COUNT(*), 0) AS avg_order_amount,
+    MAX(dof.create_time) AS last_order_time,
+    MIN(dof.create_time) AS first_order_time,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.user_id
+——etl/R0002.sql——
+/* R0002: RFM 评分中间表（基于 R0001 订单聚合指标，用 NTILE(5) 窗口函数跨全量用户打分，产出 RFM 三维分数与价值分层） */
+WITH
+/* CTE order_agg: 引用 R0001 产出的 dwb_user_center_f_tmp1 订单聚合结果，并计算 R 值（最近下单距今天数） */
+order_agg AS (
+    SELECT
+        tmp1.user_id AS user_id,
+        tmp1.total_order_cnt AS total_order_cnt,
+        tmp1.total_pay_amount AS total_pay_amount,
+        /* R 值 = 当前日期 - 最近下单时间的天数；越小代表越近消费（越优） */
+        DATEDIFF(CURDATE(), tmp1.last_order_time) AS r_days
+    FROM slusr.dwb_user_center_f_tmp1 tmp1
+    WHERE tmp1.del_flag = 'N'
+),
+/* CTE rfm_scores: 在全量用户范围内对 R/F/M 三个维度分别用 NTILE(5) 窗口函数打 1~5 分 */
+rfm_scores AS (
+    SELECT
+        user_id,
+        /* R 分：NTILE(5) 升序把天数最小的分到第 1 组；语义要求天数越小分数越高（5→1），用 6 - NTILE(...) 反转 */
+        (6 - NTILE(5) OVER (ORDER BY r_days ASC NULLS LAST)) AS r_score,
+        /* F 分：按订单数降序，订单越多分越高（直接降序即高分在前，无需反转） */
+        NTILE(5) OVER (ORDER BY total_order_cnt DESC NULLS LAST) AS f_score,
+        /* M 分：按金额降序，金额越高分越高（直接降序即高分在前，无需反转） */
+        NTILE(5) OVER (ORDER BY total_pay_amount DESC NULLS LAST) AS m_score
+    FROM order_agg
+)
+SELECT
+    rfm_scores.user_id AS user_id,
+    rfm_scores.r_score AS rfm_r_score,
+    rfm_scores.f_score AS rfm_f_score,
+    rfm_scores.m_score AS rfm_m_score,
+    /* 价值分层判定顺序：高价值 &gt; 流失 &gt; 中价值 &gt; 低价值（前置优先，避免相互覆盖） */
+    CASE
+        /* 高价值：R/F/M 三维均 ≥ 4 */
+        WHEN rfm_scores.r_score &gt;= 4
+         AND rfm_scores.f_score &gt;= 4
+         AND rfm_scores.m_score &gt;= 4 THEN '高价值'
+        /* 流失：R ≤ 2 且 F ≤ 2（长期未消费且频次低），优先于中/低价值判定 */
+        WHEN rfm_scores.r_score &lt;= 2
+         AND rfm_scores.f_score &lt;= 2 THEN '流失'
+        /* 中价值：R/F/M 任两维 ≥ 4 */
+        WHEN (rfm_scores.r_score &gt;= 4 AND rfm_scores.f_score &gt;= 4)
+          OR (rfm_scores.r_score &gt;= 4 AND rfm_scores.m_score &gt;= 4)
+          OR (rfm_scores.f_score &gt;= 4 AND rfm_scores.m_score &gt;= 4) THEN '中价值'
+        /* 低价值：任一维 ≥ 3（兜底 ELSE 同样归入低价值，确保非空） */
+        WHEN rfm_scores.r_score &gt;= 3
+          OR rfm_scores.f_score &gt;= 3
+          OR rfm_scores.m_score &gt;= 3 THEN '低价值'
+        ELSE '低价值'
+    END AS rfm_segment,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM rfm_scores
+——etl/R0003.sql——
+/* R0003: 用户中心宽表装配（以 dim_user_f 为主表，左联等级/地区/来源维度表与订单/RFM 中间表，CTE 聚合行为/优惠/退款/购物车事实，计算派生转化率与用户标签，产出最终用户中心宽表） */
+WITH
+/* CTE behavior_agg: 从 dwd_user_behavior_f 按 user_id 聚合浏览/收藏/加购历史次数 */
+behavior_agg AS (
+    SELECT
+        dub.user_id AS user_id,
+        COALESCE(SUM(dub.pv_cnt), 0) AS total_pv_cnt,
+        COALESCE(SUM(dub.collect_cnt), 0) AS total_collect_cnt,
+        COALESCE(SUM(dub.cart_cnt), 0) AS total_cart_cnt
+    FROM sdlog.dwd_user_behavior_f dub
+    GROUP BY dub.user_id
+),
+/* CTE coupon_agg: 从 dwd_coupon_use_f 按 user_id 聚合优惠券使用次数与金额 */
+coupon_agg AS (
+    SELECT
+        dcu.user_id AS user_id,
+        COUNT(*) AS coupon_used_cnt,
+        COALESCE(SUM(dcu.coupon_amount), 0) AS coupon_total_amount
+    FROM sdmar.dwd_coupon_use_f dcu
+    GROUP BY dcu.user_id
+),
+/* CTE refund_agg: 从 dwd_refund_f 按 user_id 聚合退款次数 */
+refund_agg AS (
+    SELECT
+        drf7.user_id AS user_id,
+        COUNT(*) AS refund_cnt
+    FROM sdref.dwd_refund_f drf7
+    GROUP BY drf7.user_id
+),
+/* CTE cart_agg: 从 dwd_cart_f（过滤 del_flag='N' 有效记录）按 user_id 聚合购物车商品数与金额 */
+cart_agg AS (
+    SELECT
+        dcf.user_id AS user_id,
+        COUNT(*) AS cart_product_cnt,
+        COALESCE(SUM(dcf.qty * dcf.price), 0) AS cart_total_amount
+    FROM sdlog.dwd_cart_f dcf
+    WHERE dcf.del_flag = 'N'
+    GROUP BY dcf.user_id
+)
+SELECT
+    duf.user_id AS user_id,
+    duf.user_name AS user_name,
+    /* 手机号脱敏：保留前 3 位与后 4 位，中间用 **** 屏蔽 */
+    CONCAT(LEFT(duf.user_phone, 3), '****', RIGHT(duf.user_phone, 4)) AS user_phone_masked,
+    /* 性别代码转中文：M→男，F→女，其他→未知 */
+    CASE duf.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_name,
+    duf.birthday AS birthday,
+    /* 年龄 = 当前年份 - 出生年份（按年粗算，未做生日日精确校验） */
+    YEAR(CURDATE()) - YEAR(duf.birthday) AS age,
+    duf.register_time AS register_time,
+    /* 注册天数 = 当前日期 - 注册日期 */
+    DATEDIFF(CURDATE(), duf.register_time) AS register_days,
+    duf.last_login_time AS last_login_time,
+    duf.level_id AS level_id,
+    dul.level_name AS level_name,
+    dul.min_points AS level_min_points,
+    duf.province_code AS province_code,
+    drf.region_name AS province_name,
+    duf.city_code AS city_code,
+    /* 城市名称：通过 city_code 二次关联 dim_region_f（drf_city 别名）取城市名称，与省份关联分开 */
+    drf_city.region_name AS city_name,
+    dus.source_name AS source_name,
+    duf.member_points AS member_points,
+    duf.member_balance AS member_balance,
+    /* 用户状态代码转中文：ACTIVE→正常，INACTIVE→未激活，FROZEN→冻结，其他→其他 */
+    CASE duf.user_status
+        WHEN 'ACTIVE' THEN '正常'
+        WHEN 'INACTIVE' THEN '未激活'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS user_status_name,
+    COALESCE(behavior_agg.total_pv_cnt, 0) AS total_pv_cnt,
+    COALESCE(behavior_agg.total_collect_cnt, 0) AS total_collect_cnt,
+    COALESCE(behavior_agg.total_cart_cnt, 0) AS total_cart_cnt,
+    /* 浏览-下单转化率(%) = 历史订单数 / 浏览次数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(tmp1.total_order_cnt, 0) * 100 / NULLIF(COALESCE(behavior_agg.total_pv_cnt, 0), 0) AS pv_to_order_rate,
+    /* 浏览-加购转化率(%) = 加购次数 / 浏览次数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(behavior_agg.total_cart_cnt, 0) * 100 / NULLIF(COALESCE(behavior_agg.total_pv_cnt, 0), 0) AS pv_to_cart_rate,
+    COALESCE(coupon_agg.coupon_used_cnt, 0) AS coupon_used_cnt,
+    COALESCE(coupon_agg.coupon_total_amount, 0) AS coupon_total_amount,
+    COALESCE(refund_agg.refund_cnt, 0) AS refund_cnt,
+    /* 退款率(%) = 退款次数 / 历史订单数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(refund_agg.refund_cnt, 0) * 100 / NULLIF(COALESCE(tmp1.total_order_cnt, 0), 0) AS refund_rate,
+    COALESCE(cart_agg.cart_product_cnt, 0) AS cart_product_cnt,
+    COALESCE(cart_agg.cart_total_amount, 0) AS cart_total_amount,
+    /* 下单频率标签：按订单数阶梯判定，前置优先（≥10→高频 &gt; ≥3→中频 &gt; ≥1→低频 &gt; 未购买） */
+    CASE
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 10 THEN '高频用户'
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 3 THEN '中频用户'
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 1 THEN '低频用户'
+        ELSE '未购买'
+    END AS order_freq_label,
+    /* 消费能力标签：按消费金额阶梯判定，前置优先（≥10000→高消费 &gt; ≥1000→中消费 &gt; ≥100→低消费 &gt; 无消费） */
+    CASE
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 10000 THEN '高消费'
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 1000 THEN '中消费'
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 100 THEN '低消费'
+        ELSE '无消费'
+    END AS consume_level_label,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_user_f duf
+LEFT JOIN dim.dim_user_level_f dul
+    ON duf.level_id = dul.level_id
+LEFT JOIN dim.dim_region_f drf
+    ON duf.province_code = drf.region_code
+LEFT JOIN dim.dim_region_f drf_city
+    ON duf.city_code = drf_city.region_code
+LEFT JOIN dim.dim_user_source_f dus
+    ON duf.source_id = dus.source_id
+LEFT JOIN slusr.dwb_user_center_f_tmp1 tmp1
+    ON duf.user_id = tmp1.user_id
+LEFT JOIN slusr.dwb_user_center_f_tmp2 tmp2
+    ON duf.user_id = tmp2.user_id
+LEFT JOIN behavior_agg
+    ON duf.user_id = behavior_agg.user_id
+LEFT JOIN coupon_agg
+    ON duf.user_id = coupon_agg.user_id
+LEFT JOIN refund_agg
+    ON duf.user_id = refund_agg.user_id
+LEFT JOIN cart_agg
+    ON duf.user_id = cart_agg.user_id
+——dq/dq_dwb_user_center_f.sql——
+-- ============================================================
+-- DQ 检查: slusr.dwb_user_center_f
+-- 规则: R0003
+-- ============================================================
+-- 无定制 DQ（ts.json dq_rules 为空）
+-- 标准 DQ（脚本自动生成）
+-- 主键唯一性（键: user_id）
+SELECT user_id, COUNT(*) AS cnt
+FROM slusr.dwb_user_center_f
+GROUP BY user_id
+HAVING COUNT(*) &gt; 1;
+-- 审计字段非空
+SELECT COUNT(*) AS null_count_del_flag
+FROM slusr.dwb_user_center_f
+WHERE del_flag IS NULL;
+SELECT COUNT(*) AS null_count_crt_cycle_id
+FROM slusr.dwb_user_center_f
+WHERE crt_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_last_upd_cycle_id
+FROM slusr.dwb_user_center_f
+WHERE last_upd_cycle_id IS NULL;
+SELECT COUNT(*) AS null_count_dw_last_update_date
+FROM slusr.dwb_user_center_f
+WHERE dw_last_update_date IS NULL;
+-- 记录数合理性
+SELECT COUNT(*) AS total_count
+FROM slusr.dwb_user_center_f;
+档案来源：../10_project_deliver/dwb_user_center_f</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slusr.dwb_user_center_f，粒度：每行一个用户记录
+- 目标字段 46 项：user_id, user_name, user_phone_masked, gender_name, birthday, age, register_time, register_days, last_login_time, level_id, level_name, level_min_points, province_code, province_name, city_code, city_name, source_name, member_points, member_balance, user_status_name, total_order_cnt, total_pay_amount, avg_order_amount, last_order_time, first_order_time, rfm_r_score, rfm_f_score, rfm_m_score, rfm_segment, total_pv_cnt, total_collect_cnt, total_cart_cnt, pv_to_order_rate, pv_to_cart_rate, coupon_used_cnt, coupon_total_amount, refund_cnt, refund_rate, cart_product_cnt, cart_total_amount, order_freq_label, consume_level_label, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 9 张：dim_user_f, dim_user_level_f, dim_region_f, dim_user_source_f, dwd_order_f, dwd_user_behavior_f, dwd_coupon_use_f, dwd_refund_f, dwd_cart_f
+- 建表 DDL（create_table_dwb_user_center_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 46 项（源→规则→目标）：
+dim_user_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dim_user_f.user_phone --[数据加工]--&gt; user_phone_masked(手机号(脱敏))
+dim_user_f.gender --[数据加工]--&gt; gender_name(性别)
+dim_user_f.birthday --[直接复制]--&gt; birthday(出生日期)
+（无源声明） --[数据加工]--&gt; age(年龄)
+dim_user_f.register_time --[直接复制]--&gt; register_time(注册时间)
+（无源声明） --[数据加工]--&gt; register_days(注册天数)
+dim_user_f.last_login_time --[直接复制]--&gt; last_login_time(最近登录时间)
+dim_user_f.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_f.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_f.min_points --[直接复制]--&gt; level_min_points(等级所需积分)
+dim_user_f.province_code --[直接复制]--&gt; province_code(省份编码)
+dim_region_f.region_name --[直接复制]--&gt; province_name(省份名称)
+dim_user_f.city_code --[直接复制]--&gt; city_code(城市编码)
+dim_region_f.region_name --[数据加工]--&gt; city_name(城市名称)
+dim_user_source_f.source_name --[直接复制]--&gt; source_name(注册来源)
+dim_user_f.member_points --[直接复制]--&gt; member_points(会员积分)
+dim_user_f.member_balance --[直接复制]--&gt; member_balance(会员余额)
+dim_user_f.user_status --[数据加工]--&gt; user_status_name(用户状态)
+（无源声明） --[数据加工]--&gt; total_order_cnt(历史订单数)
+（无源声明） --[数据加工]--&gt; total_pay_amount(历史消费金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f.create_time --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f.create_time --[数据加工]--&gt; first_order_time(首次下单时间)
+（无源声明） --[数据加工]--&gt; rfm_r_score(RFM-R值)
+（无源声明） --[数据加工]--&gt; rfm_f_score(RFM-F值)
+（无源声明） --[数据加工]--&gt; rfm_m_score(RFM-M值)
+（无源声明） --[数据加工]--&gt; rfm_segment(用户价值分层)
+dwd_user_behavior_f.pv_cnt --[数据加工]--&gt; total_pv_cnt(浏览次数)
+dwd_user_behavior_f.collect_cnt --[数据加工]--&gt; total_collect_cnt(收藏次数)
+dwd_user_behavior_f.cart_cnt --[数据加工]--&gt; total_cart_cnt(加购次数)
+（无源声明） --[数据加工]--&gt; pv_to_order_rate(浏览-下单转化率(%))
+（无源声明） --[数据加工]--&gt; pv_to_cart_rate(浏览-加购转化率(%))
+（无源声明） --[数据加工]--&gt; coupon_used_cnt(优惠券使用次数)
+（无源声明） --[数据加工]--&gt; coupon_total_amount(优惠券使用金额)
+（无源声明） --[数据加工]--&gt; refund_cnt(退款次数)
+（无源声明） --[数据加工]--&gt; refund_rate(退款率(%))
+（无源声明） --[数据加工]--&gt; cart_product_cnt(购物车商品数)
+（无源声明） --[数据加工]--&gt; cart_total_amount(购物车金额)
+（无源声明） --[数据加工]--&gt; order_freq_label(下单频率标签)
+（无源声明） --[数据加工]--&gt; consume_level_label(消费能力标签)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户中心宽表
+粒度：每行一个用户记录
+调度：全量调度 / T+1，一天一调
+映射字段 46 项，来源表 9 张。
+本规则：R0001（订单聚合中间表），step_type=full，目标表 dwb_user_center_f_tmp1——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* R0001: 订单聚合中间表（将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用） */
+SELECT
+    dof.user_id AS user_id,
+    COUNT(*) AS total_order_cnt,
+    COALESCE(SUM(dof.pay_amount), 0) AS total_pay_amount,
+    /* 平均客单价 = 总消费金额 / 历史订单数；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(SUM(dof.pay_amount), 0) / NULLIF(COUNT(*), 0) AS avg_order_amount,
+    MAX(dof.create_time) AS last_order_time,
+    MIN(dof.create_time) AS first_order_time,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM sdord.dwd_order_f dof
+WHERE dof.order_status NOT IN ('CANCELLED', 'DELETED')
+GROUP BY dof.user_id
+——ddl/create_table_dwb_user_center_f_tmp1.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp1
+   规则: R0001 - 订单聚合中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 将订单明细事实表聚合到用户粒度，产出历史订单统计指标，供 RFM 评分与最终宽表复用
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp1 (
+    total_order_cnt  int,
+    total_pay_amount decimal(18,2),
+    avg_order_amount decimal(18,2),
+    last_order_time  datetime,
+    first_order_time datetime,
+    /* 审计字段 */
+    del_flag         NVARCHAR(1),
+    crt_cycle_id     BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp1 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_order_cnt IS '历史订单数';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.total_pay_amount IS '历史消费金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.avg_order_amount IS '平均客单价';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_order_time IS '最近下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.first_order_time IS '首次下单时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp1.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_user_center_f</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 5 项：total_order_cnt, total_pay_amount, avg_order_amount, last_order_time, first_order_time（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_center_f_tmp1 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 5 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; total_order_cnt(历史订单数)
+（无源声明） --[数据加工]--&gt; total_pay_amount(历史消费金额)
+（无源声明） --[数据加工]--&gt; avg_order_amount(平均客单价)
+dwd_order_f.create_time --[数据加工]--&gt; last_order_time(最近下单时间)
+dwd_order_f.create_time --[数据加工]--&gt; first_order_time(首次下单时间)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户中心宽表
+粒度：每行一个用户记录
+调度：全量调度 / T+1，一天一调
+映射字段 46 项，来源表 9 张。
+本规则：R0002（RFM 评分中间表），step_type=full，目标表 dwb_user_center_f_tmp2——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>——etl/R0002.sql——
+/* R0002: RFM 评分中间表（基于 R0001 订单聚合指标，用 NTILE(5) 窗口函数跨全量用户打分，产出 RFM 三维分数与价值分层） */
+WITH
+/* CTE order_agg: 引用 R0001 产出的 dwb_user_center_f_tmp1 订单聚合结果，并计算 R 值（最近下单距今天数） */
+order_agg AS (
+    SELECT
+        tmp1.user_id AS user_id,
+        tmp1.total_order_cnt AS total_order_cnt,
+        tmp1.total_pay_amount AS total_pay_amount,
+        /* R 值 = 当前日期 - 最近下单时间的天数；越小代表越近消费（越优） */
+        DATEDIFF(CURDATE(), tmp1.last_order_time) AS r_days
+    FROM slusr.dwb_user_center_f_tmp1 tmp1
+    WHERE tmp1.del_flag = 'N'
+),
+/* CTE rfm_scores: 在全量用户范围内对 R/F/M 三个维度分别用 NTILE(5) 窗口函数打 1~5 分 */
+rfm_scores AS (
+    SELECT
+        user_id,
+        /* R 分：NTILE(5) 升序把天数最小的分到第 1 组；语义要求天数越小分数越高（5→1），用 6 - NTILE(...) 反转 */
+        (6 - NTILE(5) OVER (ORDER BY r_days ASC NULLS LAST)) AS r_score,
+        /* F 分：按订单数降序，订单越多分越高（直接降序即高分在前，无需反转） */
+        NTILE(5) OVER (ORDER BY total_order_cnt DESC NULLS LAST) AS f_score,
+        /* M 分：按金额降序，金额越高分越高（直接降序即高分在前，无需反转） */
+        NTILE(5) OVER (ORDER BY total_pay_amount DESC NULLS LAST) AS m_score
+    FROM order_agg
+)
+SELECT
+    rfm_scores.user_id AS user_id,
+    rfm_scores.r_score AS rfm_r_score,
+    rfm_scores.f_score AS rfm_f_score,
+    rfm_scores.m_score AS rfm_m_score,
+    /* 价值分层判定顺序：高价值 &gt; 流失 &gt; 中价值 &gt; 低价值（前置优先，避免相互覆盖） */
+    CASE
+        /* 高价值：R/F/M 三维均 ≥ 4 */
+        WHEN rfm_scores.r_score &gt;= 4
+         AND rfm_scores.f_score &gt;= 4
+         AND rfm_scores.m_score &gt;= 4 THEN '高价值'
+        /* 流失：R ≤ 2 且 F ≤ 2（长期未消费且频次低），优先于中/低价值判定 */
+        WHEN rfm_scores.r_score &lt;= 2
+         AND rfm_scores.f_score &lt;= 2 THEN '流失'
+        /* 中价值：R/F/M 任两维 ≥ 4 */
+        WHEN (rfm_scores.r_score &gt;= 4 AND rfm_scores.f_score &gt;= 4)
+          OR (rfm_scores.r_score &gt;= 4 AND rfm_scores.m_score &gt;= 4)
+          OR (rfm_scores.f_score &gt;= 4 AND rfm_scores.m_score &gt;= 4) THEN '中价值'
+        /* 低价值：任一维 ≥ 3（兜底 ELSE 同样归入低价值，确保非空） */
+        WHEN rfm_scores.r_score &gt;= 3
+          OR rfm_scores.f_score &gt;= 3
+          OR rfm_scores.m_score &gt;= 3 THEN '低价值'
+        ELSE '低价值'
+    END AS rfm_segment,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM rfm_scores
+——ddl/create_table_dwb_user_center_f_tmp2.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f_tmp2
+   规则: R0002 - RFM 评分中间表
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 基于订单聚合指标用 NTILE(5) 窗口函数跨全量用户打分，产出 RFM 三维分数与价值分层
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f_tmp2 (
+    rfm_r_score int,
+    rfm_f_score int,
+    rfm_m_score int,
+    rfm_segment varchar(20),
+    /* 审计字段 */
+    del_flag    NVARCHAR(1),
+    crt_cycle_id BIGINT,
+    last_upd_cycle_id BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f_tmp2 IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_r_score IS 'RFM-R值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_f_score IS 'RFM-F值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_m_score IS 'RFM-M值';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.rfm_segment IS '用户价值分层';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.del_flag IS '删除标识: Y-已删除, N-正常';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f_tmp2.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_user_center_f</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 4 项：rfm_r_score, rfm_f_score, rfm_m_score, rfm_segment（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0002.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_center_f_tmp2 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 4 项）（源→规则→目标）：
+（无源声明） --[数据加工]--&gt; rfm_r_score(RFM-R值)
+（无源声明） --[数据加工]--&gt; rfm_f_score(RFM-F值)
+（无源声明） --[数据加工]--&gt; rfm_m_score(RFM-M值)
+（无源声明） --[数据加工]--&gt; rfm_segment(用户价值分层)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_center_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户中心宽表
+粒度：每行一个用户记录
+调度：全量调度 / T+1，一天一调
+映射字段 46 项，来源表 9 张。
+本规则：R0003（用户中心宽表装配），step_type=full，目标表 dwb_user_center_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>——etl/R0003.sql——
+/* R0003: 用户中心宽表装配（以 dim_user_f 为主表，左联等级/地区/来源维度表与订单/RFM 中间表，CTE 聚合行为/优惠/退款/购物车事实，计算派生转化率与用户标签，产出最终用户中心宽表） */
+WITH
+/* CTE behavior_agg: 从 dwd_user_behavior_f 按 user_id 聚合浏览/收藏/加购历史次数 */
+behavior_agg AS (
+    SELECT
+        dub.user_id AS user_id,
+        COALESCE(SUM(dub.pv_cnt), 0) AS total_pv_cnt,
+        COALESCE(SUM(dub.collect_cnt), 0) AS total_collect_cnt,
+        COALESCE(SUM(dub.cart_cnt), 0) AS total_cart_cnt
+    FROM sdlog.dwd_user_behavior_f dub
+    GROUP BY dub.user_id
+),
+/* CTE coupon_agg: 从 dwd_coupon_use_f 按 user_id 聚合优惠券使用次数与金额 */
+coupon_agg AS (
+    SELECT
+        dcu.user_id AS user_id,
+        COUNT(*) AS coupon_used_cnt,
+        COALESCE(SUM(dcu.coupon_amount), 0) AS coupon_total_amount
+    FROM sdmar.dwd_coupon_use_f dcu
+    GROUP BY dcu.user_id
+),
+/* CTE refund_agg: 从 dwd_refund_f 按 user_id 聚合退款次数 */
+refund_agg AS (
+    SELECT
+        drf7.user_id AS user_id,
+        COUNT(*) AS refund_cnt
+    FROM sdref.dwd_refund_f drf7
+    GROUP BY drf7.user_id
+),
+/* CTE cart_agg: 从 dwd_cart_f（过滤 del_flag='N' 有效记录）按 user_id 聚合购物车商品数与金额 */
+cart_agg AS (
+    SELECT
+        dcf.user_id AS user_id,
+        COUNT(*) AS cart_product_cnt,
+        COALESCE(SUM(dcf.qty * dcf.price), 0) AS cart_total_amount
+    FROM sdlog.dwd_cart_f dcf
+    WHERE dcf.del_flag = 'N'
+    GROUP BY dcf.user_id
+)
+SELECT
+    duf.user_id AS user_id,
+    duf.user_name AS user_name,
+    /* 手机号脱敏：保留前 3 位与后 4 位，中间用 **** 屏蔽 */
+    CONCAT(LEFT(duf.user_phone, 3), '****', RIGHT(duf.user_phone, 4)) AS user_phone_masked,
+    /* 性别代码转中文：M→男，F→女，其他→未知 */
+    CASE duf.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_name,
+    duf.birthday AS birthday,
+    /* 年龄 = 当前年份 - 出生年份（按年粗算，未做生日日精确校验） */
+    YEAR(CURDATE()) - YEAR(duf.birthday) AS age,
+    duf.register_time AS register_time,
+    /* 注册天数 = 当前日期 - 注册日期 */
+    DATEDIFF(CURDATE(), duf.register_time) AS register_days,
+    duf.last_login_time AS last_login_time,
+    duf.level_id AS level_id,
+    dul.level_name AS level_name,
+    dul.min_points AS level_min_points,
+    duf.province_code AS province_code,
+    drf.region_name AS province_name,
+    duf.city_code AS city_code,
+    /* 城市名称：通过 city_code 二次关联 dim_region_f（drf_city 别名）取城市名称，与省份关联分开 */
+    drf_city.region_name AS city_name,
+    dus.source_name AS source_name,
+    duf.member_points AS member_points,
+    duf.member_balance AS member_balance,
+    /* 用户状态代码转中文：ACTIVE→正常，INACTIVE→未激活，FROZEN→冻结，其他→其他 */
+    CASE duf.user_status
+        WHEN 'ACTIVE' THEN '正常'
+        WHEN 'INACTIVE' THEN '未激活'
+        WHEN 'FROZEN' THEN '冻结'
+        ELSE '其他'
+    END AS user_status_name,
+    COALESCE(behavior_agg.total_pv_cnt, 0) AS total_pv_cnt,
+    COALESCE(behavior_agg.total_collect_cnt, 0) AS total_collect_cnt,
+    COALESCE(behavior_agg.total_cart_cnt, 0) AS total_cart_cnt,
+    /* 浏览-下单转化率(%) = 历史订单数 / 浏览次数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(tmp1.total_order_cnt, 0) * 100 / NULLIF(COALESCE(behavior_agg.total_pv_cnt, 0), 0) AS pv_to_order_rate,
+    /* 浏览-加购转化率(%) = 加购次数 / 浏览次数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(behavior_agg.total_cart_cnt, 0) * 100 / NULLIF(COALESCE(behavior_agg.total_pv_cnt, 0), 0) AS pv_to_cart_rate,
+    COALESCE(coupon_agg.coupon_used_cnt, 0) AS coupon_used_cnt,
+    COALESCE(coupon_agg.coupon_total_amount, 0) AS coupon_total_amount,
+    COALESCE(refund_agg.refund_cnt, 0) AS refund_cnt,
+    /* 退款率(%) = 退款次数 / 历史订单数 × 100；NULLIF 防除零，分母为 0 时返回 NULL */
+    COALESCE(refund_agg.refund_cnt, 0) * 100 / NULLIF(COALESCE(tmp1.total_order_cnt, 0), 0) AS refund_rate,
+    COALESCE(cart_agg.cart_product_cnt, 0) AS cart_product_cnt,
+    COALESCE(cart_agg.cart_total_amount, 0) AS cart_total_amount,
+    /* 下单频率标签：按订单数阶梯判定，前置优先（≥10→高频 &gt; ≥3→中频 &gt; ≥1→低频 &gt; 未购买） */
+    CASE
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 10 THEN '高频用户'
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 3 THEN '中频用户'
+        WHEN COALESCE(tmp1.total_order_cnt, 0) &gt;= 1 THEN '低频用户'
+        ELSE '未购买'
+    END AS order_freq_label,
+    /* 消费能力标签：按消费金额阶梯判定，前置优先（≥10000→高消费 &gt; ≥1000→中消费 &gt; ≥100→低消费 &gt; 无消费） */
+    CASE
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 10000 THEN '高消费'
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 1000 THEN '中消费'
+        WHEN COALESCE(tmp1.total_pay_amount, 0) &gt;= 100 THEN '低消费'
+        ELSE '无消费'
+    END AS consume_level_label,
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM dim.dim_user_f duf
+LEFT JOIN dim.dim_user_level_f dul
+    ON duf.level_id = dul.level_id
+LEFT JOIN dim.dim_region_f drf
+    ON duf.province_code = drf.region_code
+LEFT JOIN dim.dim_region_f drf_city
+    ON duf.city_code = drf_city.region_code
+LEFT JOIN dim.dim_user_source_f dus
+    ON duf.source_id = dus.source_id
+LEFT JOIN slusr.dwb_user_center_f_tmp1 tmp1
+    ON duf.user_id = tmp1.user_id
+LEFT JOIN slusr.dwb_user_center_f_tmp2 tmp2
+    ON duf.user_id = tmp2.user_id
+LEFT JOIN behavior_agg
+    ON duf.user_id = behavior_agg.user_id
+LEFT JOIN coupon_agg
+    ON duf.user_id = coupon_agg.user_id
+LEFT JOIN refund_agg
+    ON duf.user_id = refund_agg.user_id
+LEFT JOIN cart_agg
+    ON duf.user_id = cart_agg.user_id
+——ddl/create_table_dwb_user_center_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_center_f
+   规则: R0003 - 用户中心宽表装配
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-05
+   说明: 以 dim_user_f 为主表左联维度表与中间表，CTE 聚合行为/优惠/退款/购物车事实，计算派生转化率与标签，产出最终宽表
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_center_f (
+    user_id             bigint,
+    user_name           varchar(100),
+    user_phone_masked   varchar(20),
+    gender_name         varchar(10),
+    birthday            date,
+    age                 int,
+    register_time       datetime,
+    register_days       int,
+    last_login_time     datetime,
+    level_id            int,
+    level_name          varchar(50),
+    level_min_points    int,
+    province_code       varchar(20),
+    province_name       varchar(50),
+    city_code           varchar(20),
+    city_name           varchar(50),
+    source_name         varchar(50),
+    member_points       int,
+    member_balance      decimal(18,2),
+    user_status_name    varchar(20),
+    total_pv_cnt        int,
+    total_collect_cnt   int,
+    total_cart_cnt      int,
+    pv_to_order_rate    decimal(5,2),
+    pv_to_cart_rate     decimal(5,2),
+    coupon_used_cnt     int,
+    coupon_total_amount decimal(18,2),
+    refund_cnt          int,
+    refund_rate         decimal(5,2),
+    cart_product_cnt    int,
+    cart_total_amount   decimal(18,2),
+    order_freq_label    varchar(20),
+    consume_level_label varchar(20),
+    del_flag            NVARCHAR(1),
+    crt_cycle_id        BIGINT,
+    last_upd_cycle_id   BIGINT,
+    dw_last_update_date TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_center_f IS '用户中心宽表';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.gender_name IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_center_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_center_f.age IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.register_days IS '注册天数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_login_time IS '最近登录时间';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.level_min_points IS '等级所需积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_code IS '省份编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_code IS '城市编码';
+COMMENT ON COLUMN slusr.dwb_user_center_f.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_center_f.source_name IS '注册来源';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_center_f.member_balance IS '会员余额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.user_status_name IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_pv_cnt IS '浏览次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_collect_cnt IS '收藏次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.total_cart_cnt IS '加购次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_order_rate IS '浏览-下单转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.pv_to_cart_rate IS '浏览-加购转化率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_used_cnt IS '优惠券使用次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.coupon_total_amount IS '优惠券使用金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_cnt IS '退款次数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.refund_rate IS '退款率(%)';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_product_cnt IS '购物车商品数';
+COMMENT ON COLUMN slusr.dwb_user_center_f.cart_total_amount IS '购物车金额';
+COMMENT ON COLUMN slusr.dwb_user_center_f.order_freq_label IS '下单频率标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.consume_level_label IS '消费能力标签';
+COMMENT ON COLUMN slusr.dwb_user_center_f.del_flag IS '删除标识';
+COMMENT ON COLUMN slusr.dwb_user_center_f.crt_cycle_id IS '创建批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.last_upd_cycle_id IS '最后更新批次ID';
+COMMENT ON COLUMN slusr.dwb_user_center_f.dw_last_update_date IS '数仓最后更新时间';
+档案来源：../10_project_deliver/dwb_user_center_f</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 37 项：user_id, user_name, user_phone_masked, gender_name, birthday, age, register_time, register_days, last_login_time, level_id, level_name, level_min_points, province_code, province_name, city_code, city_name, source_name, member_points, member_balance, user_status_name, total_pv_cnt, total_collect_cnt, total_cart_cnt, pv_to_order_rate, pv_to_cart_rate, coupon_used_cnt, coupon_total_amount, refund_cnt, refund_rate, cart_product_cnt, cart_total_amount, order_freq_label, consume_level_label, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0003.sql），加工口径与 mapping 一致
+- 与目标表 dwb_user_center_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 37 项）（源→规则→目标）：
+dim_user_f.user_id --[直接复制]--&gt; user_id(用户ID)
+dim_user_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+dim_user_f.user_phone --[数据加工]--&gt; user_phone_masked(手机号(脱敏))
+dim_user_f.gender --[数据加工]--&gt; gender_name(性别)
+dim_user_f.birthday --[直接复制]--&gt; birthday(出生日期)
+（无源声明） --[数据加工]--&gt; age(年龄)
+dim_user_f.register_time --[直接复制]--&gt; register_time(注册时间)
+（无源声明） --[数据加工]--&gt; register_days(注册天数)
+dim_user_f.last_login_time --[直接复制]--&gt; last_login_time(最近登录时间)
+dim_user_f.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_f.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_f.min_points --[直接复制]--&gt; level_min_points(等级所需积分)
+dim_user_f.province_code --[直接复制]--&gt; province_code(省份编码)
+dim_region_f.region_name --[直接复制]--&gt; province_name(省份名称)
+dim_user_f.city_code --[直接复制]--&gt; city_code(城市编码)
+dim_region_f.region_name --[数据加工]--&gt; city_name(城市名称)
+dim_user_source_f.source_name --[直接复制]--&gt; source_name(注册来源)
+dim_user_f.member_points --[直接复制]--&gt; member_points(会员积分)
+dim_user_f.member_balance --[直接复制]--&gt; member_balance(会员余额)
+dim_user_f.user_status --[数据加工]--&gt; user_status_name(用户状态)
+dwd_user_behavior_f.pv_cnt --[数据加工]--&gt; total_pv_cnt(浏览次数)
+dwd_user_behavior_f.collect_cnt --[数据加工]--&gt; total_collect_cnt(收藏次数)
+dwd_user_behavior_f.cart_cnt --[数据加工]--&gt; total_cart_cnt(加购次数)
+（无源声明） --[数据加工]--&gt; pv_to_order_rate(浏览-下单转化率(%))
+（无源声明） --[数据加工]--&gt; pv_to_cart_rate(浏览-加购转化率(%))
+（无源声明） --[数据加工]--&gt; coupon_used_cnt(优惠券使用次数)
+（无源声明） --[数据加工]--&gt; coupon_total_amount(优惠券使用金额)
+（无源声明） --[数据加工]--&gt; refund_cnt(退款次数)
+（无源声明） --[数据加工]--&gt; refund_rate(退款率(%))
+（无源声明） --[数据加工]--&gt; cart_product_cnt(购物车商品数)
+（无源声明） --[数据加工]--&gt; cart_total_amount(购物车金额)
+（无源声明） --[数据加工]--&gt; order_freq_label(下单频率标签)
+（无源声明） --[数据加工]--&gt; consume_level_label(消费能力标签)
+（无源声明） --[赋值]--&gt; del_flag(删除标识)
+（无源声明） --[赋值]--&gt; crt_cycle_id(创建批次ID)
+（无源声明） --[赋值]--&gt; last_upd_cycle_id(最后更新批次ID)
+（无源声明） --[赋值]--&gt; dw_last_update_date(数仓最后更新时间)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_profile_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户画像宽表
+粒度：每行一个用户画像记录
+调度：全量调度 / T+1，一天一调
+映射字段 187 项，来源表 4 张。</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>产物内容（真实运行档案，文件原文）：
+——设计概述（ts.md §1 概述）——
+## 1. 概述
+| 项目 | 内容 |
+|------|------|
+| **F 表** | `slusr.dwb_user_profile_f`（用户画像宽表） |
+| **I 视图** | `slusr.dwb_user_profile_i`（F表镜像，对外查询） |
+| **业务主键** | user_id |
+| **写入策略** | 全量（可随时重刷） |
+| **字段统计** | 187 |
+| **规则数** | 1 |
+**来源表**:
+| # | 表名 | 中文名 | 别名 |
+|---|------|--------|------|
+| 1 | ods.ods_user_basic_f | 用户基础信息表 | oub |
+| 2 | dim.dim_user_level_d | 用户等级维度表 | dul |
+| 3 | dim.dim_region_d | 地区维度表 | drd |
+| 4 | dim.dim_user_source_d | 用户来源维度表 | dus |
+---
+——ddl/create_table_dwb_user_profile_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_profile_f
+   规则: R0001 - 用户画像宽表全量加工
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 用户画像宽表全量重写：以 oub 用户基础表为主表，LEFT JOIN 等级/地区/来源三张维表补齐画像属性，并对敏感字段脱敏、枚举字段转中文、派生时间维度字段。无粒度变化、无聚合，单条 INSERT 即可完成。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_profile_f (
+    user_id                    bigint,
+    user_name                  varchar(100),
+    user_phone_processed       varchar(20),
+    user_phone_masked          varchar(20),
+    email                      varchar(100),
+    gender_processed           varchar(10),
+    birthday                   date,
+    age_processed              int,
+    id_card                    varchar(20),
+    id_card_masked_processed   varchar(20),
+    real_name                  varchar(50),
+    nick_name                  varchar(50),
+    avatar_url                 varchar(500),
+    user_status                varchar(20),
+    user_status_name_processed varchar(20),
+    register_time              timestamp,
+    register_date_processed    date,
+    register_hour_processed    int,
+    register_weekday_processed int,
+    last_login_time            timestamp,
+    last_login_date_processed  date,
+    login_count                int,
+    province_code              varchar(20),
+    province_name              varchar(50),
+    city_code                  varchar(20),
+    city_name                  varchar(50),
+    district_code              varchar(20),
+    district_name              varchar(50),
+    address                    varchar(500),
+    zip_code                   varchar(10),
+    source_id                  int,
+    source_name                varchar(50),
+    source_type                varchar(20),
+    device_type                varchar(20),
+    os_type                    varchar(20),
+    app_version                varchar(20),
+    ip_address                 varchar(50),
+    longitude                  decimal(10,6),
+    latitude                   decimal(10,6),
+    language                   varchar(20),
+    timezone                   varchar(50),
+    currency                   varchar(10),
+    vip_level                  int,
+    vip_expire_time            timestamp,
+    is_vip_processed           int,
+    member_points              int,
+    balance                    decimal(18,2),
+    credit_score               int,
+    risk_level                 varchar(20),
+    verify_status              varchar(20),
+    level_id                   int,
+    level_name                 varchar(50),
+    level_code                 varchar(20),
+    level_rank                 int,
+    min_points                 int,
+    max_points                 int,
+    level_icon                 varchar(500),
+    level_color                varchar(20),
+    upgrade_points             int,
+    current_level_points       int,
+    next_level_points          int,
+    progress_percentage        decimal(5,2),
+    privilege_list             varchar(1000),
+    discount_rate              decimal(5,2),
+    points_rate                decimal(5,2),
+    free_shipping              int,
+    exclusive_products         int,
+    priority_support           int,
+    birthday_bonus             int,
+    monthly_coupon             int,
+    annual_gift                int,
+    vip_service                int,
+    invite_quota               int,
+    max_orders_per_day         int,
+    max_return_days            int,
+    level_benefits             varchar(1000),
+    upgrade_time               timestamp,
+    downgrade_time             timestamp,
+    maintain_days              int,
+    level_status               varchar(20),
+    create_time                timestamp,
+    update_time                timestamp,
+    valid_from                 timestamp,
+    valid_to                   timestamp,
+    is_active                  int,
+    level_tier                 int,
+    level_group                varchar(50),
+    level_category             varchar(50),
+    points_required            int,
+    orders_required            int,
+    amount_required            decimal(18,2),
+    days_required              int,
+    growth_value               int,
+    experience_value           int,
+    contribution_value         int,
+    activity_value             int,
+    loyalty_score              decimal(5,2),
+    engagement_score           decimal(5,2),
+    satisfaction_score         decimal(5,2),
+    retention_score            decimal(5,2),
+    region_id                  int,
+    region_code                varchar(20),
+    region_name                varchar(100),
+    parent_id                  int,
+    region_level               int,
+    region_path                varchar(500),
+    province_id                int,
+    province_abbr              varchar(20),
+    city_id                    int,
+    city_abbr                  varchar(20),
+    district_id                int,
+    district_abbr              varchar(20),
+    street_id                  int,
+    street_code                varchar(20),
+    street_name                varchar(50),
+    center_longitude           decimal(10,6),
+    center_latitude            decimal(10,6),
+    area_size                  decimal(18,2),
+    population                 int,
+    gdp                        decimal(18,2),
+    gdp_per_capita             decimal(18,2),
+    climate_type               varchar(50),
+    economy_level              varchar(50),
+    development_level          varchar(50),
+    urban_rate                 decimal(5,2),
+    region_type                varchar(50),
+    is_coastal                 int,
+    is_border                  int,
+    is_capital                 int,
+    is_special                 int,
+    postal_code_prefix         varchar(10),
+    phone_area_code            varchar(20),
+    car_plate_prefix           varchar(10),
+    airport_code               varchar(10),
+    railway_station_code       varchar(20),
+    port_code                  varchar(20),
+    weather_station_code       varchar(20),
+    customs_code               varchar(20),
+    statistical_code           varchar(20),
+    iso_code                   varchar(20),
+    source_code                varchar(50),
+    source_category            varchar(50),
+    channel_id                 int,
+    channel_code               varchar(50),
+    channel_name               varchar(100),
+    channel_type               varchar(50),
+    channel_category           varchar(50),
+    campaign_id                int,
+    campaign_code              varchar(50),
+    campaign_name              varchar(100),
+    campaign_type              varchar(50),
+    medium_id                  int,
+    medium_code                varchar(50),
+    medium_name                varchar(100),
+    medium_type                varchar(50),
+    term_id                    int,
+    term_keyword               varchar(200),
+    content_id                 int,
+    content_name               varchar(200),
+    referral_url               varchar(500),
+    landing_page               varchar(500),
+    utm_source                 varchar(100),
+    utm_medium                 varchar(100),
+    utm_campaign               varchar(100),
+    utm_term                   varchar(100),
+    utm_content                varchar(100),
+    cost_per_acquisition       decimal(18,2),
+    conversion_rate            decimal(5,2),
+    quality_score              decimal(5,2),
+    retention_rate_7d          decimal(5,2),
+    retention_rate_30d         decimal(5,2),
+    lifetime_value             decimal(18,2),
+    first_order_amount         decimal(18,2),
+    first_order_days           int,
+    register_device            varchar(50),
+    register_os                varchar(50),
+    register_browser           varchar(50),
+    register_network           varchar(50),
+    register_location          varchar(200),
+    attribution_model          varchar(50),
+    lookback_days              int,
+    priority                   int,
+    is_paid                    int,
+    del_flag                   NVARCHAR(1),
+    crt_cycle_id               BIGINT,
+    last_upd_cycle_id          BIGINT,
+    dw_last_update_date        TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_profile_f IS '用户画像宽表';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_processed IS '手机号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.email IS '电子邮箱';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.gender_processed IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.age_processed IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card IS '身份证号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card_masked_processed IS '身份证号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.real_name IS '真实姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.nick_name IS '昵称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.avatar_url IS '头像URL';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status_name_processed IS '用户状态名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_date_processed IS '注册日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_hour_processed IS '注册小时';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_weekday_processed IS '注册星期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.last_login_time IS '最后登录时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.last_login_date_processed IS '最后登录日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.login_count IS '登录次数';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.province_code IS '省份代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.city_code IS '城市代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.district_code IS '区县代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.district_name IS '区县名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.address IS '详细地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.zip_code IS '邮政编码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_id IS '来源渠道ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_name IS '来源渠道名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_type IS '来源类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.device_type IS '设备类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.os_type IS '操作系统';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.app_version IS 'APP版本';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.ip_address IS 'IP地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.longitude IS '经度';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.latitude IS '纬度';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.language IS '语言';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.timezone IS '时区';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.currency IS '货币';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.vip_level IS 'VIP等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.vip_expire_time IS 'VIP到期时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.is_vip_processed IS '是否VIP';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.balance IS '账户余额';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.credit_score IS '信用分';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.risk_level IS '风险等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.verify_status IS '认证状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_code IS '等级代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_rank IS '等级排序';
+COMMENT ON CO…（截断）
+——ddl/create_view_dwb_user_profile_i.sql——
+/* I视图: slusr.dwb_user_profile_i（用户画像宽表，F表镜像，对外消费接口） */
+CREATE OR REPLACE VIEW slusr.dwb_user_profile_i AS
+SELECT
+    user_id,
+    user_name,
+    user_phone_processed,
+    user_phone_masked,
+    email,
+    gender_processed,
+    birthday,
+    age_processed,
+    id_card,
+    id_card_masked_processed,
+    real_name,
+    nick_name,
+    avatar_url,
+    user_status,
+    user_status_name_processed,
+    register_time,
+    register_date_processed,
+    register_hour_processed,
+    register_weekday_processed,
+    last_login_time,
+    last_login_date_processed,
+    login_count,
+    province_code,
+    province_name,
+    city_code,
+    city_name,
+    district_code,
+    district_name,
+    address,
+    zip_code,
+    source_id,
+    source_name,
+    source_type,
+    device_type,
+    os_type,
+    app_version,
+    ip_address,
+    longitude,
+    latitude,
+    language,
+    timezone,
+    currency,
+    vip_level,
+    vip_expire_time,
+    is_vip_processed,
+    member_points,
+    balance,
+    credit_score,
+    risk_level,
+    verify_status,
+    level_id,
+    level_name,
+    level_code,
+    level_rank,
+    min_points,
+    max_points,
+    level_icon,
+    level_color,
+    upgrade_points,
+    current_level_points,
+    next_level_points,
+    progress_percentage,
+    privilege_list,
+    discount_rate,
+    points_rate,
+    free_shipping,
+    exclusive_products,
+    priority_support,
+    birthday_bonus,
+    monthly_coupon,
+    annual_gift,
+    vip_service,
+    invite_quota,
+    max_orders_per_day,
+    max_return_days,
+    level_benefits,
+    upgrade_time,
+    downgrade_time,
+    maintain_days,
+    level_status,
+    create_time,
+    update_time,
+    valid_from,
+    valid_to,
+    is_active,
+    level_tier,
+    level_group,
+    level_category,
+    points_required,
+    orders_required,
+    amount_required,
+    days_required,
+    growth_value,
+    experience_value,
+    contribution_value,
+    activity_value,
+    loyalty_score,
+    engagement_score,
+    satisfaction_score,
+    retention_score,
+    region_id,
+    region_code,
+    region_name,
+    parent_id,
+    region_level,
+    region_path,
+    province_id,
+    province_abbr,
+    city_id,
+    city_abbr,
+    district_id,
+    district_abbr,
+    street_id,
+    street_code,
+    street_name,
+    center_longitude,
+    center_latitude,
+    area_size,
+    population,
+    gdp,
+    gdp_per_capita,
+    climate_type,
+    economy_level,
+    development_level,
+    urban_rate,
+    region_type,
+    is_coastal,
+    is_border,
+    is_capital,
+    is_special,
+    postal_code_prefix,
+    phone_area_code,
+    car_plate_prefix,
+    airport_code,
+    railway_station_code,
+    port_code,
+    weather_station_code,
+    customs_code,
+    statistical_code,
+    iso_code,
+    source_code,
+    source_category,
+    channel_id,
+    channel_code,
+    channel_name,
+    channel_type,
+    channel_category,
+    campaign_id,
+    campaign_code,
+    campaign_name,
+    campaign_type,
+    medium_id,
+    medium_code,
+    medium_name,
+    medium_type,
+    term_id,
+    term_keyword,
+    content_id,
+    content_name,
+    referral_url,
+    landing_page,
+    utm_source,
+    utm_medium,
+    utm_campaign,
+    utm_term,
+    utm_content,
+    cost_per_acquisition,
+    conversion_rate,
+    quality_score,
+    retention_rate_7d,
+    retention_rate_30d,
+    lifetime_value,
+    first_order_amount,
+    first_order_days,
+    register_device,
+    register_os,
+    register_browser,
+    register_network,
+    register_location,
+    attribution_model,
+    lookback_days,
+    priority,
+    is_paid,
+    del_flag,
+    crt_cycle_id,
+    last_upd_cycle_id,
+    dw_last_update_date
+FROM slusr.dwb_user_profile_f;
+COMMENT ON TABLE slusr.dwb_user_profile_i IS '用户画像宽表（视图）';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_phone_processed IS '手机号';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.email IS '电子邮箱';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.gender_processed IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.age_processed IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.id_card IS '身份证号';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.id_card_masked_processed IS '身份证号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.real_name IS '真实姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.nick_name IS '昵称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.avatar_url IS '头像URL';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_status IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.user_status_name_processed IS '用户状态名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.register_date_processed IS '注册日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.register_hour_processed IS '注册小时';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.register_weekday_processed IS '注册星期';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.last_login_time IS '最后登录时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.last_login_date_processed IS '最后登录日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.login_count IS '登录次数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.province_code IS '省份代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.city_code IS '城市代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.district_code IS '区县代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.district_name IS '区县名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.address IS '详细地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.zip_code IS '邮政编码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.source_id IS '来源渠道ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.source_name IS '来源渠道名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.source_type IS '来源类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.device_type IS '设备类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.os_type IS '操作系统';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.app_version IS 'APP版本';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.ip_address IS 'IP地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.longitude IS '经度';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.latitude IS '纬度';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.language IS '语言';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.timezone IS '时区';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.currency IS '货币';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.vip_level IS 'VIP等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.vip_expire_time IS 'VIP到期时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.is_vip_processed IS '是否VIP';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.balance IS '账户余额';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.credit_score IS '信用分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.risk_level IS '风险等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.verify_status IS '认证状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_code IS '等级代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_rank IS '等级排序';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.min_points IS '最小积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.max_points IS '最大积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_icon IS '等级图标';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_color IS '等级颜色';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.upgrade_points IS '升级所需积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.current_level_points IS '当前等级积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.next_level_points IS '下一等级积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.progress_percentage IS '升级进度百分比';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.privilege_list IS '权限列表';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.discount_rate IS '折扣率';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.points_rate IS '积分倍率';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.free_shipping IS '免费配送';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.exclusive_products IS '专属商品';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.priority_support IS '优先客服';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.birthday_bonus IS '生日礼金';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.monthly_coupon IS '月度优惠券';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.annual_gift IS '年度礼品';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.vip_service IS 'VIP服务';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.invite_quota IS '邀请名额';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.max_orders_per_day IS '每日最大订单数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.max_return_days IS '最大退货天数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_benefits IS '等级权益';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.upgrade_time IS '升级时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.downgrade_time IS '降级时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.maintain_days IS '维持天数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_status IS '等级状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.create_time IS '创建时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.update_time IS '更新时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.valid_from IS '生效开始时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.valid_to IS '生效结束时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.is_active IS '是否激活';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_tier IS '等级层级';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_group IS '等级分组';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.level_category IS '等级分类';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.points_required IS '所需积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.orders_required IS '所需订单数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.amount_required IS '所需金额';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.days_required IS '所需天数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.growth_value IS '成长值';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.experience_value IS '经验值';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.contribution_value IS '贡献值';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.activity_value IS '活跃值';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.loyalty_score IS '忠诚度分数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.engagement_score IS '参与度分数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.satisfaction_score IS '满意度分数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.retention_score IS '留存率分数';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.region_id IS '地区ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.region_code IS '地区代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.region_name IS '地区名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.parent_id IS '父级ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.region_level IS '地区层级';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.region_path IS '地区路径';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.province_id IS '省份ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.province_abbr IS '省份简称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.city_id IS '城市ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.city_abbr IS '城市简称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.district_id IS '区县ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.district_abbr IS '区县简称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.street_id IS '街道ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.street_code IS '街道代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.street_name IS '街道名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.center_longitude IS '中心经度';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.center_latitude IS '中心纬度';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.area_size IS '区域面积';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.population IS '人口数量';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.gdp IS 'GDP';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.gdp_per_capita IS '人均GDP';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.climate_type IS '气候类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_i.economy_level IS '经济水平';
+COMM…（截断）
+——etl/R0001.sql——
+/* =====================================================
+   ETL 转换脚本（纯 SELECT，由调度/UT 包装 INSERT）
+   规则: R0001 - 用户画像宽表全量加工
+   目标表: slusr.dwb_user_profile_f
+   来源表:
+     - ods.ods_user_basic_f (oub) - 用户基础主表
+     - dim.dim_user_level_d  (dul) - 用户等级维
+     - dim.dim_region_d      (drd) - 地区维
+     - dim.dim_user_source_d (dus) - 用户来源维
+   写入方式: 全量重写（truncate_table）
+   设计意图: 以 oub 为主表，LEFT JOIN 三张维表补齐画像属性，
+             对敏感字段脱敏、枚举字段转中文、派生时间维度字段。
+             无粒度变化、无聚合，单条 SELECT 即可完成。
+   ===================================================== */
+SELECT
+    oub.user_id AS user_id,
+    COALESCE(oub.user_name, '') AS user_name,
+    /* 手机号脱敏：保留前3位+后4位，中间4个星号屏蔽；NULL 安全兜底为空串 */
+    COALESCE(
+        LEFT(oub.user_phone, 3) || '****' || RIGHT(oub.user_phone, 4),
+        ''
+    ) AS user_phone_processed,
+    COALESCE(oub.user_phone_masked, '') AS user_phone_masked,
+    COALESCE(oub.email, '') AS email,
+    /* 性别代码转中文：M→男 F→女 其余→未知（NULL 走 ELSE 兜底为未知） */
+    CASE oub.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_processed,
+    oub.birthday AS birthday,
+    /* 年龄：当前年份减出生年份（birthday 为 NULL 时返回 0） */
+    COALESCE(
+        EXTRACT(YEAR FROM CURRENT_DATE)::int - EXTRACT(YEAR FROM oub.birthday)::int,
+        0
+    ) AS age_processed,
+    COALESCE(oub.id_card, '') AS id_card,
+    /* 身份证脱敏：保留前6位+后4位，中间8个星号屏蔽；NULL 安全兜底为空串 */
+    COA…（截断）</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>任务完成标准（自 RS 派生，逐项可核验）：
+- 目标表 slusr.dwb_user_profile_f，粒度：每行一个用户画像记录
+- 目标字段 187 项：user_id, user_name, user_phone_processed, user_phone_masked, email, gender_processed, birthday, age_processed, id_card, id_card_masked_processed, real_name, nick_name, avatar_url, user_status, user_status_name_processed, register_time, register_date_processed, register_hour_processed, register_weekday_processed, last_login_time, last_login_date_processed, login_count, province_code, province_name, city_code, city_name, district_code, district_name, address, zip_code, source_id, source_name, source_type, device_type, os_type, app_version, ip_address, longitude, latitude, language, timezone, currency, vip_level, vip_expire_time, is_vip_processed, member_points, balance, credit_score, risk_level, verify_status, level_id, level_name, level_code, level_rank, min_points, max_points, level_icon, level_color, upgrade_points, current_level_points, next_level_points, progress_percentage, privilege_list, discount_rate, points_rate, free_shipping, exclusive_products, priority_support, birthday_bonus, monthly_coupon, annual_gift, vip_service, invite_quota, max_orders_per_day, max_return_days, level_benefits, upgrade_time, downgrade_time, maintain_days, level_status, create_time, update_time, valid_from, valid_to, is_active, level_tier, level_group, level_category, points_required, orders_required, amount_required, days_required, growth_value, experience_value, contribution_value, activity_value, loyalty_score, engagement_score, satisfaction_score, retention_score, region_id, region_code, region_name, parent_id, region_level, region_path, province_id, province_abbr, city_id, city_abbr, district_id, district_abbr, street_id, street_code, street_name, center_longitude, center_latitude, area_size, population, gdp, gdp_per_capita, climate_type, economy_level, development_level, urban_rate, region_type, is_coastal, is_border, is_capital, is_special, postal_code_prefix, phone_area_code, car_plate_prefix, airport_code, railway_station_code, port_code, weather_station_code, customs_code, statistical_code, iso_code, source_code, source_category, channel_id, channel_code, channel_name, channel_type, channel_category, campaign_id, campaign_code, campaign_name, campaign_type, medium_id, medium_code, medium_name, medium_type, term_id, term_keyword, content_id, content_name, referral_url, landing_page, utm_source, utm_medium, utm_campaign, utm_term, utm_content, cost_per_acquisition, conversion_rate, quality_score, retention_rate_7d, retention_rate_30d, lifetime_value, first_order_amount, first_order_days, register_device, register_os, register_browser, register_network, register_location, attribution_model, lookback_days, priority, is_paid, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 DDL 与 SELECT 输出列中，标准审计字段允许另加）
+- 来源表 4 张：ods_user_basic_f, dim_user_level_d, dim_region_d, dim_user_source_d
+- 建表 DDL（create_table_dwb_user_profile_f.sql）与映射结构一致；ETL 每规则一个 SELECT 文件
+- 调度方案：全量调度</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射 187 项（源→规则→目标）：
+ods_user_basic_f.user_id --[直接复制]--&gt; user_id(用户ID)
+ods_user_basic_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+ods_user_basic_f.user_phone --[数据加工]--&gt; user_phone_processed(手机号)
+ods_user_basic_f.user_phone_masked --[直接复制]--&gt; user_phone_masked(手机号(脱敏))
+ods_user_basic_f.email --[直接复制]--&gt; email(电子邮箱)
+ods_user_basic_f.gender --[数据加工]--&gt; gender_processed(性别)
+ods_user_basic_f.birthday --[直接复制]--&gt; birthday(出生日期)
+ods_user_basic_f.age --[数据加工]--&gt; age_processed(年龄)
+ods_user_basic_f.id_card --[直接复制]--&gt; id_card(身份证号)
+ods_user_basic_f.id_card_masked --[数据加工]--&gt; id_card_masked_processed(身份证号(脱敏))
+ods_user_basic_f.real_name --[直接复制]--&gt; real_name(真实姓名)
+ods_user_basic_f.nick_name --[直接复制]--&gt; nick_name(昵称)
+ods_user_basic_f.avatar_url --[直接复制]--&gt; avatar_url(头像URL)
+ods_user_basic_f.user_status --[直接复制]--&gt; user_status(用户状态)
+ods_user_basic_f.user_status_name --[数据加工]--&gt; user_status_name_processed(用户状态名称)
+ods_user_basic_f.register_time --[直接复制]--&gt; register_time(注册时间)
+ods_user_basic_f.register_date --[数据加工]--&gt; register_date_processed(注册日期)
+ods_user_basic_f.register_hour --[数据加工]--&gt; register_hour_processed(注册小时)
+ods_user_basic_f.register_weekday --[数据加工]--&gt; register_weekday_processed(注册星期)
+ods_user_basic_f.last_login_time --[直接复制]--&gt; last_login_time(最后登录时间)
+ods_user_basic_f.last_login_date --[数据加工]--&gt; last_login_date_processed(最后登录日期)
+ods_user_basic_f.login_count --[直接复制]--&gt; login_count(登录次数)
+ods_user_basic_f.province_code --[直接复制]--&gt; province_code(省份代码)
+ods_user_basic_f.province_name --[直接复制]--&gt; province_name(省份名称)
+ods_user_basic_f.city_code --[直接复制]--&gt; city_code(城市代码)
+ods_user_basic_f.city_name --[直接复制]--&gt; city_name(城市名称)
+ods_user_basic_f.district_code --[直接复制]--&gt; district_code(区县代码)
+ods_user_basic_f.district_name --[直接复制]--&gt; district_name(区县名称)
+ods_user_basic_f.address --[直接复制]--&gt; address(详细地址)
+ods_user_basic_f.zip_code --[直接复制]--&gt; zip_code(邮政编码)
+ods_user_basic_f.source_id --[直接复制]--&gt; source_id(来源渠道ID)
+ods_user_basic_f.source_name --[直接复制]--&gt; source_name(来源渠道名称)
+ods_user_basic_f.source_type --[直接复制]--&gt; source_type(来源类型)
+ods_user_basic_f.device_type --[直接复制]--&gt; device_type(设备类型)
+ods_user_basic_f.os_type --[直接复制]--&gt; os_type(操作系统)
+ods_user_basic_f.app_version --[直接复制]--&gt; app_version(APP版本)
+ods_user_basic_f.ip_address --[直接复制]--&gt; ip_address(IP地址)
+ods_user_basic_f.longitude --[直接复制]--&gt; longitude(经度)
+ods_user_basic_f.latitude --[直接复制]--&gt; latitude(纬度)
+ods_user_basic_f.language --[直接复制]--&gt; language(语言)
+ods_user_basic_f.timezone --[直接复制]--&gt; timezone(时区)
+ods_user_basic_f.currency --[直接复制]--&gt; currency(货币)
+ods_user_basic_f.vip_level --[直接复制]--&gt; vip_level(VIP等级)
+ods_user_basic_f.vip_expire_time --[直接复制]--&gt; vip_expire_time(VIP到期时间)
+ods_user_basic_f.is_vip --[数据加工]--&gt; is_vip_processed(是否VIP)
+ods_user_basic_f.member_points --[直接复制]--&gt; member_points(会员积分)
+ods_user_basic_f.balance --[直接复制]--&gt; balance(账户余额)
+ods_user_basic_f.credit_score --[直接复制]--&gt; credit_score(信用分)
+ods_user_basic_f.risk_level --[直接复制]--&gt; risk_level(风险等级)
+ods_user_basic_f.verify_status --[直接复制]--&gt; verify_status(认证状态)
+dim_user_level_d.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_d.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_d.level_code --[直接复制]--&gt; level_code(等级代码)
+dim_user_level_d.level_rank --[直接复制]--&gt; level_rank(等级排序)
+dim_user_level_d.min_points --[直接复制]--&gt; min_points(最小积分)
+dim_user_level_d.max_points --[直接复制]--&gt; max_points(最大积分)
+dim_user_level_d.level_icon --[直接复制]--&gt; level_icon(等级图标)
+dim_user_level_d.level_color --[直接复制]--&gt; level_color(等级颜色)
+dim_user_level_d.upgrade_points --[直接复制]--&gt; upgrade_points(升级所需积分)
+dim_user_level_d.current_level_points --[直接复制]--&gt; current_level_points(当前等级积分)
+dim_user_level_d.next_level_points --[直接复制]--&gt; next_level_points(下一等级积分)
+dim_user_level_d.progress_percentage --[数据加工]--&gt; progress_percentage(升级进度百分比)
+dim_user_level_d.privilege_list --[直接复制]--&gt; privilege_list(权限列表)
+dim_user_level_d.discount_rate --[直接复制]--&gt; discount_rate(折扣率)
+dim_user_level_d.points_rate --[直接复制]--&gt; points_rate(积分倍率)
+dim_user_level_d.free_shipping --[直接复制]--&gt; free_shipping(免费配送)
+dim_user_level_d.exclusive_products --[直接复制]--&gt; exclusive_products(专属商品)
+dim_user_level_d.priority_support --[直接复制]--&gt; priority_support(优先客服)
+dim_user_level_d.birthday_bonus --[直接复制]--&gt; birthday_bonus(生日礼金)
+dim_user_level_d.monthly_coupon --[直接复制]--&gt; monthly_coupon(月度优惠券)
+dim_user_level_d.annual_gift --[直接复制]--&gt; annual_gift(年度礼品)
+dim_user_level_d.vip_service --[直接复制]--&gt; vip_service(VIP服务)
+dim_user_level_d.invite_quota --[直接复制]--&gt; invite_quota(邀请名额)
+dim_user_level_d.max_orders_per_day --[直接复制]--&gt; max_orders_per_day(每日最大订单数)
+dim_user_level_d.max_return_days --[直接复制]--&gt; max_return_days(最大退货天数)
+dim_user_level_d.level_benefits --[直接复制]--&gt; level_benefits(等级权益)
+dim_user_level_d.upgrade_time --[直接复制]--&gt; upgrade_time(升级时间)
+dim_user_level_d.downgrade_time --[直接复制]--&gt; downgrade_time(降级时间)
+dim_user_level_d.maintain_days --[直接复制]--&gt; maintain_days(维持天数)
+dim_user_level_d.level_status --[直接复制]--&gt; level_status(等级状态)
+dim_user_level_d.create_time --[直接复制]--&gt; create_time(创建时间)
+di…（截断）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>任务：为 slusr.dwb_user_profile_f 完成设计、评审、开发及测试（输入=RS+mapping，流程=设计→闸口→编码→UT）。
+表说明：用户画像宽表
+粒度：每行一个用户画像记录
+调度：全量调度 / T+1，一天一调
+映射字段 187 项，来源表 4 张。
+本规则：R0001（用户画像宽表全量加工），step_type=full，目标表 slusr.dwb_user_profile_f——产出该规则的加工 SELECT。</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>——etl/R0001.sql——
+/* =====================================================
+   ETL 转换脚本（纯 SELECT，由调度/UT 包装 INSERT）
+   规则: R0001 - 用户画像宽表全量加工
+   目标表: slusr.dwb_user_profile_f
+   来源表:
+     - ods.ods_user_basic_f (oub) - 用户基础主表
+     - dim.dim_user_level_d  (dul) - 用户等级维
+     - dim.dim_region_d      (drd) - 地区维
+     - dim.dim_user_source_d (dus) - 用户来源维
+   写入方式: 全量重写（truncate_table）
+   设计意图: 以 oub 为主表，LEFT JOIN 三张维表补齐画像属性，
+             对敏感字段脱敏、枚举字段转中文、派生时间维度字段。
+             无粒度变化、无聚合，单条 SELECT 即可完成。
+   ===================================================== */
+SELECT
+    oub.user_id AS user_id,
+    COALESCE(oub.user_name, '') AS user_name,
+    /* 手机号脱敏：保留前3位+后4位，中间4个星号屏蔽；NULL 安全兜底为空串 */
+    COALESCE(
+        LEFT(oub.user_phone, 3) || '****' || RIGHT(oub.user_phone, 4),
+        ''
+    ) AS user_phone_processed,
+    COALESCE(oub.user_phone_masked, '') AS user_phone_masked,
+    COALESCE(oub.email, '') AS email,
+    /* 性别代码转中文：M→男 F→女 其余→未知（NULL 走 ELSE 兜底为未知） */
+    CASE oub.gender
+        WHEN 'M' THEN '男'
+        WHEN 'F' THEN '女'
+        ELSE '未知'
+    END AS gender_processed,
+    oub.birthday AS birthday,
+    /* 年龄：当前年份减出生年份（birthday 为 NULL 时返回 0） */
+    COALESCE(
+        EXTRACT(YEAR FROM CURRENT_DATE)::int - EXTRACT(YEAR FROM oub.birthday)::int,
+        0
+    ) AS age_processed,
+    COALESCE(oub.id_card, '') AS id_card,
+    /* 身份证脱敏：保留前6位+后4位，中间8个星号屏蔽；NULL 安全兜底为空串 */
+    COALESCE(
+        LEFT(oub.id_card_masked, 6) || '********' || RIGHT(oub.id_card_masked, 4),
+        ''
+    ) AS id_card_masked_processed,
+    COALESCE(oub.real_name, '') AS real_name,
+    COALESCE(oub.nick_name, '') AS nick_name,
+    COALESCE(oub.avatar_url, '') AS avatar_url,
+    COALESCE(oub.user_status, '') AS user_status,
+    /* 用户状态代码转中文：ACTIVE→正常 INACTIVE→未激活 BANNED→封禁 其余→未知
+       注：切片 source_fields 标记为 user_status_name，但 oub 表无此字段，按 design_logic 用 user_status */
+    CASE oub.user_status
+        WHEN 'ACTIVE' THEN '正常'
+        WHEN 'INACTIVE' THEN '未激活'
+        WHEN 'BANNED' THEN '封禁'
+        ELSE '未知'
+    END AS user_status_name_processed,
+    oub.register_time AS register_time,
+    /* 注册日期：从注册时间戳提取日期部分 */
+    CAST(oub.register_time AS DATE) AS register_date_processed,
+    /* 注册小时：从注册时间戳提取小时（24小时制），NULL 时返回 0 */
+    COALESCE(EXTRACT(HOUR FROM oub.register_time)::int, 0) AS register_hour_processed,
+    /* 注册星期：从注册时间戳提取星期几（DOW：0=周日,1=周一...6=周六），NULL 时返回 0 */
+    COALESCE(EXTRACT(DOW FROM oub.register_time)::int, 0) AS register_weekday_processed,
+    oub.last_login_time AS last_login_time,
+    /* 最后登录日期：从最后登录时间戳提取日期部分 */
+    CAST(oub.last_login_time AS DATE) AS last_login_date_processed,
+    COALESCE(oub.login_count, 0) AS login_count,
+    COALESCE(oub.province_code, '') AS province_code,
+    COALESCE(oub.province_name, '') AS province_name,
+    COALESCE(oub.city_code, '') AS city_code,
+    COALESCE(oub.city_name, '') AS city_name,
+    COALESCE(oub.district_code, '') AS district_code,
+    COALESCE(oub.district_name, '') AS district_name,
+    COALESCE(oub.address, '') AS address,
+    COALESCE(oub.zip_code, '') AS zip_code,
+    COALESCE(oub.source_id, 0) AS source_id,
+    COALESCE(oub.source_name, '') AS source_name,
+    COALESCE(oub.source_type, '') AS source_type,
+    COALESCE(oub.device_type, '') AS device_type,
+    COALESCE(oub.os_type, '') AS os_type,
+    COALESCE(oub.app_version, '') AS app_version,
+    COALESCE(oub.ip_address, '') AS ip_address,
+    COALESCE(oub.longitude, 0) AS longitude,
+    COALESCE(oub.latitude, 0) AS latitude,
+    COALESCE(oub.language, '') AS language,
+    COALESCE(oub.timezone, '') AS timezone,
+    COALESCE(oub.currency, '') AS currency,
+    COALESCE(oub.vip_level, 0) AS vip_level,
+    oub.vip_expire_time AS vip_expire_time,
+    /* 是否VIP：VIP到期时间 &gt; 当前时间则为 1，否则为 0（NULL 走 ELSE 返回 0） */
+    CASE
+        WHEN oub.vip_expire_time &gt; CURRENT_TIMESTAMP THEN 1
+        ELSE 0
+    END AS is_vip_processed,
+    COALESCE(oub.member_points, 0) AS member_points,
+    COALESCE(oub.balance, 0) AS balance,
+    COALESCE(oub.credit_score, 0) AS credit_score,
+    COALESCE(oub.risk_level, '') AS risk_level,
+    COALESCE(oub.verify_status, '') AS verify_status,
+    COALESCE(dul.level_id, 0) AS level_id,
+    COALESCE(dul.level_name, '') AS level_name,
+    COALESCE(dul.level_code, '') AS level_code,
+    COALESCE(dul.level_rank, 0) AS level_rank,
+    COALESCE(dul.min_points, 0) AS min_points,
+    COALESCE(dul.max_points, 0) AS max_points,
+    COALESCE(dul.level_icon, '') AS level_icon,
+    COALESCE(dul.level_color, '') AS level_color,
+    COALESCE(dul.upgrade_points, 0) AS upgrade_points,
+    COALESCE(dul.current_level_points, 0) AS current_level_points,
+    COALESCE(dul.next_level_points, 0) AS next_level_points,
+    /* 升级进度百分比：当前等级积分 / 升级所需积分 * 100，防 NULL 除零 */
+    CASE
+        WHEN COALESCE(dul.upgrade_points, 0) &gt; 0
+        THEN ROUND(COALESCE(dul.current_level_points, 0) * 100.0 / dul.upgrade_points, 2)
+        ELSE 0
+    END AS progress_percentage,
+    COALESCE(dul.privilege_list, '') AS privilege_list,
+    COALESCE(dul.discount_rate, 0) AS discount_rate,
+    COALESCE(dul.points_rate, 0) AS points_rate,
+    COALESCE(dul.free_shipping, 0) AS free_shipping,
+    COALESCE(dul.exclusive_products, 0) AS exclusive_products,
+    COALESCE(dul.priority_support, 0) AS priority_support,
+    COALESCE(dul.birthday_bonus, 0) AS birthday_bonus,
+    COALESCE(dul.monthly_coupon, 0) AS monthly_coupon,
+    COALESCE(dul.annual_gift, 0) AS annual_gift,
+    COALESCE(dul.vip_service, 0) AS vip_service,
+    COALESCE(dul.invite_quota, 0) AS invite_quota,
+    COALESCE(dul.max_orders_per_day, 0) AS max_orders_per_day,
+    COALESCE(dul.max_return_days, 0) AS max_return_days,
+    COALESCE(dul.level_benefits, '') AS level_benefits,
+    dul.upgrade_time AS upgrade_time,
+    dul.downgrade_time AS downgrade_time,
+    COALESCE(dul.maintain_days, 0) AS maintain_days,
+    COALESCE(dul.level_status, '') AS level_status,
+    dul.create_time AS create_time,
+    dul.update_time AS update_time,
+    dul.valid_from AS valid_from,
+    dul.valid_to AS valid_to,
+    COALESCE(dul.is_active, 0) AS is_active,
+    COALESCE(dul.level_tier, 0) AS level_tier,
+    COALESCE(dul.level_group, '') AS level_group,
+    COALESCE(dul.level_category, '') AS level_category,
+    COALESCE(dul.points_required, 0) AS points_required,
+    COALESCE(dul.orders_required, 0) AS orders_required,
+    COALESCE(dul.amount_required, 0) AS amount_required,
+    COALESCE(dul.days_required, 0) AS days_required,
+    COALESCE(dul.growth_value, 0) AS growth_value,
+    COALESCE(dul.experience_value, 0) AS experience_value,
+    COALESCE(dul.contribution_value, 0) AS contribution_value,
+    COALESCE(dul.activity_value, 0) AS activity_value,
+    COALESCE(dul.loyalty_score, 0) AS loyalty_score,
+    COALESCE(dul.engagement_score, 0) AS engagement_score,
+    COALESCE(dul.satisfaction_score, 0) AS satisfaction_score,
+    COALESCE(dul.retention_score, 0) AS retention_score,
+    COALESCE(drd.region_id, 0) AS region_id,
+    COALESCE(drd.region_code, '') AS region_code,
+    COALESCE(drd.region_name, '') AS region_name,
+    COALESCE(drd.parent_id, 0) AS parent_id,
+    COALESCE(drd.region_level, 0) AS region_level,
+    COALESCE(drd.region_path, '') AS region_path,
+    COALESCE(drd.province_id, 0) AS province_id,
+    COALESCE(drd.province_abbr, '') AS province_abbr,
+    COALESCE(drd.city_id, 0) AS city_id,
+    COALESCE(drd.city_abbr, '') AS city_abbr,
+    COALESCE(drd.district_id, 0) AS district_id,
+    COALESCE(drd.district_abbr, '') AS district_abbr,
+    COALESCE(drd.street_id, 0) AS street_id,
+    COALESCE(drd.street_code, '') AS street_code,
+    COALESCE(drd.street_name, '') AS street_name,
+    COALESCE(drd.center_longitude, 0) AS center_longitude,
+    COALESCE(drd.center_latitude, 0) AS center_latitude,
+    COALESCE(drd.area_size, 0) AS area_size,
+    COALESCE(drd.population, 0) AS population,
+    COALESCE(drd.gdp, 0) AS gdp,
+    COALESCE(drd.gdp_per_capita, 0) AS gdp_per_capita,
+    COALESCE(drd.climate_type, '') AS climate_type,
+    COALESCE(drd.economy_level, '') AS economy_level,
+    COALESCE(drd.development_level, '') AS development_level,
+    COALESCE(drd.urban_rate, 0) AS urban_rate,
+    COALESCE(drd.region_type, '') AS region_type,
+    COALESCE(drd.is_coastal, 0) AS is_coastal,
+    COALESCE(drd.is_border, 0) AS is_border,
+    COALESCE(drd.is_capital, 0) AS is_capital,
+    COALESCE(drd.is_special, 0) AS is_special,
+    COALESCE(drd.postal_code_prefix, '') AS postal_code_prefix,
+    COALESCE(drd.phone_area_code, '') AS phone_area_code,
+    COALESCE(drd.car_plate_prefix, '') AS car_plate_prefix,
+    COALESCE(drd.airport_code, '') AS airport_code,
+    COALESCE(drd.railway_station_code, '') AS railway_station_code,
+    COALESCE(drd.port_code, '') AS port_code,
+    COALESCE(drd.weather_station_code, '') AS weather_station_code,
+    COALESCE(drd.customs_code, '') AS customs_code,
+    COALESCE(drd.statistical_code, '') AS statistical_code,
+    COALESCE(drd.iso_code, '') AS iso_code,
+    COALESCE(dus.source_code, '') AS source_code,
+    COALESCE(dus.source_category, '') AS source_category,
+    COALESCE(dus.channel_id, 0) AS channel_id,
+    COALESCE(dus.channel_code, '') AS channel_code,
+    COALESCE(dus.channel_name, '') AS channel_name,
+    COALESCE(dus.channel_type, '') AS channel_type,
+    COALESCE(dus.channel_category, '') AS channel_category,
+    COALESCE(dus.campaign_id, 0) AS campaign_id,
+    COALESCE(dus.campaign_code, '') AS campaign_code,
+    COALESCE(dus.campaign_name, '') AS campaign_name,
+    COALESCE(dus.campaign_type, '') AS campaign_type,
+    COALESCE(dus.medium_id, 0) AS medium_id,
+    COALESCE(dus.medium_code, '') AS medium_code,
+    COALESCE(dus.medium_name, '') AS medium_name,
+    COALESCE(dus.medium_type, '') AS medium_type,
+    COALESCE(dus.term_id, 0) AS term_id,
+    COALESCE(dus.term_keyword, '') AS term_keyword,
+    COALESCE(dus.content_id, 0) AS content_id,
+    COALESCE(dus.content_name, '') AS content_name,
+    COALESCE(dus.referral_url, '') AS referral_url,
+    COALESCE(dus.landing_page, '') AS landing_page,
+    COALESCE(dus.utm_source, '') AS utm_source,
+    COALESCE(dus.utm_medium, '') AS utm_medium,
+    COALESCE(dus.utm_campaign, '') AS utm_campaign,
+    COALESCE(dus.utm_term, '') AS utm_term,
+    COALESCE(dus.utm_content, '') AS utm_content,
+    COALESCE(dus.cost_per_acquisition, 0) AS cost_per_acquisition,
+    COALESCE(dus.conversion_rate, 0) AS conversion_rate,
+    COALESCE(dus.quality_score, 0) AS quality_score,
+    COALESCE(dus.retention_rate_7d, 0) AS retention_rate_7d,
+    COALESCE(dus.retention_rate_30d, 0) AS retention_rate_30d,
+    COALESCE(dus.lifetime_value, 0) AS lifetime_value,
+    COALESCE(dus.first_order_amount, 0) AS first_order_amount,
+    COALESCE(dus.first_order_days, 0) AS first_order_days,
+    COALESCE(dus.register_device, '') AS register_device,
+    COALESCE(dus.register_os, '') AS register_os,
+    COALESCE(dus.register_browser, '') AS register_browser,
+    COALESCE(dus.register_network, '') AS register_network,
+    COALESCE(dus.register_location, '') AS register_location,
+    COALESCE(dus.attribution_model, '') AS attribution_model,
+    COALESCE(dus.lookback_days, 0) AS lookback_days,
+    COALESCE(dus.priority, 0) AS priority,
+    COALESCE(dus.is_paid, 0) AS is_paid,
+    /* 审计字段（4个，全部必带） */
+    'N' AS del_flag,
+    '${P_CYCLE_ID}' AS crt_cycle_id,
+    '${P_CYCLE_ID}' AS last_upd_cycle_id,
+    CURRENT_TIMESTAMP AS dw_last_update_date
+FROM ods.ods_user_basic_f oub
+LEFT JOIN dim.dim_user_level_d dul
+    ON oub.level_id = dul.level_id
+    AND COALESCE(dul.del_flag, 'N') = 'N'
+LEFT JOIN dim.dim_region_d drd
+    ON oub.province_code = drd.region_code
+    AND COALESCE(drd.del_flag, 'N') = 'N'
+LEFT JOIN dim.dim_user_source_d dus
+    ON oub.source_id = dus.source_id
+    AND COALESCE(dus.del_flag, 'N') = 'N'
+WHERE COALESCE(oub.del_flag, 'N') = 'N';
+——ddl/create_table_dwb_user_profile_f.sql——
+/* =====================================================
+   表名: slusr.dwb_user_profile_f
+   规则: R0001 - 用户画像宽表全量加工
+   分布键: user_id
+   逻辑集群: LC_DW1
+   生成时间: 2026-08-04
+   说明: 用户画像宽表全量重写：以 oub 用户基础表为主表，LEFT JOIN 等级/地区/来源三张维表补齐画像属性，并对敏感字段脱敏、枚举字段转中文、派生时间维度字段。无粒度变化、无聚合，单条 INSERT 即可完成。
+   ===================================================== */
+CREATE TABLE IF NOT EXISTS slusr.dwb_user_profile_f (
+    user_id                    bigint,
+    user_name                  varchar(100),
+    user_phone_processed       varchar(20),
+    user_phone_masked          varchar(20),
+    email                      varchar(100),
+    gender_processed           varchar(10),
+    birthday                   date,
+    age_processed              int,
+    id_card                    varchar(20),
+    id_card_masked_processed   varchar(20),
+    real_name                  varchar(50),
+    nick_name                  varchar(50),
+    avatar_url                 varchar(500),
+    user_status                varchar(20),
+    user_status_name_processed varchar(20),
+    register_time              timestamp,
+    register_date_processed    date,
+    register_hour_processed    int,
+    register_weekday_processed int,
+    last_login_time            timestamp,
+    last_login_date_processed  date,
+    login_count                int,
+    province_code              varchar(20),
+    province_name              varchar(50),
+    city_code                  varchar(20),
+    city_name                  varchar(50),
+    district_code              varchar(20),
+    district_name              varchar(50),
+    address                    varchar(500),
+    zip_code                   varchar(10),
+    source_id                  int,
+    source_name                varchar(50),
+    source_type                varchar(20),
+    device_type                varchar(20),
+    os_type                    varchar(20),
+    app_version                varchar(20),
+    ip_address                 varchar(50),
+    longitude                  decimal(10,6),
+    latitude                   decimal(10,6),
+    language                   varchar(20),
+    timezone                   varchar(50),
+    currency                   varchar(10),
+    vip_level                  int,
+    vip_expire_time            timestamp,
+    is_vip_processed           int,
+    member_points              int,
+    balance                    decimal(18,2),
+    credit_score               int,
+    risk_level                 varchar(20),
+    verify_status              varchar(20),
+    level_id                   int,
+    level_name                 varchar(50),
+    level_code                 varchar(20),
+    level_rank                 int,
+    min_points                 int,
+    max_points                 int,
+    level_icon                 varchar(500),
+    level_color                varchar(20),
+    upgrade_points             int,
+    current_level_points       int,
+    next_level_points          int,
+    progress_percentage        decimal(5,2),
+    privilege_list             varchar(1000),
+    discount_rate              decimal(5,2),
+    points_rate                decimal(5,2),
+    free_shipping              int,
+    exclusive_products         int,
+    priority_support           int,
+    birthday_bonus             int,
+    monthly_coupon             int,
+    annual_gift                int,
+    vip_service                int,
+    invite_quota               int,
+    max_orders_per_day         int,
+    max_return_days            int,
+    level_benefits             varchar(1000),
+    upgrade_time               timestamp,
+    downgrade_time             timestamp,
+    maintain_days              int,
+    level_status               varchar(20),
+    create_time                timestamp,
+    update_time                timestamp,
+    valid_from                 timestamp,
+    valid_to                   timestamp,
+    is_active                  int,
+    level_tier                 int,
+    level_group                varchar(50),
+    level_category             varchar(50),
+    points_required            int,
+    orders_required            int,
+    amount_required            decimal(18,2),
+    days_required              int,
+    growth_value               int,
+    experience_value           int,
+    contribution_value         int,
+    activity_value             int,
+    loyalty_score              decimal(5,2),
+    engagement_score           decimal(5,2),
+    satisfaction_score         decimal(5,2),
+    retention_score            decimal(5,2),
+    region_id                  int,
+    region_code                varchar(20),
+    region_name                varchar(100),
+    parent_id                  int,
+    region_level               int,
+    region_path                varchar(500),
+    province_id                int,
+    province_abbr              varchar(20),
+    city_id                    int,
+    city_abbr                  varchar(20),
+    district_id                int,
+    district_abbr              varchar(20),
+    street_id                  int,
+    street_code                varchar(20),
+    street_name                varchar(50),
+    center_longitude           decimal(10,6),
+    center_latitude            decimal(10,6),
+    area_size                  decimal(18,2),
+    population                 int,
+    gdp                        decimal(18,2),
+    gdp_per_capita             decimal(18,2),
+    climate_type               varchar(50),
+    economy_level              varchar(50),
+    development_level          varchar(50),
+    urban_rate                 decimal(5,2),
+    region_type                varchar(50),
+    is_coastal                 int,
+    is_border                  int,
+    is_capital                 int,
+    is_special                 int,
+    postal_code_prefix         varchar(10),
+    phone_area_code            varchar(20),
+    car_plate_prefix           varchar(10),
+    airport_code               varchar(10),
+    railway_station_code       varchar(20),
+    port_code                  varchar(20),
+    weather_station_code       varchar(20),
+    customs_code               varchar(20),
+    statistical_code           varchar(20),
+    iso_code                   varchar(20),
+    source_code                varchar(50),
+    source_category            varchar(50),
+    channel_id                 int,
+    channel_code               varchar(50),
+    channel_name               varchar(100),
+    channel_type               varchar(50),
+    channel_category           varchar(50),
+    campaign_id                int,
+    campaign_code              varchar(50),
+    campaign_name              varchar(100),
+    campaign_type              varchar(50),
+    medium_id                  int,
+    medium_code                varchar(50),
+    medium_name                varchar(100),
+    medium_type                varchar(50),
+    term_id                    int,
+    term_keyword               varchar(200),
+    content_id                 int,
+    content_name               varchar(200),
+    referral_url               varchar(500),
+    landing_page               varchar(500),
+    utm_source                 varchar(100),
+    utm_medium                 varchar(100),
+    utm_campaign               varchar(100),
+    utm_term                   varchar(100),
+    utm_content                varchar(100),
+    cost_per_acquisition       decimal(18,2),
+    conversion_rate            decimal(5,2),
+    quality_score              decimal(5,2),
+    retention_rate_7d          decimal(5,2),
+    retention_rate_30d         decimal(5,2),
+    lifetime_value             decimal(18,2),
+    first_order_amount         decimal(18,2),
+    first_order_days           int,
+    register_device            varchar(50),
+    register_os                varchar(50),
+    register_browser           varchar(50),
+    register_network           varchar(50),
+    register_location          varchar(200),
+    attribution_model          varchar(50),
+    lookback_days              int,
+    priority                   int,
+    is_paid                    int,
+    del_flag                   NVARCHAR(1),
+    crt_cycle_id               BIGINT,
+    last_upd_cycle_id          BIGINT,
+    dw_last_update_date        TIMESTAMP(0) WITHOUT TIME ZONE
+)
+WITH (
+    ORIENTATION = COLUMN,
+    COMPRESSION = LOW
+)
+DISTRIBUTE BY HASH(user_id)
+TO GROUP "LC_DW1";
+COMMENT ON TABLE slusr.dwb_user_profile_f IS '用户画像宽表';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_id IS '用户ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_name IS '用户姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_processed IS '手机号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_phone_masked IS '手机号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.email IS '电子邮箱';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.gender_processed IS '性别';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.birthday IS '出生日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.age_processed IS '年龄';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card IS '身份证号';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.id_card_masked_processed IS '身份证号(脱敏)';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.real_name IS '真实姓名';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.nick_name IS '昵称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.avatar_url IS '头像URL';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status IS '用户状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.user_status_name_processed IS '用户状态名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_time IS '注册时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_date_processed IS '注册日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_hour_processed IS '注册小时';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.register_weekday_processed IS '注册星期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.last_login_time IS '最后登录时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.last_login_date_processed IS '最后登录日期';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.login_count IS '登录次数';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.province_code IS '省份代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.province_name IS '省份名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.city_code IS '城市代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.city_name IS '城市名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.district_code IS '区县代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.district_name IS '区县名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.address IS '详细地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.zip_code IS '邮政编码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_id IS '来源渠道ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_name IS '来源渠道名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.source_type IS '来源类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.device_type IS '设备类型';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.os_type IS '操作系统';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.app_version IS 'APP版本';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.ip_address IS 'IP地址';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.longitude IS '经度';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.latitude IS '纬度';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.language IS '语言';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.timezone IS '时区';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.currency IS '货币';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.vip_level IS 'VIP等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.vip_expire_time IS 'VIP到期时间';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.is_vip_processed IS '是否VIP';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.member_points IS '会员积分';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.balance IS '账户余额';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.credit_score IS '信用分';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.risk_level IS '风险等级';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.verify_status IS '认证状态';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_id IS '等级ID';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_name IS '等级名称';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_code IS '等级代码';
+COMMENT ON COLUMN slusr.dwb_user_profile_f.level_rank IS '等级排序';
+COMMENT ON CO…（截断）
+档案来源：../10_project_deliver/dwb_user_profile_f</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>规则完成标准（自 ts 设计派生，逐项可核验）：
+- 本规则输出列 187 项：user_id, user_name, user_phone_processed, user_phone_masked, email, gender_processed, birthday, age_processed, id_card, id_card_masked_processed, real_name, nick_name, avatar_url, user_status, user_status_name_processed, register_time, register_date_processed, register_hour_processed, register_weekday_processed, last_login_time, last_login_date_processed, login_count, province_code, province_name, city_code, city_name, district_code, district_name, address, zip_code, source_id, source_name, source_type, device_type, os_type, app_version, ip_address, longitude, latitude, language, timezone, currency, vip_level, vip_expire_time, is_vip_processed, member_points, balance, credit_score, risk_level, verify_status, level_id, level_name, level_code, level_rank, min_points, max_points, level_icon, level_color, upgrade_points, current_level_points, next_level_points, progress_percentage, privilege_list, discount_rate, points_rate, free_shipping, exclusive_products, priority_support, birthday_bonus, monthly_coupon, annual_gift, vip_service, invite_quota, max_orders_per_day, max_return_days, level_benefits, upgrade_time, downgrade_time, maintain_days, level_status, create_time, update_time, valid_from, valid_to, is_active, level_tier, level_group, level_category, points_required, orders_required, amount_required, days_required, growth_value, experience_value, contribution_value, activity_value, loyalty_score, engagement_score, satisfaction_score, retention_score, region_id, region_code, region_name, parent_id, region_level, region_path, province_id, province_abbr, city_id, city_abbr, district_id, district_abbr, street_id, street_code, street_name, center_longitude, center_latitude, area_size, population, gdp, gdp_per_capita, climate_type, economy_level, development_level, urban_rate, region_type, is_coastal, is_border, is_capital, is_special, postal_code_prefix, phone_area_code, car_plate_prefix, airport_code, railway_station_code, port_code, weather_station_code, customs_code, statistical_code, iso_code, source_code, source_category, channel_id, channel_code, channel_name, channel_type, channel_category, campaign_id, campaign_code, campaign_name, campaign_type, medium_id, medium_code, medium_name, medium_type, term_id, term_keyword, content_id, content_name, referral_url, landing_page, utm_source, utm_medium, utm_campaign, utm_term, utm_content, cost_per_acquisition, conversion_rate, quality_score, retention_rate_7d, retention_rate_30d, lifetime_value, first_order_amount, first_order_days, register_device, register_os, register_browser, register_network, register_location, attribution_model, lookback_days, priority, is_paid, del_flag, crt_cycle_id, last_upd_cycle_id, dw_last_update_date（应全部出现在 SELECT 输出列中）
+- SELECT 落盘为一个文件（R0001.sql），加工口径与 mapping 一致
+- 与目标表 slusr.dwb_user_profile_f 的 DDL 结构一致</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>输入材料：mapping 字段映射（本规则 187 项）（源→规则→目标）：
+ods_user_basic_f.user_id --[直接复制]--&gt; user_id(用户ID)
+ods_user_basic_f.user_name --[直接复制]--&gt; user_name(用户姓名)
+ods_user_basic_f.user_phone --[数据加工]--&gt; user_phone_processed(手机号)
+ods_user_basic_f.user_phone_masked --[直接复制]--&gt; user_phone_masked(手机号(脱敏))
+ods_user_basic_f.email --[直接复制]--&gt; email(电子邮箱)
+ods_user_basic_f.gender --[数据加工]--&gt; gender_processed(性别)
+ods_user_basic_f.birthday --[直接复制]--&gt; birthday(出生日期)
+ods_user_basic_f.age --[数据加工]--&gt; age_processed(年龄)
+ods_user_basic_f.id_card --[直接复制]--&gt; id_card(身份证号)
+ods_user_basic_f.id_card_masked --[数据加工]--&gt; id_card_masked_processed(身份证号(脱敏))
+ods_user_basic_f.real_name --[直接复制]--&gt; real_name(真实姓名)
+ods_user_basic_f.nick_name --[直接复制]--&gt; nick_name(昵称)
+ods_user_basic_f.avatar_url --[直接复制]--&gt; avatar_url(头像URL)
+ods_user_basic_f.user_status --[直接复制]--&gt; user_status(用户状态)
+ods_user_basic_f.user_status_name --[数据加工]--&gt; user_status_name_processed(用户状态名称)
+ods_user_basic_f.register_time --[直接复制]--&gt; register_time(注册时间)
+ods_user_basic_f.register_date --[数据加工]--&gt; register_date_processed(注册日期)
+ods_user_basic_f.register_hour --[数据加工]--&gt; register_hour_processed(注册小时)
+ods_user_basic_f.register_weekday --[数据加工]--&gt; register_weekday_processed(注册星期)
+ods_user_basic_f.last_login_time --[直接复制]--&gt; last_login_time(最后登录时间)
+ods_user_basic_f.last_login_date --[数据加工]--&gt; last_login_date_processed(最后登录日期)
+ods_user_basic_f.login_count --[直接复制]--&gt; login_count(登录次数)
+ods_user_basic_f.province_code --[直接复制]--&gt; province_code(省份代码)
+ods_user_basic_f.province_name --[直接复制]--&gt; province_name(省份名称)
+ods_user_basic_f.city_code --[直接复制]--&gt; city_code(城市代码)
+ods_user_basic_f.city_name --[直接复制]--&gt; city_name(城市名称)
+ods_user_basic_f.district_code --[直接复制]--&gt; district_code(区县代码)
+ods_user_basic_f.district_name --[直接复制]--&gt; district_name(区县名称)
+ods_user_basic_f.address --[直接复制]--&gt; address(详细地址)
+ods_user_basic_f.zip_code --[直接复制]--&gt; zip_code(邮政编码)
+ods_user_basic_f.source_id --[直接复制]--&gt; source_id(来源渠道ID)
+ods_user_basic_f.source_name --[直接复制]--&gt; source_name(来源渠道名称)
+ods_user_basic_f.source_type --[直接复制]--&gt; source_type(来源类型)
+ods_user_basic_f.device_type --[直接复制]--&gt; device_type(设备类型)
+ods_user_basic_f.os_type --[直接复制]--&gt; os_type(操作系统)
+ods_user_basic_f.app_version --[直接复制]--&gt; app_version(APP版本)
+ods_user_basic_f.ip_address --[直接复制]--&gt; ip_address(IP地址)
+ods_user_basic_f.longitude --[直接复制]--&gt; longitude(经度)
+ods_user_basic_f.latitude --[直接复制]--&gt; latitude(纬度)
+ods_user_basic_f.language --[直接复制]--&gt; language(语言)
+ods_user_basic_f.timezone --[直接复制]--&gt; timezone(时区)
+ods_user_basic_f.currency --[直接复制]--&gt; currency(货币)
+ods_user_basic_f.vip_level --[直接复制]--&gt; vip_level(VIP等级)
+ods_user_basic_f.vip_expire_time --[直接复制]--&gt; vip_expire_time(VIP到期时间)
+ods_user_basic_f.is_vip --[数据加工]--&gt; is_vip_processed(是否VIP)
+ods_user_basic_f.member_points --[直接复制]--&gt; member_points(会员积分)
+ods_user_basic_f.balance --[直接复制]--&gt; balance(账户余额)
+ods_user_basic_f.credit_score --[直接复制]--&gt; credit_score(信用分)
+ods_user_basic_f.risk_level --[直接复制]--&gt; risk_level(风险等级)
+ods_user_basic_f.verify_status --[直接复制]--&gt; verify_status(认证状态)
+dim_user_level_d.level_id --[直接复制]--&gt; level_id(等级ID)
+dim_user_level_d.level_name --[直接复制]--&gt; level_name(等级名称)
+dim_user_level_d.level_code --[直接复制]--&gt; level_code(等级代码)
+dim_user_level_d.level_rank --[直接复制]--&gt; level_rank(等级排序)
+dim_user_level_d.min_points --[直接复制]--&gt; min_points(最小积分)
+dim_user_level_d.max_points --[直接复制]--&gt; max_points(最大积分)
+dim_user_level_d.level_icon --[直接复制]--&gt; level_icon(等级图标)
+dim_user_level_d.level_color --[直接复制]--&gt; level_color(等级颜色)
+dim_user_level_d.upgrade_points --[直接复制]--&gt; upgrade_points(升级所需积分)
+dim_user_level_d.current_level_points --[直接复制]--&gt; current_level_points(当前等级积分)
+dim_user_level_d.next_level_points --[直接复制]--&gt; next_level_points(下一等级积分)
+dim_user_level_d.progress_percentage --[数据加工]--&gt; progress_percentage(升级进度百分比)
+dim_user_level_d.privilege_list --[直接复制]--&gt; privilege_list(权限列表)
+dim_user_level_d.discount_rate --[直接复制]--&gt; discount_rate(折扣率)
+dim_user_level_d.points_rate --[直接复制]--&gt; points_rate(积分倍率)
+dim_user_level_d.free_shipping --[直接复制]--&gt; free_shipping(免费配送)
+dim_user_level_d.exclusive_products --[直接复制]--&gt; exclusive_products(专属商品)
+dim_user_level_d.priority_support --[直接复制]--&gt; priority_support(优先客服)
+dim_user_level_d.birthday_bonus --[直接复制]--&gt; birthday_bonus(生日礼金)
+dim_user_level_d.monthly_coupon --[直接复制]--&gt; monthly_coupon(月度优惠券)
+dim_user_level_d.annual_gift --[直接复制]--&gt; annual_gift(年度礼品)
+dim_user_level_d.vip_service --[直接复制]--&gt; vip_service(VIP服务)
+dim_user_level_d.invite_quota --[直接复制]--&gt; invite_quota(邀请名额)
+dim_user_level_d.max_orders_per_day --[直接复制]--&gt; max_orders_per_day(每日最大订单数)
+dim_user_level_d.max_return_days --[直接复制]--&gt; max_return_days(最大退货天数)
+dim_user_level_d.level_benefits --[直接复制]--&gt; level_benefits(等级权益)
+dim_user_level_d.upgrade_time --[直接复制]--&gt; upgrade_time(升级时间)
+dim_user_level_d.downgrade_time --[直接复制]--&gt; downgrade_time(降级时间)
+dim_user_level_d.maintain_days --[直接复制]--&gt; maintain_days(维持天数)
+dim_user_level_d.level_status --[直接复制]--&gt; level_status(等级状态)
+dim_user_level_d.create_time --[直接复制]--&gt; create_time(创建时…（截断）</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
